--- a/data/material_market_share.xlsx
+++ b/data/material_market_share.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\GitHub\FLIM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80062442-E212-4F24-844A-681253114E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C8FF16-EB4F-4FD8-87F1-13E1A4CF8F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -535,9 +535,6 @@
     <t>Zacht PVC</t>
   </si>
   <si>
-    <t>Gerecycled Metaal</t>
-  </si>
-  <si>
     <t>Jute</t>
   </si>
   <si>
@@ -581,6 +578,9 @@
   </si>
   <si>
     <t>material</t>
+  </si>
+  <si>
+    <t>Gerecycled metaal</t>
   </si>
 </sst>
 </file>
@@ -959,7 +959,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -12649,7 +12649,7 @@
         <v>0.49230269587589581</v>
       </c>
       <c r="D836" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="837" spans="1:4" x14ac:dyDescent="0.3">
@@ -12663,7 +12663,7 @@
         <v>0.11023519823071019</v>
       </c>
       <c r="D837" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="838" spans="1:4" x14ac:dyDescent="0.3">
@@ -12677,7 +12677,7 @@
         <v>5.5535601988050777E-2</v>
       </c>
       <c r="D838" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="839" spans="1:4" x14ac:dyDescent="0.3">
@@ -12691,7 +12691,7 @@
         <v>4.5296906380373952E-2</v>
       </c>
       <c r="D839" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="840" spans="1:4" x14ac:dyDescent="0.3">
@@ -12705,7 +12705,7 @@
         <v>4.331742754279938E-2</v>
       </c>
       <c r="D840" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="841" spans="1:4" x14ac:dyDescent="0.3">
@@ -12719,7 +12719,7 @@
         <v>3.069477602583242E-2</v>
       </c>
       <c r="D841" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="842" spans="1:4" x14ac:dyDescent="0.3">
@@ -12733,7 +12733,7 @@
         <v>2.9189195681513611E-2</v>
       </c>
       <c r="D842" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="843" spans="1:4" x14ac:dyDescent="0.3">
@@ -12747,7 +12747,7 @@
         <v>1.8984691713662939E-2</v>
       </c>
       <c r="D843" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="844" spans="1:4" x14ac:dyDescent="0.3">
@@ -12761,7 +12761,7 @@
         <v>1.7007184779190831E-2</v>
       </c>
       <c r="D844" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="845" spans="1:4" x14ac:dyDescent="0.3">
@@ -12775,7 +12775,7 @@
         <v>1.47171996372294E-2</v>
       </c>
       <c r="D845" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="846" spans="1:4" x14ac:dyDescent="0.3">
@@ -12789,7 +12789,7 @@
         <v>7.8638340075726093E-3</v>
       </c>
       <c r="D846" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="847" spans="1:4" x14ac:dyDescent="0.3">
@@ -12803,7 +12803,7 @@
         <v>7.8623564909186712E-3</v>
       </c>
       <c r="D847" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="848" spans="1:4" x14ac:dyDescent="0.3">
@@ -12817,7 +12817,7 @@
         <v>7.4777655950945942E-3</v>
       </c>
       <c r="D848" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="849" spans="1:4" x14ac:dyDescent="0.3">
@@ -12831,7 +12831,7 @@
         <v>6.8494556756922504E-3</v>
       </c>
       <c r="D849" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="850" spans="1:4" x14ac:dyDescent="0.3">
@@ -12845,7 +12845,7 @@
         <v>6.7544806206707919E-3</v>
       </c>
       <c r="D850" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="851" spans="1:4" x14ac:dyDescent="0.3">
@@ -12859,7 +12859,7 @@
         <v>6.2123589399165329E-3</v>
       </c>
       <c r="D851" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="852" spans="1:4" x14ac:dyDescent="0.3">
@@ -12873,7 +12873,7 @@
         <v>6.1137440451461871E-3</v>
       </c>
       <c r="D852" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="853" spans="1:4" x14ac:dyDescent="0.3">
@@ -12887,7 +12887,7 @@
         <v>6.0548838703763444E-3</v>
       </c>
       <c r="D853" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="854" spans="1:4" x14ac:dyDescent="0.3">
@@ -12901,7 +12901,7 @@
         <v>5.634374861343867E-3</v>
       </c>
       <c r="D854" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="855" spans="1:4" x14ac:dyDescent="0.3">
@@ -12915,7 +12915,7 @@
         <v>4.6041310320027277E-3</v>
       </c>
       <c r="D855" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="856" spans="1:4" x14ac:dyDescent="0.3">
@@ -12929,7 +12929,7 @@
         <v>4.5733979796779437E-3</v>
       </c>
       <c r="D856" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="857" spans="1:4" x14ac:dyDescent="0.3">
@@ -12943,7 +12943,7 @@
         <v>4.4466453840446537E-3</v>
       </c>
       <c r="D857" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="858" spans="1:4" x14ac:dyDescent="0.3">
@@ -12957,7 +12957,7 @@
         <v>4.2866814574447883E-3</v>
       </c>
       <c r="D858" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="859" spans="1:4" x14ac:dyDescent="0.3">
@@ -12971,7 +12971,7 @@
         <v>3.690185751588913E-3</v>
       </c>
       <c r="D859" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="860" spans="1:4" x14ac:dyDescent="0.3">
@@ -12985,7 +12985,7 @@
         <v>3.4305314103855022E-3</v>
       </c>
       <c r="D860" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="861" spans="1:4" x14ac:dyDescent="0.3">
@@ -12999,7 +12999,7 @@
         <v>3.359870849850176E-3</v>
       </c>
       <c r="D861" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="862" spans="1:4" x14ac:dyDescent="0.3">
@@ -13013,7 +13013,7 @@
         <v>2.9177929178431858E-3</v>
       </c>
       <c r="D862" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="863" spans="1:4" x14ac:dyDescent="0.3">
@@ -13027,7 +13027,7 @@
         <v>2.5361492969517602E-3</v>
       </c>
       <c r="D863" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="864" spans="1:4" x14ac:dyDescent="0.3">
@@ -13041,7 +13041,7 @@
         <v>2.4328098755059349E-3</v>
       </c>
       <c r="D864" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="865" spans="1:4" x14ac:dyDescent="0.3">
@@ -13055,7 +13055,7 @@
         <v>2.27740403442224E-3</v>
       </c>
       <c r="D865" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="866" spans="1:4" x14ac:dyDescent="0.3">
@@ -13069,7 +13069,7 @@
         <v>2.1374095042935009E-3</v>
       </c>
       <c r="D866" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="867" spans="1:4" x14ac:dyDescent="0.3">
@@ -13083,7 +13083,7 @@
         <v>2.0485645561019381E-3</v>
       </c>
       <c r="D867" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="868" spans="1:4" x14ac:dyDescent="0.3">
@@ -13097,7 +13097,7 @@
         <v>2.0388207040399069E-3</v>
       </c>
       <c r="D868" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="869" spans="1:4" x14ac:dyDescent="0.3">
@@ -13111,7 +13111,7 @@
         <v>1.9520823635533031E-3</v>
       </c>
       <c r="D869" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="870" spans="1:4" x14ac:dyDescent="0.3">
@@ -13125,7 +13125,7 @@
         <v>1.9391401634951629E-3</v>
       </c>
       <c r="D870" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="871" spans="1:4" x14ac:dyDescent="0.3">
@@ -13139,7 +13139,7 @@
         <v>1.934643434757469E-3</v>
       </c>
       <c r="D871" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="872" spans="1:4" x14ac:dyDescent="0.3">
@@ -13153,7 +13153,7 @@
         <v>1.6914068078853529E-3</v>
       </c>
       <c r="D872" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="873" spans="1:4" x14ac:dyDescent="0.3">
@@ -13167,7 +13167,7 @@
         <v>1.5710114133122401E-3</v>
       </c>
       <c r="D873" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="874" spans="1:4" x14ac:dyDescent="0.3">
@@ -13181,7 +13181,7 @@
         <v>1.5183187246207541E-3</v>
       </c>
       <c r="D874" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="875" spans="1:4" x14ac:dyDescent="0.3">
@@ -13195,7 +13195,7 @@
         <v>1.4468407687254999E-3</v>
       </c>
       <c r="D875" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="876" spans="1:4" x14ac:dyDescent="0.3">
@@ -13209,7 +13209,7 @@
         <v>1.3616025130530961E-3</v>
       </c>
       <c r="D876" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="877" spans="1:4" x14ac:dyDescent="0.3">
@@ -13223,7 +13223,7 @@
         <v>1.3538989742365661E-3</v>
       </c>
       <c r="D877" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="878" spans="1:4" x14ac:dyDescent="0.3">
@@ -13237,7 +13237,7 @@
         <v>1.279954023779653E-3</v>
       </c>
       <c r="D878" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="879" spans="1:4" x14ac:dyDescent="0.3">
@@ -13251,7 +13251,7 @@
         <v>1.17188795932319E-3</v>
       </c>
       <c r="D879" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="880" spans="1:4" x14ac:dyDescent="0.3">
@@ -13265,7 +13265,7 @@
         <v>1.161847192866512E-3</v>
       </c>
       <c r="D880" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="881" spans="1:4" x14ac:dyDescent="0.3">
@@ -13279,7 +13279,7 @@
         <v>1.066011722499759E-3</v>
       </c>
       <c r="D881" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="882" spans="1:4" x14ac:dyDescent="0.3">
@@ -13293,7 +13293,7 @@
         <v>9.8747553864536619E-4</v>
       </c>
       <c r="D882" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="883" spans="1:4" x14ac:dyDescent="0.3">
@@ -13307,7 +13307,7 @@
         <v>9.410215675210962E-4</v>
       </c>
       <c r="D883" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="884" spans="1:4" x14ac:dyDescent="0.3">
@@ -13321,7 +13321,7 @@
         <v>8.6640803238428388E-4</v>
       </c>
       <c r="D884" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="885" spans="1:4" x14ac:dyDescent="0.3">
@@ -13335,7 +13335,7 @@
         <v>7.9774970018374827E-4</v>
       </c>
       <c r="D885" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="886" spans="1:4" x14ac:dyDescent="0.3">
@@ -13349,7 +13349,7 @@
         <v>7.9169435054761959E-4</v>
       </c>
       <c r="D886" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="887" spans="1:4" x14ac:dyDescent="0.3">
@@ -13363,7 +13363,7 @@
         <v>6.6053670949059841E-4</v>
       </c>
       <c r="D887" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="888" spans="1:4" x14ac:dyDescent="0.3">
@@ -13377,7 +13377,7 @@
         <v>6.58997130395938E-4</v>
       </c>
       <c r="D888" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="889" spans="1:4" x14ac:dyDescent="0.3">
@@ -13391,7 +13391,7 @@
         <v>6.5010311460973649E-4</v>
       </c>
       <c r="D889" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="890" spans="1:4" x14ac:dyDescent="0.3">
@@ -13405,7 +13405,7 @@
         <v>6.2037928700711307E-4</v>
       </c>
       <c r="D890" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="891" spans="1:4" x14ac:dyDescent="0.3">
@@ -13419,7 +13419,7 @@
         <v>6.0643844064469786E-4</v>
       </c>
       <c r="D891" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="892" spans="1:4" x14ac:dyDescent="0.3">
@@ -13433,7 +13433,7 @@
         <v>6.0549268903617112E-4</v>
       </c>
       <c r="D892" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="893" spans="1:4" x14ac:dyDescent="0.3">
@@ -13447,7 +13447,7 @@
         <v>5.6563429597932956E-4</v>
       </c>
       <c r="D893" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="894" spans="1:4" x14ac:dyDescent="0.3">
@@ -13461,7 +13461,7 @@
         <v>5.5181263877212118E-4</v>
       </c>
       <c r="D894" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="895" spans="1:4" x14ac:dyDescent="0.3">
@@ -13475,7 +13475,7 @@
         <v>5.5068492990541858E-4</v>
       </c>
       <c r="D895" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="896" spans="1:4" x14ac:dyDescent="0.3">
@@ -13489,7 +13489,7 @@
         <v>4.9549280508479044E-4</v>
       </c>
       <c r="D896" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="897" spans="1:4" x14ac:dyDescent="0.3">
@@ -13503,7 +13503,7 @@
         <v>4.8108155175860252E-4</v>
       </c>
       <c r="D897" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="898" spans="1:4" x14ac:dyDescent="0.3">
@@ -13517,7 +13517,7 @@
         <v>4.7700374661342461E-4</v>
       </c>
       <c r="D898" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="899" spans="1:4" x14ac:dyDescent="0.3">
@@ -13531,7 +13531,7 @@
         <v>4.5774243040581892E-4</v>
       </c>
       <c r="D899" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="900" spans="1:4" x14ac:dyDescent="0.3">
@@ -13545,7 +13545,7 @@
         <v>4.47572601386714E-4</v>
       </c>
       <c r="D900" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="901" spans="1:4" x14ac:dyDescent="0.3">
@@ -13559,7 +13559,7 @@
         <v>4.1365037011395608E-4</v>
       </c>
       <c r="D901" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="902" spans="1:4" x14ac:dyDescent="0.3">
@@ -13573,7 +13573,7 @@
         <v>3.9008979722253672E-4</v>
       </c>
       <c r="D902" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="903" spans="1:4" x14ac:dyDescent="0.3">
@@ -13587,7 +13587,7 @@
         <v>3.6095415506598108E-4</v>
       </c>
       <c r="D903" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="904" spans="1:4" x14ac:dyDescent="0.3">
@@ -13601,7 +13601,7 @@
         <v>3.5792295389142819E-4</v>
       </c>
       <c r="D904" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="905" spans="1:4" x14ac:dyDescent="0.3">
@@ -13615,7 +13615,7 @@
         <v>3.5017780445928062E-4</v>
       </c>
       <c r="D905" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="906" spans="1:4" x14ac:dyDescent="0.3">
@@ -13629,7 +13629,7 @@
         <v>3.3526652199291772E-4</v>
       </c>
       <c r="D906" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="907" spans="1:4" x14ac:dyDescent="0.3">
@@ -13643,7 +13643,7 @@
         <v>3.2688099808119922E-4</v>
       </c>
       <c r="D907" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="908" spans="1:4" x14ac:dyDescent="0.3">
@@ -13657,7 +13657,7 @@
         <v>2.6129900402732301E-4</v>
       </c>
       <c r="D908" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="909" spans="1:4" x14ac:dyDescent="0.3">
@@ -13671,7 +13671,7 @@
         <v>2.5162920349681192E-4</v>
       </c>
       <c r="D909" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="910" spans="1:4" x14ac:dyDescent="0.3">
@@ -13685,7 +13685,7 @@
         <v>2.000289607587226E-4</v>
       </c>
       <c r="D910" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="911" spans="1:4" x14ac:dyDescent="0.3">
@@ -13699,7 +13699,7 @@
         <v>1.7610588467544401E-4</v>
       </c>
       <c r="D911" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="912" spans="1:4" x14ac:dyDescent="0.3">
@@ -13713,7 +13713,7 @@
         <v>1.6090826818706151E-4</v>
       </c>
       <c r="D912" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="913" spans="1:4" x14ac:dyDescent="0.3">
@@ -13727,7 +13727,7 @@
         <v>1.60421639462176E-4</v>
       </c>
       <c r="D913" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="914" spans="1:4" x14ac:dyDescent="0.3">
@@ -13741,7 +13741,7 @@
         <v>1.380910378208882E-4</v>
       </c>
       <c r="D914" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="915" spans="1:4" x14ac:dyDescent="0.3">
@@ -13755,7 +13755,7 @@
         <v>1.3252936897104151E-4</v>
       </c>
       <c r="D915" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="916" spans="1:4" x14ac:dyDescent="0.3">
@@ -13769,7 +13769,7 @@
         <v>1.264147769368517E-4</v>
       </c>
       <c r="D916" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="917" spans="1:4" x14ac:dyDescent="0.3">
@@ -13783,7 +13783,7 @@
         <v>1.2537663635211579E-4</v>
       </c>
       <c r="D917" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="918" spans="1:4" x14ac:dyDescent="0.3">
@@ -13797,7 +13797,7 @@
         <v>1.2244840257165699E-4</v>
       </c>
       <c r="D918" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="919" spans="1:4" x14ac:dyDescent="0.3">
@@ -13811,7 +13811,7 @@
         <v>1.1742414080728701E-4</v>
       </c>
       <c r="D919" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="920" spans="1:4" x14ac:dyDescent="0.3">
@@ -13825,7 +13825,7 @@
         <v>1.106543638569063E-4</v>
       </c>
       <c r="D920" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="921" spans="1:4" x14ac:dyDescent="0.3">
@@ -13839,7 +13839,7 @@
         <v>1.104759336068E-4</v>
       </c>
       <c r="D921" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="922" spans="1:4" x14ac:dyDescent="0.3">
@@ -13853,7 +13853,7 @@
         <v>1.014182973555314E-4</v>
       </c>
       <c r="D922" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="923" spans="1:4" x14ac:dyDescent="0.3">
@@ -13867,7 +13867,7 @@
         <v>9.4400269339097999E-5</v>
       </c>
       <c r="D923" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="924" spans="1:4" x14ac:dyDescent="0.3">
@@ -13881,7 +13881,7 @@
         <v>8.6011219070890755E-5</v>
       </c>
       <c r="D924" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="925" spans="1:4" x14ac:dyDescent="0.3">
@@ -13895,7 +13895,7 @@
         <v>6.5069270812239207E-5</v>
       </c>
       <c r="D925" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="926" spans="1:4" x14ac:dyDescent="0.3">
@@ -13909,7 +13909,7 @@
         <v>5.8706428363577821E-5</v>
       </c>
       <c r="D926" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="927" spans="1:4" x14ac:dyDescent="0.3">
@@ -13923,7 +13923,7 @@
         <v>4.9108564332590117E-5</v>
       </c>
       <c r="D927" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="928" spans="1:4" x14ac:dyDescent="0.3">
@@ -13937,7 +13937,7 @@
         <v>4.1131384943921597E-5</v>
       </c>
       <c r="D928" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="929" spans="1:4" x14ac:dyDescent="0.3">
@@ -13951,7 +13951,7 @@
         <v>4.042330533198136E-5</v>
       </c>
       <c r="D929" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="930" spans="1:4" x14ac:dyDescent="0.3">
@@ -13965,7 +13965,7 @@
         <v>3.4848941729091609E-5</v>
       </c>
       <c r="D930" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="931" spans="1:4" x14ac:dyDescent="0.3">
@@ -13979,7 +13979,7 @@
         <v>3.039805497416952E-5</v>
       </c>
       <c r="D931" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="932" spans="1:4" x14ac:dyDescent="0.3">
@@ -13993,7 +13993,7 @@
         <v>2.1019526146659579E-5</v>
       </c>
       <c r="D932" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="933" spans="1:4" x14ac:dyDescent="0.3">
@@ -14007,7 +14007,7 @@
         <v>1.9649208905551011E-5</v>
       </c>
       <c r="D933" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="934" spans="1:4" x14ac:dyDescent="0.3">
@@ -14021,7 +14021,7 @@
         <v>1.857227905102058E-5</v>
       </c>
       <c r="D934" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="935" spans="1:4" x14ac:dyDescent="0.3">
@@ -14035,7 +14035,7 @@
         <v>1.8271133940799741E-5</v>
       </c>
       <c r="D935" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="936" spans="1:4" x14ac:dyDescent="0.3">
@@ -14049,7 +14049,7 @@
         <v>1.8199197441276381E-5</v>
       </c>
       <c r="D936" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="937" spans="1:4" x14ac:dyDescent="0.3">
@@ -14063,7 +14063,7 @@
         <v>1.5964937846803101E-5</v>
       </c>
       <c r="D937" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="938" spans="1:4" x14ac:dyDescent="0.3">
@@ -14077,7 +14077,7 @@
         <v>1.0457573714036349E-5</v>
       </c>
       <c r="D938" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="939" spans="1:4" x14ac:dyDescent="0.3">
@@ -14091,7 +14091,7 @@
         <v>7.8213179504060922E-7</v>
       </c>
       <c r="D939" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="940" spans="1:4" x14ac:dyDescent="0.3">
@@ -14105,7 +14105,7 @@
         <v>2.3837765883287659E-7</v>
       </c>
       <c r="D940" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="941" spans="1:4" x14ac:dyDescent="0.3">
@@ -14119,7 +14119,7 @@
         <v>6.0652419391978331E-8</v>
       </c>
       <c r="D941" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="942" spans="1:4" x14ac:dyDescent="0.3">
@@ -14133,7 +14133,7 @@
         <v>2.2568160262776621E-8</v>
       </c>
       <c r="D942" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="943" spans="1:4" x14ac:dyDescent="0.3">
@@ -14147,7 +14147,7 @@
         <v>1.4106729116789291E-9</v>
       </c>
       <c r="D943" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="944" spans="1:4" x14ac:dyDescent="0.3">
@@ -14161,7 +14161,7 @@
         <v>7.0501066532868414E-10</v>
       </c>
       <c r="D944" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="945" spans="1:4" x14ac:dyDescent="0.3">
@@ -14175,7 +14175,7 @@
         <v>0.61725284035848527</v>
       </c>
       <c r="D945" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="946" spans="1:4" x14ac:dyDescent="0.3">
@@ -14189,7 +14189,7 @@
         <v>0.1799369151172065</v>
       </c>
       <c r="D946" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="947" spans="1:4" x14ac:dyDescent="0.3">
@@ -14203,7 +14203,7 @@
         <v>0.1231618365617011</v>
       </c>
       <c r="D947" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="948" spans="1:4" x14ac:dyDescent="0.3">
@@ -14217,7 +14217,7 @@
         <v>4.9838967971444319E-2</v>
       </c>
       <c r="D948" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="949" spans="1:4" x14ac:dyDescent="0.3">
@@ -14231,7 +14231,7 @@
         <v>2.240497000595278E-2</v>
       </c>
       <c r="D949" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="950" spans="1:4" x14ac:dyDescent="0.3">
@@ -14245,7 +14245,7 @@
         <v>1.63118144133721E-3</v>
       </c>
       <c r="D950" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="951" spans="1:4" x14ac:dyDescent="0.3">
@@ -14259,7 +14259,7 @@
         <v>1.5760015362803099E-3</v>
       </c>
       <c r="D951" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="952" spans="1:4" x14ac:dyDescent="0.3">
@@ -14273,7 +14273,7 @@
         <v>1.1103341512009729E-3</v>
       </c>
       <c r="D952" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="953" spans="1:4" x14ac:dyDescent="0.3">
@@ -14287,7 +14287,7 @@
         <v>9.0127703261453545E-4</v>
       </c>
       <c r="D953" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="954" spans="1:4" x14ac:dyDescent="0.3">
@@ -14301,7 +14301,7 @@
         <v>7.4605484723818663E-4</v>
       </c>
       <c r="D954" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="955" spans="1:4" x14ac:dyDescent="0.3">
@@ -14315,7 +14315,7 @@
         <v>5.4013820682841671E-4</v>
       </c>
       <c r="D955" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="956" spans="1:4" x14ac:dyDescent="0.3">
@@ -14329,7 +14329,7 @@
         <v>3.1986580528270089E-4</v>
       </c>
       <c r="D956" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="957" spans="1:4" x14ac:dyDescent="0.3">
@@ -14343,7 +14343,7 @@
         <v>1.9694408246223079E-4</v>
       </c>
       <c r="D957" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="958" spans="1:4" x14ac:dyDescent="0.3">
@@ -14357,7 +14357,7 @@
         <v>1.2471640020003609E-4</v>
       </c>
       <c r="D958" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="959" spans="1:4" x14ac:dyDescent="0.3">
@@ -14371,7 +14371,7 @@
         <v>9.2864399751476208E-5</v>
       </c>
       <c r="D959" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="960" spans="1:4" x14ac:dyDescent="0.3">
@@ -14385,7 +14385,7 @@
         <v>8.120024020973365E-5</v>
       </c>
       <c r="D960" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="961" spans="1:4" x14ac:dyDescent="0.3">
@@ -14399,7 +14399,7 @@
         <v>4.8899363178709553E-5</v>
       </c>
       <c r="D961" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="962" spans="1:4" x14ac:dyDescent="0.3">
@@ -14413,7 +14413,7 @@
         <v>1.6598900622830849E-5</v>
       </c>
       <c r="D962" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="963" spans="1:4" x14ac:dyDescent="0.3">
@@ -14427,7 +14427,7 @@
         <v>4.9347410810882953E-6</v>
       </c>
       <c r="D963" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="964" spans="1:4" x14ac:dyDescent="0.3">
@@ -14441,7 +14441,7 @@
         <v>4.0374023913053143E-6</v>
       </c>
       <c r="D964" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="965" spans="1:4" x14ac:dyDescent="0.3">
@@ -14455,7 +14455,7 @@
         <v>2.2431394868847509E-6</v>
       </c>
       <c r="D965" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="966" spans="1:4" x14ac:dyDescent="0.3">
@@ -14469,7 +14469,7 @@
         <v>2.2431394868847509E-6</v>
       </c>
       <c r="D966" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="967" spans="1:4" x14ac:dyDescent="0.3">
@@ -14483,7 +14483,7 @@
         <v>1.345800797101772E-6</v>
       </c>
       <c r="D967" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="968" spans="1:4" x14ac:dyDescent="0.3">
@@ -14497,7 +14497,7 @@
         <v>8.9733868978297981E-7</v>
       </c>
       <c r="D968" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="969" spans="1:4" x14ac:dyDescent="0.3">
@@ -14511,7 +14511,7 @@
         <v>8.9733868978297981E-7</v>
       </c>
       <c r="D969" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="970" spans="1:4" x14ac:dyDescent="0.3">
@@ -14525,7 +14525,7 @@
         <v>8.9733868978297981E-7</v>
       </c>
       <c r="D970" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="971" spans="1:4" x14ac:dyDescent="0.3">
@@ -14539,7 +14539,7 @@
         <v>8.9733868978297981E-7</v>
       </c>
       <c r="D971" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="972" spans="1:4" x14ac:dyDescent="0.3">
@@ -14553,7 +14553,7 @@
         <v>0.38987612982235631</v>
       </c>
       <c r="D972" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="973" spans="1:4" x14ac:dyDescent="0.3">
@@ -14567,7 +14567,7 @@
         <v>0.23514099695939419</v>
       </c>
       <c r="D973" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="974" spans="1:4" x14ac:dyDescent="0.3">
@@ -14581,7 +14581,7 @@
         <v>0.12878420651841499</v>
       </c>
       <c r="D974" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="975" spans="1:4" x14ac:dyDescent="0.3">
@@ -14595,7 +14595,7 @@
         <v>8.7785549978782823E-2</v>
       </c>
       <c r="D975" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="976" spans="1:4" x14ac:dyDescent="0.3">
@@ -14609,7 +14609,7 @@
         <v>6.0979662182137989E-2</v>
       </c>
       <c r="D976" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="977" spans="1:4" x14ac:dyDescent="0.3">
@@ -14623,7 +14623,7 @@
         <v>2.3789502986158811E-2</v>
       </c>
       <c r="D977" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="978" spans="1:4" x14ac:dyDescent="0.3">
@@ -14637,7 +14637,7 @@
         <v>2.3631778844105489E-2</v>
       </c>
       <c r="D978" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="979" spans="1:4" x14ac:dyDescent="0.3">
@@ -14651,7 +14651,7 @@
         <v>1.982701392775962E-2</v>
       </c>
       <c r="D979" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="980" spans="1:4" x14ac:dyDescent="0.3">
@@ -14665,7 +14665,7 @@
         <v>1.3085569110414971E-2</v>
       </c>
       <c r="D980" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="981" spans="1:4" x14ac:dyDescent="0.3">
@@ -14679,7 +14679,7 @@
         <v>9.1537820864604387E-3</v>
       </c>
       <c r="D981" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="982" spans="1:4" x14ac:dyDescent="0.3">
@@ -14693,7 +14693,7 @@
         <v>1.7598888642838971E-3</v>
       </c>
       <c r="D982" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="983" spans="1:4" x14ac:dyDescent="0.3">
@@ -14707,7 +14707,7 @@
         <v>1.721120074880505E-3</v>
       </c>
       <c r="D983" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="984" spans="1:4" x14ac:dyDescent="0.3">
@@ -14721,7 +14721,7 @@
         <v>1.462018940136184E-3</v>
       </c>
       <c r="D984" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="985" spans="1:4" x14ac:dyDescent="0.3">
@@ -14735,7 +14735,7 @@
         <v>9.6380318816659044E-4</v>
       </c>
       <c r="D985" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="986" spans="1:4" x14ac:dyDescent="0.3">
@@ -14749,7 +14749,7 @@
         <v>6.6773918752519935E-4</v>
       </c>
       <c r="D986" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="987" spans="1:4" x14ac:dyDescent="0.3">
@@ -14763,7 +14763,7 @@
         <v>4.8846343132615813E-4</v>
       </c>
       <c r="D987" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="988" spans="1:4" x14ac:dyDescent="0.3">
@@ -14777,7 +14777,7 @@
         <v>3.7239766752277068E-4</v>
       </c>
       <c r="D988" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="989" spans="1:4" x14ac:dyDescent="0.3">
@@ -14791,7 +14791,7 @@
         <v>3.3158201649697032E-4</v>
       </c>
       <c r="D989" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="990" spans="1:4" x14ac:dyDescent="0.3">
@@ -14805,7 +14805,7 @@
         <v>7.6333666881379657E-5</v>
       </c>
       <c r="D990" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="991" spans="1:4" x14ac:dyDescent="0.3">
@@ -14819,7 +14819,7 @@
         <v>6.622005030024559E-5</v>
       </c>
       <c r="D991" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="992" spans="1:4" x14ac:dyDescent="0.3">
@@ -14833,7 +14833,7 @@
         <v>1.6133621153883648E-5</v>
       </c>
       <c r="D992" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="993" spans="1:4" x14ac:dyDescent="0.3">
@@ -14847,7 +14847,7 @@
         <v>1.1919651323889141E-5</v>
       </c>
       <c r="D993" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="994" spans="1:4" x14ac:dyDescent="0.3">
@@ -14861,7 +14861,7 @@
         <v>3.130415726201874E-6</v>
       </c>
       <c r="D994" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="995" spans="1:4" x14ac:dyDescent="0.3">
@@ -14875,7 +14875,7 @@
         <v>2.1672194440192988E-6</v>
       </c>
       <c r="D995" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="996" spans="1:4" x14ac:dyDescent="0.3">
@@ -14889,7 +14889,7 @@
         <v>1.444850041490873E-6</v>
       </c>
       <c r="D996" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="997" spans="1:4" x14ac:dyDescent="0.3">
@@ -14903,7 +14903,7 @@
         <v>1.324380983446788E-6</v>
       </c>
       <c r="D997" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="998" spans="1:4" x14ac:dyDescent="0.3">
@@ -14917,7 +14917,7 @@
         <v>1.2035782161006429E-7</v>
       </c>
       <c r="D998" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="999" spans="1:4" x14ac:dyDescent="0.3">
@@ -14931,7 +14931,7 @@
         <v>0.14024276545471301</v>
       </c>
       <c r="D999" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1000" spans="1:4" x14ac:dyDescent="0.3">
@@ -14945,7 +14945,7 @@
         <v>0.13684941428237449</v>
       </c>
       <c r="D1000" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1001" spans="1:4" x14ac:dyDescent="0.3">
@@ -14959,7 +14959,7 @@
         <v>0.1281602123455754</v>
       </c>
       <c r="D1001" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1002" spans="1:4" x14ac:dyDescent="0.3">
@@ -14973,7 +14973,7 @@
         <v>7.0525250468071898E-2</v>
       </c>
       <c r="D1002" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1003" spans="1:4" x14ac:dyDescent="0.3">
@@ -14987,7 +14987,7 @@
         <v>6.8244672089354377E-2</v>
       </c>
       <c r="D1003" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1004" spans="1:4" x14ac:dyDescent="0.3">
@@ -15001,7 +15001,7 @@
         <v>5.5121196245682548E-2</v>
       </c>
       <c r="D1004" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1005" spans="1:4" x14ac:dyDescent="0.3">
@@ -15015,7 +15015,7 @@
         <v>5.2586117934460559E-2</v>
       </c>
       <c r="D1005" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1006" spans="1:4" x14ac:dyDescent="0.3">
@@ -15029,7 +15029,7 @@
         <v>4.9498684685453639E-2</v>
       </c>
       <c r="D1006" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1007" spans="1:4" x14ac:dyDescent="0.3">
@@ -15043,7 +15043,7 @@
         <v>4.8110020455253727E-2</v>
       </c>
       <c r="D1007" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1008" spans="1:4" x14ac:dyDescent="0.3">
@@ -15057,7 +15057,7 @@
         <v>4.2557631509372633E-2</v>
       </c>
       <c r="D1008" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1009" spans="1:4" x14ac:dyDescent="0.3">
@@ -15071,7 +15071,7 @@
         <v>4.1397325785461361E-2</v>
       </c>
       <c r="D1009" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1010" spans="1:4" x14ac:dyDescent="0.3">
@@ -15085,7 +15085,7 @@
         <v>2.508548382281775E-2</v>
       </c>
       <c r="D1010" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1011" spans="1:4" x14ac:dyDescent="0.3">
@@ -15099,7 +15099,7 @@
         <v>2.3313754405699261E-2</v>
       </c>
       <c r="D1011" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1012" spans="1:4" x14ac:dyDescent="0.3">
@@ -15113,7 +15113,7 @@
         <v>2.1654937373661219E-2</v>
       </c>
       <c r="D1012" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1013" spans="1:4" x14ac:dyDescent="0.3">
@@ -15127,7 +15127,7 @@
         <v>1.6719091400874991E-2</v>
       </c>
       <c r="D1013" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1014" spans="1:4" x14ac:dyDescent="0.3">
@@ -15141,7 +15141,7 @@
         <v>1.5799333155347189E-2</v>
       </c>
       <c r="D1014" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1015" spans="1:4" x14ac:dyDescent="0.3">
@@ -15155,7 +15155,7 @@
         <v>1.3839294058905049E-2</v>
       </c>
       <c r="D1015" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1016" spans="1:4" x14ac:dyDescent="0.3">
@@ -15169,7 +15169,7 @@
         <v>7.8963017741316768E-3</v>
       </c>
       <c r="D1016" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1017" spans="1:4" x14ac:dyDescent="0.3">
@@ -15183,7 +15183,7 @@
         <v>7.642353635149879E-3</v>
       </c>
       <c r="D1017" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1018" spans="1:4" x14ac:dyDescent="0.3">
@@ -15197,7 +15197,7 @@
         <v>6.9924351358630231E-3</v>
       </c>
       <c r="D1018" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1019" spans="1:4" x14ac:dyDescent="0.3">
@@ -15211,7 +15211,7 @@
         <v>3.9738114613409306E-3</v>
       </c>
       <c r="D1019" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1020" spans="1:4" x14ac:dyDescent="0.3">
@@ -15225,7 +15225,7 @@
         <v>3.3978015432415522E-3</v>
       </c>
       <c r="D1020" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1021" spans="1:4" x14ac:dyDescent="0.3">
@@ -15239,7 +15239,7 @@
         <v>2.370901081821356E-3</v>
       </c>
       <c r="D1021" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1022" spans="1:4" x14ac:dyDescent="0.3">
@@ -15253,7 +15253,7 @@
         <v>2.209766590523409E-3</v>
       </c>
       <c r="D1022" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1023" spans="1:4" x14ac:dyDescent="0.3">
@@ -15267,7 +15267,7 @@
         <v>1.903652722894982E-3</v>
       </c>
       <c r="D1023" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1024" spans="1:4" x14ac:dyDescent="0.3">
@@ -15281,7 +15281,7 @@
         <v>1.7581665980904769E-3</v>
       </c>
       <c r="D1024" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1025" spans="1:4" x14ac:dyDescent="0.3">
@@ -15295,7 +15295,7 @@
         <v>1.670064577597992E-3</v>
       </c>
       <c r="D1025" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1026" spans="1:4" x14ac:dyDescent="0.3">
@@ -15309,7 +15309,7 @@
         <v>1.632092288256369E-3</v>
       </c>
       <c r="D1026" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1027" spans="1:4" x14ac:dyDescent="0.3">
@@ -15323,7 +15323,7 @@
         <v>1.2708555369740969E-3</v>
       </c>
       <c r="D1027" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1028" spans="1:4" x14ac:dyDescent="0.3">
@@ -15337,7 +15337,7 @@
         <v>1.2424528942616951E-3</v>
       </c>
       <c r="D1028" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1029" spans="1:4" x14ac:dyDescent="0.3">
@@ -15351,7 +15351,7 @@
         <v>6.9829826109380161E-4</v>
       </c>
       <c r="D1029" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1030" spans="1:4" x14ac:dyDescent="0.3">
@@ -15365,7 +15365,7 @@
         <v>6.7847429266768282E-4</v>
       </c>
       <c r="D1030" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1031" spans="1:4" x14ac:dyDescent="0.3">
@@ -15379,7 +15379,7 @@
         <v>5.4855320476206735E-4</v>
       </c>
       <c r="D1031" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1032" spans="1:4" x14ac:dyDescent="0.3">
@@ -15393,7 +15393,7 @@
         <v>5.4280781159923993E-4</v>
       </c>
       <c r="D1032" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1033" spans="1:4" x14ac:dyDescent="0.3">
@@ -15407,7 +15407,7 @@
         <v>4.545008411293478E-4</v>
       </c>
       <c r="D1033" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1034" spans="1:4" x14ac:dyDescent="0.3">
@@ -15421,7 +15421,7 @@
         <v>3.0291122251618549E-4</v>
       </c>
       <c r="D1034" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1035" spans="1:4" x14ac:dyDescent="0.3">
@@ -15435,7 +15435,7 @@
         <v>2.9891354727716292E-4</v>
       </c>
       <c r="D1035" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1036" spans="1:4" x14ac:dyDescent="0.3">
@@ -15449,7 +15449,7 @@
         <v>2.704545982539602E-4</v>
       </c>
       <c r="D1036" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1037" spans="1:4" x14ac:dyDescent="0.3">
@@ -15463,7 +15463,7 @@
         <v>2.3891462450136879E-4</v>
       </c>
       <c r="D1037" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1038" spans="1:4" x14ac:dyDescent="0.3">
@@ -15477,7 +15477,7 @@
         <v>2.2244194901568671E-4</v>
       </c>
       <c r="D1038" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1039" spans="1:4" x14ac:dyDescent="0.3">
@@ -15491,7 +15491,7 @@
         <v>1.952757687512453E-4</v>
       </c>
       <c r="D1039" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1040" spans="1:4" x14ac:dyDescent="0.3">
@@ -15505,7 +15505,7 @@
         <v>1.8832319200591459E-4</v>
       </c>
       <c r="D1040" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1041" spans="1:4" x14ac:dyDescent="0.3">
@@ -15519,7 +15519,7 @@
         <v>1.797400127986084E-4</v>
       </c>
       <c r="D1041" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1042" spans="1:4" x14ac:dyDescent="0.3">
@@ -15533,7 +15533,7 @@
         <v>1.698415423082206E-4</v>
       </c>
       <c r="D1042" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1043" spans="1:4" x14ac:dyDescent="0.3">
@@ -15547,7 +15547,7 @@
         <v>1.673483442272979E-4</v>
       </c>
       <c r="D1043" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1044" spans="1:4" x14ac:dyDescent="0.3">
@@ -15561,7 +15561,7 @@
         <v>1.6466145535033391E-4</v>
       </c>
       <c r="D1044" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1045" spans="1:4" x14ac:dyDescent="0.3">
@@ -15575,7 +15575,7 @@
         <v>1.242229932923376E-4</v>
       </c>
       <c r="D1045" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1046" spans="1:4" x14ac:dyDescent="0.3">
@@ -15589,7 +15589,7 @@
         <v>1.1824337128664641E-4</v>
       </c>
       <c r="D1046" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1047" spans="1:4" x14ac:dyDescent="0.3">
@@ -15603,7 +15603,7 @@
         <v>1.139889425996448E-4</v>
       </c>
       <c r="D1047" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1048" spans="1:4" x14ac:dyDescent="0.3">
@@ -15617,7 +15617,7 @@
         <v>9.5872149888918178E-5</v>
       </c>
       <c r="D1048" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1049" spans="1:4" x14ac:dyDescent="0.3">
@@ -15631,7 +15631,7 @@
         <v>8.7757432528929536E-5</v>
       </c>
       <c r="D1049" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1050" spans="1:4" x14ac:dyDescent="0.3">
@@ -15645,7 +15645,7 @@
         <v>8.6552498285745233E-5</v>
       </c>
       <c r="D1050" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1051" spans="1:4" x14ac:dyDescent="0.3">
@@ -15659,7 +15659,7 @@
         <v>8.4640370512151466E-5</v>
       </c>
       <c r="D1051" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1052" spans="1:4" x14ac:dyDescent="0.3">
@@ -15673,7 +15673,7 @@
         <v>8.2809322993792641E-5</v>
       </c>
       <c r="D1052" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1053" spans="1:4" x14ac:dyDescent="0.3">
@@ -15687,7 +15687,7 @@
         <v>6.9079838534285282E-5</v>
       </c>
       <c r="D1053" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1054" spans="1:4" x14ac:dyDescent="0.3">
@@ -15701,7 +15701,7 @@
         <v>5.4140919072160418E-5</v>
       </c>
       <c r="D1054" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1055" spans="1:4" x14ac:dyDescent="0.3">
@@ -15715,7 +15715,7 @@
         <v>4.6800960734747067E-5</v>
       </c>
       <c r="D1055" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1056" spans="1:4" x14ac:dyDescent="0.3">
@@ -15729,7 +15729,7 @@
         <v>2.3481560622608471E-5</v>
       </c>
       <c r="D1056" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1057" spans="1:4" x14ac:dyDescent="0.3">
@@ -15743,7 +15743,7 @@
         <v>1.5641610152306201E-5</v>
       </c>
       <c r="D1057" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1058" spans="1:4" x14ac:dyDescent="0.3">
@@ -15757,7 +15757,7 @@
         <v>4.6598258015864777E-6</v>
       </c>
       <c r="D1058" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1059" spans="1:4" x14ac:dyDescent="0.3">
@@ -15771,7 +15771,7 @@
         <v>1.8175348360846361E-6</v>
       </c>
       <c r="D1059" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1060" spans="1:4" x14ac:dyDescent="0.3">
@@ -15785,7 +15785,7 @@
         <v>1.2342110278467249E-6</v>
       </c>
       <c r="D1060" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1061" spans="1:4" x14ac:dyDescent="0.3">
@@ -15799,7 +15799,7 @@
         <v>7.9052728655337729E-7</v>
       </c>
       <c r="D1061" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1062" spans="1:4" x14ac:dyDescent="0.3">
@@ -15813,7 +15813,7 @@
         <v>5.3602733948334866E-7</v>
       </c>
       <c r="D1062" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1063" spans="1:4" x14ac:dyDescent="0.3">
@@ -15827,7 +15827,7 @@
         <v>2.0720347831546651E-7</v>
       </c>
       <c r="D1063" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1064" spans="1:4" x14ac:dyDescent="0.3">
@@ -15841,7 +15841,7 @@
         <v>1.3738448524064989E-7</v>
       </c>
       <c r="D1064" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1065" spans="1:4" x14ac:dyDescent="0.3">
@@ -15855,7 +15855,7 @@
         <v>7.4323914097853432E-8</v>
       </c>
       <c r="D1065" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1066" spans="1:4" x14ac:dyDescent="0.3">
@@ -15869,7 +15869,7 @@
         <v>9.0098420460736692E-9</v>
       </c>
       <c r="D1066" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1067" spans="1:4" x14ac:dyDescent="0.3">
@@ -15883,7 +15883,7 @@
         <v>0.7779850553408888</v>
       </c>
       <c r="D1067" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1068" spans="1:4" x14ac:dyDescent="0.3">
@@ -15897,7 +15897,7 @@
         <v>8.9451268003513273E-2</v>
       </c>
       <c r="D1068" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1069" spans="1:4" x14ac:dyDescent="0.3">
@@ -15911,7 +15911,7 @@
         <v>5.9967797154663778E-2</v>
       </c>
       <c r="D1069" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1070" spans="1:4" x14ac:dyDescent="0.3">
@@ -15925,7 +15925,7 @@
         <v>2.8634714418190429E-2</v>
       </c>
       <c r="D1070" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1071" spans="1:4" x14ac:dyDescent="0.3">
@@ -15939,7 +15939,7 @@
         <v>1.9582588524514982E-2</v>
       </c>
       <c r="D1071" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1072" spans="1:4" x14ac:dyDescent="0.3">
@@ -15953,7 +15953,7 @@
         <v>1.280724770347156E-2</v>
       </c>
       <c r="D1072" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1073" spans="1:4" x14ac:dyDescent="0.3">
@@ -15967,7 +15967,7 @@
         <v>4.4091199803535071E-3</v>
       </c>
       <c r="D1073" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1074" spans="1:4" x14ac:dyDescent="0.3">
@@ -15981,7 +15981,7 @@
         <v>1.8131318661856249E-3</v>
       </c>
       <c r="D1074" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1075" spans="1:4" x14ac:dyDescent="0.3">
@@ -15995,7 +15995,7 @@
         <v>1.7263440213611679E-3</v>
       </c>
       <c r="D1075" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1076" spans="1:4" x14ac:dyDescent="0.3">
@@ -16009,7 +16009,7 @@
         <v>1.2262102498667559E-3</v>
       </c>
       <c r="D1076" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1077" spans="1:4" x14ac:dyDescent="0.3">
@@ -16023,7 +16023,7 @@
         <v>7.2931258738663084E-4</v>
       </c>
       <c r="D1077" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1078" spans="1:4" x14ac:dyDescent="0.3">
@@ -16037,7 +16037,7 @@
         <v>6.9253820125308129E-4</v>
       </c>
       <c r="D1078" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1079" spans="1:4" x14ac:dyDescent="0.3">
@@ -16051,7 +16051,7 @@
         <v>2.9860920047374072E-4</v>
       </c>
       <c r="D1079" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1080" spans="1:4" x14ac:dyDescent="0.3">
@@ -16065,7 +16065,7 @@
         <v>2.5389131644479811E-4</v>
       </c>
       <c r="D1080" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1081" spans="1:4" x14ac:dyDescent="0.3">
@@ -16079,7 +16079,7 @@
         <v>1.5562977182023011E-4</v>
       </c>
       <c r="D1081" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1082" spans="1:4" x14ac:dyDescent="0.3">
@@ -16093,7 +16093,7 @@
         <v>1.097352444246783E-4</v>
       </c>
       <c r="D1082" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1083" spans="1:4" x14ac:dyDescent="0.3">
@@ -16107,7 +16107,7 @@
         <v>9.7084901257958665E-5</v>
       </c>
       <c r="D1083" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1084" spans="1:4" x14ac:dyDescent="0.3">
@@ -16121,7 +16121,7 @@
         <v>2.7066059090687389E-5</v>
       </c>
       <c r="D1084" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1085" spans="1:4" x14ac:dyDescent="0.3">
@@ -16135,7 +16135,7 @@
         <v>2.088793395254256E-5</v>
       </c>
       <c r="D1085" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1086" spans="1:4" x14ac:dyDescent="0.3">
@@ -16149,7 +16149,7 @@
         <v>5.5896675523954484E-6</v>
       </c>
       <c r="D1086" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1087" spans="1:4" x14ac:dyDescent="0.3">
@@ -16163,7 +16163,7 @@
         <v>3.8245666000367779E-6</v>
       </c>
       <c r="D1087" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1088" spans="1:4" x14ac:dyDescent="0.3">
@@ -16177,7 +16177,7 @@
         <v>1.765100952358669E-6</v>
       </c>
       <c r="D1088" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1089" spans="1:4" x14ac:dyDescent="0.3">
@@ -16191,7 +16191,7 @@
         <v>2.9409289042994769E-7</v>
       </c>
       <c r="D1089" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1090" spans="1:4" x14ac:dyDescent="0.3">
@@ -16205,7 +16205,7 @@
         <v>2.9409289042994769E-7</v>
       </c>
       <c r="D1090" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1091" spans="1:4" x14ac:dyDescent="0.3">
@@ -16219,7 +16219,7 @@
         <v>0.14260123545571449</v>
       </c>
       <c r="D1091" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1092" spans="1:4" x14ac:dyDescent="0.3">
@@ -16233,7 +16233,7 @@
         <v>0.1362865141683183</v>
       </c>
       <c r="D1092" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1093" spans="1:4" x14ac:dyDescent="0.3">
@@ -16247,7 +16247,7 @@
         <v>0.1163788860918752</v>
       </c>
       <c r="D1093" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1094" spans="1:4" x14ac:dyDescent="0.3">
@@ -16261,7 +16261,7 @@
         <v>8.3123682376212413E-2</v>
       </c>
       <c r="D1094" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1095" spans="1:4" x14ac:dyDescent="0.3">
@@ -16275,7 +16275,7 @@
         <v>7.1473815480432065E-2</v>
       </c>
       <c r="D1095" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1096" spans="1:4" x14ac:dyDescent="0.3">
@@ -16289,7 +16289,7 @@
         <v>7.0018099396109035E-2</v>
       </c>
       <c r="D1096" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1097" spans="1:4" x14ac:dyDescent="0.3">
@@ -16303,7 +16303,7 @@
         <v>4.4794654916189093E-2</v>
       </c>
       <c r="D1097" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1098" spans="1:4" x14ac:dyDescent="0.3">
@@ -16317,7 +16317,7 @@
         <v>4.2973449687317512E-2</v>
       </c>
       <c r="D1098" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1099" spans="1:4" x14ac:dyDescent="0.3">
@@ -16331,7 +16331,7 @@
         <v>4.1166072526058167E-2</v>
       </c>
       <c r="D1099" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1100" spans="1:4" x14ac:dyDescent="0.3">
@@ -16345,7 +16345,7 @@
         <v>3.4083035880946903E-2</v>
       </c>
       <c r="D1100" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1101" spans="1:4" x14ac:dyDescent="0.3">
@@ -16359,7 +16359,7 @@
         <v>2.628735147338886E-2</v>
       </c>
       <c r="D1101" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1102" spans="1:4" x14ac:dyDescent="0.3">
@@ -16373,7 +16373,7 @@
         <v>2.307461769062219E-2</v>
       </c>
       <c r="D1102" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1103" spans="1:4" x14ac:dyDescent="0.3">
@@ -16387,7 +16387,7 @@
         <v>2.023296425996688E-2</v>
       </c>
       <c r="D1103" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1104" spans="1:4" x14ac:dyDescent="0.3">
@@ -16401,7 +16401,7 @@
         <v>1.9008021799154749E-2</v>
       </c>
       <c r="D1104" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1105" spans="1:4" x14ac:dyDescent="0.3">
@@ -16415,7 +16415,7 @@
         <v>1.252183485565953E-2</v>
       </c>
       <c r="D1105" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1106" spans="1:4" x14ac:dyDescent="0.3">
@@ -16429,7 +16429,7 @@
         <v>1.010195776025731E-2</v>
       </c>
       <c r="D1106" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1107" spans="1:4" x14ac:dyDescent="0.3">
@@ -16443,7 +16443,7 @@
         <v>8.8863705988914358E-3</v>
       </c>
       <c r="D1107" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1108" spans="1:4" x14ac:dyDescent="0.3">
@@ -16457,7 +16457,7 @@
         <v>8.8560539652870994E-3</v>
       </c>
       <c r="D1108" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1109" spans="1:4" x14ac:dyDescent="0.3">
@@ -16471,7 +16471,7 @@
         <v>7.6753888347962399E-3</v>
       </c>
       <c r="D1109" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1110" spans="1:4" x14ac:dyDescent="0.3">
@@ -16485,7 +16485,7 @@
         <v>7.5989509304551601E-3</v>
       </c>
       <c r="D1110" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1111" spans="1:4" x14ac:dyDescent="0.3">
@@ -16499,7 +16499,7 @@
         <v>7.01378941478963E-3</v>
       </c>
       <c r="D1111" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1112" spans="1:4" x14ac:dyDescent="0.3">
@@ -16513,7 +16513,7 @@
         <v>6.4203177962863971E-3</v>
       </c>
       <c r="D1112" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1113" spans="1:4" x14ac:dyDescent="0.3">
@@ -16527,7 +16527,7 @@
         <v>6.3353164076128147E-3</v>
       </c>
       <c r="D1113" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1114" spans="1:4" x14ac:dyDescent="0.3">
@@ -16541,7 +16541,7 @@
         <v>5.9972290255436494E-3</v>
       </c>
       <c r="D1114" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1115" spans="1:4" x14ac:dyDescent="0.3">
@@ -16555,7 +16555,7 @@
         <v>5.4992315451356964E-3</v>
       </c>
       <c r="D1115" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1116" spans="1:4" x14ac:dyDescent="0.3">
@@ -16569,7 +16569,7 @@
         <v>5.0811094375836129E-3</v>
       </c>
       <c r="D1116" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1117" spans="1:4" x14ac:dyDescent="0.3">
@@ -16583,7 +16583,7 @@
         <v>4.6824075937135492E-3</v>
       </c>
       <c r="D1117" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1118" spans="1:4" x14ac:dyDescent="0.3">
@@ -16597,7 +16597,7 @@
         <v>4.2406210911287486E-3</v>
       </c>
       <c r="D1118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1119" spans="1:4" x14ac:dyDescent="0.3">
@@ -16611,7 +16611,7 @@
         <v>2.764395997342288E-3</v>
       </c>
       <c r="D1119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1120" spans="1:4" x14ac:dyDescent="0.3">
@@ -16625,7 +16625,7 @@
         <v>2.585393248111537E-3</v>
       </c>
       <c r="D1120" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1121" spans="1:4" x14ac:dyDescent="0.3">
@@ -16639,7 +16639,7 @@
         <v>2.4225158201100958E-3</v>
       </c>
       <c r="D1121" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1122" spans="1:4" x14ac:dyDescent="0.3">
@@ -16653,7 +16653,7 @@
         <v>2.1283771652363089E-3</v>
       </c>
       <c r="D1122" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1123" spans="1:4" x14ac:dyDescent="0.3">
@@ -16667,7 +16667,7 @@
         <v>2.0902166099607822E-3</v>
       </c>
       <c r="D1123" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1124" spans="1:4" x14ac:dyDescent="0.3">
@@ -16681,7 +16681,7 @@
         <v>2.0717099032040152E-3</v>
       </c>
       <c r="D1124" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1125" spans="1:4" x14ac:dyDescent="0.3">
@@ -16695,7 +16695,7 @@
         <v>1.9731684700498939E-3</v>
       </c>
       <c r="D1125" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1126" spans="1:4" x14ac:dyDescent="0.3">
@@ -16709,7 +16709,7 @@
         <v>1.527624804274806E-3</v>
       </c>
       <c r="D1126" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1127" spans="1:4" x14ac:dyDescent="0.3">
@@ -16723,7 +16723,7 @@
         <v>1.253662597138494E-3</v>
       </c>
       <c r="D1127" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1128" spans="1:4" x14ac:dyDescent="0.3">
@@ -16737,7 +16737,7 @@
         <v>1.249431332838259E-3</v>
       </c>
       <c r="D1128" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1129" spans="1:4" x14ac:dyDescent="0.3">
@@ -16751,7 +16751,7 @@
         <v>1.0216577008696701E-3</v>
       </c>
       <c r="D1129" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1130" spans="1:4" x14ac:dyDescent="0.3">
@@ -16765,7 +16765,7 @@
         <v>9.6053647607917728E-4</v>
       </c>
       <c r="D1130" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1131" spans="1:4" x14ac:dyDescent="0.3">
@@ -16779,7 +16779,7 @@
         <v>8.3448044617014246E-4</v>
       </c>
       <c r="D1131" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1132" spans="1:4" x14ac:dyDescent="0.3">
@@ -16793,7 +16793,7 @@
         <v>6.7840075380993126E-4</v>
       </c>
       <c r="D1132" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1133" spans="1:4" x14ac:dyDescent="0.3">
@@ -16807,7 +16807,7 @@
         <v>5.2712144332018685E-4</v>
       </c>
       <c r="D1133" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1134" spans="1:4" x14ac:dyDescent="0.3">
@@ -16821,7 +16821,7 @@
         <v>5.0485757245869562E-4</v>
       </c>
       <c r="D1134" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1135" spans="1:4" x14ac:dyDescent="0.3">
@@ -16835,7 +16835,7 @@
         <v>4.7097380949907689E-4</v>
       </c>
       <c r="D1135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1136" spans="1:4" x14ac:dyDescent="0.3">
@@ -16849,7 +16849,7 @@
         <v>4.3026261819723759E-4</v>
       </c>
       <c r="D1136" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1137" spans="1:4" x14ac:dyDescent="0.3">
@@ -16863,7 +16863,7 @@
         <v>3.2777992363182401E-4</v>
       </c>
       <c r="D1137" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1138" spans="1:4" x14ac:dyDescent="0.3">
@@ -16877,7 +16877,7 @@
         <v>2.8639964844912719E-4</v>
       </c>
       <c r="D1138" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1139" spans="1:4" x14ac:dyDescent="0.3">
@@ -16891,7 +16891,7 @@
         <v>2.6470588457927382E-4</v>
       </c>
       <c r="D1139" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1140" spans="1:4" x14ac:dyDescent="0.3">
@@ -16905,7 +16905,7 @@
         <v>2.566145206850341E-4</v>
       </c>
       <c r="D1140" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1141" spans="1:4" x14ac:dyDescent="0.3">
@@ -16919,7 +16919,7 @@
         <v>1.7504763134758731E-4</v>
       </c>
       <c r="D1141" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1142" spans="1:4" x14ac:dyDescent="0.3">
@@ -16933,7 +16933,7 @@
         <v>1.7024032169840389E-4</v>
       </c>
       <c r="D1142" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1143" spans="1:4" x14ac:dyDescent="0.3">
@@ -16947,7 +16947,7 @@
         <v>1.54763299184927E-4</v>
       </c>
       <c r="D1143" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1144" spans="1:4" x14ac:dyDescent="0.3">
@@ -16961,7 +16961,7 @@
         <v>1.359824266827749E-4</v>
       </c>
       <c r="D1144" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1145" spans="1:4" x14ac:dyDescent="0.3">
@@ -16975,7 +16975,7 @@
         <v>1.1590099632002119E-4</v>
       </c>
       <c r="D1145" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1146" spans="1:4" x14ac:dyDescent="0.3">
@@ -16989,7 +16989,7 @@
         <v>1.007367407033235E-4</v>
       </c>
       <c r="D1146" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1147" spans="1:4" x14ac:dyDescent="0.3">
@@ -17003,7 +17003,7 @@
         <v>3.2105147217882313E-5</v>
       </c>
       <c r="D1147" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1148" spans="1:4" x14ac:dyDescent="0.3">
@@ -17017,7 +17017,7 @@
         <v>3.0702644203843263E-5</v>
       </c>
       <c r="D1148" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1149" spans="1:4" x14ac:dyDescent="0.3">
@@ -17031,7 +17031,7 @@
         <v>1.7110142100039001E-5</v>
       </c>
       <c r="D1149" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1150" spans="1:4" x14ac:dyDescent="0.3">
@@ -17045,7 +17045,7 @@
         <v>6.0524397934269026E-6</v>
       </c>
       <c r="D1150" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1151" spans="1:4" x14ac:dyDescent="0.3">
@@ -17059,7 +17059,7 @@
         <v>3.3830311342759872E-6</v>
       </c>
       <c r="D1151" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1152" spans="1:4" x14ac:dyDescent="0.3">
@@ -17073,7 +17073,7 @@
         <v>3.1910166275848401E-6</v>
       </c>
       <c r="D1152" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1153" spans="1:4" x14ac:dyDescent="0.3">
@@ -17087,7 +17087,7 @@
         <v>3.0217661287304469E-6</v>
       </c>
       <c r="D1153" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1154" spans="1:4" x14ac:dyDescent="0.3">
@@ -17101,7 +17101,7 @@
         <v>2.231929857784928E-6</v>
       </c>
       <c r="D1154" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1155" spans="1:4" x14ac:dyDescent="0.3">
@@ -17115,7 +17115,7 @@
         <v>1.9448970619353789E-6</v>
       </c>
       <c r="D1155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1156" spans="1:4" x14ac:dyDescent="0.3">
@@ -17129,7 +17129,7 @@
         <v>1.0679615308290591E-6</v>
       </c>
       <c r="D1156" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1157" spans="1:4" x14ac:dyDescent="0.3">
@@ -17143,7 +17143,7 @@
         <v>7.6608101282777259E-7</v>
       </c>
       <c r="D1157" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1158" spans="1:4" x14ac:dyDescent="0.3">
@@ -17157,7 +17157,7 @@
         <v>4.5925338779680643E-7</v>
       </c>
       <c r="D1158" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1159" spans="1:4" x14ac:dyDescent="0.3">
@@ -17171,7 +17171,7 @@
         <v>4.3351928686718782E-7</v>
       </c>
       <c r="D1159" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1160" spans="1:4" x14ac:dyDescent="0.3">
@@ -17185,7 +17185,7 @@
         <v>4.1966190055891389E-7</v>
       </c>
       <c r="D1160" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1161" spans="1:4" x14ac:dyDescent="0.3">
@@ -17199,7 +17199,7 @@
         <v>3.9095862097395911E-7</v>
       </c>
       <c r="D1161" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1162" spans="1:4" x14ac:dyDescent="0.3">
@@ -17213,7 +17213,7 @@
         <v>3.2761370449337689E-7</v>
       </c>
       <c r="D1162" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1163" spans="1:4" x14ac:dyDescent="0.3">
@@ -17227,7 +17227,7 @@
         <v>2.6426878801279482E-7</v>
       </c>
       <c r="D1163" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1164" spans="1:4" x14ac:dyDescent="0.3">
@@ -17241,7 +17241,7 @@
         <v>6.928418822878317E-8</v>
       </c>
       <c r="D1164" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1165" spans="1:4" x14ac:dyDescent="0.3">
@@ -17255,7 +17255,7 @@
         <v>6.8293852385318697E-8</v>
       </c>
       <c r="D1165" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1166" spans="1:4" x14ac:dyDescent="0.3">
@@ -17269,7 +17269,7 @@
         <v>4.948844460983695E-8</v>
       </c>
       <c r="D1166" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1167" spans="1:4" x14ac:dyDescent="0.3">
@@ -17283,7 +17283,7 @@
         <v>1.9797572494003401E-9</v>
       </c>
       <c r="D1167" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1168" spans="1:4" x14ac:dyDescent="0.3">
@@ -17297,7 +17297,7 @@
         <v>0.40611681632435059</v>
       </c>
       <c r="D1168" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1169" spans="1:4" x14ac:dyDescent="0.3">
@@ -17311,7 +17311,7 @@
         <v>0.25095467104449543</v>
       </c>
       <c r="D1169" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1170" spans="1:4" x14ac:dyDescent="0.3">
@@ -17325,7 +17325,7 @@
         <v>7.5060969116757775E-2</v>
       </c>
       <c r="D1170" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1171" spans="1:4" x14ac:dyDescent="0.3">
@@ -17339,7 +17339,7 @@
         <v>6.1930958844059983E-2</v>
       </c>
       <c r="D1171" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1172" spans="1:4" x14ac:dyDescent="0.3">
@@ -17353,7 +17353,7 @@
         <v>4.5639197839736308E-2</v>
       </c>
       <c r="D1172" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1173" spans="1:4" x14ac:dyDescent="0.3">
@@ -17367,7 +17367,7 @@
         <v>3.4164964832600578E-2</v>
       </c>
       <c r="D1173" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1174" spans="1:4" x14ac:dyDescent="0.3">
@@ -17381,7 +17381,7 @@
         <v>2.2353685352927519E-2</v>
       </c>
       <c r="D1174" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1175" spans="1:4" x14ac:dyDescent="0.3">
@@ -17395,7 +17395,7 @@
         <v>1.6591894403574239E-2</v>
       </c>
       <c r="D1175" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1176" spans="1:4" x14ac:dyDescent="0.3">
@@ -17409,7 +17409,7 @@
         <v>1.198567883204526E-2</v>
       </c>
       <c r="D1176" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1177" spans="1:4" x14ac:dyDescent="0.3">
@@ -17423,7 +17423,7 @@
         <v>1.049384572862112E-2</v>
       </c>
       <c r="D1177" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1178" spans="1:4" x14ac:dyDescent="0.3">
@@ -17437,7 +17437,7 @@
         <v>1.0268704050647681E-2</v>
       </c>
       <c r="D1178" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1179" spans="1:4" x14ac:dyDescent="0.3">
@@ -17451,7 +17451,7 @@
         <v>7.8427871339853197E-3</v>
       </c>
       <c r="D1179" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1180" spans="1:4" x14ac:dyDescent="0.3">
@@ -17465,7 +17465,7 @@
         <v>6.5110289725943482E-3</v>
       </c>
       <c r="D1180" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1181" spans="1:4" x14ac:dyDescent="0.3">
@@ -17479,7 +17479,7 @@
         <v>6.2027846897695256E-3</v>
       </c>
       <c r="D1181" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1182" spans="1:4" x14ac:dyDescent="0.3">
@@ -17493,7 +17493,7 @@
         <v>5.2729425480975752E-3</v>
       </c>
       <c r="D1182" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1183" spans="1:4" x14ac:dyDescent="0.3">
@@ -17507,7 +17507,7 @@
         <v>4.2577060672476649E-3</v>
       </c>
       <c r="D1183" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1184" spans="1:4" x14ac:dyDescent="0.3">
@@ -17521,7 +17521,7 @@
         <v>3.8845615626245801E-3</v>
       </c>
       <c r="D1184" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1185" spans="1:4" x14ac:dyDescent="0.3">
@@ -17535,7 +17535,7 @@
         <v>3.2664823660892009E-3</v>
       </c>
       <c r="D1185" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1186" spans="1:4" x14ac:dyDescent="0.3">
@@ -17549,7 +17549,7 @@
         <v>2.812180813501364E-3</v>
       </c>
       <c r="D1186" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1187" spans="1:4" x14ac:dyDescent="0.3">
@@ -17563,7 +17563,7 @@
         <v>2.602323179202717E-3</v>
       </c>
       <c r="D1187" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1188" spans="1:4" x14ac:dyDescent="0.3">
@@ -17577,7 +17577,7 @@
         <v>2.5411826201021202E-3</v>
       </c>
       <c r="D1188" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1189" spans="1:4" x14ac:dyDescent="0.3">
@@ -17591,7 +17591,7 @@
         <v>1.5135892037586439E-3</v>
       </c>
       <c r="D1189" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1190" spans="1:4" x14ac:dyDescent="0.3">
@@ -17605,7 +17605,7 @@
         <v>1.19663809882761E-3</v>
       </c>
       <c r="D1190" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1191" spans="1:4" x14ac:dyDescent="0.3">
@@ -17619,7 +17619,7 @@
         <v>1.034652646780653E-3</v>
       </c>
       <c r="D1191" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1192" spans="1:4" x14ac:dyDescent="0.3">
@@ -17633,7 +17633,7 @@
         <v>9.4330769918265014E-4</v>
       </c>
       <c r="D1192" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1193" spans="1:4" x14ac:dyDescent="0.3">
@@ -17647,7 +17647,7 @@
         <v>7.8985379439379096E-4</v>
       </c>
       <c r="D1193" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1194" spans="1:4" x14ac:dyDescent="0.3">
@@ -17661,7 +17661,7 @@
         <v>7.3440093751364415E-4</v>
       </c>
       <c r="D1194" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1195" spans="1:4" x14ac:dyDescent="0.3">
@@ -17675,7 +17675,7 @@
         <v>4.9748510937428381E-4</v>
       </c>
       <c r="D1195" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1196" spans="1:4" x14ac:dyDescent="0.3">
@@ -17689,7 +17689,7 @@
         <v>4.7465983044210343E-4</v>
       </c>
       <c r="D1196" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1197" spans="1:4" x14ac:dyDescent="0.3">
@@ -17703,7 +17703,7 @@
         <v>3.943528705511804E-4</v>
       </c>
       <c r="D1197" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1198" spans="1:4" x14ac:dyDescent="0.3">
@@ -17717,7 +17717,7 @@
         <v>3.1191192976956462E-4</v>
       </c>
       <c r="D1198" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1199" spans="1:4" x14ac:dyDescent="0.3">
@@ -17731,7 +17731,7 @@
         <v>2.8161113706940831E-4</v>
       </c>
       <c r="D1199" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1200" spans="1:4" x14ac:dyDescent="0.3">
@@ -17745,7 +17745,7 @@
         <v>2.186389466971611E-4</v>
       </c>
       <c r="D1200" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1201" spans="1:4" x14ac:dyDescent="0.3">
@@ -17759,7 +17759,7 @@
         <v>1.8059534962799371E-4</v>
       </c>
       <c r="D1201" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1202" spans="1:4" x14ac:dyDescent="0.3">
@@ -17773,7 +17773,7 @@
         <v>1.765377176643438E-4</v>
       </c>
       <c r="D1202" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1203" spans="1:4" x14ac:dyDescent="0.3">
@@ -17787,7 +17787,7 @@
         <v>1.4445349376972089E-4</v>
       </c>
       <c r="D1203" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1204" spans="1:4" x14ac:dyDescent="0.3">
@@ -17801,7 +17801,7 @@
         <v>1.0901274135228621E-4</v>
       </c>
       <c r="D1204" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1205" spans="1:4" x14ac:dyDescent="0.3">
@@ -17815,7 +17815,7 @@
         <v>6.5697725393466395E-5</v>
       </c>
       <c r="D1205" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1206" spans="1:4" x14ac:dyDescent="0.3">
@@ -17829,7 +17829,7 @@
         <v>4.4988897842974722E-5</v>
       </c>
       <c r="D1206" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1207" spans="1:4" x14ac:dyDescent="0.3">
@@ -17843,7 +17843,7 @@
         <v>4.2648967487604437E-5</v>
       </c>
       <c r="D1207" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1208" spans="1:4" x14ac:dyDescent="0.3">
@@ -17857,7 +17857,7 @@
         <v>1.9503805378991189E-5</v>
       </c>
       <c r="D1208" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1209" spans="1:4" x14ac:dyDescent="0.3">
@@ -17871,7 +17871,7 @@
         <v>1.570908771170375E-5</v>
       </c>
       <c r="D1209" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1210" spans="1:4" x14ac:dyDescent="0.3">
@@ -17885,7 +17885,7 @@
         <v>8.4351430553470734E-6</v>
       </c>
       <c r="D1210" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1211" spans="1:4" x14ac:dyDescent="0.3">
@@ -17899,7 +17899,7 @@
         <v>8.2379583451716213E-6</v>
       </c>
       <c r="D1211" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1212" spans="1:4" x14ac:dyDescent="0.3">
@@ -17913,7 +17913,7 @@
         <v>7.9531382351323286E-6</v>
       </c>
       <c r="D1212" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1213" spans="1:4" x14ac:dyDescent="0.3">
@@ -17927,7 +17927,7 @@
         <v>5.8805025291827584E-6</v>
       </c>
       <c r="D1213" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1214" spans="1:4" x14ac:dyDescent="0.3">
@@ -17941,7 +17941,7 @@
         <v>5.6351136934389249E-6</v>
       </c>
       <c r="D1214" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1215" spans="1:4" x14ac:dyDescent="0.3">
@@ -17955,7 +17955,7 @@
         <v>5.2232188124694327E-6</v>
       </c>
       <c r="D1215" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1216" spans="1:4" x14ac:dyDescent="0.3">
@@ -17969,7 +17969,7 @@
         <v>4.3950406007012596E-6</v>
       </c>
       <c r="D1216" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1217" spans="1:4" x14ac:dyDescent="0.3">
@@ -17983,7 +17983,7 @@
         <v>2.9227237797800661E-6</v>
       </c>
       <c r="D1217" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1218" spans="1:4" x14ac:dyDescent="0.3">
@@ -17997,7 +17997,7 @@
         <v>1.722086009723311E-6</v>
       </c>
       <c r="D1218" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1219" spans="1:4" x14ac:dyDescent="0.3">
@@ -18011,7 +18011,7 @@
         <v>1.314567433426652E-6</v>
       </c>
       <c r="D1219" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1220" spans="1:4" x14ac:dyDescent="0.3">
@@ -18025,7 +18025,7 @@
         <v>1.183112309438167E-6</v>
       </c>
       <c r="D1220" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1221" spans="1:4" x14ac:dyDescent="0.3">
@@ -18039,7 +18039,7 @@
         <v>8.6761353444908187E-7</v>
       </c>
       <c r="D1221" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1222" spans="1:4" x14ac:dyDescent="0.3">
@@ -18053,7 +18053,7 @@
         <v>2.6291429636242061E-7</v>
       </c>
       <c r="D1222" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1223" spans="1:4" x14ac:dyDescent="0.3">
@@ -18067,7 +18067,7 @@
         <v>1.5336498605080731E-7</v>
       </c>
       <c r="D1223" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1224" spans="1:4" x14ac:dyDescent="0.3">
@@ -18081,7 +18081,7 @@
         <v>1.2269441787191661E-7</v>
       </c>
       <c r="D1224" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1225" spans="1:4" x14ac:dyDescent="0.3">
@@ -18095,7 +18095,7 @@
         <v>3.0674616564341973E-8</v>
       </c>
       <c r="D1225" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1226" spans="1:4" x14ac:dyDescent="0.3">
@@ -18109,7 +18109,7 @@
         <v>2.1909862062322651E-8</v>
       </c>
       <c r="D1226" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1227" spans="1:4" x14ac:dyDescent="0.3">
@@ -18123,7 +18123,7 @@
         <v>2.1909862062322651E-8</v>
       </c>
       <c r="D1227" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1228" spans="1:4" x14ac:dyDescent="0.3">
@@ -18137,7 +18137,7 @@
         <v>0.33140024145292613</v>
       </c>
       <c r="D1228" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1229" spans="1:4" x14ac:dyDescent="0.3">
@@ -18151,7 +18151,7 @@
         <v>0.21551903054771179</v>
       </c>
       <c r="D1229" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1230" spans="1:4" x14ac:dyDescent="0.3">
@@ -18165,7 +18165,7 @@
         <v>6.9014658021507316E-2</v>
       </c>
       <c r="D1230" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1231" spans="1:4" x14ac:dyDescent="0.3">
@@ -18179,7 +18179,7 @@
         <v>5.8805183412076453E-2</v>
       </c>
       <c r="D1231" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1232" spans="1:4" x14ac:dyDescent="0.3">
@@ -18193,7 +18193,7 @@
         <v>4.4691113034902627E-2</v>
       </c>
       <c r="D1232" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1233" spans="1:4" x14ac:dyDescent="0.3">
@@ -18207,7 +18207,7 @@
         <v>2.6728700412388989E-2</v>
       </c>
       <c r="D1233" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1234" spans="1:4" x14ac:dyDescent="0.3">
@@ -18221,7 +18221,7 @@
         <v>2.3453366393074011E-2</v>
       </c>
       <c r="D1234" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1235" spans="1:4" x14ac:dyDescent="0.3">
@@ -18235,7 +18235,7 @@
         <v>2.2551453638427161E-2</v>
       </c>
       <c r="D1235" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1236" spans="1:4" x14ac:dyDescent="0.3">
@@ -18249,7 +18249,7 @@
         <v>2.1772992061619291E-2</v>
       </c>
       <c r="D1236" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1237" spans="1:4" x14ac:dyDescent="0.3">
@@ -18263,7 +18263,7 @@
         <v>1.9974403874845299E-2</v>
       </c>
       <c r="D1237" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1238" spans="1:4" x14ac:dyDescent="0.3">
@@ -18277,7 +18277,7 @@
         <v>1.822218349609319E-2</v>
       </c>
       <c r="D1238" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1239" spans="1:4" x14ac:dyDescent="0.3">
@@ -18291,7 +18291,7 @@
         <v>1.6082533954396249E-2</v>
       </c>
       <c r="D1239" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1240" spans="1:4" x14ac:dyDescent="0.3">
@@ -18305,7 +18305,7 @@
         <v>1.402763049923593E-2</v>
       </c>
       <c r="D1240" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1241" spans="1:4" x14ac:dyDescent="0.3">
@@ -18319,7 +18319,7 @@
         <v>1.345396200801535E-2</v>
       </c>
       <c r="D1241" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1242" spans="1:4" x14ac:dyDescent="0.3">
@@ -18333,7 +18333,7 @@
         <v>1.1045611435003299E-2</v>
       </c>
       <c r="D1242" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1243" spans="1:4" x14ac:dyDescent="0.3">
@@ -18347,7 +18347,7 @@
         <v>9.6792690953370914E-3</v>
       </c>
       <c r="D1243" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1244" spans="1:4" x14ac:dyDescent="0.3">
@@ -18361,7 +18361,7 @@
         <v>9.5526410184978549E-3</v>
       </c>
       <c r="D1244" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1245" spans="1:4" x14ac:dyDescent="0.3">
@@ -18375,7 +18375,7 @@
         <v>9.1465220626561865E-3</v>
       </c>
       <c r="D1245" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1246" spans="1:4" x14ac:dyDescent="0.3">
@@ -18389,7 +18389,7 @@
         <v>8.761682529491199E-3</v>
       </c>
       <c r="D1246" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1247" spans="1:4" x14ac:dyDescent="0.3">
@@ -18403,7 +18403,7 @@
         <v>8.3456330648204562E-3</v>
       </c>
       <c r="D1247" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1248" spans="1:4" x14ac:dyDescent="0.3">
@@ -18417,7 +18417,7 @@
         <v>5.5418173480688039E-3</v>
       </c>
       <c r="D1248" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1249" spans="1:4" x14ac:dyDescent="0.3">
@@ -18431,7 +18431,7 @@
         <v>4.8703866066850459E-3</v>
       </c>
       <c r="D1249" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1250" spans="1:4" x14ac:dyDescent="0.3">
@@ -18445,7 +18445,7 @@
         <v>4.7536741071922597E-3</v>
       </c>
       <c r="D1250" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1251" spans="1:4" x14ac:dyDescent="0.3">
@@ -18459,7 +18459,7 @@
         <v>4.5708771125322328E-3</v>
       </c>
       <c r="D1251" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1252" spans="1:4" x14ac:dyDescent="0.3">
@@ -18473,7 +18473,7 @@
         <v>4.0197106951545512E-3</v>
       </c>
       <c r="D1252" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1253" spans="1:4" x14ac:dyDescent="0.3">
@@ -18487,7 +18487,7 @@
         <v>3.2489831680710271E-3</v>
       </c>
       <c r="D1253" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1254" spans="1:4" x14ac:dyDescent="0.3">
@@ -18501,7 +18501,7 @@
         <v>2.2870875578175709E-3</v>
       </c>
       <c r="D1254" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1255" spans="1:4" x14ac:dyDescent="0.3">
@@ -18515,7 +18515,7 @@
         <v>2.245970343892888E-3</v>
       </c>
       <c r="D1255" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1256" spans="1:4" x14ac:dyDescent="0.3">
@@ -18529,7 +18529,7 @@
         <v>2.088487352928325E-3</v>
       </c>
       <c r="D1256" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1257" spans="1:4" x14ac:dyDescent="0.3">
@@ -18543,7 +18543,7 @@
         <v>1.8885964790802221E-3</v>
       </c>
       <c r="D1257" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1258" spans="1:4" x14ac:dyDescent="0.3">
@@ -18557,7 +18557,7 @@
         <v>1.655732206160042E-3</v>
       </c>
       <c r="D1258" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1259" spans="1:4" x14ac:dyDescent="0.3">
@@ -18571,7 +18571,7 @@
         <v>1.6281305037551381E-3</v>
       </c>
       <c r="D1259" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1260" spans="1:4" x14ac:dyDescent="0.3">
@@ -18585,7 +18585,7 @@
         <v>1.4918788242745281E-3</v>
       </c>
       <c r="D1260" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1261" spans="1:4" x14ac:dyDescent="0.3">
@@ -18599,7 +18599,7 @@
         <v>1.425651660032297E-3</v>
       </c>
       <c r="D1261" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1262" spans="1:4" x14ac:dyDescent="0.3">
@@ -18613,7 +18613,7 @@
         <v>1.3834494888990999E-3</v>
       </c>
       <c r="D1262" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1263" spans="1:4" x14ac:dyDescent="0.3">
@@ -18627,7 +18627,7 @@
         <v>1.103568755966394E-3</v>
       </c>
       <c r="D1263" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1264" spans="1:4" x14ac:dyDescent="0.3">
@@ -18641,7 +18641,7 @@
         <v>8.7309835590837503E-4</v>
       </c>
       <c r="D1264" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1265" spans="1:4" x14ac:dyDescent="0.3">
@@ -18655,7 +18655,7 @@
         <v>6.6084494554164526E-4</v>
       </c>
       <c r="D1265" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1266" spans="1:4" x14ac:dyDescent="0.3">
@@ -18669,7 +18669,7 @@
         <v>5.0008053979653296E-4</v>
       </c>
       <c r="D1266" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1267" spans="1:4" x14ac:dyDescent="0.3">
@@ -18683,7 +18683,7 @@
         <v>4.8012164597857192E-4</v>
       </c>
       <c r="D1267" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1268" spans="1:4" x14ac:dyDescent="0.3">
@@ -18697,7 +18697,7 @@
         <v>2.8378259664375892E-4</v>
       </c>
       <c r="D1268" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1269" spans="1:4" x14ac:dyDescent="0.3">
@@ -18711,7 +18711,7 @@
         <v>1.820836446869977E-4</v>
       </c>
       <c r="D1269" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1270" spans="1:4" x14ac:dyDescent="0.3">
@@ -18725,7 +18725,7 @@
         <v>1.721531358579226E-4</v>
       </c>
       <c r="D1270" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1271" spans="1:4" x14ac:dyDescent="0.3">
@@ -18739,7 +18739,7 @@
         <v>1.6873568702478861E-4</v>
       </c>
       <c r="D1271" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1272" spans="1:4" x14ac:dyDescent="0.3">
@@ -18753,7 +18753,7 @@
         <v>7.5888921710994423E-5</v>
       </c>
       <c r="D1272" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1273" spans="1:4" x14ac:dyDescent="0.3">
@@ -18767,7 +18767,7 @@
         <v>4.9207939401891723E-5</v>
       </c>
       <c r="D1273" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1274" spans="1:4" x14ac:dyDescent="0.3">
@@ -18781,7 +18781,7 @@
         <v>2.368490874391871E-5</v>
       </c>
       <c r="D1274" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1275" spans="1:4" x14ac:dyDescent="0.3">
@@ -18795,7 +18795,7 @@
         <v>2.3648410756265001E-5</v>
       </c>
       <c r="D1275" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1276" spans="1:4" x14ac:dyDescent="0.3">
@@ -18809,7 +18809,7 @@
         <v>1.679194811765873E-5</v>
       </c>
       <c r="D1276" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1277" spans="1:4" x14ac:dyDescent="0.3">
@@ -18823,7 +18823,7 @@
         <v>9.397982758427002E-6</v>
       </c>
       <c r="D1277" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1278" spans="1:4" x14ac:dyDescent="0.3">
@@ -18837,7 +18837,7 @@
         <v>8.047593999840835E-6</v>
       </c>
       <c r="D1278" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1279" spans="1:4" x14ac:dyDescent="0.3">
@@ -18851,7 +18851,7 @@
         <v>7.7390279070172816E-6</v>
       </c>
       <c r="D1279" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1280" spans="1:4" x14ac:dyDescent="0.3">
@@ -18865,7 +18865,7 @@
         <v>6.6474356760973524E-6</v>
       </c>
       <c r="D1280" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1281" spans="1:4" x14ac:dyDescent="0.3">
@@ -18879,7 +18879,7 @@
         <v>6.038598417976461E-6</v>
       </c>
       <c r="D1281" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1282" spans="1:4" x14ac:dyDescent="0.3">
@@ -18893,7 +18893,7 @@
         <v>5.1908712320988932E-6</v>
       </c>
       <c r="D1282" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1283" spans="1:4" x14ac:dyDescent="0.3">
@@ -18907,7 +18907,7 @@
         <v>4.3348506513868141E-6</v>
       </c>
       <c r="D1283" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1284" spans="1:4" x14ac:dyDescent="0.3">
@@ -18921,7 +18921,7 @@
         <v>3.3295244405862012E-6</v>
       </c>
       <c r="D1284" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1285" spans="1:4" x14ac:dyDescent="0.3">
@@ -18935,7 +18935,7 @@
         <v>2.4635490272276319E-6</v>
       </c>
       <c r="D1285" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1286" spans="1:4" x14ac:dyDescent="0.3">
@@ -18949,7 +18949,7 @@
         <v>1.235921211031072E-6</v>
       </c>
       <c r="D1286" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1287" spans="1:4" x14ac:dyDescent="0.3">
@@ -18963,7 +18963,7 @@
         <v>1.1397018909569761E-6</v>
       </c>
       <c r="D1287" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1288" spans="1:4" x14ac:dyDescent="0.3">
@@ -18977,7 +18977,7 @@
         <v>1.1065237135438071E-6</v>
       </c>
       <c r="D1288" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1289" spans="1:4" x14ac:dyDescent="0.3">
@@ -18991,7 +18991,7 @@
         <v>1.8580361774224049E-7</v>
       </c>
       <c r="D1289" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1290" spans="1:4" x14ac:dyDescent="0.3">
@@ -19005,7 +19005,7 @@
         <v>7.7971092593096103E-8</v>
       </c>
       <c r="D1290" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1291" spans="1:4" x14ac:dyDescent="0.3">
@@ -19019,7 +19019,7 @@
         <v>5.9722865112096683E-8</v>
       </c>
       <c r="D1291" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1292" spans="1:4" x14ac:dyDescent="0.3">
@@ -19033,7 +19033,7 @@
         <v>4.6451287608487253E-8</v>
       </c>
       <c r="D1292" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1293" spans="1:4" x14ac:dyDescent="0.3">
@@ -19047,7 +19047,7 @@
         <v>1.1613205075048929E-8</v>
       </c>
       <c r="D1293" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1294" spans="1:4" x14ac:dyDescent="0.3">
@@ -19061,7 +19061,7 @@
         <v>4.9766499773899789E-9</v>
       </c>
       <c r="D1294" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1295" spans="1:4" x14ac:dyDescent="0.3">
@@ -19075,7 +19075,7 @@
         <v>4.9766499773899789E-9</v>
       </c>
       <c r="D1295" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1296" spans="1:4" x14ac:dyDescent="0.3">
@@ -19089,7 +19089,7 @@
         <v>0.23737492362583121</v>
       </c>
       <c r="D1296" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1297" spans="1:4" x14ac:dyDescent="0.3">
@@ -19103,7 +19103,7 @@
         <v>0.21219499481822171</v>
       </c>
       <c r="D1297" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1298" spans="1:4" x14ac:dyDescent="0.3">
@@ -19117,7 +19117,7 @@
         <v>0.162788361975549</v>
       </c>
       <c r="D1298" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1299" spans="1:4" x14ac:dyDescent="0.3">
@@ -19131,7 +19131,7 @@
         <v>7.9087044945683083E-2</v>
       </c>
       <c r="D1299" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1300" spans="1:4" x14ac:dyDescent="0.3">
@@ -19145,7 +19145,7 @@
         <v>7.2520507730200634E-2</v>
       </c>
       <c r="D1300" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1301" spans="1:4" x14ac:dyDescent="0.3">
@@ -19159,7 +19159,7 @@
         <v>7.0790668383710759E-2</v>
       </c>
       <c r="D1301" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1302" spans="1:4" x14ac:dyDescent="0.3">
@@ -19173,7 +19173,7 @@
         <v>5.5722584688568493E-2</v>
       </c>
       <c r="D1302" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1303" spans="1:4" x14ac:dyDescent="0.3">
@@ -19187,7 +19187,7 @@
         <v>2.446083380614349E-2</v>
       </c>
       <c r="D1303" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1304" spans="1:4" x14ac:dyDescent="0.3">
@@ -19201,7 +19201,7 @@
         <v>2.30084890116336E-2</v>
       </c>
       <c r="D1304" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1305" spans="1:4" x14ac:dyDescent="0.3">
@@ -19215,7 +19215,7 @@
         <v>1.7819821194029379E-2</v>
       </c>
       <c r="D1305" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1306" spans="1:4" x14ac:dyDescent="0.3">
@@ -19229,7 +19229,7 @@
         <v>1.135321801871908E-2</v>
       </c>
       <c r="D1306" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1307" spans="1:4" x14ac:dyDescent="0.3">
@@ -19243,7 +19243,7 @@
         <v>9.5838652360301299E-3</v>
       </c>
       <c r="D1307" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1308" spans="1:4" x14ac:dyDescent="0.3">
@@ -19257,7 +19257,7 @@
         <v>8.3861571536461132E-3</v>
       </c>
       <c r="D1308" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1309" spans="1:4" x14ac:dyDescent="0.3">
@@ -19271,7 +19271,7 @@
         <v>6.1190347502964072E-3</v>
       </c>
       <c r="D1309" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1310" spans="1:4" x14ac:dyDescent="0.3">
@@ -19285,7 +19285,7 @@
         <v>2.6314965617182341E-3</v>
       </c>
       <c r="D1310" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1311" spans="1:4" x14ac:dyDescent="0.3">
@@ -19299,7 +19299,7 @@
         <v>1.644910412181428E-3</v>
       </c>
       <c r="D1311" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1312" spans="1:4" x14ac:dyDescent="0.3">
@@ -19313,7 +19313,7 @@
         <v>1.238221877458111E-3</v>
       </c>
       <c r="D1312" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1313" spans="1:4" x14ac:dyDescent="0.3">
@@ -19327,7 +19327,7 @@
         <v>1.0178467636477819E-3</v>
       </c>
       <c r="D1313" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1314" spans="1:4" x14ac:dyDescent="0.3">
@@ -19341,7 +19341,7 @@
         <v>7.9372044268685542E-4</v>
       </c>
       <c r="D1314" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1315" spans="1:4" x14ac:dyDescent="0.3">
@@ -19355,7 +19355,7 @@
         <v>6.3946785829053566E-4</v>
       </c>
       <c r="D1315" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1316" spans="1:4" x14ac:dyDescent="0.3">
@@ -19369,7 +19369,7 @@
         <v>3.5487088768666047E-4</v>
       </c>
       <c r="D1316" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1317" spans="1:4" x14ac:dyDescent="0.3">
@@ -19383,7 +19383,7 @@
         <v>2.0501987309831131E-4</v>
       </c>
       <c r="D1317" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1318" spans="1:4" x14ac:dyDescent="0.3">
@@ -19397,7 +19397,7 @@
         <v>5.5018767710534393E-5</v>
       </c>
       <c r="D1318" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1319" spans="1:4" x14ac:dyDescent="0.3">
@@ -19411,7 +19411,7 @@
         <v>3.6112317686565323E-5</v>
       </c>
       <c r="D1319" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1320" spans="1:4" x14ac:dyDescent="0.3">
@@ -19425,7 +19425,7 @@
         <v>3.4511780454737108E-5</v>
       </c>
       <c r="D1320" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1321" spans="1:4" x14ac:dyDescent="0.3">
@@ -19439,7 +19439,7 @@
         <v>3.1160615191652977E-5</v>
       </c>
       <c r="D1321" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1322" spans="1:4" x14ac:dyDescent="0.3">
@@ -19453,7 +19453,7 @@
         <v>2.270774905467183E-5</v>
       </c>
       <c r="D1322" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1323" spans="1:4" x14ac:dyDescent="0.3">
@@ -19467,7 +19467,7 @@
         <v>1.895644948363065E-5</v>
       </c>
       <c r="D1323" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1324" spans="1:4" x14ac:dyDescent="0.3">
@@ -19481,7 +19481,7 @@
         <v>1.870635976487981E-5</v>
       </c>
       <c r="D1324" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1325" spans="1:4" x14ac:dyDescent="0.3">
@@ -19495,7 +19495,7 @@
         <v>1.50051058637217E-5</v>
       </c>
       <c r="D1325" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1326" spans="1:4" x14ac:dyDescent="0.3">
@@ -19509,7 +19509,7 @@
         <v>1.2804344064847159E-5</v>
       </c>
       <c r="D1326" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1327" spans="1:4" x14ac:dyDescent="0.3">
@@ -19523,7 +19523,7 @@
         <v>8.8030009852766443E-6</v>
       </c>
       <c r="D1327" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1328" spans="1:4" x14ac:dyDescent="0.3">
@@ -19537,7 +19537,7 @@
         <v>4.8016579057061233E-6</v>
       </c>
       <c r="D1328" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1329" spans="1:4" x14ac:dyDescent="0.3">
@@ -19551,7 +19551,7 @@
         <v>2.3008069284191731E-6</v>
       </c>
       <c r="D1329" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1330" spans="1:4" x14ac:dyDescent="0.3">
@@ -19565,7 +19565,7 @@
         <v>1.9006264102406229E-6</v>
       </c>
       <c r="D1330" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1331" spans="1:4" x14ac:dyDescent="0.3">
@@ -19579,7 +19579,7 @@
         <v>1.150403464209587E-6</v>
       </c>
       <c r="D1331" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1332" spans="1:4" x14ac:dyDescent="0.3">
@@ -19593,7 +19593,7 @@
         <v>0.22183996193259301</v>
       </c>
       <c r="D1332" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1333" spans="1:4" x14ac:dyDescent="0.3">
@@ -19607,7 +19607,7 @@
         <v>0.17627334933169361</v>
       </c>
       <c r="D1333" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1334" spans="1:4" x14ac:dyDescent="0.3">
@@ -19621,7 +19621,7 @@
         <v>0.16298296550556901</v>
       </c>
       <c r="D1334" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1335" spans="1:4" x14ac:dyDescent="0.3">
@@ -19635,7 +19635,7 @@
         <v>0.12973584657735079</v>
       </c>
       <c r="D1335" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1336" spans="1:4" x14ac:dyDescent="0.3">
@@ -19649,7 +19649,7 @@
         <v>9.8035822407204667E-2</v>
       </c>
       <c r="D1336" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1337" spans="1:4" x14ac:dyDescent="0.3">
@@ -19663,7 +19663,7 @@
         <v>7.795736058557251E-2</v>
       </c>
       <c r="D1337" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1338" spans="1:4" x14ac:dyDescent="0.3">
@@ -19677,7 +19677,7 @@
         <v>3.7389792633098481E-2</v>
       </c>
       <c r="D1338" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1339" spans="1:4" x14ac:dyDescent="0.3">
@@ -19691,7 +19691,7 @@
         <v>2.4096379151411339E-2</v>
       </c>
       <c r="D1339" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1340" spans="1:4" x14ac:dyDescent="0.3">
@@ -19705,7 +19705,7 @@
         <v>1.747855066178898E-2</v>
       </c>
       <c r="D1340" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1341" spans="1:4" x14ac:dyDescent="0.3">
@@ -19719,7 +19719,7 @@
         <v>1.6146349468064852E-2</v>
       </c>
       <c r="D1341" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1342" spans="1:4" x14ac:dyDescent="0.3">
@@ -19733,7 +19733,7 @@
         <v>1.000557659770103E-2</v>
       </c>
       <c r="D1342" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1343" spans="1:4" x14ac:dyDescent="0.3">
@@ -19747,7 +19747,7 @@
         <v>9.0871748188303507E-3</v>
       </c>
       <c r="D1343" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1344" spans="1:4" x14ac:dyDescent="0.3">
@@ -19761,7 +19761,7 @@
         <v>6.3487869868839022E-3</v>
       </c>
       <c r="D1344" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1345" spans="1:4" x14ac:dyDescent="0.3">
@@ -19775,7 +19775,7 @@
         <v>3.3815151208409942E-3</v>
       </c>
       <c r="D1345" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1346" spans="1:4" x14ac:dyDescent="0.3">
@@ -19789,7 +19789,7 @@
         <v>3.037484715582931E-3</v>
       </c>
       <c r="D1346" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1347" spans="1:4" x14ac:dyDescent="0.3">
@@ -19803,7 +19803,7 @@
         <v>2.47120851367141E-3</v>
       </c>
       <c r="D1347" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1348" spans="1:4" x14ac:dyDescent="0.3">
@@ -19817,7 +19817,7 @@
         <v>1.247206691180198E-3</v>
       </c>
       <c r="D1348" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1349" spans="1:4" x14ac:dyDescent="0.3">
@@ -19831,7 +19831,7 @@
         <v>1.105999462965273E-3</v>
       </c>
       <c r="D1349" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1350" spans="1:4" x14ac:dyDescent="0.3">
@@ -19845,7 +19845,7 @@
         <v>2.4358849870750979E-4</v>
       </c>
       <c r="D1350" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1351" spans="1:4" x14ac:dyDescent="0.3">
@@ -19859,7 +19859,7 @@
         <v>2.2971381600539359E-4</v>
       </c>
       <c r="D1351" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1352" spans="1:4" x14ac:dyDescent="0.3">
@@ -19873,7 +19873,7 @@
         <v>1.9452537578226761E-4</v>
       </c>
       <c r="D1352" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1353" spans="1:4" x14ac:dyDescent="0.3">
@@ -19887,7 +19887,7 @@
         <v>1.4609906824092711E-4</v>
       </c>
       <c r="D1353" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1354" spans="1:4" x14ac:dyDescent="0.3">
@@ -19901,7 +19901,7 @@
         <v>1.1353505120355279E-4</v>
       </c>
       <c r="D1354" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1355" spans="1:4" x14ac:dyDescent="0.3">
@@ -19915,7 +19915,7 @@
         <v>9.6235116854031716E-5</v>
       </c>
       <c r="D1355" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1356" spans="1:4" x14ac:dyDescent="0.3">
@@ -19929,7 +19929,7 @@
         <v>9.351420594864407E-5</v>
       </c>
       <c r="D1356" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1357" spans="1:4" x14ac:dyDescent="0.3">
@@ -19943,7 +19943,7 @@
         <v>7.6445836777705995E-5</v>
       </c>
       <c r="D1357" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1358" spans="1:4" x14ac:dyDescent="0.3">
@@ -19957,7 +19957,7 @@
         <v>4.5666815810880438E-5</v>
       </c>
       <c r="D1358" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1359" spans="1:4" x14ac:dyDescent="0.3">
@@ -19971,7 +19971,7 @@
         <v>3.5526138327613027E-5</v>
       </c>
       <c r="D1359" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1360" spans="1:4" x14ac:dyDescent="0.3">
@@ -19985,7 +19985,7 @@
         <v>2.7257290514023469E-5</v>
       </c>
       <c r="D1360" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1361" spans="1:4" x14ac:dyDescent="0.3">
@@ -19999,7 +19999,7 @@
         <v>2.4169736971105708E-5</v>
       </c>
       <c r="D1361" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1362" spans="1:4" x14ac:dyDescent="0.3">
@@ -20013,7 +20013,7 @@
         <v>1.3845738169073241E-5</v>
       </c>
       <c r="D1362" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1363" spans="1:4" x14ac:dyDescent="0.3">
@@ -20027,7 +20027,7 @@
         <v>1.1587966535090351E-5</v>
       </c>
       <c r="D1363" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1364" spans="1:4" x14ac:dyDescent="0.3">
@@ -20041,7 +20041,7 @@
         <v>8.4328787198183987E-6</v>
       </c>
       <c r="D1364" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1365" spans="1:4" x14ac:dyDescent="0.3">
@@ -20055,7 +20055,7 @@
         <v>4.9979729519067539E-6</v>
       </c>
       <c r="D1365" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1366" spans="1:4" x14ac:dyDescent="0.3">
@@ -20069,7 +20069,7 @@
         <v>4.1874903697468097E-6</v>
       </c>
       <c r="D1366" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1367" spans="1:4" x14ac:dyDescent="0.3">
@@ -20083,7 +20083,7 @@
         <v>3.840138144752921E-6</v>
       </c>
       <c r="D1367" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1368" spans="1:4" x14ac:dyDescent="0.3">
@@ -20097,7 +20097,7 @@
         <v>2.9621212902387789E-6</v>
       </c>
       <c r="D1368" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1369" spans="1:4" x14ac:dyDescent="0.3">
@@ -20111,7 +20111,7 @@
         <v>9.9380390092500347E-7</v>
       </c>
       <c r="D1369" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1370" spans="1:4" x14ac:dyDescent="0.3">
@@ -20125,7 +20125,7 @@
         <v>8.8767097502095268E-7</v>
       </c>
       <c r="D1370" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1371" spans="1:4" x14ac:dyDescent="0.3">
@@ -20139,7 +20139,7 @@
         <v>2.8945424466911048E-7</v>
       </c>
       <c r="D1371" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1372" spans="1:4" x14ac:dyDescent="0.3">
@@ -20153,7 +20153,7 @@
         <v>1.9297543927187039E-7</v>
       </c>
       <c r="D1372" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1373" spans="1:4" x14ac:dyDescent="0.3">
@@ -20167,7 +20167,7 @@
         <v>1.7367611249694439E-7</v>
       </c>
       <c r="D1373" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1374" spans="1:4" x14ac:dyDescent="0.3">
@@ -20181,7 +20181,7 @@
         <v>0.32958971051824593</v>
       </c>
       <c r="D1374" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1375" spans="1:4" x14ac:dyDescent="0.3">
@@ -20195,7 +20195,7 @@
         <v>0.1439902741824694</v>
       </c>
       <c r="D1375" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1376" spans="1:4" x14ac:dyDescent="0.3">
@@ -20209,7 +20209,7 @@
         <v>0.11942472392886939</v>
       </c>
       <c r="D1376" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1377" spans="1:4" x14ac:dyDescent="0.3">
@@ -20223,7 +20223,7 @@
         <v>8.357280160471281E-2</v>
       </c>
       <c r="D1377" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1378" spans="1:4" x14ac:dyDescent="0.3">
@@ -20237,7 +20237,7 @@
         <v>5.156225747693205E-2</v>
       </c>
       <c r="D1378" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1379" spans="1:4" x14ac:dyDescent="0.3">
@@ -20251,7 +20251,7 @@
         <v>4.2137472311439543E-2</v>
       </c>
       <c r="D1379" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1380" spans="1:4" x14ac:dyDescent="0.3">
@@ -20265,7 +20265,7 @@
         <v>3.3455547839205783E-2</v>
       </c>
       <c r="D1380" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1381" spans="1:4" x14ac:dyDescent="0.3">
@@ -20279,7 +20279,7 @@
         <v>3.0954621492070188E-2</v>
       </c>
       <c r="D1381" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1382" spans="1:4" x14ac:dyDescent="0.3">
@@ -20293,7 +20293,7 @@
         <v>2.3914659898659572E-2</v>
       </c>
       <c r="D1382" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1383" spans="1:4" x14ac:dyDescent="0.3">
@@ -20307,7 +20307,7 @@
         <v>2.352734505768202E-2</v>
       </c>
       <c r="D1383" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1384" spans="1:4" x14ac:dyDescent="0.3">
@@ -20321,7 +20321,7 @@
         <v>2.065117988047405E-2</v>
       </c>
       <c r="D1384" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1385" spans="1:4" x14ac:dyDescent="0.3">
@@ -20335,7 +20335,7 @@
         <v>2.024037642803465E-2</v>
       </c>
       <c r="D1385" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1386" spans="1:4" x14ac:dyDescent="0.3">
@@ -20349,7 +20349,7 @@
         <v>1.390373534449965E-2</v>
       </c>
       <c r="D1386" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1387" spans="1:4" x14ac:dyDescent="0.3">
@@ -20363,7 +20363,7 @@
         <v>1.220479881195252E-2</v>
       </c>
       <c r="D1387" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1388" spans="1:4" x14ac:dyDescent="0.3">
@@ -20377,7 +20377,7 @@
         <v>1.064060906314282E-2</v>
       </c>
       <c r="D1388" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1389" spans="1:4" x14ac:dyDescent="0.3">
@@ -20391,7 +20391,7 @@
         <v>8.706148709696767E-3</v>
       </c>
       <c r="D1389" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1390" spans="1:4" x14ac:dyDescent="0.3">
@@ -20405,7 +20405,7 @@
         <v>6.6011994710765401E-3</v>
       </c>
       <c r="D1390" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1391" spans="1:4" x14ac:dyDescent="0.3">
@@ -20419,7 +20419,7 @@
         <v>5.5536637029825033E-3</v>
       </c>
       <c r="D1391" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1392" spans="1:4" x14ac:dyDescent="0.3">
@@ -20433,7 +20433,7 @@
         <v>3.883696866252501E-3</v>
       </c>
       <c r="D1392" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1393" spans="1:4" x14ac:dyDescent="0.3">
@@ -20447,7 +20447,7 @@
         <v>3.6386417371846178E-3</v>
       </c>
       <c r="D1393" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1394" spans="1:4" x14ac:dyDescent="0.3">
@@ -20461,7 +20461,7 @@
         <v>2.5916702338842322E-3</v>
       </c>
       <c r="D1394" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1395" spans="1:4" x14ac:dyDescent="0.3">
@@ -20475,7 +20475,7 @@
         <v>2.1027754095119672E-3</v>
       </c>
       <c r="D1395" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1396" spans="1:4" x14ac:dyDescent="0.3">
@@ -20489,7 +20489,7 @@
         <v>1.753677604199587E-3</v>
       </c>
       <c r="D1396" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1397" spans="1:4" x14ac:dyDescent="0.3">
@@ -20503,7 +20503,7 @@
         <v>9.3169125842405159E-4</v>
       </c>
       <c r="D1397" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1398" spans="1:4" x14ac:dyDescent="0.3">
@@ -20517,7 +20517,7 @@
         <v>8.7934800766504943E-4</v>
       </c>
       <c r="D1398" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1399" spans="1:4" x14ac:dyDescent="0.3">
@@ -20531,7 +20531,7 @@
         <v>8.4345045711676473E-4</v>
       </c>
       <c r="D1399" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1400" spans="1:4" x14ac:dyDescent="0.3">
@@ -20545,7 +20545,7 @@
         <v>6.7541080097213257E-4</v>
       </c>
       <c r="D1400" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1401" spans="1:4" x14ac:dyDescent="0.3">
@@ -20559,7 +20559,7 @@
         <v>6.0240883225000581E-4</v>
       </c>
       <c r="D1401" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1402" spans="1:4" x14ac:dyDescent="0.3">
@@ -20573,7 +20573,7 @@
         <v>3.2557736965858989E-4</v>
       </c>
       <c r="D1402" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1403" spans="1:4" x14ac:dyDescent="0.3">
@@ -20587,7 +20587,7 @@
         <v>2.349632268226027E-4</v>
       </c>
       <c r="D1403" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1404" spans="1:4" x14ac:dyDescent="0.3">
@@ -20601,7 +20601,7 @@
         <v>2.161882495229273E-4</v>
       </c>
       <c r="D1404" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1405" spans="1:4" x14ac:dyDescent="0.3">
@@ -20615,7 +20615,7 @@
         <v>1.5829169875597731E-4</v>
       </c>
       <c r="D1405" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1406" spans="1:4" x14ac:dyDescent="0.3">
@@ -20629,7 +20629,7 @@
         <v>1.4492191717989429E-4</v>
       </c>
       <c r="D1406" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1407" spans="1:4" x14ac:dyDescent="0.3">
@@ -20643,7 +20643,7 @@
         <v>6.7052091018183395E-5</v>
       </c>
       <c r="D1407" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1408" spans="1:4" x14ac:dyDescent="0.3">
@@ -20657,7 +20657,7 @@
         <v>6.3552667047068017E-5</v>
       </c>
       <c r="D1408" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1409" spans="1:4" x14ac:dyDescent="0.3">
@@ -20671,7 +20671,7 @@
         <v>6.3386203521856045E-5</v>
       </c>
       <c r="D1409" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1410" spans="1:4" x14ac:dyDescent="0.3">
@@ -20685,7 +20685,7 @@
         <v>5.4059302063110112E-5</v>
       </c>
       <c r="D1410" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1411" spans="1:4" x14ac:dyDescent="0.3">
@@ -20699,7 +20699,7 @@
         <v>3.4398147333031231E-5</v>
       </c>
       <c r="D1411" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1412" spans="1:4" x14ac:dyDescent="0.3">
@@ -20713,7 +20713,7 @@
         <v>2.316547525265156E-5</v>
       </c>
       <c r="D1412" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1413" spans="1:4" x14ac:dyDescent="0.3">
@@ -20727,7 +20727,7 @@
         <v>2.1694223250326011E-5</v>
       </c>
       <c r="D1413" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1414" spans="1:4" x14ac:dyDescent="0.3">
@@ -20741,7 +20741,7 @@
         <v>1.313232483980002E-5</v>
       </c>
       <c r="D1414" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1415" spans="1:4" x14ac:dyDescent="0.3">
@@ -20755,7 +20755,7 @@
         <v>1.040647118568991E-5</v>
       </c>
       <c r="D1415" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1416" spans="1:4" x14ac:dyDescent="0.3">
@@ -20769,7 +20769,7 @@
         <v>9.8067092210825484E-6</v>
       </c>
       <c r="D1416" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1417" spans="1:4" x14ac:dyDescent="0.3">
@@ -20783,7 +20783,7 @@
         <v>7.5545443362523753E-6</v>
       </c>
       <c r="D1417" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1418" spans="1:4" x14ac:dyDescent="0.3">
@@ -20797,7 +20797,7 @@
         <v>5.1909959104666623E-6</v>
       </c>
       <c r="D1418" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1419" spans="1:4" x14ac:dyDescent="0.3">
@@ -20811,7 +20811,7 @@
         <v>2.8103106854237182E-6</v>
       </c>
       <c r="D1419" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1420" spans="1:4" x14ac:dyDescent="0.3">
@@ -20825,7 +20825,7 @@
         <v>1.8213158520067239E-6</v>
       </c>
       <c r="D1420" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1421" spans="1:4" x14ac:dyDescent="0.3">
@@ -20839,7 +20839,7 @@
         <v>1.470027299039582E-6</v>
       </c>
       <c r="D1421" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1422" spans="1:4" x14ac:dyDescent="0.3">
@@ -20853,7 +20853,7 @@
         <v>1.2876505470130571E-6</v>
       </c>
       <c r="D1422" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1423" spans="1:4" x14ac:dyDescent="0.3">
@@ -20867,7 +20867,7 @@
         <v>1.0807944302299481E-6</v>
       </c>
       <c r="D1423" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1424" spans="1:4" x14ac:dyDescent="0.3">
@@ -20881,7 +20881,7 @@
         <v>1.050193810730101E-6</v>
       </c>
       <c r="D1424" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1425" spans="1:4" x14ac:dyDescent="0.3">
@@ -20895,7 +20895,7 @@
         <v>1.0281627217021629E-6</v>
       </c>
       <c r="D1425" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1426" spans="1:4" x14ac:dyDescent="0.3">
@@ -20909,7 +20909,7 @@
         <v>8.3109744614705352E-7</v>
       </c>
       <c r="D1426" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1427" spans="1:4" x14ac:dyDescent="0.3">
@@ -20923,7 +20923,7 @@
         <v>5.8507344107877451E-7</v>
       </c>
       <c r="D1427" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1428" spans="1:4" x14ac:dyDescent="0.3">
@@ -20937,7 +20937,7 @@
         <v>3.439448566244954E-7</v>
       </c>
       <c r="D1428" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1429" spans="1:4" x14ac:dyDescent="0.3">
@@ -20951,7 +20951,7 @@
         <v>1.6891293178390939E-7</v>
       </c>
       <c r="D1429" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1430" spans="1:4" x14ac:dyDescent="0.3">
@@ -20965,7 +20965,7 @@
         <v>1.113846717988319E-7</v>
       </c>
       <c r="D1430" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1431" spans="1:4" x14ac:dyDescent="0.3">
@@ -20979,7 +20979,7 @@
         <v>6.2423680599077334E-8</v>
       </c>
       <c r="D1431" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1432" spans="1:4" x14ac:dyDescent="0.3">
@@ -20993,7 +20993,7 @@
         <v>5.0184563642431357E-8</v>
       </c>
       <c r="D1432" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1433" spans="1:4" x14ac:dyDescent="0.3">
@@ -21007,7 +21007,7 @@
         <v>2.815234377120034E-8</v>
       </c>
       <c r="D1433" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1434" spans="1:4" x14ac:dyDescent="0.3">
@@ -21021,7 +21021,7 @@
         <v>1.7135668413938498E-8</v>
       </c>
       <c r="D1434" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1435" spans="1:4" x14ac:dyDescent="0.3">
@@ -21035,7 +21035,7 @@
         <v>7.3436963426461148E-9</v>
       </c>
       <c r="D1435" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1436" spans="1:4" x14ac:dyDescent="0.3">
@@ -21049,7 +21049,7 @@
         <v>4.8965514572925277E-9</v>
       </c>
       <c r="D1436" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1437" spans="1:4" x14ac:dyDescent="0.3">
@@ -21063,7 +21063,7 @@
         <v>2.4482757286462639E-9</v>
       </c>
       <c r="D1437" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1438" spans="1:4" x14ac:dyDescent="0.3">
@@ -21077,7 +21077,7 @@
         <v>0.87836999408727479</v>
       </c>
       <c r="D1438" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1439" spans="1:4" x14ac:dyDescent="0.3">
@@ -21091,7 +21091,7 @@
         <v>0.1022804011865803</v>
       </c>
       <c r="D1439" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1440" spans="1:4" x14ac:dyDescent="0.3">
@@ -21105,7 +21105,7 @@
         <v>6.2643733845971598E-3</v>
       </c>
       <c r="D1440" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1441" spans="1:4" x14ac:dyDescent="0.3">
@@ -21119,7 +21119,7 @@
         <v>6.1731338276210202E-3</v>
       </c>
       <c r="D1441" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1442" spans="1:4" x14ac:dyDescent="0.3">
@@ -21133,7 +21133,7 @@
         <v>3.6898204405822728E-3</v>
       </c>
       <c r="D1442" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1443" spans="1:4" x14ac:dyDescent="0.3">
@@ -21147,7 +21147,7 @@
         <v>1.9252236320753779E-3</v>
       </c>
       <c r="D1443" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1444" spans="1:4" x14ac:dyDescent="0.3">
@@ -21161,7 +21161,7 @@
         <v>2.1589589821120029E-4</v>
       </c>
       <c r="D1444" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1445" spans="1:4" x14ac:dyDescent="0.3">
@@ -21175,7 +21175,7 @@
         <v>1.486609750578159E-4</v>
       </c>
       <c r="D1445" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1446" spans="1:4" x14ac:dyDescent="0.3">
@@ -21189,7 +21189,7 @@
         <v>1.3727885689086399E-4</v>
       </c>
       <c r="D1446" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1447" spans="1:4" x14ac:dyDescent="0.3">
@@ -21203,7 +21203,7 @@
         <v>9.5179526142334119E-5</v>
       </c>
       <c r="D1447" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1448" spans="1:4" x14ac:dyDescent="0.3">
@@ -21217,7 +21217,7 @@
         <v>9.5070053530960002E-5</v>
       </c>
       <c r="D1448" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1449" spans="1:4" x14ac:dyDescent="0.3">
@@ -21231,7 +21231,7 @@
         <v>7.6282254763960876E-5</v>
       </c>
       <c r="D1449" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1450" spans="1:4" x14ac:dyDescent="0.3">
@@ -21245,7 +21245,7 @@
         <v>7.0408752563068687E-5</v>
       </c>
       <c r="D1450" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1451" spans="1:4" x14ac:dyDescent="0.3">
@@ -21259,7 +21259,7 @@
         <v>6.9679148616512239E-5</v>
       </c>
       <c r="D1451" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1452" spans="1:4" x14ac:dyDescent="0.3">
@@ -21273,7 +21273,7 @@
         <v>6.5228419612644456E-5</v>
       </c>
       <c r="D1452" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1453" spans="1:4" x14ac:dyDescent="0.3">
@@ -21287,7 +21287,7 @@
         <v>6.2930101456979261E-5</v>
       </c>
       <c r="D1453" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1454" spans="1:4" x14ac:dyDescent="0.3">
@@ -21301,7 +21301,7 @@
         <v>4.7790389832005843E-5</v>
       </c>
       <c r="D1454" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1455" spans="1:4" x14ac:dyDescent="0.3">
@@ -21315,7 +21315,7 @@
         <v>4.6841908071944639E-5</v>
       </c>
       <c r="D1455" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1456" spans="1:4" x14ac:dyDescent="0.3">
@@ -21329,7 +21329,7 @@
         <v>4.4434117304905327E-5</v>
       </c>
       <c r="D1456" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1457" spans="1:4" x14ac:dyDescent="0.3">
@@ -21343,7 +21343,7 @@
         <v>4.2208769655282303E-5</v>
       </c>
       <c r="D1457" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1458" spans="1:4" x14ac:dyDescent="0.3">
@@ -21357,7 +21357,7 @@
         <v>1.751100028668076E-5</v>
       </c>
       <c r="D1458" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1459" spans="1:4" x14ac:dyDescent="0.3">
@@ -21371,7 +21371,7 @@
         <v>1.678136263550258E-5</v>
       </c>
       <c r="D1459" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1460" spans="1:4" x14ac:dyDescent="0.3">
@@ -21385,7 +21385,7 @@
         <v>1.2403604137676961E-5</v>
       </c>
       <c r="D1460" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1461" spans="1:4" x14ac:dyDescent="0.3">
@@ -21399,7 +21399,7 @@
         <v>9.1567705173288265E-6</v>
       </c>
       <c r="D1461" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1462" spans="1:4" x14ac:dyDescent="0.3">
@@ -21413,7 +21413,7 @@
         <v>7.2962416932948861E-6</v>
       </c>
       <c r="D1462" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1463" spans="1:4" x14ac:dyDescent="0.3">
@@ -21427,7 +21427,7 @@
         <v>3.7940618587317701E-6</v>
       </c>
       <c r="D1463" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1464" spans="1:4" x14ac:dyDescent="0.3">
@@ -21441,7 +21441,7 @@
         <v>2.9914537015114259E-6</v>
       </c>
       <c r="D1464" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1465" spans="1:4" x14ac:dyDescent="0.3">
@@ -21455,7 +21455,7 @@
         <v>2.954985300801209E-6</v>
       </c>
       <c r="D1465" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1466" spans="1:4" x14ac:dyDescent="0.3">
@@ -21469,7 +21469,7 @@
         <v>1.751089917281558E-6</v>
       </c>
       <c r="D1466" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1467" spans="1:4" x14ac:dyDescent="0.3">
@@ -21483,7 +21483,7 @@
         <v>1.751089917281558E-6</v>
       </c>
       <c r="D1467" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1468" spans="1:4" x14ac:dyDescent="0.3">
@@ -21497,7 +21497,7 @@
         <v>1.6781531158611231E-6</v>
       </c>
       <c r="D1468" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1469" spans="1:4" x14ac:dyDescent="0.3">
@@ -21511,7 +21511,7 @@
         <v>9.1204706397272496E-7</v>
       </c>
       <c r="D1469" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1470" spans="1:4" x14ac:dyDescent="0.3">
@@ -21525,7 +21525,7 @@
         <v>7.2970506042163692E-8</v>
       </c>
       <c r="D1470" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1471" spans="1:4" x14ac:dyDescent="0.3">
@@ -21539,7 +21539,7 @@
         <v>7.2970506042163692E-8</v>
       </c>
       <c r="D1471" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1472" spans="1:4" x14ac:dyDescent="0.3">
@@ -21553,7 +21553,7 @@
         <v>3.6468400710217613E-8</v>
       </c>
       <c r="D1472" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1473" spans="1:4" x14ac:dyDescent="0.3">
@@ -21567,7 +21567,7 @@
         <v>0.42741836600679822</v>
       </c>
       <c r="D1473" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1474" spans="1:4" x14ac:dyDescent="0.3">
@@ -21581,7 +21581,7 @@
         <v>0.23194183742658761</v>
       </c>
       <c r="D1474" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1475" spans="1:4" x14ac:dyDescent="0.3">
@@ -21595,7 +21595,7 @@
         <v>0.1228856896939787</v>
       </c>
       <c r="D1475" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1476" spans="1:4" x14ac:dyDescent="0.3">
@@ -21609,7 +21609,7 @@
         <v>5.1049350592614798E-2</v>
       </c>
       <c r="D1476" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1477" spans="1:4" x14ac:dyDescent="0.3">
@@ -21623,7 +21623,7 @@
         <v>4.390896308500656E-2</v>
       </c>
       <c r="D1477" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1478" spans="1:4" x14ac:dyDescent="0.3">
@@ -21637,7 +21637,7 @@
         <v>3.8958776778428003E-2</v>
       </c>
       <c r="D1478" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1479" spans="1:4" x14ac:dyDescent="0.3">
@@ -21651,7 +21651,7 @@
         <v>3.5144775910885412E-2</v>
       </c>
       <c r="D1479" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1480" spans="1:4" x14ac:dyDescent="0.3">
@@ -21665,7 +21665,7 @@
         <v>9.4868755120319625E-3</v>
       </c>
       <c r="D1480" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1481" spans="1:4" x14ac:dyDescent="0.3">
@@ -21679,7 +21679,7 @@
         <v>8.8240623603318882E-3</v>
       </c>
       <c r="D1481" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1482" spans="1:4" x14ac:dyDescent="0.3">
@@ -21693,7 +21693,7 @@
         <v>5.5265766785084882E-3</v>
       </c>
       <c r="D1482" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1483" spans="1:4" x14ac:dyDescent="0.3">
@@ -21707,7 +21707,7 @@
         <v>5.0588883715352679E-3</v>
       </c>
       <c r="D1483" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1484" spans="1:4" x14ac:dyDescent="0.3">
@@ -21721,7 +21721,7 @@
         <v>3.689759932872641E-3</v>
       </c>
       <c r="D1484" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1485" spans="1:4" x14ac:dyDescent="0.3">
@@ -21735,7 +21735,7 @@
         <v>3.5569275668787511E-3</v>
       </c>
       <c r="D1485" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1486" spans="1:4" x14ac:dyDescent="0.3">
@@ -21749,7 +21749,7 @@
         <v>2.971693073144654E-3</v>
       </c>
       <c r="D1486" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1487" spans="1:4" x14ac:dyDescent="0.3">
@@ -21763,7 +21763,7 @@
         <v>2.3561480415623249E-3</v>
       </c>
       <c r="D1487" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1488" spans="1:4" x14ac:dyDescent="0.3">
@@ -21777,7 +21777,7 @@
         <v>1.5087955958247789E-3</v>
       </c>
       <c r="D1488" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1489" spans="1:4" x14ac:dyDescent="0.3">
@@ -21791,7 +21791,7 @@
         <v>1.447769607246667E-3</v>
       </c>
       <c r="D1489" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1490" spans="1:4" x14ac:dyDescent="0.3">
@@ -21805,7 +21805,7 @@
         <v>1.072233739221473E-3</v>
       </c>
       <c r="D1490" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1491" spans="1:4" x14ac:dyDescent="0.3">
@@ -21819,7 +21819,7 @@
         <v>8.1165019037452183E-4</v>
       </c>
       <c r="D1491" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1492" spans="1:4" x14ac:dyDescent="0.3">
@@ -21833,7 +21833,7 @@
         <v>5.9427346212475999E-4</v>
       </c>
       <c r="D1492" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1493" spans="1:4" x14ac:dyDescent="0.3">
@@ -21847,7 +21847,7 @@
         <v>5.7685921265096106E-4</v>
       </c>
       <c r="D1493" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1494" spans="1:4" x14ac:dyDescent="0.3">
@@ -21861,7 +21861,7 @@
         <v>5.2728644441928064E-4</v>
       </c>
       <c r="D1494" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1495" spans="1:4" x14ac:dyDescent="0.3">
@@ -21875,7 +21875,7 @@
         <v>2.5158111507023612E-4</v>
       </c>
       <c r="D1495" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1496" spans="1:4" x14ac:dyDescent="0.3">
@@ -21889,7 +21889,7 @@
         <v>1.572945191230434E-4</v>
       </c>
       <c r="D1496" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1497" spans="1:4" x14ac:dyDescent="0.3">
@@ -21903,7 +21903,7 @@
         <v>6.7239708185706025E-5</v>
       </c>
       <c r="D1497" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1498" spans="1:4" x14ac:dyDescent="0.3">
@@ -21917,7 +21917,7 @@
         <v>6.3583324359536698E-5</v>
       </c>
       <c r="D1498" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1499" spans="1:4" x14ac:dyDescent="0.3">
@@ -21931,7 +21931,7 @@
         <v>5.3326573944725328E-5</v>
       </c>
       <c r="D1499" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1500" spans="1:4" x14ac:dyDescent="0.3">
@@ -21945,7 +21945,7 @@
         <v>4.0268930218565399E-5</v>
       </c>
       <c r="D1500" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1501" spans="1:4" x14ac:dyDescent="0.3">
@@ -21959,7 +21959,7 @@
         <v>2.3375281413901099E-5</v>
       </c>
       <c r="D1501" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1502" spans="1:4" x14ac:dyDescent="0.3">
@@ -21973,7 +21973,7 @@
         <v>8.5183705342616939E-6</v>
       </c>
       <c r="D1502" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1503" spans="1:4" x14ac:dyDescent="0.3">
@@ -21987,7 +21987,7 @@
         <v>8.3265701396997282E-6</v>
       </c>
       <c r="D1503" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1504" spans="1:4" x14ac:dyDescent="0.3">
@@ -22001,7 +22001,7 @@
         <v>5.3277868626757384E-6</v>
       </c>
       <c r="D1504" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1505" spans="1:4" x14ac:dyDescent="0.3">
@@ -22015,7 +22015,7 @@
         <v>3.4767597610993442E-6</v>
       </c>
       <c r="D1505" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1506" spans="1:4" x14ac:dyDescent="0.3">
@@ -22029,7 +22029,7 @@
         <v>1.2177735859451921E-7</v>
       </c>
       <c r="D1506" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1507" spans="1:4" x14ac:dyDescent="0.3">
@@ -22043,7 +22043,7 @@
         <v>0.23231266198185591</v>
       </c>
       <c r="D1507" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1508" spans="1:4" x14ac:dyDescent="0.3">
@@ -22057,7 +22057,7 @@
         <v>0.17665037003903411</v>
       </c>
       <c r="D1508" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1509" spans="1:4" x14ac:dyDescent="0.3">
@@ -22071,7 +22071,7 @@
         <v>0.12631797309203549</v>
       </c>
       <c r="D1509" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1510" spans="1:4" x14ac:dyDescent="0.3">
@@ -22085,7 +22085,7 @@
         <v>7.732250425882245E-2</v>
       </c>
       <c r="D1510" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1511" spans="1:4" x14ac:dyDescent="0.3">
@@ -22099,7 +22099,7 @@
         <v>6.8893616817312375E-2</v>
       </c>
       <c r="D1511" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1512" spans="1:4" x14ac:dyDescent="0.3">
@@ -22113,7 +22113,7 @@
         <v>5.9026546581412501E-2</v>
       </c>
       <c r="D1512" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1513" spans="1:4" x14ac:dyDescent="0.3">
@@ -22127,7 +22127,7 @@
         <v>5.6542715745731463E-2</v>
       </c>
       <c r="D1513" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1514" spans="1:4" x14ac:dyDescent="0.3">
@@ -22141,7 +22141,7 @@
         <v>4.283141882555324E-2</v>
       </c>
       <c r="D1514" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1515" spans="1:4" x14ac:dyDescent="0.3">
@@ -22155,7 +22155,7 @@
         <v>2.3104945388067882E-2</v>
       </c>
       <c r="D1515" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1516" spans="1:4" x14ac:dyDescent="0.3">
@@ -22169,7 +22169,7 @@
         <v>1.6086889458059549E-2</v>
       </c>
       <c r="D1516" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1517" spans="1:4" x14ac:dyDescent="0.3">
@@ -22183,7 +22183,7 @@
         <v>1.533763834800073E-2</v>
       </c>
       <c r="D1517" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1518" spans="1:4" x14ac:dyDescent="0.3">
@@ -22197,7 +22197,7 @@
         <v>1.5328954618887451E-2</v>
       </c>
       <c r="D1518" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1519" spans="1:4" x14ac:dyDescent="0.3">
@@ -22211,7 +22211,7 @@
         <v>1.358797460055302E-2</v>
       </c>
       <c r="D1519" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1520" spans="1:4" x14ac:dyDescent="0.3">
@@ -22225,7 +22225,7 @@
         <v>1.356982375576244E-2</v>
       </c>
       <c r="D1520" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1521" spans="1:4" x14ac:dyDescent="0.3">
@@ -22239,7 +22239,7 @@
         <v>1.1213448772990769E-2</v>
       </c>
       <c r="D1521" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1522" spans="1:4" x14ac:dyDescent="0.3">
@@ -22253,7 +22253,7 @@
         <v>1.093223584842771E-2</v>
       </c>
       <c r="D1522" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1523" spans="1:4" x14ac:dyDescent="0.3">
@@ -22267,7 +22267,7 @@
         <v>1.0044295042365399E-2</v>
       </c>
       <c r="D1523" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1524" spans="1:4" x14ac:dyDescent="0.3">
@@ -22281,7 +22281,7 @@
         <v>7.5143120774281442E-3</v>
       </c>
       <c r="D1524" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1525" spans="1:4" x14ac:dyDescent="0.3">
@@ -22295,7 +22295,7 @@
         <v>5.4949859262126109E-3</v>
       </c>
       <c r="D1525" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1526" spans="1:4" x14ac:dyDescent="0.3">
@@ -22309,7 +22309,7 @@
         <v>3.5601803219793659E-3</v>
       </c>
       <c r="D1526" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1527" spans="1:4" x14ac:dyDescent="0.3">
@@ -22323,7 +22323,7 @@
         <v>3.0455566677094199E-3</v>
       </c>
       <c r="D1527" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1528" spans="1:4" x14ac:dyDescent="0.3">
@@ -22337,7 +22337,7 @@
         <v>1.975340796543532E-3</v>
       </c>
       <c r="D1528" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1529" spans="1:4" x14ac:dyDescent="0.3">
@@ -22351,7 +22351,7 @@
         <v>1.6715935086978461E-3</v>
       </c>
       <c r="D1529" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1530" spans="1:4" x14ac:dyDescent="0.3">
@@ -22365,7 +22365,7 @@
         <v>1.4220153698733661E-3</v>
       </c>
       <c r="D1530" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1531" spans="1:4" x14ac:dyDescent="0.3">
@@ -22379,7 +22379,7 @@
         <v>1.391713972033631E-3</v>
       </c>
       <c r="D1531" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1532" spans="1:4" x14ac:dyDescent="0.3">
@@ -22393,7 +22393,7 @@
         <v>6.6251378837096778E-4</v>
       </c>
       <c r="D1532" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1533" spans="1:4" x14ac:dyDescent="0.3">
@@ -22407,7 +22407,7 @@
         <v>5.2209067270010245E-4</v>
       </c>
       <c r="D1533" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1534" spans="1:4" x14ac:dyDescent="0.3">
@@ -22421,7 +22421,7 @@
         <v>5.1610705793170752E-4</v>
       </c>
       <c r="D1534" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1535" spans="1:4" x14ac:dyDescent="0.3">
@@ -22435,7 +22435,7 @@
         <v>4.74205123776516E-4</v>
       </c>
       <c r="D1535" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1536" spans="1:4" x14ac:dyDescent="0.3">
@@ -22449,7 +22449,7 @@
         <v>4.025685008871839E-4</v>
       </c>
       <c r="D1536" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1537" spans="1:4" x14ac:dyDescent="0.3">
@@ -22463,7 +22463,7 @@
         <v>3.5909983980056133E-4</v>
       </c>
       <c r="D1537" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1538" spans="1:4" x14ac:dyDescent="0.3">
@@ -22477,7 +22477,7 @@
         <v>2.9776368847615731E-4</v>
       </c>
       <c r="D1538" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1539" spans="1:4" x14ac:dyDescent="0.3">
@@ -22491,7 +22491,7 @@
         <v>2.9098004096845268E-4</v>
       </c>
       <c r="D1539" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1540" spans="1:4" x14ac:dyDescent="0.3">
@@ -22505,7 +22505,7 @@
         <v>2.3002724443954291E-4</v>
       </c>
       <c r="D1540" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1541" spans="1:4" x14ac:dyDescent="0.3">
@@ -22519,7 +22519,7 @@
         <v>1.6125741323217021E-4</v>
       </c>
       <c r="D1541" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1542" spans="1:4" x14ac:dyDescent="0.3">
@@ -22533,7 +22533,7 @@
         <v>1.2285564156004161E-4</v>
       </c>
       <c r="D1542" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1543" spans="1:4" x14ac:dyDescent="0.3">
@@ -22547,7 +22547,7 @@
         <v>8.593728894854173E-5</v>
       </c>
       <c r="D1543" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1544" spans="1:4" x14ac:dyDescent="0.3">
@@ -22561,7 +22561,7 @@
         <v>8.3187159083439823E-5</v>
       </c>
       <c r="D1544" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1545" spans="1:4" x14ac:dyDescent="0.3">
@@ -22575,7 +22575,7 @@
         <v>8.2003771548636023E-5</v>
       </c>
       <c r="D1545" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1546" spans="1:4" x14ac:dyDescent="0.3">
@@ -22589,7 +22589,7 @@
         <v>7.7636899231887561E-5</v>
       </c>
       <c r="D1546" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1547" spans="1:4" x14ac:dyDescent="0.3">
@@ -22603,7 +22603,7 @@
         <v>7.6486850244271743E-5</v>
       </c>
       <c r="D1547" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1548" spans="1:4" x14ac:dyDescent="0.3">
@@ -22617,7 +22617,7 @@
         <v>7.5153446946555494E-5</v>
       </c>
       <c r="D1548" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1549" spans="1:4" x14ac:dyDescent="0.3">
@@ -22631,7 +22631,7 @@
         <v>6.4402958890624304E-5</v>
       </c>
       <c r="D1549" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1550" spans="1:4" x14ac:dyDescent="0.3">
@@ -22645,7 +22645,7 @@
         <v>6.0869457860373357E-5</v>
       </c>
       <c r="D1550" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1551" spans="1:4" x14ac:dyDescent="0.3">
@@ -22659,7 +22659,7 @@
         <v>4.4468709710192967E-5</v>
       </c>
       <c r="D1551" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1552" spans="1:4" x14ac:dyDescent="0.3">
@@ -22673,7 +22673,7 @@
         <v>2.5801186733101901E-5</v>
       </c>
       <c r="D1552" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1553" spans="1:4" x14ac:dyDescent="0.3">
@@ -22687,7 +22687,7 @@
         <v>2.440112173987672E-5</v>
       </c>
       <c r="D1553" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1554" spans="1:4" x14ac:dyDescent="0.3">
@@ -22701,7 +22701,7 @@
         <v>2.1567653206238359E-5</v>
       </c>
       <c r="D1554" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1555" spans="1:4" x14ac:dyDescent="0.3">
@@ -22715,7 +22715,7 @@
         <v>1.6967441856908049E-5</v>
       </c>
       <c r="D1555" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1556" spans="1:4" x14ac:dyDescent="0.3">
@@ -22729,7 +22729,7 @@
         <v>7.5003415784775994E-6</v>
       </c>
       <c r="D1556" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1557" spans="1:4" x14ac:dyDescent="0.3">
@@ -22743,7 +22743,7 @@
         <v>6.8503092032134683E-6</v>
       </c>
       <c r="D1557" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1558" spans="1:4" x14ac:dyDescent="0.3">
@@ -22757,7 +22757,7 @@
         <v>6.3336310167013201E-6</v>
       </c>
       <c r="D1558" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1559" spans="1:4" x14ac:dyDescent="0.3">
@@ -22771,7 +22771,7 @@
         <v>5.0502278403335274E-6</v>
       </c>
       <c r="D1559" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1560" spans="1:4" x14ac:dyDescent="0.3">
@@ -22785,7 +22785,7 @@
         <v>3.183484781944658E-6</v>
       </c>
       <c r="D1560" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1561" spans="1:4" x14ac:dyDescent="0.3">
@@ -22799,7 +22799,7 @@
         <v>2.5167754336530001E-6</v>
       </c>
       <c r="D1561" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1562" spans="1:4" x14ac:dyDescent="0.3">
@@ -22813,7 +22813,7 @@
         <v>2.3334365224196181E-6</v>
       </c>
       <c r="D1562" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1563" spans="1:4" x14ac:dyDescent="0.3">
@@ -22827,7 +22827,7 @@
         <v>1.883420031416398E-6</v>
       </c>
       <c r="D1563" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1564" spans="1:4" x14ac:dyDescent="0.3">
@@ -22841,7 +22841,7 @@
         <v>1.666742572995022E-6</v>
       </c>
       <c r="D1564" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1565" spans="1:4" x14ac:dyDescent="0.3">
@@ -22855,7 +22855,7 @@
         <v>1.183387534803807E-6</v>
       </c>
       <c r="D1565" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1566" spans="1:4" x14ac:dyDescent="0.3">
@@ -22869,7 +22869,7 @@
         <v>9.1670995503396809E-7</v>
       </c>
       <c r="D1566" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1567" spans="1:4" x14ac:dyDescent="0.3">
@@ -22883,7 +22883,7 @@
         <v>6.5003237526412959E-7</v>
       </c>
       <c r="D1567" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1568" spans="1:4" x14ac:dyDescent="0.3">
@@ -22897,7 +22897,7 @@
         <v>5.0001661235168193E-7</v>
       </c>
       <c r="D1568" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1569" spans="1:4" x14ac:dyDescent="0.3">
@@ -22911,7 +22911,7 @@
         <v>3.6667782246676268E-7</v>
       </c>
       <c r="D1569" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1570" spans="1:4" x14ac:dyDescent="0.3">
@@ -22925,7 +22925,7 @@
         <v>2.6667757976983861E-7</v>
       </c>
       <c r="D1570" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1571" spans="1:4" x14ac:dyDescent="0.3">
@@ -22939,7 +22939,7 @@
         <v>2.333390325818434E-7</v>
       </c>
       <c r="D1571" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1572" spans="1:4" x14ac:dyDescent="0.3">
@@ -22953,7 +22953,7 @@
         <v>2.333390325818434E-7</v>
       </c>
       <c r="D1572" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1573" spans="1:4" x14ac:dyDescent="0.3">
@@ -22967,7 +22967,7 @@
         <v>1.6667733707291451E-7</v>
       </c>
       <c r="D1573" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1574" spans="1:4" x14ac:dyDescent="0.3">
@@ -22981,7 +22981,7 @@
         <v>6.6677094375990361E-8</v>
       </c>
       <c r="D1574" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1575" spans="1:4" x14ac:dyDescent="0.3">
@@ -22995,7 +22995,7 @@
         <v>1.6661574160466878E-8</v>
       </c>
       <c r="D1575" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1576" spans="1:4" x14ac:dyDescent="0.3">
@@ -23009,7 +23009,7 @@
         <v>1.6661574160466878E-8</v>
       </c>
       <c r="D1576" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1577" spans="1:4" x14ac:dyDescent="0.3">
@@ -23023,7 +23023,7 @@
         <v>0.31544723207531611</v>
       </c>
       <c r="D1577" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1578" spans="1:4" x14ac:dyDescent="0.3">
@@ -23037,7 +23037,7 @@
         <v>0.19847429324547089</v>
       </c>
       <c r="D1578" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1579" spans="1:4" x14ac:dyDescent="0.3">
@@ -23051,7 +23051,7 @@
         <v>0.17720741060638989</v>
       </c>
       <c r="D1579" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1580" spans="1:4" x14ac:dyDescent="0.3">
@@ -23065,7 +23065,7 @@
         <v>0.11378070925157351</v>
       </c>
       <c r="D1580" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1581" spans="1:4" x14ac:dyDescent="0.3">
@@ -23079,7 +23079,7 @@
         <v>4.4543672845349713E-2</v>
       </c>
       <c r="D1581" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1582" spans="1:4" x14ac:dyDescent="0.3">
@@ -23093,7 +23093,7 @@
         <v>3.1398634777178552E-2</v>
       </c>
       <c r="D1582" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1583" spans="1:4" x14ac:dyDescent="0.3">
@@ -23107,7 +23107,7 @@
         <v>1.2875841118903259E-2</v>
       </c>
       <c r="D1583" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1584" spans="1:4" x14ac:dyDescent="0.3">
@@ -23121,7 +23121,7 @@
         <v>1.2638719151433161E-2</v>
       </c>
       <c r="D1584" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1585" spans="1:4" x14ac:dyDescent="0.3">
@@ -23135,7 +23135,7 @@
         <v>9.5326517843563052E-3</v>
       </c>
       <c r="D1585" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1586" spans="1:4" x14ac:dyDescent="0.3">
@@ -23149,7 +23149,7 @@
         <v>9.3432904644371231E-3</v>
       </c>
       <c r="D1586" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1587" spans="1:4" x14ac:dyDescent="0.3">
@@ -23163,7 +23163,7 @@
         <v>7.6641393978782802E-3</v>
       </c>
       <c r="D1587" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1588" spans="1:4" x14ac:dyDescent="0.3">
@@ -23177,7 +23177,7 @@
         <v>6.7358392784492328E-3</v>
       </c>
       <c r="D1588" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1589" spans="1:4" x14ac:dyDescent="0.3">
@@ -23191,7 +23191,7 @@
         <v>6.4473201301457278E-3</v>
       </c>
       <c r="D1589" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1590" spans="1:4" x14ac:dyDescent="0.3">
@@ -23205,7 +23205,7 @@
         <v>6.0169699130478713E-3</v>
       </c>
       <c r="D1590" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1591" spans="1:4" x14ac:dyDescent="0.3">
@@ -23219,7 +23219,7 @@
         <v>5.9749006923533882E-3</v>
       </c>
       <c r="D1591" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1592" spans="1:4" x14ac:dyDescent="0.3">
@@ -23233,7 +23233,7 @@
         <v>5.7249512220656166E-3</v>
       </c>
       <c r="D1592" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1593" spans="1:4" x14ac:dyDescent="0.3">
@@ -23247,7 +23247,7 @@
         <v>5.3594421578416181E-3</v>
       </c>
       <c r="D1593" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1594" spans="1:4" x14ac:dyDescent="0.3">
@@ -23261,7 +23261,7 @@
         <v>4.880889174601521E-3</v>
       </c>
       <c r="D1594" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1595" spans="1:4" x14ac:dyDescent="0.3">
@@ -23275,7 +23275,7 @@
         <v>4.8387203233310524E-3</v>
       </c>
       <c r="D1595" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1596" spans="1:4" x14ac:dyDescent="0.3">
@@ -23289,7 +23289,7 @@
         <v>4.5699032221062329E-3</v>
       </c>
       <c r="D1596" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1597" spans="1:4" x14ac:dyDescent="0.3">
@@ -23303,7 +23303,7 @@
         <v>4.1612912598941428E-3</v>
       </c>
       <c r="D1597" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1598" spans="1:4" x14ac:dyDescent="0.3">
@@ -23317,7 +23317,7 @@
         <v>2.598994996265347E-3</v>
       </c>
       <c r="D1598" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1599" spans="1:4" x14ac:dyDescent="0.3">
@@ -23331,7 +23331,7 @@
         <v>1.8824794161659011E-3</v>
       </c>
       <c r="D1599" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1600" spans="1:4" x14ac:dyDescent="0.3">
@@ -23345,7 +23345,7 @@
         <v>1.3285243929734649E-3</v>
       </c>
       <c r="D1600" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1601" spans="1:4" x14ac:dyDescent="0.3">
@@ -23359,7 +23359,7 @@
         <v>1.175117439820895E-3</v>
       </c>
       <c r="D1601" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1602" spans="1:4" x14ac:dyDescent="0.3">
@@ -23373,7 +23373,7 @@
         <v>7.9691786338295602E-4</v>
       </c>
       <c r="D1602" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1603" spans="1:4" x14ac:dyDescent="0.3">
@@ -23387,7 +23387,7 @@
         <v>7.6786917615148231E-4</v>
       </c>
       <c r="D1603" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1604" spans="1:4" x14ac:dyDescent="0.3">
@@ -23401,7 +23401,7 @@
         <v>6.5786401271495916E-4</v>
       </c>
       <c r="D1604" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1605" spans="1:4" x14ac:dyDescent="0.3">
@@ -23415,7 +23415,7 @@
         <v>5.2044161704347433E-4</v>
       </c>
       <c r="D1605" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1606" spans="1:4" x14ac:dyDescent="0.3">
@@ -23429,7 +23429,7 @@
         <v>3.2084320654125878E-4</v>
       </c>
       <c r="D1606" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1607" spans="1:4" x14ac:dyDescent="0.3">
@@ -23443,7 +23443,7 @@
         <v>2.7554843012848711E-4</v>
       </c>
       <c r="D1607" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1608" spans="1:4" x14ac:dyDescent="0.3">
@@ -23457,7 +23457,7 @@
         <v>2.6615819944132761E-4</v>
       </c>
       <c r="D1608" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1609" spans="1:4" x14ac:dyDescent="0.3">
@@ -23471,7 +23471,7 @@
         <v>2.6422784696385313E-4</v>
       </c>
       <c r="D1609" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1610" spans="1:4" x14ac:dyDescent="0.3">
@@ -23485,7 +23485,7 @@
         <v>2.53909805818706E-4</v>
       </c>
       <c r="D1610" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1611" spans="1:4" x14ac:dyDescent="0.3">
@@ -23499,7 +23499,7 @@
         <v>1.9941782936411649E-4</v>
       </c>
       <c r="D1611" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1612" spans="1:4" x14ac:dyDescent="0.3">
@@ -23513,7 +23513,7 @@
         <v>1.8807234143198971E-4</v>
       </c>
       <c r="D1612" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1613" spans="1:4" x14ac:dyDescent="0.3">
@@ -23527,7 +23527,7 @@
         <v>1.322789369829649E-4</v>
       </c>
       <c r="D1613" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1614" spans="1:4" x14ac:dyDescent="0.3">
@@ -23541,7 +23541,7 @@
         <v>1.2659996538677651E-4</v>
       </c>
       <c r="D1614" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1615" spans="1:4" x14ac:dyDescent="0.3">
@@ -23555,7 +23555,7 @@
         <v>1.199122327704869E-4</v>
       </c>
       <c r="D1615" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1616" spans="1:4" x14ac:dyDescent="0.3">
@@ -23569,7 +23569,7 @@
         <v>1.190404566011063E-4</v>
       </c>
       <c r="D1616" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1617" spans="1:4" x14ac:dyDescent="0.3">
@@ -23583,7 +23583,7 @@
         <v>9.7775449827773071E-5</v>
       </c>
       <c r="D1617" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1618" spans="1:4" x14ac:dyDescent="0.3">
@@ -23597,7 +23597,7 @@
         <v>7.1429254914162339E-5</v>
       </c>
       <c r="D1618" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1619" spans="1:4" x14ac:dyDescent="0.3">
@@ -23611,7 +23611,7 @@
         <v>6.459207643389496E-5</v>
       </c>
       <c r="D1619" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1620" spans="1:4" x14ac:dyDescent="0.3">
@@ -23625,7 +23625,7 @@
         <v>4.2660785149779917E-5</v>
       </c>
       <c r="D1620" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1621" spans="1:4" x14ac:dyDescent="0.3">
@@ -23639,7 +23639,7 @@
         <v>2.8812060298753561E-5</v>
       </c>
       <c r="D1621" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1622" spans="1:4" x14ac:dyDescent="0.3">
@@ -23653,7 +23653,7 @@
         <v>2.2504169972533139E-5</v>
       </c>
       <c r="D1622" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1623" spans="1:4" x14ac:dyDescent="0.3">
@@ -23667,7 +23667,7 @@
         <v>1.6407996058532899E-5</v>
       </c>
       <c r="D1623" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1624" spans="1:4" x14ac:dyDescent="0.3">
@@ -23681,7 +23681,7 @@
         <v>1.6264774948176619E-5</v>
       </c>
       <c r="D1624" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1625" spans="1:4" x14ac:dyDescent="0.3">
@@ -23695,7 +23695,7 @@
         <v>1.0697889188223329E-5</v>
       </c>
       <c r="D1625" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1626" spans="1:4" x14ac:dyDescent="0.3">
@@ -23709,7 +23709,7 @@
         <v>6.7437784109107044E-6</v>
       </c>
       <c r="D1626" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1627" spans="1:4" x14ac:dyDescent="0.3">
@@ -23723,7 +23723,7 @@
         <v>5.5917962804530936E-6</v>
       </c>
       <c r="D1627" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1628" spans="1:4" x14ac:dyDescent="0.3">
@@ -23737,7 +23737,7 @@
         <v>1.4757843789128451E-6</v>
       </c>
       <c r="D1628" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1629" spans="1:4" x14ac:dyDescent="0.3">
@@ -23751,7 +23751,7 @@
         <v>1.382378556549133E-6</v>
       </c>
       <c r="D1629" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1630" spans="1:4" x14ac:dyDescent="0.3">
@@ -23765,7 +23765,7 @@
         <v>7.6591508676694506E-7</v>
       </c>
       <c r="D1630" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1631" spans="1:4" x14ac:dyDescent="0.3">
@@ -23779,7 +23779,7 @@
         <v>5.9778920891789789E-7</v>
       </c>
       <c r="D1631" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1632" spans="1:4" x14ac:dyDescent="0.3">
@@ -23793,7 +23793,7 @@
         <v>5.5419867454675657E-7</v>
       </c>
       <c r="D1632" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1633" spans="1:4" x14ac:dyDescent="0.3">
@@ -23807,7 +23807,7 @@
         <v>2.4285168634142591E-7</v>
       </c>
       <c r="D1633" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1634" spans="1:4" x14ac:dyDescent="0.3">
@@ -23821,7 +23821,7 @@
         <v>2.366211797129521E-7</v>
       </c>
       <c r="D1634" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1635" spans="1:4" x14ac:dyDescent="0.3">
@@ -23835,7 +23835,7 @@
         <v>1.120858362350461E-7</v>
       </c>
       <c r="D1635" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1636" spans="1:4" x14ac:dyDescent="0.3">
@@ -23849,7 +23849,7 @@
         <v>8.717531573523859E-8</v>
       </c>
       <c r="D1636" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1637" spans="1:4" x14ac:dyDescent="0.3">
@@ -23863,7 +23863,7 @@
         <v>2.49105204998075E-8</v>
       </c>
       <c r="D1637" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -23881,6 +23881,16 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="03763a1d-3ef6-4dac-84db-711c24c35716">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004E32BC299DDA75418A481CE8C1C04767" ma:contentTypeVersion="10" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="0fa4796f6798a7b079311364fca30a32">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="03763a1d-3ef6-4dac-84db-711c24c35716" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ccd651f340b356ff6f610107a3061652" ns2:_="">
     <xsd:import namespace="03763a1d-3ef6-4dac-84db-711c24c35716"/>
@@ -24058,16 +24068,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="03763a1d-3ef6-4dac-84db-711c24c35716">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2543F6D-492F-4C9B-8AF7-7639E4005A4C}">
   <ds:schemaRefs>
@@ -24077,6 +24077,16 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C50C39B-429F-409A-A7E6-0609DFF42D17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="03763a1d-3ef6-4dac-84db-711c24c35716"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613F8F29-F909-4A5C-BFEC-CB47403B45C6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24092,14 +24102,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C50C39B-429F-409A-A7E6-0609DFF42D17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="03763a1d-3ef6-4dac-84db-711c24c35716"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/material_market_share.xlsx
+++ b/data/material_market_share.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\GitHub\FLIM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C8FF16-EB4F-4FD8-87F1-13E1A4CF8F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607C465D-4EFC-41B1-9174-6FCC4236BA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -523,16 +536,10 @@
     <t>Leer</t>
   </si>
   <si>
-    <t>Plastics algemeen</t>
-  </si>
-  <si>
     <t>Thermoloft (non/woven)</t>
   </si>
   <si>
     <t>LDPE</t>
-  </si>
-  <si>
-    <t>Zacht PVC</t>
   </si>
   <si>
     <t>Jute</t>
@@ -574,13 +581,19 @@
     <t>Katoen</t>
   </si>
   <si>
-    <t>Gerecycled Plastic</t>
-  </si>
-  <si>
     <t>material</t>
   </si>
   <si>
-    <t>Gerecycled metaal</t>
+    <t>PVC (zacht)</t>
+  </si>
+  <si>
+    <t>Kunststof algemeen</t>
+  </si>
+  <si>
+    <t>Kunststof (gerecycled)</t>
+  </si>
+  <si>
+    <t>Metaal (gerecycled)</t>
   </si>
 </sst>
 </file>
@@ -959,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -8827,7 +8840,7 @@
         <v>0.31020687415783721</v>
       </c>
       <c r="D563" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.3">
@@ -8841,7 +8854,7 @@
         <v>0.13747311891599531</v>
       </c>
       <c r="D564" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.3">
@@ -8855,7 +8868,7 @@
         <v>6.6851776484848968E-2</v>
       </c>
       <c r="D565" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.3">
@@ -8869,7 +8882,7 @@
         <v>5.606177855361269E-2</v>
       </c>
       <c r="D566" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.3">
@@ -8883,7 +8896,7 @@
         <v>5.5201117442186892E-2</v>
       </c>
       <c r="D567" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.3">
@@ -8897,7 +8910,7 @@
         <v>5.1137777799324068E-2</v>
       </c>
       <c r="D568" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.3">
@@ -8911,7 +8924,7 @@
         <v>3.2291764404665517E-2</v>
       </c>
       <c r="D569" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.3">
@@ -8925,7 +8938,7 @@
         <v>3.088262692698068E-2</v>
       </c>
       <c r="D570" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.3">
@@ -8939,7 +8952,7 @@
         <v>2.9367978846214421E-2</v>
       </c>
       <c r="D571" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.3">
@@ -8953,7 +8966,7 @@
         <v>2.556539746678109E-2</v>
       </c>
       <c r="D572" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.3">
@@ -8967,7 +8980,7 @@
         <v>2.1039164213287321E-2</v>
       </c>
       <c r="D573" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.3">
@@ -8981,7 +8994,7 @@
         <v>1.8666108725327799E-2</v>
       </c>
       <c r="D574" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.3">
@@ -8995,7 +9008,7 @@
         <v>1.791645157719882E-2</v>
       </c>
       <c r="D575" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.3">
@@ -9009,7 +9022,7 @@
         <v>1.317913025096094E-2</v>
       </c>
       <c r="D576" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.3">
@@ -9023,7 +9036,7 @@
         <v>1.262746471969523E-2</v>
       </c>
       <c r="D577" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.3">
@@ -9037,7 +9050,7 @@
         <v>1.2528306518743371E-2</v>
       </c>
       <c r="D578" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.3">
@@ -9051,7 +9064,7 @@
         <v>1.2117527851756269E-2</v>
       </c>
       <c r="D579" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.3">
@@ -9065,7 +9078,7 @@
         <v>9.6709912414705626E-3</v>
       </c>
       <c r="D580" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.3">
@@ -9079,7 +9092,7 @@
         <v>8.6924886345599289E-3</v>
       </c>
       <c r="D581" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.3">
@@ -9093,7 +9106,7 @@
         <v>7.0427977626547102E-3</v>
       </c>
       <c r="D582" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.3">
@@ -9107,7 +9120,7 @@
         <v>6.5467181388802398E-3</v>
       </c>
       <c r="D583" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
@@ -9121,7 +9134,7 @@
         <v>5.3597830494389511E-3</v>
       </c>
       <c r="D584" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.3">
@@ -9135,7 +9148,7 @@
         <v>5.0075754410211469E-3</v>
       </c>
       <c r="D585" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.3">
@@ -9149,7 +9162,7 @@
         <v>4.7853798754735827E-3</v>
       </c>
       <c r="D586" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.3">
@@ -9163,7 +9176,7 @@
         <v>4.5799782604338188E-3</v>
       </c>
       <c r="D587" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
@@ -9177,7 +9190,7 @@
         <v>4.4397723513941454E-3</v>
       </c>
       <c r="D588" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.3">
@@ -9191,7 +9204,7 @@
         <v>4.2590604971775997E-3</v>
       </c>
       <c r="D589" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.3">
@@ -9205,7 +9218,7 @@
         <v>4.2157611317290844E-3</v>
       </c>
       <c r="D590" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.3">
@@ -9219,7 +9232,7 @@
         <v>3.9749832548617433E-3</v>
       </c>
       <c r="D591" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.3">
@@ -9233,7 +9246,7 @@
         <v>3.3859504511888519E-3</v>
       </c>
       <c r="D592" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.3">
@@ -9247,7 +9260,7 @@
         <v>3.1864331665361419E-3</v>
       </c>
       <c r="D593" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.3">
@@ -9261,7 +9274,7 @@
         <v>3.0535697063807988E-3</v>
       </c>
       <c r="D594" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.3">
@@ -9275,7 +9288,7 @@
         <v>3.044960188985904E-3</v>
       </c>
       <c r="D595" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.3">
@@ -9289,7 +9302,7 @@
         <v>2.224697216197398E-3</v>
       </c>
       <c r="D596" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.3">
@@ -9303,7 +9316,7 @@
         <v>1.773710095137965E-3</v>
       </c>
       <c r="D597" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.3">
@@ -9317,7 +9330,7 @@
         <v>1.679895145003475E-3</v>
       </c>
       <c r="D598" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.3">
@@ -9331,7 +9344,7 @@
         <v>1.499919514086996E-3</v>
       </c>
       <c r="D599" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.3">
@@ -9345,7 +9358,7 @@
         <v>1.3446445610637891E-3</v>
       </c>
       <c r="D600" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.3">
@@ -9359,7 +9372,7 @@
         <v>1.301798939254915E-3</v>
       </c>
       <c r="D601" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
@@ -9373,7 +9386,7 @@
         <v>1.247143034633167E-3</v>
       </c>
       <c r="D602" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
@@ -9387,7 +9400,7 @@
         <v>1.060359893786529E-3</v>
       </c>
       <c r="D603" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
@@ -9401,7 +9414,7 @@
         <v>7.7652828680765127E-4</v>
       </c>
       <c r="D604" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
@@ -9415,7 +9428,7 @@
         <v>4.8608294946803429E-4</v>
       </c>
       <c r="D605" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
@@ -9429,7 +9442,7 @@
         <v>4.5575176401203268E-4</v>
       </c>
       <c r="D606" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.3">
@@ -9443,7 +9456,7 @@
         <v>3.4007390598622428E-4</v>
       </c>
       <c r="D607" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
@@ -9457,7 +9470,7 @@
         <v>2.8787298994291231E-4</v>
       </c>
       <c r="D608" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
@@ -9471,7 +9484,7 @@
         <v>2.7088526112646941E-4</v>
       </c>
       <c r="D609" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.3">
@@ -9485,7 +9498,7 @@
         <v>2.0572571736934169E-4</v>
       </c>
       <c r="D610" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.3">
@@ -9499,7 +9512,7 @@
         <v>7.7963284357581981E-5</v>
       </c>
       <c r="D611" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.3">
@@ -9513,7 +9526,7 @@
         <v>7.7582549805900558E-5</v>
       </c>
       <c r="D612" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.3">
@@ -9527,7 +9540,7 @@
         <v>7.2480158501351174E-5</v>
       </c>
       <c r="D613" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
@@ -9541,7 +9554,7 @@
         <v>6.9942609186643244E-5</v>
       </c>
       <c r="D614" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.3">
@@ -9555,7 +9568,7 @@
         <v>5.7952876167982442E-5</v>
       </c>
       <c r="D615" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.3">
@@ -9569,7 +9582,7 @@
         <v>5.6348741385950153E-5</v>
       </c>
       <c r="D616" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.3">
@@ -9583,7 +9596,7 @@
         <v>3.8372329975693292E-5</v>
       </c>
       <c r="D617" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.3">
@@ -9597,7 +9610,7 @@
         <v>3.1809091221548422E-5</v>
       </c>
       <c r="D618" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
@@ -9611,7 +9624,7 @@
         <v>2.6658937262723888E-5</v>
       </c>
       <c r="D619" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.3">
@@ -9625,7 +9638,7 @@
         <v>2.4263310489098941E-5</v>
       </c>
       <c r="D620" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.3">
@@ -9639,7 +9652,7 @@
         <v>2.2328932761979391E-5</v>
       </c>
       <c r="D621" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
@@ -9653,7 +9666,7 @@
         <v>2.0363850066147439E-5</v>
       </c>
       <c r="D622" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.3">
@@ -9667,7 +9680,7 @@
         <v>1.985825065894577E-5</v>
       </c>
       <c r="D623" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.3">
@@ -9681,7 +9694,7 @@
         <v>1.9207317047470858E-5</v>
       </c>
       <c r="D624" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.3">
@@ -9695,7 +9708,7 @@
         <v>1.427687054184564E-5</v>
       </c>
       <c r="D625" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
@@ -9709,7 +9722,7 @@
         <v>1.2134384512062819E-5</v>
       </c>
       <c r="D626" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
@@ -9723,7 +9736,7 @@
         <v>8.2192305645138114E-6</v>
       </c>
       <c r="D627" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
@@ -9737,7 +9750,7 @@
         <v>7.7729929621232997E-6</v>
       </c>
       <c r="D628" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.3">
@@ -9751,7 +9764,7 @@
         <v>7.2476062866512464E-6</v>
       </c>
       <c r="D629" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.3">
@@ -9765,7 +9778,7 @@
         <v>5.9887252634324753E-6</v>
       </c>
       <c r="D630" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.3">
@@ -9779,7 +9792,7 @@
         <v>4.9345402492980977E-6</v>
       </c>
       <c r="D631" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.3">
@@ -9793,7 +9806,7 @@
         <v>2.1349799925310602E-6</v>
       </c>
       <c r="D632" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.3">
@@ -9807,7 +9820,7 @@
         <v>2.0449138493961059E-6</v>
       </c>
       <c r="D633" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.3">
@@ -9821,7 +9834,7 @@
         <v>1.686695518304111E-6</v>
       </c>
       <c r="D634" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.3">
@@ -9835,7 +9848,7 @@
         <v>5.8952493482731016E-7</v>
       </c>
       <c r="D635" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.3">
@@ -9849,7 +9862,7 @@
         <v>4.735302775240411E-7</v>
       </c>
       <c r="D636" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.3">
@@ -9863,7 +9876,7 @@
         <v>4.694365338511658E-7</v>
       </c>
       <c r="D637" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.3">
@@ -9877,7 +9890,7 @@
         <v>4.1621534454932178E-7</v>
       </c>
       <c r="D638" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.3">
@@ -9891,7 +9904,7 @@
         <v>2.3062452325270749E-7</v>
       </c>
       <c r="D639" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.3">
@@ -9905,7 +9918,7 @@
         <v>2.2243640551834071E-7</v>
       </c>
       <c r="D640" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.3">
@@ -9919,7 +9932,7 @@
         <v>8.1195944917980258E-8</v>
       </c>
       <c r="D641" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.3">
@@ -9933,7 +9946,7 @@
         <v>7.6420120762497713E-8</v>
       </c>
       <c r="D642" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.3">
@@ -9947,7 +9960,7 @@
         <v>4.5033071567477118E-8</v>
       </c>
       <c r="D643" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.3">
@@ -9961,7 +9974,7 @@
         <v>4.4350991084869927E-8</v>
       </c>
       <c r="D644" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.3">
@@ -9975,7 +9988,7 @@
         <v>3.8892456058164093E-8</v>
       </c>
       <c r="D645" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.3">
@@ -9989,7 +10002,7 @@
         <v>2.7975386004752438E-8</v>
       </c>
       <c r="D646" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.3">
@@ -10003,7 +10016,7 @@
         <v>2.729267513352915E-8</v>
       </c>
       <c r="D647" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.3">
@@ -10017,7 +10030,7 @@
         <v>1.432873324367981E-8</v>
       </c>
       <c r="D648" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.3">
@@ -10031,7 +10044,7 @@
         <v>4.776454544098634E-9</v>
       </c>
       <c r="D649" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.3">
@@ -10045,7 +10058,7 @@
         <v>4.776454544098634E-9</v>
       </c>
       <c r="D650" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.3">
@@ -10059,7 +10072,7 @@
         <v>1.364791353830479E-9</v>
       </c>
       <c r="D651" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.3">
@@ -10073,7 +10086,7 @@
         <v>1.364791353830479E-9</v>
       </c>
       <c r="D652" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.3">
@@ -10087,7 +10100,7 @@
         <v>0.26929749833927641</v>
       </c>
       <c r="D653" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.3">
@@ -10101,7 +10114,7 @@
         <v>9.1496046803567696E-2</v>
       </c>
       <c r="D654" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.3">
@@ -10115,7 +10128,7 @@
         <v>8.050100950988269E-2</v>
       </c>
       <c r="D655" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.3">
@@ -10129,7 +10142,7 @@
         <v>6.9433511584760646E-2</v>
       </c>
       <c r="D656" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.3">
@@ -10143,7 +10156,7 @@
         <v>6.1908011123324863E-2</v>
       </c>
       <c r="D657" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.3">
@@ -10157,7 +10170,7 @@
         <v>5.4509476182504422E-2</v>
       </c>
       <c r="D658" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.3">
@@ -10171,7 +10184,7 @@
         <v>5.433549240601708E-2</v>
       </c>
       <c r="D659" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.3">
@@ -10185,7 +10198,7 @@
         <v>4.7788430766938721E-2</v>
       </c>
       <c r="D660" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.3">
@@ -10199,7 +10212,7 @@
         <v>3.6059460013700813E-2</v>
       </c>
       <c r="D661" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.3">
@@ -10213,7 +10226,7 @@
         <v>3.5178741600145648E-2</v>
       </c>
       <c r="D662" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.3">
@@ -10227,7 +10240,7 @@
         <v>3.007521170217789E-2</v>
       </c>
       <c r="D663" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.3">
@@ -10241,7 +10254,7 @@
         <v>2.9812756391927639E-2</v>
       </c>
       <c r="D664" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
@@ -10255,7 +10268,7 @@
         <v>2.7233282497499369E-2</v>
       </c>
       <c r="D665" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.3">
@@ -10269,7 +10282,7 @@
         <v>2.6780394847417521E-2</v>
       </c>
       <c r="D666" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.3">
@@ -10283,7 +10296,7 @@
         <v>1.5564294654413949E-2</v>
       </c>
       <c r="D667" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.3">
@@ -10297,7 +10310,7 @@
         <v>1.3058179906100691E-2</v>
       </c>
       <c r="D668" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.3">
@@ -10311,7 +10324,7 @@
         <v>1.26471542128296E-2</v>
       </c>
       <c r="D669" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.3">
@@ -10325,7 +10338,7 @@
         <v>8.0917310336049136E-3</v>
       </c>
       <c r="D670" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
@@ -10339,7 +10352,7 @@
         <v>6.995543683488631E-3</v>
       </c>
       <c r="D671" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.3">
@@ -10353,7 +10366,7 @@
         <v>4.8697631993224327E-3</v>
       </c>
       <c r="D672" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.3">
@@ -10367,7 +10380,7 @@
         <v>3.3049961239827309E-3</v>
       </c>
       <c r="D673" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.3">
@@ -10381,7 +10394,7 @@
         <v>3.1617472511061128E-3</v>
       </c>
       <c r="D674" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.3">
@@ -10395,7 +10408,7 @@
         <v>3.0732409350760141E-3</v>
       </c>
       <c r="D675" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.3">
@@ -10409,7 +10422,7 @@
         <v>1.999791729627057E-3</v>
       </c>
       <c r="D676" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.3">
@@ -10423,7 +10436,7 @@
         <v>1.922771873739302E-3</v>
       </c>
       <c r="D677" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.3">
@@ -10437,7 +10450,7 @@
         <v>1.4042290939935999E-3</v>
       </c>
       <c r="D678" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.3">
@@ -10451,7 +10464,7 @@
         <v>1.3686915007731081E-3</v>
       </c>
       <c r="D679" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.3">
@@ -10465,7 +10478,7 @@
         <v>1.1910730992050361E-3</v>
       </c>
       <c r="D680" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.3">
@@ -10479,7 +10492,7 @@
         <v>8.9563950810588088E-4</v>
       </c>
       <c r="D681" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.3">
@@ -10493,7 +10506,7 @@
         <v>8.562499066598118E-4</v>
       </c>
       <c r="D682" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.3">
@@ -10507,7 +10520,7 @@
         <v>8.5522676333473575E-4</v>
       </c>
       <c r="D683" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.3">
@@ -10521,7 +10534,7 @@
         <v>7.7758084806009117E-4</v>
       </c>
       <c r="D684" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.3">
@@ -10535,7 +10548,7 @@
         <v>6.7022896999062681E-4</v>
       </c>
       <c r="D685" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.3">
@@ -10549,7 +10562,7 @@
         <v>5.4706038813246902E-4</v>
       </c>
       <c r="D686" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.3">
@@ -10563,7 +10576,7 @@
         <v>5.3133932821454032E-4</v>
       </c>
       <c r="D687" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.3">
@@ -10577,7 +10590,7 @@
         <v>3.5767437891147109E-4</v>
       </c>
       <c r="D688" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.3">
@@ -10591,7 +10604,7 @@
         <v>2.6064089645531279E-4</v>
       </c>
       <c r="D689" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.3">
@@ -10605,7 +10618,7 @@
         <v>2.3632020817043121E-4</v>
       </c>
       <c r="D690" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.3">
@@ -10619,7 +10632,7 @@
         <v>2.2756406629566829E-4</v>
       </c>
       <c r="D691" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.3">
@@ -10633,7 +10646,7 @@
         <v>2.063968675864056E-4</v>
       </c>
       <c r="D692" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.3">
@@ -10647,7 +10660,7 @@
         <v>8.6544080946863555E-5</v>
       </c>
       <c r="D693" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.3">
@@ -10661,7 +10674,7 @@
         <v>7.3947525828196403E-5</v>
       </c>
       <c r="D694" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.3">
@@ -10675,7 +10688,7 @@
         <v>6.1574145989571333E-5</v>
       </c>
       <c r="D695" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.3">
@@ -10689,7 +10702,7 @@
         <v>5.0435497807865981E-5</v>
       </c>
       <c r="D696" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.3">
@@ -10703,7 +10716,7 @@
         <v>4.7861698403744547E-5</v>
       </c>
       <c r="D697" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.3">
@@ -10717,7 +10730,7 @@
         <v>3.9433075932780361E-5</v>
       </c>
       <c r="D698" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.3">
@@ -10731,7 +10744,7 @@
         <v>3.0543605157903588E-5</v>
       </c>
       <c r="D699" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.3">
@@ -10745,7 +10758,7 @@
         <v>2.55583146704823E-5</v>
       </c>
       <c r="D700" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.3">
@@ -10759,7 +10772,7 @@
         <v>2.3314932076665311E-5</v>
       </c>
       <c r="D701" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.3">
@@ -10773,7 +10786,7 @@
         <v>1.9573065465681121E-5</v>
       </c>
       <c r="D702" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.3">
@@ -10787,7 +10800,7 @@
         <v>1.7434026995620701E-5</v>
       </c>
       <c r="D703" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.3">
@@ -10801,7 +10814,7 @@
         <v>1.281683567002832E-5</v>
       </c>
       <c r="D704" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.3">
@@ -10815,7 +10828,7 @@
         <v>9.7039285302644482E-6</v>
       </c>
       <c r="D705" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.3">
@@ -10829,7 +10842,7 @@
         <v>3.6607124505734091E-6</v>
       </c>
       <c r="D706" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.3">
@@ -10843,7 +10856,7 @@
         <v>2.8781368780488909E-6</v>
       </c>
       <c r="D707" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.3">
@@ -10857,7 +10870,7 @@
         <v>2.5274275109044561E-6</v>
       </c>
       <c r="D708" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.3">
@@ -10871,7 +10884,7 @@
         <v>1.562251060718379E-6</v>
       </c>
       <c r="D709" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.3">
@@ -10885,7 +10898,7 @@
         <v>1.4984866949920699E-6</v>
       </c>
       <c r="D710" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.3">
@@ -10899,7 +10912,7 @@
         <v>8.9851200012911076E-7</v>
       </c>
       <c r="D711" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.3">
@@ -10913,7 +10926,7 @@
         <v>8.6372973293529944E-7</v>
       </c>
       <c r="D712" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.3">
@@ -10927,7 +10940,7 @@
         <v>5.3041283830020364E-7</v>
       </c>
       <c r="D713" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.3">
@@ -10941,7 +10954,7 @@
         <v>4.8113818292771003E-7</v>
       </c>
       <c r="D714" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.3">
@@ -10955,7 +10968,7 @@
         <v>4.5795089740679151E-7</v>
       </c>
       <c r="D715" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.3">
@@ -10969,7 +10982,7 @@
         <v>4.1447373287074422E-7</v>
       </c>
       <c r="D716" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.3">
@@ -10983,7 +10996,7 @@
         <v>3.7969414350179971E-7</v>
       </c>
       <c r="D717" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.3">
@@ -10997,7 +11010,7 @@
         <v>2.3767034604563191E-7</v>
       </c>
       <c r="D718" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.3">
@@ -11011,7 +11024,7 @@
         <v>1.3912371312551129E-7</v>
       </c>
       <c r="D719" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.3">
@@ -11025,7 +11038,7 @@
         <v>1.3622630661972151E-7</v>
       </c>
       <c r="D720" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.3">
@@ -11039,7 +11052,7 @@
         <v>4.9271977547626913E-8</v>
       </c>
       <c r="D721" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.3">
@@ -11053,7 +11066,7 @@
         <v>4.9271977547626913E-8</v>
       </c>
       <c r="D722" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.3">
@@ -11067,7 +11080,7 @@
         <v>2.0289879015128759E-8</v>
       </c>
       <c r="D723" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.3">
@@ -11081,7 +11094,7 @@
         <v>1.449238817868244E-8</v>
       </c>
       <c r="D724" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.3">
@@ -11095,7 +11108,7 @@
         <v>5.797490836446318E-9</v>
       </c>
       <c r="D725" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.3">
@@ -11109,7 +11122,7 @@
         <v>0.36728334255326378</v>
       </c>
       <c r="D726" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.3">
@@ -11123,7 +11136,7 @@
         <v>0.2133516813066112</v>
       </c>
       <c r="D727" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.3">
@@ -11137,7 +11150,7 @@
         <v>0.1459925915679362</v>
       </c>
       <c r="D728" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.3">
@@ -11151,7 +11164,7 @@
         <v>7.8988223811419622E-2</v>
       </c>
       <c r="D729" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.3">
@@ -11165,7 +11178,7 @@
         <v>2.7226261589560079E-2</v>
       </c>
       <c r="D730" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.3">
@@ -11179,7 +11192,7 @@
         <v>2.4074827646465471E-2</v>
       </c>
       <c r="D731" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.3">
@@ -11193,7 +11206,7 @@
         <v>2.163262076832291E-2</v>
       </c>
       <c r="D732" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="733" spans="1:4" x14ac:dyDescent="0.3">
@@ -11207,7 +11220,7 @@
         <v>1.650001907277646E-2</v>
       </c>
       <c r="D733" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="734" spans="1:4" x14ac:dyDescent="0.3">
@@ -11221,7 +11234,7 @@
         <v>1.543930972515787E-2</v>
       </c>
       <c r="D734" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.3">
@@ -11235,7 +11248,7 @@
         <v>1.3282628120341261E-2</v>
       </c>
       <c r="D735" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.3">
@@ -11249,7 +11262,7 @@
         <v>1.3199150414694209E-2</v>
       </c>
       <c r="D736" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.3">
@@ -11263,7 +11276,7 @@
         <v>1.0652795425041439E-2</v>
       </c>
       <c r="D737" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="738" spans="1:4" x14ac:dyDescent="0.3">
@@ -11277,7 +11290,7 @@
         <v>9.8103621527081478E-3</v>
       </c>
       <c r="D738" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.3">
@@ -11291,7 +11304,7 @@
         <v>7.7001531949237086E-3</v>
       </c>
       <c r="D739" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.3">
@@ -11305,7 +11318,7 @@
         <v>7.1128233790254012E-3</v>
       </c>
       <c r="D740" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="741" spans="1:4" x14ac:dyDescent="0.3">
@@ -11319,7 +11332,7 @@
         <v>3.7711377064092132E-3</v>
       </c>
       <c r="D741" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.3">
@@ -11333,7 +11346,7 @@
         <v>2.7568663929973271E-3</v>
       </c>
       <c r="D742" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.3">
@@ -11347,7 +11360,7 @@
         <v>2.1522443220296128E-3</v>
       </c>
       <c r="D743" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.3">
@@ -11361,7 +11374,7 @@
         <v>2.075460614457863E-3</v>
       </c>
       <c r="D744" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.3">
@@ -11375,7 +11388,7 @@
         <v>2.0121756679155351E-3</v>
       </c>
       <c r="D745" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.3">
@@ -11389,7 +11402,7 @@
         <v>1.930181672711194E-3</v>
       </c>
       <c r="D746" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.3">
@@ -11403,7 +11416,7 @@
         <v>1.7076067616770289E-3</v>
       </c>
       <c r="D747" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.3">
@@ -11417,7 +11430,7 @@
         <v>1.432525143096941E-3</v>
       </c>
       <c r="D748" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.3">
@@ -11431,7 +11444,7 @@
         <v>1.421557691158699E-3</v>
       </c>
       <c r="D749" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.3">
@@ -11445,7 +11458,7 @@
         <v>1.067943298096382E-3</v>
       </c>
       <c r="D750" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.3">
@@ -11459,7 +11472,7 @@
         <v>9.579503390142487E-4</v>
       </c>
       <c r="D751" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.3">
@@ -11473,7 +11486,7 @@
         <v>9.2983138784553802E-4</v>
       </c>
       <c r="D752" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.3">
@@ -11487,7 +11500,7 @@
         <v>7.1159454085546346E-4</v>
       </c>
       <c r="D753" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.3">
@@ -11501,7 +11514,7 @@
         <v>6.5437134338177576E-4</v>
       </c>
       <c r="D754" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.3">
@@ -11515,7 +11528,7 @@
         <v>5.4788805999279855E-4</v>
       </c>
       <c r="D755" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.3">
@@ -11529,7 +11542,7 @@
         <v>4.9943328721147073E-4</v>
       </c>
       <c r="D756" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.3">
@@ -11543,7 +11556,7 @@
         <v>4.6127679786730678E-4</v>
       </c>
       <c r="D757" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.3">
@@ -11557,7 +11570,7 @@
         <v>4.5987846402190688E-4</v>
       </c>
       <c r="D758" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.3">
@@ -11571,7 +11584,7 @@
         <v>4.3466693689538202E-4</v>
       </c>
       <c r="D759" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.3">
@@ -11585,7 +11598,7 @@
         <v>4.2646384649143502E-4</v>
       </c>
       <c r="D760" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.3">
@@ -11599,7 +11612,7 @@
         <v>3.0155764371994111E-4</v>
       </c>
       <c r="D761" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.3">
@@ -11613,7 +11626,7 @@
         <v>2.3607597446882831E-4</v>
       </c>
       <c r="D762" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.3">
@@ -11627,7 +11640,7 @@
         <v>1.8470224003682819E-4</v>
       </c>
       <c r="D763" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.3">
@@ -11641,7 +11654,7 @@
         <v>1.185029451817368E-4</v>
       </c>
       <c r="D764" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.3">
@@ -11655,7 +11668,7 @@
         <v>8.1031777416903385E-5</v>
       </c>
       <c r="D765" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.3">
@@ -11669,7 +11682,7 @@
         <v>7.9365776171072289E-5</v>
       </c>
       <c r="D766" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.3">
@@ -11683,7 +11696,7 @@
         <v>6.4177942942559625E-5</v>
       </c>
       <c r="D767" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.3">
@@ -11697,7 +11710,7 @@
         <v>5.5681801120396967E-5</v>
       </c>
       <c r="D768" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.3">
@@ -11711,7 +11724,7 @@
         <v>4.9723888396278131E-5</v>
       </c>
       <c r="D769" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.3">
@@ -11725,7 +11738,7 @@
         <v>4.9675431293377431E-5</v>
       </c>
       <c r="D770" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="771" spans="1:4" x14ac:dyDescent="0.3">
@@ -11739,7 +11752,7 @@
         <v>4.9068562040784578E-5</v>
       </c>
       <c r="D771" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="772" spans="1:4" x14ac:dyDescent="0.3">
@@ -11753,7 +11766,7 @@
         <v>3.361767688160668E-5</v>
       </c>
       <c r="D772" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="773" spans="1:4" x14ac:dyDescent="0.3">
@@ -11767,7 +11780,7 @@
         <v>1.3334927841656E-5</v>
       </c>
       <c r="D773" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="774" spans="1:4" x14ac:dyDescent="0.3">
@@ -11781,7 +11794,7 @@
         <v>1.008599527835406E-5</v>
       </c>
       <c r="D774" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="775" spans="1:4" x14ac:dyDescent="0.3">
@@ -11795,7 +11808,7 @@
         <v>9.7929459919952014E-6</v>
       </c>
       <c r="D775" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="776" spans="1:4" x14ac:dyDescent="0.3">
@@ -11809,7 +11822,7 @@
         <v>2.8405071920778711E-6</v>
       </c>
       <c r="D776" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="777" spans="1:4" x14ac:dyDescent="0.3">
@@ -11823,7 +11836,7 @@
         <v>1.01067702219426E-6</v>
       </c>
       <c r="D777" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="778" spans="1:4" x14ac:dyDescent="0.3">
@@ -11837,7 +11850,7 @@
         <v>7.1762560397869494E-7</v>
       </c>
       <c r="D778" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="779" spans="1:4" x14ac:dyDescent="0.3">
@@ -11851,7 +11864,7 @@
         <v>5.2149052342124773E-7</v>
       </c>
       <c r="D779" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="780" spans="1:4" x14ac:dyDescent="0.3">
@@ -11865,7 +11878,7 @@
         <v>2.5151432217872508E-7</v>
       </c>
       <c r="D780" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="781" spans="1:4" x14ac:dyDescent="0.3">
@@ -11879,7 +11892,7 @@
         <v>1.384491699815471E-7</v>
       </c>
       <c r="D781" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="782" spans="1:4" x14ac:dyDescent="0.3">
@@ -11893,7 +11906,7 @@
         <v>1.199894227744545E-7</v>
       </c>
       <c r="D782" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="783" spans="1:4" x14ac:dyDescent="0.3">
@@ -11907,7 +11920,7 @@
         <v>4.1534964180134622E-8</v>
       </c>
       <c r="D783" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="784" spans="1:4" x14ac:dyDescent="0.3">
@@ -11921,7 +11934,7 @@
         <v>3.9226163368807508E-8</v>
       </c>
       <c r="D784" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="785" spans="1:4" x14ac:dyDescent="0.3">
@@ -11935,7 +11948,7 @@
         <v>2.7690686738991349E-8</v>
       </c>
       <c r="D785" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="786" spans="1:4" x14ac:dyDescent="0.3">
@@ -11949,7 +11962,7 @@
         <v>2.5381885927664258E-8</v>
       </c>
       <c r="D786" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="787" spans="1:4" x14ac:dyDescent="0.3">
@@ -11963,7 +11976,7 @@
         <v>1.845974720709263E-8</v>
       </c>
       <c r="D787" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="788" spans="1:4" x14ac:dyDescent="0.3">
@@ -11977,7 +11990,7 @@
         <v>4.6154697659493644E-9</v>
       </c>
       <c r="D788" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="789" spans="1:4" x14ac:dyDescent="0.3">
@@ -11991,7 +12004,7 @@
         <v>2.3066689546222691E-9</v>
       </c>
       <c r="D789" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="790" spans="1:4" x14ac:dyDescent="0.3">
@@ -12005,7 +12018,7 @@
         <v>0.19389267234486021</v>
       </c>
       <c r="D790" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="791" spans="1:4" x14ac:dyDescent="0.3">
@@ -12019,7 +12032,7 @@
         <v>0.15870780556683819</v>
       </c>
       <c r="D791" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="792" spans="1:4" x14ac:dyDescent="0.3">
@@ -12033,7 +12046,7 @@
         <v>0.106662942147218</v>
       </c>
       <c r="D792" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="793" spans="1:4" x14ac:dyDescent="0.3">
@@ -12047,7 +12060,7 @@
         <v>9.921777319410334E-2</v>
       </c>
       <c r="D793" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="794" spans="1:4" x14ac:dyDescent="0.3">
@@ -12061,7 +12074,7 @@
         <v>7.0198696465555058E-2</v>
       </c>
       <c r="D794" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="795" spans="1:4" x14ac:dyDescent="0.3">
@@ -12075,7 +12088,7 @@
         <v>5.042597054702401E-2</v>
       </c>
       <c r="D795" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="796" spans="1:4" x14ac:dyDescent="0.3">
@@ -12089,7 +12102,7 @@
         <v>4.9963159247655937E-2</v>
       </c>
       <c r="D796" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="797" spans="1:4" x14ac:dyDescent="0.3">
@@ -12103,7 +12116,7 @@
         <v>4.7801099917873811E-2</v>
       </c>
       <c r="D797" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="798" spans="1:4" x14ac:dyDescent="0.3">
@@ -12117,7 +12130,7 @@
         <v>3.9507092206462008E-2</v>
       </c>
       <c r="D798" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="799" spans="1:4" x14ac:dyDescent="0.3">
@@ -12131,7 +12144,7 @@
         <v>3.5757959341955768E-2</v>
       </c>
       <c r="D799" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="800" spans="1:4" x14ac:dyDescent="0.3">
@@ -12145,7 +12158,7 @@
         <v>3.5126907795650787E-2</v>
       </c>
       <c r="D800" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="801" spans="1:4" x14ac:dyDescent="0.3">
@@ -12159,7 +12172,7 @@
         <v>3.0667551503928071E-2</v>
       </c>
       <c r="D801" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.3">
@@ -12173,7 +12186,7 @@
         <v>2.1333035920436609E-2</v>
       </c>
       <c r="D802" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="803" spans="1:4" x14ac:dyDescent="0.3">
@@ -12187,7 +12200,7 @@
         <v>1.7701542139876739E-2</v>
       </c>
       <c r="D803" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="804" spans="1:4" x14ac:dyDescent="0.3">
@@ -12201,7 +12214,7 @@
         <v>1.3401626820984889E-2</v>
       </c>
       <c r="D804" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="805" spans="1:4" x14ac:dyDescent="0.3">
@@ -12215,7 +12228,7 @@
         <v>9.28537738176256E-3</v>
       </c>
       <c r="D805" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="806" spans="1:4" x14ac:dyDescent="0.3">
@@ -12229,7 +12242,7 @@
         <v>7.785651073983324E-3</v>
       </c>
       <c r="D806" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.3">
@@ -12243,7 +12256,7 @@
         <v>3.6118083827668202E-3</v>
       </c>
       <c r="D807" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.3">
@@ -12257,7 +12270,7 @@
         <v>2.5451824124775408E-3</v>
       </c>
       <c r="D808" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="809" spans="1:4" x14ac:dyDescent="0.3">
@@ -12271,7 +12284,7 @@
         <v>1.904836782718311E-3</v>
       </c>
       <c r="D809" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.3">
@@ -12285,7 +12298,7 @@
         <v>1.897586515895759E-3</v>
       </c>
       <c r="D810" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="811" spans="1:4" x14ac:dyDescent="0.3">
@@ -12299,7 +12312,7 @@
         <v>4.2034244946168828E-4</v>
       </c>
       <c r="D811" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="812" spans="1:4" x14ac:dyDescent="0.3">
@@ -12313,7 +12326,7 @@
         <v>3.5394994323812459E-4</v>
       </c>
       <c r="D812" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="813" spans="1:4" x14ac:dyDescent="0.3">
@@ -12327,7 +12340,7 @@
         <v>3.2025888077813431E-4</v>
       </c>
       <c r="D813" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="814" spans="1:4" x14ac:dyDescent="0.3">
@@ -12341,7 +12354,7 @@
         <v>2.7432626605103871E-4</v>
       </c>
       <c r="D814" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="815" spans="1:4" x14ac:dyDescent="0.3">
@@ -12355,7 +12368,7 @@
         <v>2.1841112018813891E-4</v>
       </c>
       <c r="D815" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.3">
@@ -12369,7 +12382,7 @@
         <v>2.0474967936197209E-4</v>
       </c>
       <c r="D816" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="817" spans="1:4" x14ac:dyDescent="0.3">
@@ -12383,7 +12396,7 @@
         <v>2.028994613103132E-4</v>
       </c>
       <c r="D817" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="818" spans="1:4" x14ac:dyDescent="0.3">
@@ -12397,7 +12410,7 @@
         <v>1.5442820072665781E-4</v>
       </c>
       <c r="D818" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="819" spans="1:4" x14ac:dyDescent="0.3">
@@ -12411,7 +12424,7 @@
         <v>1.174239589533852E-4</v>
       </c>
       <c r="D819" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="820" spans="1:4" x14ac:dyDescent="0.3">
@@ -12425,7 +12438,7 @@
         <v>1.1101274519646861E-4</v>
       </c>
       <c r="D820" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.3">
@@ -12439,7 +12452,7 @@
         <v>5.7722330965299018E-5</v>
       </c>
       <c r="D821" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.3">
@@ -12453,7 +12466,7 @@
         <v>5.2795604882960992E-5</v>
       </c>
       <c r="D822" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.3">
@@ -12467,7 +12480,7 @@
         <v>4.03389276228591E-5</v>
       </c>
       <c r="D823" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="824" spans="1:4" x14ac:dyDescent="0.3">
@@ -12481,7 +12494,7 @@
         <v>3.5713412308688217E-5</v>
       </c>
       <c r="D824" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="825" spans="1:4" x14ac:dyDescent="0.3">
@@ -12495,7 +12508,7 @@
         <v>1.555469182708541E-5</v>
       </c>
       <c r="D825" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="826" spans="1:4" x14ac:dyDescent="0.3">
@@ -12509,7 +12522,7 @@
         <v>5.1203644156813231E-6</v>
       </c>
       <c r="D826" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="827" spans="1:4" x14ac:dyDescent="0.3">
@@ -12523,7 +12536,7 @@
         <v>4.8406800604695004E-6</v>
       </c>
       <c r="D827" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="828" spans="1:4" x14ac:dyDescent="0.3">
@@ -12537,7 +12550,7 @@
         <v>3.141067392894168E-6</v>
       </c>
       <c r="D828" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="829" spans="1:4" x14ac:dyDescent="0.3">
@@ -12551,7 +12564,7 @@
         <v>2.4525998346913479E-6</v>
       </c>
       <c r="D829" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="830" spans="1:4" x14ac:dyDescent="0.3">
@@ -12565,7 +12578,7 @@
         <v>2.2374748416945779E-6</v>
       </c>
       <c r="D830" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="831" spans="1:4" x14ac:dyDescent="0.3">
@@ -12579,7 +12592,7 @@
         <v>1.957790486482756E-6</v>
       </c>
       <c r="D831" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="832" spans="1:4" x14ac:dyDescent="0.3">
@@ -12593,7 +12606,7 @@
         <v>1.6350731820112081E-6</v>
       </c>
       <c r="D832" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="833" spans="1:4" x14ac:dyDescent="0.3">
@@ -12607,7 +12620,7 @@
         <v>1.2693229282799351E-6</v>
       </c>
       <c r="D833" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="834" spans="1:4" x14ac:dyDescent="0.3">
@@ -12621,7 +12634,7 @@
         <v>1.097211007891962E-6</v>
       </c>
       <c r="D834" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="835" spans="1:4" x14ac:dyDescent="0.3">
@@ -12635,7 +12648,7 @@
         <v>4.3032949259725328E-8</v>
       </c>
       <c r="D835" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="836" spans="1:4" x14ac:dyDescent="0.3">
@@ -14175,7 +14188,7 @@
         <v>0.61725284035848527</v>
       </c>
       <c r="D945" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="946" spans="1:4" x14ac:dyDescent="0.3">
@@ -14189,7 +14202,7 @@
         <v>0.1799369151172065</v>
       </c>
       <c r="D946" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="947" spans="1:4" x14ac:dyDescent="0.3">
@@ -14203,7 +14216,7 @@
         <v>0.1231618365617011</v>
       </c>
       <c r="D947" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="948" spans="1:4" x14ac:dyDescent="0.3">
@@ -14217,7 +14230,7 @@
         <v>4.9838967971444319E-2</v>
       </c>
       <c r="D948" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="949" spans="1:4" x14ac:dyDescent="0.3">
@@ -14231,7 +14244,7 @@
         <v>2.240497000595278E-2</v>
       </c>
       <c r="D949" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="950" spans="1:4" x14ac:dyDescent="0.3">
@@ -14245,7 +14258,7 @@
         <v>1.63118144133721E-3</v>
       </c>
       <c r="D950" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="951" spans="1:4" x14ac:dyDescent="0.3">
@@ -14259,7 +14272,7 @@
         <v>1.5760015362803099E-3</v>
       </c>
       <c r="D951" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="952" spans="1:4" x14ac:dyDescent="0.3">
@@ -14273,7 +14286,7 @@
         <v>1.1103341512009729E-3</v>
       </c>
       <c r="D952" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="953" spans="1:4" x14ac:dyDescent="0.3">
@@ -14287,7 +14300,7 @@
         <v>9.0127703261453545E-4</v>
       </c>
       <c r="D953" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="954" spans="1:4" x14ac:dyDescent="0.3">
@@ -14301,7 +14314,7 @@
         <v>7.4605484723818663E-4</v>
       </c>
       <c r="D954" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="955" spans="1:4" x14ac:dyDescent="0.3">
@@ -14315,7 +14328,7 @@
         <v>5.4013820682841671E-4</v>
       </c>
       <c r="D955" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="956" spans="1:4" x14ac:dyDescent="0.3">
@@ -14329,7 +14342,7 @@
         <v>3.1986580528270089E-4</v>
       </c>
       <c r="D956" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="957" spans="1:4" x14ac:dyDescent="0.3">
@@ -14343,7 +14356,7 @@
         <v>1.9694408246223079E-4</v>
       </c>
       <c r="D957" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="958" spans="1:4" x14ac:dyDescent="0.3">
@@ -14357,7 +14370,7 @@
         <v>1.2471640020003609E-4</v>
       </c>
       <c r="D958" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="959" spans="1:4" x14ac:dyDescent="0.3">
@@ -14371,7 +14384,7 @@
         <v>9.2864399751476208E-5</v>
       </c>
       <c r="D959" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="960" spans="1:4" x14ac:dyDescent="0.3">
@@ -14385,7 +14398,7 @@
         <v>8.120024020973365E-5</v>
       </c>
       <c r="D960" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="961" spans="1:4" x14ac:dyDescent="0.3">
@@ -14399,7 +14412,7 @@
         <v>4.8899363178709553E-5</v>
       </c>
       <c r="D961" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="962" spans="1:4" x14ac:dyDescent="0.3">
@@ -14413,7 +14426,7 @@
         <v>1.6598900622830849E-5</v>
       </c>
       <c r="D962" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="963" spans="1:4" x14ac:dyDescent="0.3">
@@ -14427,7 +14440,7 @@
         <v>4.9347410810882953E-6</v>
       </c>
       <c r="D963" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="964" spans="1:4" x14ac:dyDescent="0.3">
@@ -14441,7 +14454,7 @@
         <v>4.0374023913053143E-6</v>
       </c>
       <c r="D964" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="965" spans="1:4" x14ac:dyDescent="0.3">
@@ -14455,7 +14468,7 @@
         <v>2.2431394868847509E-6</v>
       </c>
       <c r="D965" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="966" spans="1:4" x14ac:dyDescent="0.3">
@@ -14469,7 +14482,7 @@
         <v>2.2431394868847509E-6</v>
       </c>
       <c r="D966" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="967" spans="1:4" x14ac:dyDescent="0.3">
@@ -14483,7 +14496,7 @@
         <v>1.345800797101772E-6</v>
       </c>
       <c r="D967" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="968" spans="1:4" x14ac:dyDescent="0.3">
@@ -14497,7 +14510,7 @@
         <v>8.9733868978297981E-7</v>
       </c>
       <c r="D968" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="969" spans="1:4" x14ac:dyDescent="0.3">
@@ -14511,7 +14524,7 @@
         <v>8.9733868978297981E-7</v>
       </c>
       <c r="D969" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="970" spans="1:4" x14ac:dyDescent="0.3">
@@ -14525,7 +14538,7 @@
         <v>8.9733868978297981E-7</v>
       </c>
       <c r="D970" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="971" spans="1:4" x14ac:dyDescent="0.3">
@@ -14539,7 +14552,7 @@
         <v>8.9733868978297981E-7</v>
       </c>
       <c r="D971" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="972" spans="1:4" x14ac:dyDescent="0.3">
@@ -14553,7 +14566,7 @@
         <v>0.38987612982235631</v>
       </c>
       <c r="D972" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="973" spans="1:4" x14ac:dyDescent="0.3">
@@ -14567,7 +14580,7 @@
         <v>0.23514099695939419</v>
       </c>
       <c r="D973" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="974" spans="1:4" x14ac:dyDescent="0.3">
@@ -14581,7 +14594,7 @@
         <v>0.12878420651841499</v>
       </c>
       <c r="D974" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="975" spans="1:4" x14ac:dyDescent="0.3">
@@ -14595,7 +14608,7 @@
         <v>8.7785549978782823E-2</v>
       </c>
       <c r="D975" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="976" spans="1:4" x14ac:dyDescent="0.3">
@@ -14609,7 +14622,7 @@
         <v>6.0979662182137989E-2</v>
       </c>
       <c r="D976" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="977" spans="1:4" x14ac:dyDescent="0.3">
@@ -14623,7 +14636,7 @@
         <v>2.3789502986158811E-2</v>
       </c>
       <c r="D977" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="978" spans="1:4" x14ac:dyDescent="0.3">
@@ -14637,7 +14650,7 @@
         <v>2.3631778844105489E-2</v>
       </c>
       <c r="D978" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="979" spans="1:4" x14ac:dyDescent="0.3">
@@ -14651,7 +14664,7 @@
         <v>1.982701392775962E-2</v>
       </c>
       <c r="D979" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="980" spans="1:4" x14ac:dyDescent="0.3">
@@ -14665,7 +14678,7 @@
         <v>1.3085569110414971E-2</v>
       </c>
       <c r="D980" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="981" spans="1:4" x14ac:dyDescent="0.3">
@@ -14679,7 +14692,7 @@
         <v>9.1537820864604387E-3</v>
       </c>
       <c r="D981" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="982" spans="1:4" x14ac:dyDescent="0.3">
@@ -14693,7 +14706,7 @@
         <v>1.7598888642838971E-3</v>
       </c>
       <c r="D982" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="983" spans="1:4" x14ac:dyDescent="0.3">
@@ -14707,7 +14720,7 @@
         <v>1.721120074880505E-3</v>
       </c>
       <c r="D983" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="984" spans="1:4" x14ac:dyDescent="0.3">
@@ -14721,7 +14734,7 @@
         <v>1.462018940136184E-3</v>
       </c>
       <c r="D984" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="985" spans="1:4" x14ac:dyDescent="0.3">
@@ -14735,7 +14748,7 @@
         <v>9.6380318816659044E-4</v>
       </c>
       <c r="D985" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="986" spans="1:4" x14ac:dyDescent="0.3">
@@ -14749,7 +14762,7 @@
         <v>6.6773918752519935E-4</v>
       </c>
       <c r="D986" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="987" spans="1:4" x14ac:dyDescent="0.3">
@@ -14763,7 +14776,7 @@
         <v>4.8846343132615813E-4</v>
       </c>
       <c r="D987" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="988" spans="1:4" x14ac:dyDescent="0.3">
@@ -14777,7 +14790,7 @@
         <v>3.7239766752277068E-4</v>
       </c>
       <c r="D988" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="989" spans="1:4" x14ac:dyDescent="0.3">
@@ -14791,7 +14804,7 @@
         <v>3.3158201649697032E-4</v>
       </c>
       <c r="D989" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="990" spans="1:4" x14ac:dyDescent="0.3">
@@ -14805,7 +14818,7 @@
         <v>7.6333666881379657E-5</v>
       </c>
       <c r="D990" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="991" spans="1:4" x14ac:dyDescent="0.3">
@@ -14819,7 +14832,7 @@
         <v>6.622005030024559E-5</v>
       </c>
       <c r="D991" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="992" spans="1:4" x14ac:dyDescent="0.3">
@@ -14833,7 +14846,7 @@
         <v>1.6133621153883648E-5</v>
       </c>
       <c r="D992" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="993" spans="1:4" x14ac:dyDescent="0.3">
@@ -14847,7 +14860,7 @@
         <v>1.1919651323889141E-5</v>
       </c>
       <c r="D993" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="994" spans="1:4" x14ac:dyDescent="0.3">
@@ -14861,7 +14874,7 @@
         <v>3.130415726201874E-6</v>
       </c>
       <c r="D994" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="995" spans="1:4" x14ac:dyDescent="0.3">
@@ -14875,7 +14888,7 @@
         <v>2.1672194440192988E-6</v>
       </c>
       <c r="D995" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="996" spans="1:4" x14ac:dyDescent="0.3">
@@ -14889,7 +14902,7 @@
         <v>1.444850041490873E-6</v>
       </c>
       <c r="D996" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="997" spans="1:4" x14ac:dyDescent="0.3">
@@ -14903,7 +14916,7 @@
         <v>1.324380983446788E-6</v>
       </c>
       <c r="D997" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="998" spans="1:4" x14ac:dyDescent="0.3">
@@ -14917,7 +14930,7 @@
         <v>1.2035782161006429E-7</v>
       </c>
       <c r="D998" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="999" spans="1:4" x14ac:dyDescent="0.3">
@@ -14931,7 +14944,7 @@
         <v>0.14024276545471301</v>
       </c>
       <c r="D999" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1000" spans="1:4" x14ac:dyDescent="0.3">
@@ -14945,7 +14958,7 @@
         <v>0.13684941428237449</v>
       </c>
       <c r="D1000" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1001" spans="1:4" x14ac:dyDescent="0.3">
@@ -14959,7 +14972,7 @@
         <v>0.1281602123455754</v>
       </c>
       <c r="D1001" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1002" spans="1:4" x14ac:dyDescent="0.3">
@@ -14973,7 +14986,7 @@
         <v>7.0525250468071898E-2</v>
       </c>
       <c r="D1002" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1003" spans="1:4" x14ac:dyDescent="0.3">
@@ -14987,7 +15000,7 @@
         <v>6.8244672089354377E-2</v>
       </c>
       <c r="D1003" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1004" spans="1:4" x14ac:dyDescent="0.3">
@@ -15001,7 +15014,7 @@
         <v>5.5121196245682548E-2</v>
       </c>
       <c r="D1004" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1005" spans="1:4" x14ac:dyDescent="0.3">
@@ -15015,7 +15028,7 @@
         <v>5.2586117934460559E-2</v>
       </c>
       <c r="D1005" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1006" spans="1:4" x14ac:dyDescent="0.3">
@@ -15029,7 +15042,7 @@
         <v>4.9498684685453639E-2</v>
       </c>
       <c r="D1006" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1007" spans="1:4" x14ac:dyDescent="0.3">
@@ -15043,7 +15056,7 @@
         <v>4.8110020455253727E-2</v>
       </c>
       <c r="D1007" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1008" spans="1:4" x14ac:dyDescent="0.3">
@@ -15057,7 +15070,7 @@
         <v>4.2557631509372633E-2</v>
       </c>
       <c r="D1008" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1009" spans="1:4" x14ac:dyDescent="0.3">
@@ -15071,7 +15084,7 @@
         <v>4.1397325785461361E-2</v>
       </c>
       <c r="D1009" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1010" spans="1:4" x14ac:dyDescent="0.3">
@@ -15085,7 +15098,7 @@
         <v>2.508548382281775E-2</v>
       </c>
       <c r="D1010" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1011" spans="1:4" x14ac:dyDescent="0.3">
@@ -15099,7 +15112,7 @@
         <v>2.3313754405699261E-2</v>
       </c>
       <c r="D1011" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1012" spans="1:4" x14ac:dyDescent="0.3">
@@ -15113,7 +15126,7 @@
         <v>2.1654937373661219E-2</v>
       </c>
       <c r="D1012" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1013" spans="1:4" x14ac:dyDescent="0.3">
@@ -15127,7 +15140,7 @@
         <v>1.6719091400874991E-2</v>
       </c>
       <c r="D1013" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1014" spans="1:4" x14ac:dyDescent="0.3">
@@ -15141,7 +15154,7 @@
         <v>1.5799333155347189E-2</v>
       </c>
       <c r="D1014" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1015" spans="1:4" x14ac:dyDescent="0.3">
@@ -15155,7 +15168,7 @@
         <v>1.3839294058905049E-2</v>
       </c>
       <c r="D1015" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1016" spans="1:4" x14ac:dyDescent="0.3">
@@ -15169,7 +15182,7 @@
         <v>7.8963017741316768E-3</v>
       </c>
       <c r="D1016" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1017" spans="1:4" x14ac:dyDescent="0.3">
@@ -15183,7 +15196,7 @@
         <v>7.642353635149879E-3</v>
       </c>
       <c r="D1017" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1018" spans="1:4" x14ac:dyDescent="0.3">
@@ -15197,7 +15210,7 @@
         <v>6.9924351358630231E-3</v>
       </c>
       <c r="D1018" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1019" spans="1:4" x14ac:dyDescent="0.3">
@@ -15211,7 +15224,7 @@
         <v>3.9738114613409306E-3</v>
       </c>
       <c r="D1019" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1020" spans="1:4" x14ac:dyDescent="0.3">
@@ -15225,7 +15238,7 @@
         <v>3.3978015432415522E-3</v>
       </c>
       <c r="D1020" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1021" spans="1:4" x14ac:dyDescent="0.3">
@@ -15239,7 +15252,7 @@
         <v>2.370901081821356E-3</v>
       </c>
       <c r="D1021" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1022" spans="1:4" x14ac:dyDescent="0.3">
@@ -15253,7 +15266,7 @@
         <v>2.209766590523409E-3</v>
       </c>
       <c r="D1022" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1023" spans="1:4" x14ac:dyDescent="0.3">
@@ -15267,7 +15280,7 @@
         <v>1.903652722894982E-3</v>
       </c>
       <c r="D1023" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1024" spans="1:4" x14ac:dyDescent="0.3">
@@ -15281,7 +15294,7 @@
         <v>1.7581665980904769E-3</v>
       </c>
       <c r="D1024" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1025" spans="1:4" x14ac:dyDescent="0.3">
@@ -15295,7 +15308,7 @@
         <v>1.670064577597992E-3</v>
       </c>
       <c r="D1025" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1026" spans="1:4" x14ac:dyDescent="0.3">
@@ -15309,7 +15322,7 @@
         <v>1.632092288256369E-3</v>
       </c>
       <c r="D1026" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1027" spans="1:4" x14ac:dyDescent="0.3">
@@ -15323,7 +15336,7 @@
         <v>1.2708555369740969E-3</v>
       </c>
       <c r="D1027" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1028" spans="1:4" x14ac:dyDescent="0.3">
@@ -15337,7 +15350,7 @@
         <v>1.2424528942616951E-3</v>
       </c>
       <c r="D1028" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1029" spans="1:4" x14ac:dyDescent="0.3">
@@ -15351,7 +15364,7 @@
         <v>6.9829826109380161E-4</v>
       </c>
       <c r="D1029" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1030" spans="1:4" x14ac:dyDescent="0.3">
@@ -15365,7 +15378,7 @@
         <v>6.7847429266768282E-4</v>
       </c>
       <c r="D1030" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1031" spans="1:4" x14ac:dyDescent="0.3">
@@ -15379,7 +15392,7 @@
         <v>5.4855320476206735E-4</v>
       </c>
       <c r="D1031" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1032" spans="1:4" x14ac:dyDescent="0.3">
@@ -15393,7 +15406,7 @@
         <v>5.4280781159923993E-4</v>
       </c>
       <c r="D1032" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1033" spans="1:4" x14ac:dyDescent="0.3">
@@ -15407,7 +15420,7 @@
         <v>4.545008411293478E-4</v>
       </c>
       <c r="D1033" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1034" spans="1:4" x14ac:dyDescent="0.3">
@@ -15421,7 +15434,7 @@
         <v>3.0291122251618549E-4</v>
       </c>
       <c r="D1034" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1035" spans="1:4" x14ac:dyDescent="0.3">
@@ -15435,7 +15448,7 @@
         <v>2.9891354727716292E-4</v>
       </c>
       <c r="D1035" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1036" spans="1:4" x14ac:dyDescent="0.3">
@@ -15449,7 +15462,7 @@
         <v>2.704545982539602E-4</v>
       </c>
       <c r="D1036" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1037" spans="1:4" x14ac:dyDescent="0.3">
@@ -15463,7 +15476,7 @@
         <v>2.3891462450136879E-4</v>
       </c>
       <c r="D1037" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1038" spans="1:4" x14ac:dyDescent="0.3">
@@ -15477,7 +15490,7 @@
         <v>2.2244194901568671E-4</v>
       </c>
       <c r="D1038" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1039" spans="1:4" x14ac:dyDescent="0.3">
@@ -15491,7 +15504,7 @@
         <v>1.952757687512453E-4</v>
       </c>
       <c r="D1039" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1040" spans="1:4" x14ac:dyDescent="0.3">
@@ -15505,7 +15518,7 @@
         <v>1.8832319200591459E-4</v>
       </c>
       <c r="D1040" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1041" spans="1:4" x14ac:dyDescent="0.3">
@@ -15519,7 +15532,7 @@
         <v>1.797400127986084E-4</v>
       </c>
       <c r="D1041" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1042" spans="1:4" x14ac:dyDescent="0.3">
@@ -15533,7 +15546,7 @@
         <v>1.698415423082206E-4</v>
       </c>
       <c r="D1042" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1043" spans="1:4" x14ac:dyDescent="0.3">
@@ -15547,7 +15560,7 @@
         <v>1.673483442272979E-4</v>
       </c>
       <c r="D1043" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1044" spans="1:4" x14ac:dyDescent="0.3">
@@ -15561,7 +15574,7 @@
         <v>1.6466145535033391E-4</v>
       </c>
       <c r="D1044" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1045" spans="1:4" x14ac:dyDescent="0.3">
@@ -15575,7 +15588,7 @@
         <v>1.242229932923376E-4</v>
       </c>
       <c r="D1045" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1046" spans="1:4" x14ac:dyDescent="0.3">
@@ -15589,7 +15602,7 @@
         <v>1.1824337128664641E-4</v>
       </c>
       <c r="D1046" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1047" spans="1:4" x14ac:dyDescent="0.3">
@@ -15603,7 +15616,7 @@
         <v>1.139889425996448E-4</v>
       </c>
       <c r="D1047" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1048" spans="1:4" x14ac:dyDescent="0.3">
@@ -15617,7 +15630,7 @@
         <v>9.5872149888918178E-5</v>
       </c>
       <c r="D1048" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1049" spans="1:4" x14ac:dyDescent="0.3">
@@ -15631,7 +15644,7 @@
         <v>8.7757432528929536E-5</v>
       </c>
       <c r="D1049" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1050" spans="1:4" x14ac:dyDescent="0.3">
@@ -15645,7 +15658,7 @@
         <v>8.6552498285745233E-5</v>
       </c>
       <c r="D1050" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1051" spans="1:4" x14ac:dyDescent="0.3">
@@ -15659,7 +15672,7 @@
         <v>8.4640370512151466E-5</v>
       </c>
       <c r="D1051" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1052" spans="1:4" x14ac:dyDescent="0.3">
@@ -15673,7 +15686,7 @@
         <v>8.2809322993792641E-5</v>
       </c>
       <c r="D1052" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1053" spans="1:4" x14ac:dyDescent="0.3">
@@ -15687,7 +15700,7 @@
         <v>6.9079838534285282E-5</v>
       </c>
       <c r="D1053" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1054" spans="1:4" x14ac:dyDescent="0.3">
@@ -15701,7 +15714,7 @@
         <v>5.4140919072160418E-5</v>
       </c>
       <c r="D1054" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1055" spans="1:4" x14ac:dyDescent="0.3">
@@ -15715,7 +15728,7 @@
         <v>4.6800960734747067E-5</v>
       </c>
       <c r="D1055" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1056" spans="1:4" x14ac:dyDescent="0.3">
@@ -15729,7 +15742,7 @@
         <v>2.3481560622608471E-5</v>
       </c>
       <c r="D1056" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1057" spans="1:4" x14ac:dyDescent="0.3">
@@ -15743,7 +15756,7 @@
         <v>1.5641610152306201E-5</v>
       </c>
       <c r="D1057" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1058" spans="1:4" x14ac:dyDescent="0.3">
@@ -15757,7 +15770,7 @@
         <v>4.6598258015864777E-6</v>
       </c>
       <c r="D1058" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1059" spans="1:4" x14ac:dyDescent="0.3">
@@ -15771,7 +15784,7 @@
         <v>1.8175348360846361E-6</v>
       </c>
       <c r="D1059" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1060" spans="1:4" x14ac:dyDescent="0.3">
@@ -15785,7 +15798,7 @@
         <v>1.2342110278467249E-6</v>
       </c>
       <c r="D1060" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1061" spans="1:4" x14ac:dyDescent="0.3">
@@ -15799,7 +15812,7 @@
         <v>7.9052728655337729E-7</v>
       </c>
       <c r="D1061" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1062" spans="1:4" x14ac:dyDescent="0.3">
@@ -15813,7 +15826,7 @@
         <v>5.3602733948334866E-7</v>
       </c>
       <c r="D1062" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1063" spans="1:4" x14ac:dyDescent="0.3">
@@ -15827,7 +15840,7 @@
         <v>2.0720347831546651E-7</v>
       </c>
       <c r="D1063" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1064" spans="1:4" x14ac:dyDescent="0.3">
@@ -15841,7 +15854,7 @@
         <v>1.3738448524064989E-7</v>
       </c>
       <c r="D1064" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1065" spans="1:4" x14ac:dyDescent="0.3">
@@ -15855,7 +15868,7 @@
         <v>7.4323914097853432E-8</v>
       </c>
       <c r="D1065" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1066" spans="1:4" x14ac:dyDescent="0.3">
@@ -15869,7 +15882,7 @@
         <v>9.0098420460736692E-9</v>
       </c>
       <c r="D1066" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1067" spans="1:4" x14ac:dyDescent="0.3">
@@ -15883,7 +15896,7 @@
         <v>0.7779850553408888</v>
       </c>
       <c r="D1067" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1068" spans="1:4" x14ac:dyDescent="0.3">
@@ -15897,7 +15910,7 @@
         <v>8.9451268003513273E-2</v>
       </c>
       <c r="D1068" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1069" spans="1:4" x14ac:dyDescent="0.3">
@@ -15911,7 +15924,7 @@
         <v>5.9967797154663778E-2</v>
       </c>
       <c r="D1069" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1070" spans="1:4" x14ac:dyDescent="0.3">
@@ -15925,7 +15938,7 @@
         <v>2.8634714418190429E-2</v>
       </c>
       <c r="D1070" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1071" spans="1:4" x14ac:dyDescent="0.3">
@@ -15939,7 +15952,7 @@
         <v>1.9582588524514982E-2</v>
       </c>
       <c r="D1071" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1072" spans="1:4" x14ac:dyDescent="0.3">
@@ -15953,7 +15966,7 @@
         <v>1.280724770347156E-2</v>
       </c>
       <c r="D1072" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1073" spans="1:4" x14ac:dyDescent="0.3">
@@ -15967,7 +15980,7 @@
         <v>4.4091199803535071E-3</v>
       </c>
       <c r="D1073" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1074" spans="1:4" x14ac:dyDescent="0.3">
@@ -15981,7 +15994,7 @@
         <v>1.8131318661856249E-3</v>
       </c>
       <c r="D1074" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1075" spans="1:4" x14ac:dyDescent="0.3">
@@ -15995,7 +16008,7 @@
         <v>1.7263440213611679E-3</v>
       </c>
       <c r="D1075" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1076" spans="1:4" x14ac:dyDescent="0.3">
@@ -16009,7 +16022,7 @@
         <v>1.2262102498667559E-3</v>
       </c>
       <c r="D1076" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1077" spans="1:4" x14ac:dyDescent="0.3">
@@ -16023,7 +16036,7 @@
         <v>7.2931258738663084E-4</v>
       </c>
       <c r="D1077" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1078" spans="1:4" x14ac:dyDescent="0.3">
@@ -16037,7 +16050,7 @@
         <v>6.9253820125308129E-4</v>
       </c>
       <c r="D1078" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1079" spans="1:4" x14ac:dyDescent="0.3">
@@ -16051,7 +16064,7 @@
         <v>2.9860920047374072E-4</v>
       </c>
       <c r="D1079" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1080" spans="1:4" x14ac:dyDescent="0.3">
@@ -16065,7 +16078,7 @@
         <v>2.5389131644479811E-4</v>
       </c>
       <c r="D1080" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1081" spans="1:4" x14ac:dyDescent="0.3">
@@ -16079,7 +16092,7 @@
         <v>1.5562977182023011E-4</v>
       </c>
       <c r="D1081" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1082" spans="1:4" x14ac:dyDescent="0.3">
@@ -16093,7 +16106,7 @@
         <v>1.097352444246783E-4</v>
       </c>
       <c r="D1082" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1083" spans="1:4" x14ac:dyDescent="0.3">
@@ -16107,7 +16120,7 @@
         <v>9.7084901257958665E-5</v>
       </c>
       <c r="D1083" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1084" spans="1:4" x14ac:dyDescent="0.3">
@@ -16121,7 +16134,7 @@
         <v>2.7066059090687389E-5</v>
       </c>
       <c r="D1084" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1085" spans="1:4" x14ac:dyDescent="0.3">
@@ -16135,7 +16148,7 @@
         <v>2.088793395254256E-5</v>
       </c>
       <c r="D1085" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1086" spans="1:4" x14ac:dyDescent="0.3">
@@ -16149,7 +16162,7 @@
         <v>5.5896675523954484E-6</v>
       </c>
       <c r="D1086" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1087" spans="1:4" x14ac:dyDescent="0.3">
@@ -16163,7 +16176,7 @@
         <v>3.8245666000367779E-6</v>
       </c>
       <c r="D1087" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1088" spans="1:4" x14ac:dyDescent="0.3">
@@ -16177,7 +16190,7 @@
         <v>1.765100952358669E-6</v>
       </c>
       <c r="D1088" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1089" spans="1:4" x14ac:dyDescent="0.3">
@@ -16191,7 +16204,7 @@
         <v>2.9409289042994769E-7</v>
       </c>
       <c r="D1089" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1090" spans="1:4" x14ac:dyDescent="0.3">
@@ -16205,7 +16218,7 @@
         <v>2.9409289042994769E-7</v>
       </c>
       <c r="D1090" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1091" spans="1:4" x14ac:dyDescent="0.3">
@@ -16219,7 +16232,7 @@
         <v>0.14260123545571449</v>
       </c>
       <c r="D1091" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1092" spans="1:4" x14ac:dyDescent="0.3">
@@ -16233,7 +16246,7 @@
         <v>0.1362865141683183</v>
       </c>
       <c r="D1092" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1093" spans="1:4" x14ac:dyDescent="0.3">
@@ -16247,7 +16260,7 @@
         <v>0.1163788860918752</v>
       </c>
       <c r="D1093" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1094" spans="1:4" x14ac:dyDescent="0.3">
@@ -16261,7 +16274,7 @@
         <v>8.3123682376212413E-2</v>
       </c>
       <c r="D1094" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1095" spans="1:4" x14ac:dyDescent="0.3">
@@ -16275,7 +16288,7 @@
         <v>7.1473815480432065E-2</v>
       </c>
       <c r="D1095" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1096" spans="1:4" x14ac:dyDescent="0.3">
@@ -16289,7 +16302,7 @@
         <v>7.0018099396109035E-2</v>
       </c>
       <c r="D1096" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1097" spans="1:4" x14ac:dyDescent="0.3">
@@ -16303,7 +16316,7 @@
         <v>4.4794654916189093E-2</v>
       </c>
       <c r="D1097" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1098" spans="1:4" x14ac:dyDescent="0.3">
@@ -16317,7 +16330,7 @@
         <v>4.2973449687317512E-2</v>
       </c>
       <c r="D1098" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1099" spans="1:4" x14ac:dyDescent="0.3">
@@ -16331,7 +16344,7 @@
         <v>4.1166072526058167E-2</v>
       </c>
       <c r="D1099" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1100" spans="1:4" x14ac:dyDescent="0.3">
@@ -16345,7 +16358,7 @@
         <v>3.4083035880946903E-2</v>
       </c>
       <c r="D1100" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1101" spans="1:4" x14ac:dyDescent="0.3">
@@ -16359,7 +16372,7 @@
         <v>2.628735147338886E-2</v>
       </c>
       <c r="D1101" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1102" spans="1:4" x14ac:dyDescent="0.3">
@@ -16373,7 +16386,7 @@
         <v>2.307461769062219E-2</v>
       </c>
       <c r="D1102" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1103" spans="1:4" x14ac:dyDescent="0.3">
@@ -16387,7 +16400,7 @@
         <v>2.023296425996688E-2</v>
       </c>
       <c r="D1103" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1104" spans="1:4" x14ac:dyDescent="0.3">
@@ -16401,7 +16414,7 @@
         <v>1.9008021799154749E-2</v>
       </c>
       <c r="D1104" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1105" spans="1:4" x14ac:dyDescent="0.3">
@@ -16415,7 +16428,7 @@
         <v>1.252183485565953E-2</v>
       </c>
       <c r="D1105" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1106" spans="1:4" x14ac:dyDescent="0.3">
@@ -16429,7 +16442,7 @@
         <v>1.010195776025731E-2</v>
       </c>
       <c r="D1106" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1107" spans="1:4" x14ac:dyDescent="0.3">
@@ -16443,7 +16456,7 @@
         <v>8.8863705988914358E-3</v>
       </c>
       <c r="D1107" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1108" spans="1:4" x14ac:dyDescent="0.3">
@@ -16457,7 +16470,7 @@
         <v>8.8560539652870994E-3</v>
       </c>
       <c r="D1108" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1109" spans="1:4" x14ac:dyDescent="0.3">
@@ -16471,7 +16484,7 @@
         <v>7.6753888347962399E-3</v>
       </c>
       <c r="D1109" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1110" spans="1:4" x14ac:dyDescent="0.3">
@@ -16485,7 +16498,7 @@
         <v>7.5989509304551601E-3</v>
       </c>
       <c r="D1110" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1111" spans="1:4" x14ac:dyDescent="0.3">
@@ -16499,7 +16512,7 @@
         <v>7.01378941478963E-3</v>
       </c>
       <c r="D1111" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1112" spans="1:4" x14ac:dyDescent="0.3">
@@ -16513,7 +16526,7 @@
         <v>6.4203177962863971E-3</v>
       </c>
       <c r="D1112" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1113" spans="1:4" x14ac:dyDescent="0.3">
@@ -16527,7 +16540,7 @@
         <v>6.3353164076128147E-3</v>
       </c>
       <c r="D1113" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1114" spans="1:4" x14ac:dyDescent="0.3">
@@ -16541,7 +16554,7 @@
         <v>5.9972290255436494E-3</v>
       </c>
       <c r="D1114" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1115" spans="1:4" x14ac:dyDescent="0.3">
@@ -16555,7 +16568,7 @@
         <v>5.4992315451356964E-3</v>
       </c>
       <c r="D1115" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1116" spans="1:4" x14ac:dyDescent="0.3">
@@ -16569,7 +16582,7 @@
         <v>5.0811094375836129E-3</v>
       </c>
       <c r="D1116" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1117" spans="1:4" x14ac:dyDescent="0.3">
@@ -16583,7 +16596,7 @@
         <v>4.6824075937135492E-3</v>
       </c>
       <c r="D1117" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1118" spans="1:4" x14ac:dyDescent="0.3">
@@ -16597,7 +16610,7 @@
         <v>4.2406210911287486E-3</v>
       </c>
       <c r="D1118" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1119" spans="1:4" x14ac:dyDescent="0.3">
@@ -16611,7 +16624,7 @@
         <v>2.764395997342288E-3</v>
       </c>
       <c r="D1119" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1120" spans="1:4" x14ac:dyDescent="0.3">
@@ -16625,7 +16638,7 @@
         <v>2.585393248111537E-3</v>
       </c>
       <c r="D1120" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1121" spans="1:4" x14ac:dyDescent="0.3">
@@ -16639,7 +16652,7 @@
         <v>2.4225158201100958E-3</v>
       </c>
       <c r="D1121" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1122" spans="1:4" x14ac:dyDescent="0.3">
@@ -16653,7 +16666,7 @@
         <v>2.1283771652363089E-3</v>
       </c>
       <c r="D1122" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1123" spans="1:4" x14ac:dyDescent="0.3">
@@ -16667,7 +16680,7 @@
         <v>2.0902166099607822E-3</v>
       </c>
       <c r="D1123" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1124" spans="1:4" x14ac:dyDescent="0.3">
@@ -16681,7 +16694,7 @@
         <v>2.0717099032040152E-3</v>
       </c>
       <c r="D1124" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1125" spans="1:4" x14ac:dyDescent="0.3">
@@ -16695,7 +16708,7 @@
         <v>1.9731684700498939E-3</v>
       </c>
       <c r="D1125" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1126" spans="1:4" x14ac:dyDescent="0.3">
@@ -16709,7 +16722,7 @@
         <v>1.527624804274806E-3</v>
       </c>
       <c r="D1126" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1127" spans="1:4" x14ac:dyDescent="0.3">
@@ -16723,7 +16736,7 @@
         <v>1.253662597138494E-3</v>
       </c>
       <c r="D1127" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1128" spans="1:4" x14ac:dyDescent="0.3">
@@ -16737,7 +16750,7 @@
         <v>1.249431332838259E-3</v>
       </c>
       <c r="D1128" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1129" spans="1:4" x14ac:dyDescent="0.3">
@@ -16751,7 +16764,7 @@
         <v>1.0216577008696701E-3</v>
       </c>
       <c r="D1129" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1130" spans="1:4" x14ac:dyDescent="0.3">
@@ -16765,7 +16778,7 @@
         <v>9.6053647607917728E-4</v>
       </c>
       <c r="D1130" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1131" spans="1:4" x14ac:dyDescent="0.3">
@@ -16779,7 +16792,7 @@
         <v>8.3448044617014246E-4</v>
       </c>
       <c r="D1131" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1132" spans="1:4" x14ac:dyDescent="0.3">
@@ -16793,7 +16806,7 @@
         <v>6.7840075380993126E-4</v>
       </c>
       <c r="D1132" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1133" spans="1:4" x14ac:dyDescent="0.3">
@@ -16807,7 +16820,7 @@
         <v>5.2712144332018685E-4</v>
       </c>
       <c r="D1133" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1134" spans="1:4" x14ac:dyDescent="0.3">
@@ -16821,7 +16834,7 @@
         <v>5.0485757245869562E-4</v>
       </c>
       <c r="D1134" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1135" spans="1:4" x14ac:dyDescent="0.3">
@@ -16835,7 +16848,7 @@
         <v>4.7097380949907689E-4</v>
       </c>
       <c r="D1135" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1136" spans="1:4" x14ac:dyDescent="0.3">
@@ -16849,7 +16862,7 @@
         <v>4.3026261819723759E-4</v>
       </c>
       <c r="D1136" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1137" spans="1:4" x14ac:dyDescent="0.3">
@@ -16863,7 +16876,7 @@
         <v>3.2777992363182401E-4</v>
       </c>
       <c r="D1137" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1138" spans="1:4" x14ac:dyDescent="0.3">
@@ -16877,7 +16890,7 @@
         <v>2.8639964844912719E-4</v>
       </c>
       <c r="D1138" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1139" spans="1:4" x14ac:dyDescent="0.3">
@@ -16891,7 +16904,7 @@
         <v>2.6470588457927382E-4</v>
       </c>
       <c r="D1139" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1140" spans="1:4" x14ac:dyDescent="0.3">
@@ -16905,7 +16918,7 @@
         <v>2.566145206850341E-4</v>
       </c>
       <c r="D1140" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1141" spans="1:4" x14ac:dyDescent="0.3">
@@ -16919,7 +16932,7 @@
         <v>1.7504763134758731E-4</v>
       </c>
       <c r="D1141" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1142" spans="1:4" x14ac:dyDescent="0.3">
@@ -16933,7 +16946,7 @@
         <v>1.7024032169840389E-4</v>
       </c>
       <c r="D1142" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1143" spans="1:4" x14ac:dyDescent="0.3">
@@ -16947,7 +16960,7 @@
         <v>1.54763299184927E-4</v>
       </c>
       <c r="D1143" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1144" spans="1:4" x14ac:dyDescent="0.3">
@@ -16961,7 +16974,7 @@
         <v>1.359824266827749E-4</v>
       </c>
       <c r="D1144" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1145" spans="1:4" x14ac:dyDescent="0.3">
@@ -16975,7 +16988,7 @@
         <v>1.1590099632002119E-4</v>
       </c>
       <c r="D1145" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1146" spans="1:4" x14ac:dyDescent="0.3">
@@ -16989,7 +17002,7 @@
         <v>1.007367407033235E-4</v>
       </c>
       <c r="D1146" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1147" spans="1:4" x14ac:dyDescent="0.3">
@@ -17003,7 +17016,7 @@
         <v>3.2105147217882313E-5</v>
       </c>
       <c r="D1147" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1148" spans="1:4" x14ac:dyDescent="0.3">
@@ -17017,7 +17030,7 @@
         <v>3.0702644203843263E-5</v>
       </c>
       <c r="D1148" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1149" spans="1:4" x14ac:dyDescent="0.3">
@@ -17031,7 +17044,7 @@
         <v>1.7110142100039001E-5</v>
       </c>
       <c r="D1149" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1150" spans="1:4" x14ac:dyDescent="0.3">
@@ -17045,7 +17058,7 @@
         <v>6.0524397934269026E-6</v>
       </c>
       <c r="D1150" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1151" spans="1:4" x14ac:dyDescent="0.3">
@@ -17059,7 +17072,7 @@
         <v>3.3830311342759872E-6</v>
       </c>
       <c r="D1151" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1152" spans="1:4" x14ac:dyDescent="0.3">
@@ -17073,7 +17086,7 @@
         <v>3.1910166275848401E-6</v>
       </c>
       <c r="D1152" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1153" spans="1:4" x14ac:dyDescent="0.3">
@@ -17087,7 +17100,7 @@
         <v>3.0217661287304469E-6</v>
       </c>
       <c r="D1153" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1154" spans="1:4" x14ac:dyDescent="0.3">
@@ -17101,7 +17114,7 @@
         <v>2.231929857784928E-6</v>
       </c>
       <c r="D1154" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1155" spans="1:4" x14ac:dyDescent="0.3">
@@ -17115,7 +17128,7 @@
         <v>1.9448970619353789E-6</v>
       </c>
       <c r="D1155" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1156" spans="1:4" x14ac:dyDescent="0.3">
@@ -17129,7 +17142,7 @@
         <v>1.0679615308290591E-6</v>
       </c>
       <c r="D1156" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1157" spans="1:4" x14ac:dyDescent="0.3">
@@ -17143,7 +17156,7 @@
         <v>7.6608101282777259E-7</v>
       </c>
       <c r="D1157" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1158" spans="1:4" x14ac:dyDescent="0.3">
@@ -17157,7 +17170,7 @@
         <v>4.5925338779680643E-7</v>
       </c>
       <c r="D1158" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1159" spans="1:4" x14ac:dyDescent="0.3">
@@ -17171,7 +17184,7 @@
         <v>4.3351928686718782E-7</v>
       </c>
       <c r="D1159" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1160" spans="1:4" x14ac:dyDescent="0.3">
@@ -17185,7 +17198,7 @@
         <v>4.1966190055891389E-7</v>
       </c>
       <c r="D1160" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1161" spans="1:4" x14ac:dyDescent="0.3">
@@ -17199,7 +17212,7 @@
         <v>3.9095862097395911E-7</v>
       </c>
       <c r="D1161" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1162" spans="1:4" x14ac:dyDescent="0.3">
@@ -17213,7 +17226,7 @@
         <v>3.2761370449337689E-7</v>
       </c>
       <c r="D1162" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1163" spans="1:4" x14ac:dyDescent="0.3">
@@ -17227,7 +17240,7 @@
         <v>2.6426878801279482E-7</v>
       </c>
       <c r="D1163" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1164" spans="1:4" x14ac:dyDescent="0.3">
@@ -17241,7 +17254,7 @@
         <v>6.928418822878317E-8</v>
       </c>
       <c r="D1164" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1165" spans="1:4" x14ac:dyDescent="0.3">
@@ -17255,7 +17268,7 @@
         <v>6.8293852385318697E-8</v>
       </c>
       <c r="D1165" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1166" spans="1:4" x14ac:dyDescent="0.3">
@@ -17269,7 +17282,7 @@
         <v>4.948844460983695E-8</v>
       </c>
       <c r="D1166" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1167" spans="1:4" x14ac:dyDescent="0.3">
@@ -17283,7 +17296,7 @@
         <v>1.9797572494003401E-9</v>
       </c>
       <c r="D1167" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1168" spans="1:4" x14ac:dyDescent="0.3">
@@ -17297,7 +17310,7 @@
         <v>0.40611681632435059</v>
       </c>
       <c r="D1168" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1169" spans="1:4" x14ac:dyDescent="0.3">
@@ -17311,7 +17324,7 @@
         <v>0.25095467104449543</v>
       </c>
       <c r="D1169" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1170" spans="1:4" x14ac:dyDescent="0.3">
@@ -17325,7 +17338,7 @@
         <v>7.5060969116757775E-2</v>
       </c>
       <c r="D1170" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1171" spans="1:4" x14ac:dyDescent="0.3">
@@ -17339,7 +17352,7 @@
         <v>6.1930958844059983E-2</v>
       </c>
       <c r="D1171" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1172" spans="1:4" x14ac:dyDescent="0.3">
@@ -17353,7 +17366,7 @@
         <v>4.5639197839736308E-2</v>
       </c>
       <c r="D1172" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1173" spans="1:4" x14ac:dyDescent="0.3">
@@ -17367,7 +17380,7 @@
         <v>3.4164964832600578E-2</v>
       </c>
       <c r="D1173" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1174" spans="1:4" x14ac:dyDescent="0.3">
@@ -17381,7 +17394,7 @@
         <v>2.2353685352927519E-2</v>
       </c>
       <c r="D1174" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1175" spans="1:4" x14ac:dyDescent="0.3">
@@ -17395,7 +17408,7 @@
         <v>1.6591894403574239E-2</v>
       </c>
       <c r="D1175" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1176" spans="1:4" x14ac:dyDescent="0.3">
@@ -17409,7 +17422,7 @@
         <v>1.198567883204526E-2</v>
       </c>
       <c r="D1176" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1177" spans="1:4" x14ac:dyDescent="0.3">
@@ -17423,7 +17436,7 @@
         <v>1.049384572862112E-2</v>
       </c>
       <c r="D1177" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1178" spans="1:4" x14ac:dyDescent="0.3">
@@ -17437,7 +17450,7 @@
         <v>1.0268704050647681E-2</v>
       </c>
       <c r="D1178" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1179" spans="1:4" x14ac:dyDescent="0.3">
@@ -17451,7 +17464,7 @@
         <v>7.8427871339853197E-3</v>
       </c>
       <c r="D1179" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1180" spans="1:4" x14ac:dyDescent="0.3">
@@ -17465,7 +17478,7 @@
         <v>6.5110289725943482E-3</v>
       </c>
       <c r="D1180" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1181" spans="1:4" x14ac:dyDescent="0.3">
@@ -17479,7 +17492,7 @@
         <v>6.2027846897695256E-3</v>
       </c>
       <c r="D1181" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1182" spans="1:4" x14ac:dyDescent="0.3">
@@ -17493,7 +17506,7 @@
         <v>5.2729425480975752E-3</v>
       </c>
       <c r="D1182" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1183" spans="1:4" x14ac:dyDescent="0.3">
@@ -17507,7 +17520,7 @@
         <v>4.2577060672476649E-3</v>
       </c>
       <c r="D1183" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1184" spans="1:4" x14ac:dyDescent="0.3">
@@ -17521,7 +17534,7 @@
         <v>3.8845615626245801E-3</v>
       </c>
       <c r="D1184" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1185" spans="1:4" x14ac:dyDescent="0.3">
@@ -17535,7 +17548,7 @@
         <v>3.2664823660892009E-3</v>
       </c>
       <c r="D1185" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1186" spans="1:4" x14ac:dyDescent="0.3">
@@ -17549,7 +17562,7 @@
         <v>2.812180813501364E-3</v>
       </c>
       <c r="D1186" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1187" spans="1:4" x14ac:dyDescent="0.3">
@@ -17563,7 +17576,7 @@
         <v>2.602323179202717E-3</v>
       </c>
       <c r="D1187" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1188" spans="1:4" x14ac:dyDescent="0.3">
@@ -17577,7 +17590,7 @@
         <v>2.5411826201021202E-3</v>
       </c>
       <c r="D1188" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1189" spans="1:4" x14ac:dyDescent="0.3">
@@ -17591,7 +17604,7 @@
         <v>1.5135892037586439E-3</v>
       </c>
       <c r="D1189" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1190" spans="1:4" x14ac:dyDescent="0.3">
@@ -17605,7 +17618,7 @@
         <v>1.19663809882761E-3</v>
       </c>
       <c r="D1190" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1191" spans="1:4" x14ac:dyDescent="0.3">
@@ -17619,7 +17632,7 @@
         <v>1.034652646780653E-3</v>
       </c>
       <c r="D1191" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1192" spans="1:4" x14ac:dyDescent="0.3">
@@ -17633,7 +17646,7 @@
         <v>9.4330769918265014E-4</v>
       </c>
       <c r="D1192" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1193" spans="1:4" x14ac:dyDescent="0.3">
@@ -17647,7 +17660,7 @@
         <v>7.8985379439379096E-4</v>
       </c>
       <c r="D1193" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1194" spans="1:4" x14ac:dyDescent="0.3">
@@ -17661,7 +17674,7 @@
         <v>7.3440093751364415E-4</v>
       </c>
       <c r="D1194" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1195" spans="1:4" x14ac:dyDescent="0.3">
@@ -17675,7 +17688,7 @@
         <v>4.9748510937428381E-4</v>
       </c>
       <c r="D1195" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1196" spans="1:4" x14ac:dyDescent="0.3">
@@ -17689,7 +17702,7 @@
         <v>4.7465983044210343E-4</v>
       </c>
       <c r="D1196" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1197" spans="1:4" x14ac:dyDescent="0.3">
@@ -17703,7 +17716,7 @@
         <v>3.943528705511804E-4</v>
       </c>
       <c r="D1197" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1198" spans="1:4" x14ac:dyDescent="0.3">
@@ -17717,7 +17730,7 @@
         <v>3.1191192976956462E-4</v>
       </c>
       <c r="D1198" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1199" spans="1:4" x14ac:dyDescent="0.3">
@@ -17731,7 +17744,7 @@
         <v>2.8161113706940831E-4</v>
       </c>
       <c r="D1199" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1200" spans="1:4" x14ac:dyDescent="0.3">
@@ -17745,7 +17758,7 @@
         <v>2.186389466971611E-4</v>
       </c>
       <c r="D1200" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1201" spans="1:4" x14ac:dyDescent="0.3">
@@ -17759,7 +17772,7 @@
         <v>1.8059534962799371E-4</v>
       </c>
       <c r="D1201" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1202" spans="1:4" x14ac:dyDescent="0.3">
@@ -17773,7 +17786,7 @@
         <v>1.765377176643438E-4</v>
       </c>
       <c r="D1202" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1203" spans="1:4" x14ac:dyDescent="0.3">
@@ -17787,7 +17800,7 @@
         <v>1.4445349376972089E-4</v>
       </c>
       <c r="D1203" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1204" spans="1:4" x14ac:dyDescent="0.3">
@@ -17801,7 +17814,7 @@
         <v>1.0901274135228621E-4</v>
       </c>
       <c r="D1204" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1205" spans="1:4" x14ac:dyDescent="0.3">
@@ -17815,7 +17828,7 @@
         <v>6.5697725393466395E-5</v>
       </c>
       <c r="D1205" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1206" spans="1:4" x14ac:dyDescent="0.3">
@@ -17829,7 +17842,7 @@
         <v>4.4988897842974722E-5</v>
       </c>
       <c r="D1206" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1207" spans="1:4" x14ac:dyDescent="0.3">
@@ -17843,7 +17856,7 @@
         <v>4.2648967487604437E-5</v>
       </c>
       <c r="D1207" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1208" spans="1:4" x14ac:dyDescent="0.3">
@@ -17857,7 +17870,7 @@
         <v>1.9503805378991189E-5</v>
       </c>
       <c r="D1208" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1209" spans="1:4" x14ac:dyDescent="0.3">
@@ -17871,7 +17884,7 @@
         <v>1.570908771170375E-5</v>
       </c>
       <c r="D1209" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1210" spans="1:4" x14ac:dyDescent="0.3">
@@ -17885,7 +17898,7 @@
         <v>8.4351430553470734E-6</v>
       </c>
       <c r="D1210" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1211" spans="1:4" x14ac:dyDescent="0.3">
@@ -17899,7 +17912,7 @@
         <v>8.2379583451716213E-6</v>
       </c>
       <c r="D1211" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1212" spans="1:4" x14ac:dyDescent="0.3">
@@ -17913,7 +17926,7 @@
         <v>7.9531382351323286E-6</v>
       </c>
       <c r="D1212" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1213" spans="1:4" x14ac:dyDescent="0.3">
@@ -17927,7 +17940,7 @@
         <v>5.8805025291827584E-6</v>
       </c>
       <c r="D1213" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1214" spans="1:4" x14ac:dyDescent="0.3">
@@ -17941,7 +17954,7 @@
         <v>5.6351136934389249E-6</v>
       </c>
       <c r="D1214" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1215" spans="1:4" x14ac:dyDescent="0.3">
@@ -17955,7 +17968,7 @@
         <v>5.2232188124694327E-6</v>
       </c>
       <c r="D1215" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1216" spans="1:4" x14ac:dyDescent="0.3">
@@ -17969,7 +17982,7 @@
         <v>4.3950406007012596E-6</v>
       </c>
       <c r="D1216" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1217" spans="1:4" x14ac:dyDescent="0.3">
@@ -17983,7 +17996,7 @@
         <v>2.9227237797800661E-6</v>
       </c>
       <c r="D1217" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1218" spans="1:4" x14ac:dyDescent="0.3">
@@ -17997,7 +18010,7 @@
         <v>1.722086009723311E-6</v>
       </c>
       <c r="D1218" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1219" spans="1:4" x14ac:dyDescent="0.3">
@@ -18011,7 +18024,7 @@
         <v>1.314567433426652E-6</v>
       </c>
       <c r="D1219" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1220" spans="1:4" x14ac:dyDescent="0.3">
@@ -18025,7 +18038,7 @@
         <v>1.183112309438167E-6</v>
       </c>
       <c r="D1220" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1221" spans="1:4" x14ac:dyDescent="0.3">
@@ -18039,7 +18052,7 @@
         <v>8.6761353444908187E-7</v>
       </c>
       <c r="D1221" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1222" spans="1:4" x14ac:dyDescent="0.3">
@@ -18053,7 +18066,7 @@
         <v>2.6291429636242061E-7</v>
       </c>
       <c r="D1222" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1223" spans="1:4" x14ac:dyDescent="0.3">
@@ -18067,7 +18080,7 @@
         <v>1.5336498605080731E-7</v>
       </c>
       <c r="D1223" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1224" spans="1:4" x14ac:dyDescent="0.3">
@@ -18081,7 +18094,7 @@
         <v>1.2269441787191661E-7</v>
       </c>
       <c r="D1224" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1225" spans="1:4" x14ac:dyDescent="0.3">
@@ -18095,7 +18108,7 @@
         <v>3.0674616564341973E-8</v>
       </c>
       <c r="D1225" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1226" spans="1:4" x14ac:dyDescent="0.3">
@@ -18109,7 +18122,7 @@
         <v>2.1909862062322651E-8</v>
       </c>
       <c r="D1226" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1227" spans="1:4" x14ac:dyDescent="0.3">
@@ -18123,7 +18136,7 @@
         <v>2.1909862062322651E-8</v>
       </c>
       <c r="D1227" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1228" spans="1:4" x14ac:dyDescent="0.3">
@@ -18137,7 +18150,7 @@
         <v>0.33140024145292613</v>
       </c>
       <c r="D1228" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1229" spans="1:4" x14ac:dyDescent="0.3">
@@ -18151,7 +18164,7 @@
         <v>0.21551903054771179</v>
       </c>
       <c r="D1229" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1230" spans="1:4" x14ac:dyDescent="0.3">
@@ -18165,7 +18178,7 @@
         <v>6.9014658021507316E-2</v>
       </c>
       <c r="D1230" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1231" spans="1:4" x14ac:dyDescent="0.3">
@@ -18179,7 +18192,7 @@
         <v>5.8805183412076453E-2</v>
       </c>
       <c r="D1231" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1232" spans="1:4" x14ac:dyDescent="0.3">
@@ -18193,7 +18206,7 @@
         <v>4.4691113034902627E-2</v>
       </c>
       <c r="D1232" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1233" spans="1:4" x14ac:dyDescent="0.3">
@@ -18207,7 +18220,7 @@
         <v>2.6728700412388989E-2</v>
       </c>
       <c r="D1233" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1234" spans="1:4" x14ac:dyDescent="0.3">
@@ -18221,7 +18234,7 @@
         <v>2.3453366393074011E-2</v>
       </c>
       <c r="D1234" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1235" spans="1:4" x14ac:dyDescent="0.3">
@@ -18235,7 +18248,7 @@
         <v>2.2551453638427161E-2</v>
       </c>
       <c r="D1235" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1236" spans="1:4" x14ac:dyDescent="0.3">
@@ -18249,7 +18262,7 @@
         <v>2.1772992061619291E-2</v>
       </c>
       <c r="D1236" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1237" spans="1:4" x14ac:dyDescent="0.3">
@@ -18263,7 +18276,7 @@
         <v>1.9974403874845299E-2</v>
       </c>
       <c r="D1237" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1238" spans="1:4" x14ac:dyDescent="0.3">
@@ -18277,7 +18290,7 @@
         <v>1.822218349609319E-2</v>
       </c>
       <c r="D1238" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1239" spans="1:4" x14ac:dyDescent="0.3">
@@ -18291,7 +18304,7 @@
         <v>1.6082533954396249E-2</v>
       </c>
       <c r="D1239" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1240" spans="1:4" x14ac:dyDescent="0.3">
@@ -18305,7 +18318,7 @@
         <v>1.402763049923593E-2</v>
       </c>
       <c r="D1240" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1241" spans="1:4" x14ac:dyDescent="0.3">
@@ -18319,7 +18332,7 @@
         <v>1.345396200801535E-2</v>
       </c>
       <c r="D1241" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1242" spans="1:4" x14ac:dyDescent="0.3">
@@ -18333,7 +18346,7 @@
         <v>1.1045611435003299E-2</v>
       </c>
       <c r="D1242" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1243" spans="1:4" x14ac:dyDescent="0.3">
@@ -18347,7 +18360,7 @@
         <v>9.6792690953370914E-3</v>
       </c>
       <c r="D1243" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1244" spans="1:4" x14ac:dyDescent="0.3">
@@ -18361,7 +18374,7 @@
         <v>9.5526410184978549E-3</v>
       </c>
       <c r="D1244" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1245" spans="1:4" x14ac:dyDescent="0.3">
@@ -18375,7 +18388,7 @@
         <v>9.1465220626561865E-3</v>
       </c>
       <c r="D1245" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1246" spans="1:4" x14ac:dyDescent="0.3">
@@ -18389,7 +18402,7 @@
         <v>8.761682529491199E-3</v>
       </c>
       <c r="D1246" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1247" spans="1:4" x14ac:dyDescent="0.3">
@@ -18403,7 +18416,7 @@
         <v>8.3456330648204562E-3</v>
       </c>
       <c r="D1247" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1248" spans="1:4" x14ac:dyDescent="0.3">
@@ -18417,7 +18430,7 @@
         <v>5.5418173480688039E-3</v>
       </c>
       <c r="D1248" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1249" spans="1:4" x14ac:dyDescent="0.3">
@@ -18431,7 +18444,7 @@
         <v>4.8703866066850459E-3</v>
       </c>
       <c r="D1249" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1250" spans="1:4" x14ac:dyDescent="0.3">
@@ -18445,7 +18458,7 @@
         <v>4.7536741071922597E-3</v>
       </c>
       <c r="D1250" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1251" spans="1:4" x14ac:dyDescent="0.3">
@@ -18459,7 +18472,7 @@
         <v>4.5708771125322328E-3</v>
       </c>
       <c r="D1251" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1252" spans="1:4" x14ac:dyDescent="0.3">
@@ -18473,7 +18486,7 @@
         <v>4.0197106951545512E-3</v>
       </c>
       <c r="D1252" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1253" spans="1:4" x14ac:dyDescent="0.3">
@@ -18487,7 +18500,7 @@
         <v>3.2489831680710271E-3</v>
       </c>
       <c r="D1253" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1254" spans="1:4" x14ac:dyDescent="0.3">
@@ -18501,7 +18514,7 @@
         <v>2.2870875578175709E-3</v>
       </c>
       <c r="D1254" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1255" spans="1:4" x14ac:dyDescent="0.3">
@@ -18515,7 +18528,7 @@
         <v>2.245970343892888E-3</v>
       </c>
       <c r="D1255" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1256" spans="1:4" x14ac:dyDescent="0.3">
@@ -18529,7 +18542,7 @@
         <v>2.088487352928325E-3</v>
       </c>
       <c r="D1256" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1257" spans="1:4" x14ac:dyDescent="0.3">
@@ -18543,7 +18556,7 @@
         <v>1.8885964790802221E-3</v>
       </c>
       <c r="D1257" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1258" spans="1:4" x14ac:dyDescent="0.3">
@@ -18557,7 +18570,7 @@
         <v>1.655732206160042E-3</v>
       </c>
       <c r="D1258" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1259" spans="1:4" x14ac:dyDescent="0.3">
@@ -18571,7 +18584,7 @@
         <v>1.6281305037551381E-3</v>
       </c>
       <c r="D1259" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1260" spans="1:4" x14ac:dyDescent="0.3">
@@ -18585,7 +18598,7 @@
         <v>1.4918788242745281E-3</v>
       </c>
       <c r="D1260" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1261" spans="1:4" x14ac:dyDescent="0.3">
@@ -18599,7 +18612,7 @@
         <v>1.425651660032297E-3</v>
       </c>
       <c r="D1261" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1262" spans="1:4" x14ac:dyDescent="0.3">
@@ -18613,7 +18626,7 @@
         <v>1.3834494888990999E-3</v>
       </c>
       <c r="D1262" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1263" spans="1:4" x14ac:dyDescent="0.3">
@@ -18627,7 +18640,7 @@
         <v>1.103568755966394E-3</v>
       </c>
       <c r="D1263" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1264" spans="1:4" x14ac:dyDescent="0.3">
@@ -18641,7 +18654,7 @@
         <v>8.7309835590837503E-4</v>
       </c>
       <c r="D1264" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1265" spans="1:4" x14ac:dyDescent="0.3">
@@ -18655,7 +18668,7 @@
         <v>6.6084494554164526E-4</v>
       </c>
       <c r="D1265" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1266" spans="1:4" x14ac:dyDescent="0.3">
@@ -18669,7 +18682,7 @@
         <v>5.0008053979653296E-4</v>
       </c>
       <c r="D1266" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1267" spans="1:4" x14ac:dyDescent="0.3">
@@ -18683,7 +18696,7 @@
         <v>4.8012164597857192E-4</v>
       </c>
       <c r="D1267" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1268" spans="1:4" x14ac:dyDescent="0.3">
@@ -18697,7 +18710,7 @@
         <v>2.8378259664375892E-4</v>
       </c>
       <c r="D1268" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1269" spans="1:4" x14ac:dyDescent="0.3">
@@ -18711,7 +18724,7 @@
         <v>1.820836446869977E-4</v>
       </c>
       <c r="D1269" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1270" spans="1:4" x14ac:dyDescent="0.3">
@@ -18725,7 +18738,7 @@
         <v>1.721531358579226E-4</v>
       </c>
       <c r="D1270" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1271" spans="1:4" x14ac:dyDescent="0.3">
@@ -18739,7 +18752,7 @@
         <v>1.6873568702478861E-4</v>
       </c>
       <c r="D1271" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1272" spans="1:4" x14ac:dyDescent="0.3">
@@ -18753,7 +18766,7 @@
         <v>7.5888921710994423E-5</v>
       </c>
       <c r="D1272" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1273" spans="1:4" x14ac:dyDescent="0.3">
@@ -18767,7 +18780,7 @@
         <v>4.9207939401891723E-5</v>
       </c>
       <c r="D1273" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1274" spans="1:4" x14ac:dyDescent="0.3">
@@ -18781,7 +18794,7 @@
         <v>2.368490874391871E-5</v>
       </c>
       <c r="D1274" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1275" spans="1:4" x14ac:dyDescent="0.3">
@@ -18795,7 +18808,7 @@
         <v>2.3648410756265001E-5</v>
       </c>
       <c r="D1275" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1276" spans="1:4" x14ac:dyDescent="0.3">
@@ -18809,7 +18822,7 @@
         <v>1.679194811765873E-5</v>
       </c>
       <c r="D1276" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1277" spans="1:4" x14ac:dyDescent="0.3">
@@ -18823,7 +18836,7 @@
         <v>9.397982758427002E-6</v>
       </c>
       <c r="D1277" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1278" spans="1:4" x14ac:dyDescent="0.3">
@@ -18837,7 +18850,7 @@
         <v>8.047593999840835E-6</v>
       </c>
       <c r="D1278" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1279" spans="1:4" x14ac:dyDescent="0.3">
@@ -18851,7 +18864,7 @@
         <v>7.7390279070172816E-6</v>
       </c>
       <c r="D1279" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1280" spans="1:4" x14ac:dyDescent="0.3">
@@ -18865,7 +18878,7 @@
         <v>6.6474356760973524E-6</v>
       </c>
       <c r="D1280" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1281" spans="1:4" x14ac:dyDescent="0.3">
@@ -18879,7 +18892,7 @@
         <v>6.038598417976461E-6</v>
       </c>
       <c r="D1281" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1282" spans="1:4" x14ac:dyDescent="0.3">
@@ -18893,7 +18906,7 @@
         <v>5.1908712320988932E-6</v>
       </c>
       <c r="D1282" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1283" spans="1:4" x14ac:dyDescent="0.3">
@@ -18907,7 +18920,7 @@
         <v>4.3348506513868141E-6</v>
       </c>
       <c r="D1283" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1284" spans="1:4" x14ac:dyDescent="0.3">
@@ -18921,7 +18934,7 @@
         <v>3.3295244405862012E-6</v>
       </c>
       <c r="D1284" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1285" spans="1:4" x14ac:dyDescent="0.3">
@@ -18935,7 +18948,7 @@
         <v>2.4635490272276319E-6</v>
       </c>
       <c r="D1285" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1286" spans="1:4" x14ac:dyDescent="0.3">
@@ -18949,7 +18962,7 @@
         <v>1.235921211031072E-6</v>
       </c>
       <c r="D1286" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1287" spans="1:4" x14ac:dyDescent="0.3">
@@ -18963,7 +18976,7 @@
         <v>1.1397018909569761E-6</v>
       </c>
       <c r="D1287" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1288" spans="1:4" x14ac:dyDescent="0.3">
@@ -18977,7 +18990,7 @@
         <v>1.1065237135438071E-6</v>
       </c>
       <c r="D1288" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1289" spans="1:4" x14ac:dyDescent="0.3">
@@ -18991,7 +19004,7 @@
         <v>1.8580361774224049E-7</v>
       </c>
       <c r="D1289" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1290" spans="1:4" x14ac:dyDescent="0.3">
@@ -19005,7 +19018,7 @@
         <v>7.7971092593096103E-8</v>
       </c>
       <c r="D1290" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1291" spans="1:4" x14ac:dyDescent="0.3">
@@ -19019,7 +19032,7 @@
         <v>5.9722865112096683E-8</v>
       </c>
       <c r="D1291" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1292" spans="1:4" x14ac:dyDescent="0.3">
@@ -19033,7 +19046,7 @@
         <v>4.6451287608487253E-8</v>
       </c>
       <c r="D1292" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1293" spans="1:4" x14ac:dyDescent="0.3">
@@ -19047,7 +19060,7 @@
         <v>1.1613205075048929E-8</v>
       </c>
       <c r="D1293" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1294" spans="1:4" x14ac:dyDescent="0.3">
@@ -19061,7 +19074,7 @@
         <v>4.9766499773899789E-9</v>
       </c>
       <c r="D1294" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1295" spans="1:4" x14ac:dyDescent="0.3">
@@ -19075,7 +19088,7 @@
         <v>4.9766499773899789E-9</v>
       </c>
       <c r="D1295" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1296" spans="1:4" x14ac:dyDescent="0.3">
@@ -19089,7 +19102,7 @@
         <v>0.23737492362583121</v>
       </c>
       <c r="D1296" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1297" spans="1:4" x14ac:dyDescent="0.3">
@@ -19103,7 +19116,7 @@
         <v>0.21219499481822171</v>
       </c>
       <c r="D1297" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1298" spans="1:4" x14ac:dyDescent="0.3">
@@ -19117,7 +19130,7 @@
         <v>0.162788361975549</v>
       </c>
       <c r="D1298" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1299" spans="1:4" x14ac:dyDescent="0.3">
@@ -19131,7 +19144,7 @@
         <v>7.9087044945683083E-2</v>
       </c>
       <c r="D1299" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1300" spans="1:4" x14ac:dyDescent="0.3">
@@ -19145,7 +19158,7 @@
         <v>7.2520507730200634E-2</v>
       </c>
       <c r="D1300" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1301" spans="1:4" x14ac:dyDescent="0.3">
@@ -19159,7 +19172,7 @@
         <v>7.0790668383710759E-2</v>
       </c>
       <c r="D1301" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1302" spans="1:4" x14ac:dyDescent="0.3">
@@ -19173,7 +19186,7 @@
         <v>5.5722584688568493E-2</v>
       </c>
       <c r="D1302" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1303" spans="1:4" x14ac:dyDescent="0.3">
@@ -19187,7 +19200,7 @@
         <v>2.446083380614349E-2</v>
       </c>
       <c r="D1303" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1304" spans="1:4" x14ac:dyDescent="0.3">
@@ -19201,7 +19214,7 @@
         <v>2.30084890116336E-2</v>
       </c>
       <c r="D1304" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1305" spans="1:4" x14ac:dyDescent="0.3">
@@ -19215,7 +19228,7 @@
         <v>1.7819821194029379E-2</v>
       </c>
       <c r="D1305" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1306" spans="1:4" x14ac:dyDescent="0.3">
@@ -19229,7 +19242,7 @@
         <v>1.135321801871908E-2</v>
       </c>
       <c r="D1306" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1307" spans="1:4" x14ac:dyDescent="0.3">
@@ -19243,7 +19256,7 @@
         <v>9.5838652360301299E-3</v>
       </c>
       <c r="D1307" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1308" spans="1:4" x14ac:dyDescent="0.3">
@@ -19257,7 +19270,7 @@
         <v>8.3861571536461132E-3</v>
       </c>
       <c r="D1308" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1309" spans="1:4" x14ac:dyDescent="0.3">
@@ -19271,7 +19284,7 @@
         <v>6.1190347502964072E-3</v>
       </c>
       <c r="D1309" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1310" spans="1:4" x14ac:dyDescent="0.3">
@@ -19285,7 +19298,7 @@
         <v>2.6314965617182341E-3</v>
       </c>
       <c r="D1310" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1311" spans="1:4" x14ac:dyDescent="0.3">
@@ -19299,7 +19312,7 @@
         <v>1.644910412181428E-3</v>
       </c>
       <c r="D1311" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1312" spans="1:4" x14ac:dyDescent="0.3">
@@ -19313,7 +19326,7 @@
         <v>1.238221877458111E-3</v>
       </c>
       <c r="D1312" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1313" spans="1:4" x14ac:dyDescent="0.3">
@@ -19327,7 +19340,7 @@
         <v>1.0178467636477819E-3</v>
       </c>
       <c r="D1313" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1314" spans="1:4" x14ac:dyDescent="0.3">
@@ -19341,7 +19354,7 @@
         <v>7.9372044268685542E-4</v>
       </c>
       <c r="D1314" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1315" spans="1:4" x14ac:dyDescent="0.3">
@@ -19355,7 +19368,7 @@
         <v>6.3946785829053566E-4</v>
       </c>
       <c r="D1315" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1316" spans="1:4" x14ac:dyDescent="0.3">
@@ -19369,7 +19382,7 @@
         <v>3.5487088768666047E-4</v>
       </c>
       <c r="D1316" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1317" spans="1:4" x14ac:dyDescent="0.3">
@@ -19383,7 +19396,7 @@
         <v>2.0501987309831131E-4</v>
       </c>
       <c r="D1317" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1318" spans="1:4" x14ac:dyDescent="0.3">
@@ -19397,7 +19410,7 @@
         <v>5.5018767710534393E-5</v>
       </c>
       <c r="D1318" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1319" spans="1:4" x14ac:dyDescent="0.3">
@@ -19411,7 +19424,7 @@
         <v>3.6112317686565323E-5</v>
       </c>
       <c r="D1319" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1320" spans="1:4" x14ac:dyDescent="0.3">
@@ -19425,7 +19438,7 @@
         <v>3.4511780454737108E-5</v>
       </c>
       <c r="D1320" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1321" spans="1:4" x14ac:dyDescent="0.3">
@@ -19439,7 +19452,7 @@
         <v>3.1160615191652977E-5</v>
       </c>
       <c r="D1321" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1322" spans="1:4" x14ac:dyDescent="0.3">
@@ -19453,7 +19466,7 @@
         <v>2.270774905467183E-5</v>
       </c>
       <c r="D1322" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1323" spans="1:4" x14ac:dyDescent="0.3">
@@ -19467,7 +19480,7 @@
         <v>1.895644948363065E-5</v>
       </c>
       <c r="D1323" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1324" spans="1:4" x14ac:dyDescent="0.3">
@@ -19481,7 +19494,7 @@
         <v>1.870635976487981E-5</v>
       </c>
       <c r="D1324" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1325" spans="1:4" x14ac:dyDescent="0.3">
@@ -19495,7 +19508,7 @@
         <v>1.50051058637217E-5</v>
       </c>
       <c r="D1325" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1326" spans="1:4" x14ac:dyDescent="0.3">
@@ -19509,7 +19522,7 @@
         <v>1.2804344064847159E-5</v>
       </c>
       <c r="D1326" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1327" spans="1:4" x14ac:dyDescent="0.3">
@@ -19523,7 +19536,7 @@
         <v>8.8030009852766443E-6</v>
       </c>
       <c r="D1327" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1328" spans="1:4" x14ac:dyDescent="0.3">
@@ -19537,7 +19550,7 @@
         <v>4.8016579057061233E-6</v>
       </c>
       <c r="D1328" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1329" spans="1:4" x14ac:dyDescent="0.3">
@@ -19551,7 +19564,7 @@
         <v>2.3008069284191731E-6</v>
       </c>
       <c r="D1329" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1330" spans="1:4" x14ac:dyDescent="0.3">
@@ -19565,7 +19578,7 @@
         <v>1.9006264102406229E-6</v>
       </c>
       <c r="D1330" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1331" spans="1:4" x14ac:dyDescent="0.3">
@@ -19579,7 +19592,7 @@
         <v>1.150403464209587E-6</v>
       </c>
       <c r="D1331" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1332" spans="1:4" x14ac:dyDescent="0.3">
@@ -19593,7 +19606,7 @@
         <v>0.22183996193259301</v>
       </c>
       <c r="D1332" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1333" spans="1:4" x14ac:dyDescent="0.3">
@@ -19607,7 +19620,7 @@
         <v>0.17627334933169361</v>
       </c>
       <c r="D1333" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1334" spans="1:4" x14ac:dyDescent="0.3">
@@ -19621,7 +19634,7 @@
         <v>0.16298296550556901</v>
       </c>
       <c r="D1334" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1335" spans="1:4" x14ac:dyDescent="0.3">
@@ -19635,7 +19648,7 @@
         <v>0.12973584657735079</v>
       </c>
       <c r="D1335" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1336" spans="1:4" x14ac:dyDescent="0.3">
@@ -19649,7 +19662,7 @@
         <v>9.8035822407204667E-2</v>
       </c>
       <c r="D1336" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1337" spans="1:4" x14ac:dyDescent="0.3">
@@ -19663,7 +19676,7 @@
         <v>7.795736058557251E-2</v>
       </c>
       <c r="D1337" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1338" spans="1:4" x14ac:dyDescent="0.3">
@@ -19677,7 +19690,7 @@
         <v>3.7389792633098481E-2</v>
       </c>
       <c r="D1338" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1339" spans="1:4" x14ac:dyDescent="0.3">
@@ -19691,7 +19704,7 @@
         <v>2.4096379151411339E-2</v>
       </c>
       <c r="D1339" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1340" spans="1:4" x14ac:dyDescent="0.3">
@@ -19705,7 +19718,7 @@
         <v>1.747855066178898E-2</v>
       </c>
       <c r="D1340" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1341" spans="1:4" x14ac:dyDescent="0.3">
@@ -19719,7 +19732,7 @@
         <v>1.6146349468064852E-2</v>
       </c>
       <c r="D1341" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1342" spans="1:4" x14ac:dyDescent="0.3">
@@ -19733,7 +19746,7 @@
         <v>1.000557659770103E-2</v>
       </c>
       <c r="D1342" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1343" spans="1:4" x14ac:dyDescent="0.3">
@@ -19747,7 +19760,7 @@
         <v>9.0871748188303507E-3</v>
       </c>
       <c r="D1343" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1344" spans="1:4" x14ac:dyDescent="0.3">
@@ -19761,7 +19774,7 @@
         <v>6.3487869868839022E-3</v>
       </c>
       <c r="D1344" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1345" spans="1:4" x14ac:dyDescent="0.3">
@@ -19775,7 +19788,7 @@
         <v>3.3815151208409942E-3</v>
       </c>
       <c r="D1345" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1346" spans="1:4" x14ac:dyDescent="0.3">
@@ -19789,7 +19802,7 @@
         <v>3.037484715582931E-3</v>
       </c>
       <c r="D1346" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1347" spans="1:4" x14ac:dyDescent="0.3">
@@ -19803,7 +19816,7 @@
         <v>2.47120851367141E-3</v>
       </c>
       <c r="D1347" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1348" spans="1:4" x14ac:dyDescent="0.3">
@@ -19817,7 +19830,7 @@
         <v>1.247206691180198E-3</v>
       </c>
       <c r="D1348" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1349" spans="1:4" x14ac:dyDescent="0.3">
@@ -19831,7 +19844,7 @@
         <v>1.105999462965273E-3</v>
       </c>
       <c r="D1349" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1350" spans="1:4" x14ac:dyDescent="0.3">
@@ -19845,7 +19858,7 @@
         <v>2.4358849870750979E-4</v>
       </c>
       <c r="D1350" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1351" spans="1:4" x14ac:dyDescent="0.3">
@@ -19859,7 +19872,7 @@
         <v>2.2971381600539359E-4</v>
       </c>
       <c r="D1351" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1352" spans="1:4" x14ac:dyDescent="0.3">
@@ -19873,7 +19886,7 @@
         <v>1.9452537578226761E-4</v>
       </c>
       <c r="D1352" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1353" spans="1:4" x14ac:dyDescent="0.3">
@@ -19887,7 +19900,7 @@
         <v>1.4609906824092711E-4</v>
       </c>
       <c r="D1353" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1354" spans="1:4" x14ac:dyDescent="0.3">
@@ -19901,7 +19914,7 @@
         <v>1.1353505120355279E-4</v>
       </c>
       <c r="D1354" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1355" spans="1:4" x14ac:dyDescent="0.3">
@@ -19915,7 +19928,7 @@
         <v>9.6235116854031716E-5</v>
       </c>
       <c r="D1355" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1356" spans="1:4" x14ac:dyDescent="0.3">
@@ -19929,7 +19942,7 @@
         <v>9.351420594864407E-5</v>
       </c>
       <c r="D1356" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1357" spans="1:4" x14ac:dyDescent="0.3">
@@ -19943,7 +19956,7 @@
         <v>7.6445836777705995E-5</v>
       </c>
       <c r="D1357" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1358" spans="1:4" x14ac:dyDescent="0.3">
@@ -19957,7 +19970,7 @@
         <v>4.5666815810880438E-5</v>
       </c>
       <c r="D1358" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1359" spans="1:4" x14ac:dyDescent="0.3">
@@ -19971,7 +19984,7 @@
         <v>3.5526138327613027E-5</v>
       </c>
       <c r="D1359" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1360" spans="1:4" x14ac:dyDescent="0.3">
@@ -19985,7 +19998,7 @@
         <v>2.7257290514023469E-5</v>
       </c>
       <c r="D1360" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1361" spans="1:4" x14ac:dyDescent="0.3">
@@ -19999,7 +20012,7 @@
         <v>2.4169736971105708E-5</v>
       </c>
       <c r="D1361" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1362" spans="1:4" x14ac:dyDescent="0.3">
@@ -20013,7 +20026,7 @@
         <v>1.3845738169073241E-5</v>
       </c>
       <c r="D1362" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1363" spans="1:4" x14ac:dyDescent="0.3">
@@ -20027,7 +20040,7 @@
         <v>1.1587966535090351E-5</v>
       </c>
       <c r="D1363" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1364" spans="1:4" x14ac:dyDescent="0.3">
@@ -20041,7 +20054,7 @@
         <v>8.4328787198183987E-6</v>
       </c>
       <c r="D1364" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1365" spans="1:4" x14ac:dyDescent="0.3">
@@ -20055,7 +20068,7 @@
         <v>4.9979729519067539E-6</v>
       </c>
       <c r="D1365" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1366" spans="1:4" x14ac:dyDescent="0.3">
@@ -20069,7 +20082,7 @@
         <v>4.1874903697468097E-6</v>
       </c>
       <c r="D1366" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1367" spans="1:4" x14ac:dyDescent="0.3">
@@ -20083,7 +20096,7 @@
         <v>3.840138144752921E-6</v>
       </c>
       <c r="D1367" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1368" spans="1:4" x14ac:dyDescent="0.3">
@@ -20097,7 +20110,7 @@
         <v>2.9621212902387789E-6</v>
       </c>
       <c r="D1368" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1369" spans="1:4" x14ac:dyDescent="0.3">
@@ -20111,7 +20124,7 @@
         <v>9.9380390092500347E-7</v>
       </c>
       <c r="D1369" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1370" spans="1:4" x14ac:dyDescent="0.3">
@@ -20125,7 +20138,7 @@
         <v>8.8767097502095268E-7</v>
       </c>
       <c r="D1370" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1371" spans="1:4" x14ac:dyDescent="0.3">
@@ -20139,7 +20152,7 @@
         <v>2.8945424466911048E-7</v>
       </c>
       <c r="D1371" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1372" spans="1:4" x14ac:dyDescent="0.3">
@@ -20153,7 +20166,7 @@
         <v>1.9297543927187039E-7</v>
       </c>
       <c r="D1372" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1373" spans="1:4" x14ac:dyDescent="0.3">
@@ -20167,7 +20180,7 @@
         <v>1.7367611249694439E-7</v>
       </c>
       <c r="D1373" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1374" spans="1:4" x14ac:dyDescent="0.3">
@@ -20181,7 +20194,7 @@
         <v>0.32958971051824593</v>
       </c>
       <c r="D1374" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1375" spans="1:4" x14ac:dyDescent="0.3">
@@ -20195,7 +20208,7 @@
         <v>0.1439902741824694</v>
       </c>
       <c r="D1375" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1376" spans="1:4" x14ac:dyDescent="0.3">
@@ -20209,7 +20222,7 @@
         <v>0.11942472392886939</v>
       </c>
       <c r="D1376" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1377" spans="1:4" x14ac:dyDescent="0.3">
@@ -20223,7 +20236,7 @@
         <v>8.357280160471281E-2</v>
       </c>
       <c r="D1377" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1378" spans="1:4" x14ac:dyDescent="0.3">
@@ -20237,7 +20250,7 @@
         <v>5.156225747693205E-2</v>
       </c>
       <c r="D1378" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1379" spans="1:4" x14ac:dyDescent="0.3">
@@ -20251,7 +20264,7 @@
         <v>4.2137472311439543E-2</v>
       </c>
       <c r="D1379" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1380" spans="1:4" x14ac:dyDescent="0.3">
@@ -20265,7 +20278,7 @@
         <v>3.3455547839205783E-2</v>
       </c>
       <c r="D1380" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1381" spans="1:4" x14ac:dyDescent="0.3">
@@ -20279,7 +20292,7 @@
         <v>3.0954621492070188E-2</v>
       </c>
       <c r="D1381" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1382" spans="1:4" x14ac:dyDescent="0.3">
@@ -20293,7 +20306,7 @@
         <v>2.3914659898659572E-2</v>
       </c>
       <c r="D1382" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1383" spans="1:4" x14ac:dyDescent="0.3">
@@ -20307,7 +20320,7 @@
         <v>2.352734505768202E-2</v>
       </c>
       <c r="D1383" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1384" spans="1:4" x14ac:dyDescent="0.3">
@@ -20321,7 +20334,7 @@
         <v>2.065117988047405E-2</v>
       </c>
       <c r="D1384" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1385" spans="1:4" x14ac:dyDescent="0.3">
@@ -20335,7 +20348,7 @@
         <v>2.024037642803465E-2</v>
       </c>
       <c r="D1385" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1386" spans="1:4" x14ac:dyDescent="0.3">
@@ -20349,7 +20362,7 @@
         <v>1.390373534449965E-2</v>
       </c>
       <c r="D1386" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1387" spans="1:4" x14ac:dyDescent="0.3">
@@ -20363,7 +20376,7 @@
         <v>1.220479881195252E-2</v>
       </c>
       <c r="D1387" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1388" spans="1:4" x14ac:dyDescent="0.3">
@@ -20377,7 +20390,7 @@
         <v>1.064060906314282E-2</v>
       </c>
       <c r="D1388" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1389" spans="1:4" x14ac:dyDescent="0.3">
@@ -20391,7 +20404,7 @@
         <v>8.706148709696767E-3</v>
       </c>
       <c r="D1389" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1390" spans="1:4" x14ac:dyDescent="0.3">
@@ -20405,7 +20418,7 @@
         <v>6.6011994710765401E-3</v>
       </c>
       <c r="D1390" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1391" spans="1:4" x14ac:dyDescent="0.3">
@@ -20419,7 +20432,7 @@
         <v>5.5536637029825033E-3</v>
       </c>
       <c r="D1391" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1392" spans="1:4" x14ac:dyDescent="0.3">
@@ -20433,7 +20446,7 @@
         <v>3.883696866252501E-3</v>
       </c>
       <c r="D1392" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1393" spans="1:4" x14ac:dyDescent="0.3">
@@ -20447,7 +20460,7 @@
         <v>3.6386417371846178E-3</v>
       </c>
       <c r="D1393" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1394" spans="1:4" x14ac:dyDescent="0.3">
@@ -20461,7 +20474,7 @@
         <v>2.5916702338842322E-3</v>
       </c>
       <c r="D1394" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1395" spans="1:4" x14ac:dyDescent="0.3">
@@ -20475,7 +20488,7 @@
         <v>2.1027754095119672E-3</v>
       </c>
       <c r="D1395" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1396" spans="1:4" x14ac:dyDescent="0.3">
@@ -20489,7 +20502,7 @@
         <v>1.753677604199587E-3</v>
       </c>
       <c r="D1396" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1397" spans="1:4" x14ac:dyDescent="0.3">
@@ -20503,7 +20516,7 @@
         <v>9.3169125842405159E-4</v>
       </c>
       <c r="D1397" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1398" spans="1:4" x14ac:dyDescent="0.3">
@@ -20517,7 +20530,7 @@
         <v>8.7934800766504943E-4</v>
       </c>
       <c r="D1398" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1399" spans="1:4" x14ac:dyDescent="0.3">
@@ -20531,7 +20544,7 @@
         <v>8.4345045711676473E-4</v>
       </c>
       <c r="D1399" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1400" spans="1:4" x14ac:dyDescent="0.3">
@@ -20545,7 +20558,7 @@
         <v>6.7541080097213257E-4</v>
       </c>
       <c r="D1400" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1401" spans="1:4" x14ac:dyDescent="0.3">
@@ -20559,7 +20572,7 @@
         <v>6.0240883225000581E-4</v>
       </c>
       <c r="D1401" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1402" spans="1:4" x14ac:dyDescent="0.3">
@@ -20573,7 +20586,7 @@
         <v>3.2557736965858989E-4</v>
       </c>
       <c r="D1402" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1403" spans="1:4" x14ac:dyDescent="0.3">
@@ -20587,7 +20600,7 @@
         <v>2.349632268226027E-4</v>
       </c>
       <c r="D1403" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1404" spans="1:4" x14ac:dyDescent="0.3">
@@ -20601,7 +20614,7 @@
         <v>2.161882495229273E-4</v>
       </c>
       <c r="D1404" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1405" spans="1:4" x14ac:dyDescent="0.3">
@@ -20615,7 +20628,7 @@
         <v>1.5829169875597731E-4</v>
       </c>
       <c r="D1405" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1406" spans="1:4" x14ac:dyDescent="0.3">
@@ -20629,7 +20642,7 @@
         <v>1.4492191717989429E-4</v>
       </c>
       <c r="D1406" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1407" spans="1:4" x14ac:dyDescent="0.3">
@@ -20643,7 +20656,7 @@
         <v>6.7052091018183395E-5</v>
       </c>
       <c r="D1407" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1408" spans="1:4" x14ac:dyDescent="0.3">
@@ -20657,7 +20670,7 @@
         <v>6.3552667047068017E-5</v>
       </c>
       <c r="D1408" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1409" spans="1:4" x14ac:dyDescent="0.3">
@@ -20671,7 +20684,7 @@
         <v>6.3386203521856045E-5</v>
       </c>
       <c r="D1409" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1410" spans="1:4" x14ac:dyDescent="0.3">
@@ -20685,7 +20698,7 @@
         <v>5.4059302063110112E-5</v>
       </c>
       <c r="D1410" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1411" spans="1:4" x14ac:dyDescent="0.3">
@@ -20699,7 +20712,7 @@
         <v>3.4398147333031231E-5</v>
       </c>
       <c r="D1411" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1412" spans="1:4" x14ac:dyDescent="0.3">
@@ -20713,7 +20726,7 @@
         <v>2.316547525265156E-5</v>
       </c>
       <c r="D1412" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1413" spans="1:4" x14ac:dyDescent="0.3">
@@ -20727,7 +20740,7 @@
         <v>2.1694223250326011E-5</v>
       </c>
       <c r="D1413" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1414" spans="1:4" x14ac:dyDescent="0.3">
@@ -20741,7 +20754,7 @@
         <v>1.313232483980002E-5</v>
       </c>
       <c r="D1414" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1415" spans="1:4" x14ac:dyDescent="0.3">
@@ -20755,7 +20768,7 @@
         <v>1.040647118568991E-5</v>
       </c>
       <c r="D1415" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1416" spans="1:4" x14ac:dyDescent="0.3">
@@ -20769,7 +20782,7 @@
         <v>9.8067092210825484E-6</v>
       </c>
       <c r="D1416" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1417" spans="1:4" x14ac:dyDescent="0.3">
@@ -20783,7 +20796,7 @@
         <v>7.5545443362523753E-6</v>
       </c>
       <c r="D1417" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1418" spans="1:4" x14ac:dyDescent="0.3">
@@ -20797,7 +20810,7 @@
         <v>5.1909959104666623E-6</v>
       </c>
       <c r="D1418" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1419" spans="1:4" x14ac:dyDescent="0.3">
@@ -20811,7 +20824,7 @@
         <v>2.8103106854237182E-6</v>
       </c>
       <c r="D1419" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1420" spans="1:4" x14ac:dyDescent="0.3">
@@ -20825,7 +20838,7 @@
         <v>1.8213158520067239E-6</v>
       </c>
       <c r="D1420" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1421" spans="1:4" x14ac:dyDescent="0.3">
@@ -20839,7 +20852,7 @@
         <v>1.470027299039582E-6</v>
       </c>
       <c r="D1421" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1422" spans="1:4" x14ac:dyDescent="0.3">
@@ -20853,7 +20866,7 @@
         <v>1.2876505470130571E-6</v>
       </c>
       <c r="D1422" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1423" spans="1:4" x14ac:dyDescent="0.3">
@@ -20867,7 +20880,7 @@
         <v>1.0807944302299481E-6</v>
       </c>
       <c r="D1423" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1424" spans="1:4" x14ac:dyDescent="0.3">
@@ -20881,7 +20894,7 @@
         <v>1.050193810730101E-6</v>
       </c>
       <c r="D1424" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1425" spans="1:4" x14ac:dyDescent="0.3">
@@ -20895,7 +20908,7 @@
         <v>1.0281627217021629E-6</v>
       </c>
       <c r="D1425" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1426" spans="1:4" x14ac:dyDescent="0.3">
@@ -20909,7 +20922,7 @@
         <v>8.3109744614705352E-7</v>
       </c>
       <c r="D1426" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1427" spans="1:4" x14ac:dyDescent="0.3">
@@ -20923,7 +20936,7 @@
         <v>5.8507344107877451E-7</v>
       </c>
       <c r="D1427" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1428" spans="1:4" x14ac:dyDescent="0.3">
@@ -20937,7 +20950,7 @@
         <v>3.439448566244954E-7</v>
       </c>
       <c r="D1428" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1429" spans="1:4" x14ac:dyDescent="0.3">
@@ -20951,7 +20964,7 @@
         <v>1.6891293178390939E-7</v>
       </c>
       <c r="D1429" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1430" spans="1:4" x14ac:dyDescent="0.3">
@@ -20965,7 +20978,7 @@
         <v>1.113846717988319E-7</v>
       </c>
       <c r="D1430" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1431" spans="1:4" x14ac:dyDescent="0.3">
@@ -20979,7 +20992,7 @@
         <v>6.2423680599077334E-8</v>
       </c>
       <c r="D1431" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1432" spans="1:4" x14ac:dyDescent="0.3">
@@ -20993,7 +21006,7 @@
         <v>5.0184563642431357E-8</v>
       </c>
       <c r="D1432" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1433" spans="1:4" x14ac:dyDescent="0.3">
@@ -21007,7 +21020,7 @@
         <v>2.815234377120034E-8</v>
       </c>
       <c r="D1433" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1434" spans="1:4" x14ac:dyDescent="0.3">
@@ -21021,7 +21034,7 @@
         <v>1.7135668413938498E-8</v>
       </c>
       <c r="D1434" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1435" spans="1:4" x14ac:dyDescent="0.3">
@@ -21035,7 +21048,7 @@
         <v>7.3436963426461148E-9</v>
       </c>
       <c r="D1435" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1436" spans="1:4" x14ac:dyDescent="0.3">
@@ -21049,7 +21062,7 @@
         <v>4.8965514572925277E-9</v>
       </c>
       <c r="D1436" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1437" spans="1:4" x14ac:dyDescent="0.3">
@@ -21063,7 +21076,7 @@
         <v>2.4482757286462639E-9</v>
       </c>
       <c r="D1437" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1438" spans="1:4" x14ac:dyDescent="0.3">
@@ -21077,7 +21090,7 @@
         <v>0.87836999408727479</v>
       </c>
       <c r="D1438" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1439" spans="1:4" x14ac:dyDescent="0.3">
@@ -21091,7 +21104,7 @@
         <v>0.1022804011865803</v>
       </c>
       <c r="D1439" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1440" spans="1:4" x14ac:dyDescent="0.3">
@@ -21105,7 +21118,7 @@
         <v>6.2643733845971598E-3</v>
       </c>
       <c r="D1440" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1441" spans="1:4" x14ac:dyDescent="0.3">
@@ -21119,7 +21132,7 @@
         <v>6.1731338276210202E-3</v>
       </c>
       <c r="D1441" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1442" spans="1:4" x14ac:dyDescent="0.3">
@@ -21133,7 +21146,7 @@
         <v>3.6898204405822728E-3</v>
       </c>
       <c r="D1442" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1443" spans="1:4" x14ac:dyDescent="0.3">
@@ -21147,7 +21160,7 @@
         <v>1.9252236320753779E-3</v>
       </c>
       <c r="D1443" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1444" spans="1:4" x14ac:dyDescent="0.3">
@@ -21161,7 +21174,7 @@
         <v>2.1589589821120029E-4</v>
       </c>
       <c r="D1444" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1445" spans="1:4" x14ac:dyDescent="0.3">
@@ -21175,7 +21188,7 @@
         <v>1.486609750578159E-4</v>
       </c>
       <c r="D1445" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1446" spans="1:4" x14ac:dyDescent="0.3">
@@ -21189,7 +21202,7 @@
         <v>1.3727885689086399E-4</v>
       </c>
       <c r="D1446" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1447" spans="1:4" x14ac:dyDescent="0.3">
@@ -21203,7 +21216,7 @@
         <v>9.5179526142334119E-5</v>
       </c>
       <c r="D1447" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1448" spans="1:4" x14ac:dyDescent="0.3">
@@ -21217,7 +21230,7 @@
         <v>9.5070053530960002E-5</v>
       </c>
       <c r="D1448" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1449" spans="1:4" x14ac:dyDescent="0.3">
@@ -21231,7 +21244,7 @@
         <v>7.6282254763960876E-5</v>
       </c>
       <c r="D1449" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1450" spans="1:4" x14ac:dyDescent="0.3">
@@ -21245,7 +21258,7 @@
         <v>7.0408752563068687E-5</v>
       </c>
       <c r="D1450" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1451" spans="1:4" x14ac:dyDescent="0.3">
@@ -21259,7 +21272,7 @@
         <v>6.9679148616512239E-5</v>
       </c>
       <c r="D1451" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1452" spans="1:4" x14ac:dyDescent="0.3">
@@ -21273,7 +21286,7 @@
         <v>6.5228419612644456E-5</v>
       </c>
       <c r="D1452" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1453" spans="1:4" x14ac:dyDescent="0.3">
@@ -21287,7 +21300,7 @@
         <v>6.2930101456979261E-5</v>
       </c>
       <c r="D1453" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1454" spans="1:4" x14ac:dyDescent="0.3">
@@ -21301,7 +21314,7 @@
         <v>4.7790389832005843E-5</v>
       </c>
       <c r="D1454" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1455" spans="1:4" x14ac:dyDescent="0.3">
@@ -21315,7 +21328,7 @@
         <v>4.6841908071944639E-5</v>
       </c>
       <c r="D1455" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1456" spans="1:4" x14ac:dyDescent="0.3">
@@ -21329,7 +21342,7 @@
         <v>4.4434117304905327E-5</v>
       </c>
       <c r="D1456" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1457" spans="1:4" x14ac:dyDescent="0.3">
@@ -21343,7 +21356,7 @@
         <v>4.2208769655282303E-5</v>
       </c>
       <c r="D1457" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1458" spans="1:4" x14ac:dyDescent="0.3">
@@ -21357,7 +21370,7 @@
         <v>1.751100028668076E-5</v>
       </c>
       <c r="D1458" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1459" spans="1:4" x14ac:dyDescent="0.3">
@@ -21371,7 +21384,7 @@
         <v>1.678136263550258E-5</v>
       </c>
       <c r="D1459" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1460" spans="1:4" x14ac:dyDescent="0.3">
@@ -21385,7 +21398,7 @@
         <v>1.2403604137676961E-5</v>
       </c>
       <c r="D1460" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1461" spans="1:4" x14ac:dyDescent="0.3">
@@ -21399,7 +21412,7 @@
         <v>9.1567705173288265E-6</v>
       </c>
       <c r="D1461" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1462" spans="1:4" x14ac:dyDescent="0.3">
@@ -21413,7 +21426,7 @@
         <v>7.2962416932948861E-6</v>
       </c>
       <c r="D1462" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1463" spans="1:4" x14ac:dyDescent="0.3">
@@ -21427,7 +21440,7 @@
         <v>3.7940618587317701E-6</v>
       </c>
       <c r="D1463" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1464" spans="1:4" x14ac:dyDescent="0.3">
@@ -21441,7 +21454,7 @@
         <v>2.9914537015114259E-6</v>
       </c>
       <c r="D1464" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1465" spans="1:4" x14ac:dyDescent="0.3">
@@ -21455,7 +21468,7 @@
         <v>2.954985300801209E-6</v>
       </c>
       <c r="D1465" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1466" spans="1:4" x14ac:dyDescent="0.3">
@@ -21469,7 +21482,7 @@
         <v>1.751089917281558E-6</v>
       </c>
       <c r="D1466" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1467" spans="1:4" x14ac:dyDescent="0.3">
@@ -21483,7 +21496,7 @@
         <v>1.751089917281558E-6</v>
       </c>
       <c r="D1467" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1468" spans="1:4" x14ac:dyDescent="0.3">
@@ -21497,7 +21510,7 @@
         <v>1.6781531158611231E-6</v>
       </c>
       <c r="D1468" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1469" spans="1:4" x14ac:dyDescent="0.3">
@@ -21511,7 +21524,7 @@
         <v>9.1204706397272496E-7</v>
       </c>
       <c r="D1469" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1470" spans="1:4" x14ac:dyDescent="0.3">
@@ -21525,7 +21538,7 @@
         <v>7.2970506042163692E-8</v>
       </c>
       <c r="D1470" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1471" spans="1:4" x14ac:dyDescent="0.3">
@@ -21539,7 +21552,7 @@
         <v>7.2970506042163692E-8</v>
       </c>
       <c r="D1471" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1472" spans="1:4" x14ac:dyDescent="0.3">
@@ -21553,7 +21566,7 @@
         <v>3.6468400710217613E-8</v>
       </c>
       <c r="D1472" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1473" spans="1:4" x14ac:dyDescent="0.3">
@@ -21567,7 +21580,7 @@
         <v>0.42741836600679822</v>
       </c>
       <c r="D1473" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1474" spans="1:4" x14ac:dyDescent="0.3">
@@ -21581,7 +21594,7 @@
         <v>0.23194183742658761</v>
       </c>
       <c r="D1474" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1475" spans="1:4" x14ac:dyDescent="0.3">
@@ -21595,7 +21608,7 @@
         <v>0.1228856896939787</v>
       </c>
       <c r="D1475" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1476" spans="1:4" x14ac:dyDescent="0.3">
@@ -21609,7 +21622,7 @@
         <v>5.1049350592614798E-2</v>
       </c>
       <c r="D1476" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1477" spans="1:4" x14ac:dyDescent="0.3">
@@ -21623,7 +21636,7 @@
         <v>4.390896308500656E-2</v>
       </c>
       <c r="D1477" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1478" spans="1:4" x14ac:dyDescent="0.3">
@@ -21637,7 +21650,7 @@
         <v>3.8958776778428003E-2</v>
       </c>
       <c r="D1478" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1479" spans="1:4" x14ac:dyDescent="0.3">
@@ -21651,7 +21664,7 @@
         <v>3.5144775910885412E-2</v>
       </c>
       <c r="D1479" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1480" spans="1:4" x14ac:dyDescent="0.3">
@@ -21665,7 +21678,7 @@
         <v>9.4868755120319625E-3</v>
       </c>
       <c r="D1480" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1481" spans="1:4" x14ac:dyDescent="0.3">
@@ -21679,7 +21692,7 @@
         <v>8.8240623603318882E-3</v>
       </c>
       <c r="D1481" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1482" spans="1:4" x14ac:dyDescent="0.3">
@@ -21693,7 +21706,7 @@
         <v>5.5265766785084882E-3</v>
       </c>
       <c r="D1482" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1483" spans="1:4" x14ac:dyDescent="0.3">
@@ -21707,7 +21720,7 @@
         <v>5.0588883715352679E-3</v>
       </c>
       <c r="D1483" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1484" spans="1:4" x14ac:dyDescent="0.3">
@@ -21721,7 +21734,7 @@
         <v>3.689759932872641E-3</v>
       </c>
       <c r="D1484" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1485" spans="1:4" x14ac:dyDescent="0.3">
@@ -21735,7 +21748,7 @@
         <v>3.5569275668787511E-3</v>
       </c>
       <c r="D1485" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1486" spans="1:4" x14ac:dyDescent="0.3">
@@ -21749,7 +21762,7 @@
         <v>2.971693073144654E-3</v>
       </c>
       <c r="D1486" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1487" spans="1:4" x14ac:dyDescent="0.3">
@@ -21763,7 +21776,7 @@
         <v>2.3561480415623249E-3</v>
       </c>
       <c r="D1487" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1488" spans="1:4" x14ac:dyDescent="0.3">
@@ -21777,7 +21790,7 @@
         <v>1.5087955958247789E-3</v>
       </c>
       <c r="D1488" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1489" spans="1:4" x14ac:dyDescent="0.3">
@@ -21791,7 +21804,7 @@
         <v>1.447769607246667E-3</v>
       </c>
       <c r="D1489" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1490" spans="1:4" x14ac:dyDescent="0.3">
@@ -21805,7 +21818,7 @@
         <v>1.072233739221473E-3</v>
       </c>
       <c r="D1490" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1491" spans="1:4" x14ac:dyDescent="0.3">
@@ -21819,7 +21832,7 @@
         <v>8.1165019037452183E-4</v>
       </c>
       <c r="D1491" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1492" spans="1:4" x14ac:dyDescent="0.3">
@@ -21833,7 +21846,7 @@
         <v>5.9427346212475999E-4</v>
       </c>
       <c r="D1492" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1493" spans="1:4" x14ac:dyDescent="0.3">
@@ -21847,7 +21860,7 @@
         <v>5.7685921265096106E-4</v>
       </c>
       <c r="D1493" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1494" spans="1:4" x14ac:dyDescent="0.3">
@@ -21861,7 +21874,7 @@
         <v>5.2728644441928064E-4</v>
       </c>
       <c r="D1494" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1495" spans="1:4" x14ac:dyDescent="0.3">
@@ -21875,7 +21888,7 @@
         <v>2.5158111507023612E-4</v>
       </c>
       <c r="D1495" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1496" spans="1:4" x14ac:dyDescent="0.3">
@@ -21889,7 +21902,7 @@
         <v>1.572945191230434E-4</v>
       </c>
       <c r="D1496" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1497" spans="1:4" x14ac:dyDescent="0.3">
@@ -21903,7 +21916,7 @@
         <v>6.7239708185706025E-5</v>
       </c>
       <c r="D1497" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1498" spans="1:4" x14ac:dyDescent="0.3">
@@ -21917,7 +21930,7 @@
         <v>6.3583324359536698E-5</v>
       </c>
       <c r="D1498" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1499" spans="1:4" x14ac:dyDescent="0.3">
@@ -21931,7 +21944,7 @@
         <v>5.3326573944725328E-5</v>
       </c>
       <c r="D1499" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1500" spans="1:4" x14ac:dyDescent="0.3">
@@ -21945,7 +21958,7 @@
         <v>4.0268930218565399E-5</v>
       </c>
       <c r="D1500" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1501" spans="1:4" x14ac:dyDescent="0.3">
@@ -21959,7 +21972,7 @@
         <v>2.3375281413901099E-5</v>
       </c>
       <c r="D1501" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1502" spans="1:4" x14ac:dyDescent="0.3">
@@ -21973,7 +21986,7 @@
         <v>8.5183705342616939E-6</v>
       </c>
       <c r="D1502" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1503" spans="1:4" x14ac:dyDescent="0.3">
@@ -21987,7 +22000,7 @@
         <v>8.3265701396997282E-6</v>
       </c>
       <c r="D1503" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1504" spans="1:4" x14ac:dyDescent="0.3">
@@ -22001,7 +22014,7 @@
         <v>5.3277868626757384E-6</v>
       </c>
       <c r="D1504" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1505" spans="1:4" x14ac:dyDescent="0.3">
@@ -22015,7 +22028,7 @@
         <v>3.4767597610993442E-6</v>
       </c>
       <c r="D1505" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1506" spans="1:4" x14ac:dyDescent="0.3">
@@ -22029,7 +22042,7 @@
         <v>1.2177735859451921E-7</v>
       </c>
       <c r="D1506" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1507" spans="1:4" x14ac:dyDescent="0.3">
@@ -22043,7 +22056,7 @@
         <v>0.23231266198185591</v>
       </c>
       <c r="D1507" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1508" spans="1:4" x14ac:dyDescent="0.3">
@@ -22057,7 +22070,7 @@
         <v>0.17665037003903411</v>
       </c>
       <c r="D1508" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1509" spans="1:4" x14ac:dyDescent="0.3">
@@ -22071,7 +22084,7 @@
         <v>0.12631797309203549</v>
       </c>
       <c r="D1509" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1510" spans="1:4" x14ac:dyDescent="0.3">
@@ -22085,7 +22098,7 @@
         <v>7.732250425882245E-2</v>
       </c>
       <c r="D1510" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1511" spans="1:4" x14ac:dyDescent="0.3">
@@ -22099,7 +22112,7 @@
         <v>6.8893616817312375E-2</v>
       </c>
       <c r="D1511" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1512" spans="1:4" x14ac:dyDescent="0.3">
@@ -22113,7 +22126,7 @@
         <v>5.9026546581412501E-2</v>
       </c>
       <c r="D1512" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1513" spans="1:4" x14ac:dyDescent="0.3">
@@ -22127,7 +22140,7 @@
         <v>5.6542715745731463E-2</v>
       </c>
       <c r="D1513" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1514" spans="1:4" x14ac:dyDescent="0.3">
@@ -22141,7 +22154,7 @@
         <v>4.283141882555324E-2</v>
       </c>
       <c r="D1514" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1515" spans="1:4" x14ac:dyDescent="0.3">
@@ -22155,7 +22168,7 @@
         <v>2.3104945388067882E-2</v>
       </c>
       <c r="D1515" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1516" spans="1:4" x14ac:dyDescent="0.3">
@@ -22169,7 +22182,7 @@
         <v>1.6086889458059549E-2</v>
       </c>
       <c r="D1516" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1517" spans="1:4" x14ac:dyDescent="0.3">
@@ -22183,7 +22196,7 @@
         <v>1.533763834800073E-2</v>
       </c>
       <c r="D1517" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1518" spans="1:4" x14ac:dyDescent="0.3">
@@ -22197,7 +22210,7 @@
         <v>1.5328954618887451E-2</v>
       </c>
       <c r="D1518" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1519" spans="1:4" x14ac:dyDescent="0.3">
@@ -22211,7 +22224,7 @@
         <v>1.358797460055302E-2</v>
       </c>
       <c r="D1519" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1520" spans="1:4" x14ac:dyDescent="0.3">
@@ -22225,7 +22238,7 @@
         <v>1.356982375576244E-2</v>
       </c>
       <c r="D1520" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1521" spans="1:4" x14ac:dyDescent="0.3">
@@ -22239,7 +22252,7 @@
         <v>1.1213448772990769E-2</v>
       </c>
       <c r="D1521" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1522" spans="1:4" x14ac:dyDescent="0.3">
@@ -22253,7 +22266,7 @@
         <v>1.093223584842771E-2</v>
       </c>
       <c r="D1522" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1523" spans="1:4" x14ac:dyDescent="0.3">
@@ -22267,7 +22280,7 @@
         <v>1.0044295042365399E-2</v>
       </c>
       <c r="D1523" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1524" spans="1:4" x14ac:dyDescent="0.3">
@@ -22281,7 +22294,7 @@
         <v>7.5143120774281442E-3</v>
       </c>
       <c r="D1524" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1525" spans="1:4" x14ac:dyDescent="0.3">
@@ -22295,7 +22308,7 @@
         <v>5.4949859262126109E-3</v>
       </c>
       <c r="D1525" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1526" spans="1:4" x14ac:dyDescent="0.3">
@@ -22309,7 +22322,7 @@
         <v>3.5601803219793659E-3</v>
       </c>
       <c r="D1526" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1527" spans="1:4" x14ac:dyDescent="0.3">
@@ -22323,7 +22336,7 @@
         <v>3.0455566677094199E-3</v>
       </c>
       <c r="D1527" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1528" spans="1:4" x14ac:dyDescent="0.3">
@@ -22337,7 +22350,7 @@
         <v>1.975340796543532E-3</v>
       </c>
       <c r="D1528" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1529" spans="1:4" x14ac:dyDescent="0.3">
@@ -22351,7 +22364,7 @@
         <v>1.6715935086978461E-3</v>
       </c>
       <c r="D1529" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1530" spans="1:4" x14ac:dyDescent="0.3">
@@ -22365,7 +22378,7 @@
         <v>1.4220153698733661E-3</v>
       </c>
       <c r="D1530" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1531" spans="1:4" x14ac:dyDescent="0.3">
@@ -22379,7 +22392,7 @@
         <v>1.391713972033631E-3</v>
       </c>
       <c r="D1531" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1532" spans="1:4" x14ac:dyDescent="0.3">
@@ -22393,7 +22406,7 @@
         <v>6.6251378837096778E-4</v>
       </c>
       <c r="D1532" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1533" spans="1:4" x14ac:dyDescent="0.3">
@@ -22407,7 +22420,7 @@
         <v>5.2209067270010245E-4</v>
       </c>
       <c r="D1533" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1534" spans="1:4" x14ac:dyDescent="0.3">
@@ -22421,7 +22434,7 @@
         <v>5.1610705793170752E-4</v>
       </c>
       <c r="D1534" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1535" spans="1:4" x14ac:dyDescent="0.3">
@@ -22435,7 +22448,7 @@
         <v>4.74205123776516E-4</v>
       </c>
       <c r="D1535" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1536" spans="1:4" x14ac:dyDescent="0.3">
@@ -22449,7 +22462,7 @@
         <v>4.025685008871839E-4</v>
       </c>
       <c r="D1536" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1537" spans="1:4" x14ac:dyDescent="0.3">
@@ -22463,7 +22476,7 @@
         <v>3.5909983980056133E-4</v>
       </c>
       <c r="D1537" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1538" spans="1:4" x14ac:dyDescent="0.3">
@@ -22477,7 +22490,7 @@
         <v>2.9776368847615731E-4</v>
       </c>
       <c r="D1538" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1539" spans="1:4" x14ac:dyDescent="0.3">
@@ -22491,7 +22504,7 @@
         <v>2.9098004096845268E-4</v>
       </c>
       <c r="D1539" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1540" spans="1:4" x14ac:dyDescent="0.3">
@@ -22505,7 +22518,7 @@
         <v>2.3002724443954291E-4</v>
       </c>
       <c r="D1540" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1541" spans="1:4" x14ac:dyDescent="0.3">
@@ -22519,7 +22532,7 @@
         <v>1.6125741323217021E-4</v>
       </c>
       <c r="D1541" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1542" spans="1:4" x14ac:dyDescent="0.3">
@@ -22533,7 +22546,7 @@
         <v>1.2285564156004161E-4</v>
       </c>
       <c r="D1542" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1543" spans="1:4" x14ac:dyDescent="0.3">
@@ -22547,7 +22560,7 @@
         <v>8.593728894854173E-5</v>
       </c>
       <c r="D1543" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1544" spans="1:4" x14ac:dyDescent="0.3">
@@ -22561,7 +22574,7 @@
         <v>8.3187159083439823E-5</v>
       </c>
       <c r="D1544" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1545" spans="1:4" x14ac:dyDescent="0.3">
@@ -22575,7 +22588,7 @@
         <v>8.2003771548636023E-5</v>
       </c>
       <c r="D1545" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1546" spans="1:4" x14ac:dyDescent="0.3">
@@ -22589,7 +22602,7 @@
         <v>7.7636899231887561E-5</v>
       </c>
       <c r="D1546" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1547" spans="1:4" x14ac:dyDescent="0.3">
@@ -22603,7 +22616,7 @@
         <v>7.6486850244271743E-5</v>
       </c>
       <c r="D1547" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1548" spans="1:4" x14ac:dyDescent="0.3">
@@ -22617,7 +22630,7 @@
         <v>7.5153446946555494E-5</v>
       </c>
       <c r="D1548" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1549" spans="1:4" x14ac:dyDescent="0.3">
@@ -22631,7 +22644,7 @@
         <v>6.4402958890624304E-5</v>
       </c>
       <c r="D1549" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1550" spans="1:4" x14ac:dyDescent="0.3">
@@ -22645,7 +22658,7 @@
         <v>6.0869457860373357E-5</v>
       </c>
       <c r="D1550" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1551" spans="1:4" x14ac:dyDescent="0.3">
@@ -22659,7 +22672,7 @@
         <v>4.4468709710192967E-5</v>
       </c>
       <c r="D1551" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1552" spans="1:4" x14ac:dyDescent="0.3">
@@ -22673,7 +22686,7 @@
         <v>2.5801186733101901E-5</v>
       </c>
       <c r="D1552" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1553" spans="1:4" x14ac:dyDescent="0.3">
@@ -22687,7 +22700,7 @@
         <v>2.440112173987672E-5</v>
       </c>
       <c r="D1553" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1554" spans="1:4" x14ac:dyDescent="0.3">
@@ -22701,7 +22714,7 @@
         <v>2.1567653206238359E-5</v>
       </c>
       <c r="D1554" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1555" spans="1:4" x14ac:dyDescent="0.3">
@@ -22715,7 +22728,7 @@
         <v>1.6967441856908049E-5</v>
       </c>
       <c r="D1555" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1556" spans="1:4" x14ac:dyDescent="0.3">
@@ -22729,7 +22742,7 @@
         <v>7.5003415784775994E-6</v>
       </c>
       <c r="D1556" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1557" spans="1:4" x14ac:dyDescent="0.3">
@@ -22743,7 +22756,7 @@
         <v>6.8503092032134683E-6</v>
       </c>
       <c r="D1557" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1558" spans="1:4" x14ac:dyDescent="0.3">
@@ -22757,7 +22770,7 @@
         <v>6.3336310167013201E-6</v>
       </c>
       <c r="D1558" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1559" spans="1:4" x14ac:dyDescent="0.3">
@@ -22771,7 +22784,7 @@
         <v>5.0502278403335274E-6</v>
       </c>
       <c r="D1559" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1560" spans="1:4" x14ac:dyDescent="0.3">
@@ -22785,7 +22798,7 @@
         <v>3.183484781944658E-6</v>
       </c>
       <c r="D1560" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1561" spans="1:4" x14ac:dyDescent="0.3">
@@ -22799,7 +22812,7 @@
         <v>2.5167754336530001E-6</v>
       </c>
       <c r="D1561" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1562" spans="1:4" x14ac:dyDescent="0.3">
@@ -22813,7 +22826,7 @@
         <v>2.3334365224196181E-6</v>
       </c>
       <c r="D1562" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1563" spans="1:4" x14ac:dyDescent="0.3">
@@ -22827,7 +22840,7 @@
         <v>1.883420031416398E-6</v>
       </c>
       <c r="D1563" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1564" spans="1:4" x14ac:dyDescent="0.3">
@@ -22841,7 +22854,7 @@
         <v>1.666742572995022E-6</v>
       </c>
       <c r="D1564" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1565" spans="1:4" x14ac:dyDescent="0.3">
@@ -22855,7 +22868,7 @@
         <v>1.183387534803807E-6</v>
       </c>
       <c r="D1565" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1566" spans="1:4" x14ac:dyDescent="0.3">
@@ -22869,7 +22882,7 @@
         <v>9.1670995503396809E-7</v>
       </c>
       <c r="D1566" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1567" spans="1:4" x14ac:dyDescent="0.3">
@@ -22883,7 +22896,7 @@
         <v>6.5003237526412959E-7</v>
       </c>
       <c r="D1567" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1568" spans="1:4" x14ac:dyDescent="0.3">
@@ -22897,7 +22910,7 @@
         <v>5.0001661235168193E-7</v>
       </c>
       <c r="D1568" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1569" spans="1:4" x14ac:dyDescent="0.3">
@@ -22911,7 +22924,7 @@
         <v>3.6667782246676268E-7</v>
       </c>
       <c r="D1569" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1570" spans="1:4" x14ac:dyDescent="0.3">
@@ -22925,7 +22938,7 @@
         <v>2.6667757976983861E-7</v>
       </c>
       <c r="D1570" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1571" spans="1:4" x14ac:dyDescent="0.3">
@@ -22939,7 +22952,7 @@
         <v>2.333390325818434E-7</v>
       </c>
       <c r="D1571" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1572" spans="1:4" x14ac:dyDescent="0.3">
@@ -22953,7 +22966,7 @@
         <v>2.333390325818434E-7</v>
       </c>
       <c r="D1572" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1573" spans="1:4" x14ac:dyDescent="0.3">
@@ -22967,7 +22980,7 @@
         <v>1.6667733707291451E-7</v>
       </c>
       <c r="D1573" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1574" spans="1:4" x14ac:dyDescent="0.3">
@@ -22981,7 +22994,7 @@
         <v>6.6677094375990361E-8</v>
       </c>
       <c r="D1574" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1575" spans="1:4" x14ac:dyDescent="0.3">
@@ -22995,7 +23008,7 @@
         <v>1.6661574160466878E-8</v>
       </c>
       <c r="D1575" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1576" spans="1:4" x14ac:dyDescent="0.3">
@@ -23009,7 +23022,7 @@
         <v>1.6661574160466878E-8</v>
       </c>
       <c r="D1576" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1577" spans="1:4" x14ac:dyDescent="0.3">
@@ -23023,7 +23036,7 @@
         <v>0.31544723207531611</v>
       </c>
       <c r="D1577" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1578" spans="1:4" x14ac:dyDescent="0.3">
@@ -23037,7 +23050,7 @@
         <v>0.19847429324547089</v>
       </c>
       <c r="D1578" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1579" spans="1:4" x14ac:dyDescent="0.3">
@@ -23051,7 +23064,7 @@
         <v>0.17720741060638989</v>
       </c>
       <c r="D1579" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1580" spans="1:4" x14ac:dyDescent="0.3">
@@ -23065,7 +23078,7 @@
         <v>0.11378070925157351</v>
       </c>
       <c r="D1580" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1581" spans="1:4" x14ac:dyDescent="0.3">
@@ -23079,7 +23092,7 @@
         <v>4.4543672845349713E-2</v>
       </c>
       <c r="D1581" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1582" spans="1:4" x14ac:dyDescent="0.3">
@@ -23093,7 +23106,7 @@
         <v>3.1398634777178552E-2</v>
       </c>
       <c r="D1582" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1583" spans="1:4" x14ac:dyDescent="0.3">
@@ -23107,7 +23120,7 @@
         <v>1.2875841118903259E-2</v>
       </c>
       <c r="D1583" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1584" spans="1:4" x14ac:dyDescent="0.3">
@@ -23121,7 +23134,7 @@
         <v>1.2638719151433161E-2</v>
       </c>
       <c r="D1584" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1585" spans="1:4" x14ac:dyDescent="0.3">
@@ -23135,7 +23148,7 @@
         <v>9.5326517843563052E-3</v>
       </c>
       <c r="D1585" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1586" spans="1:4" x14ac:dyDescent="0.3">
@@ -23149,7 +23162,7 @@
         <v>9.3432904644371231E-3</v>
       </c>
       <c r="D1586" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1587" spans="1:4" x14ac:dyDescent="0.3">
@@ -23163,7 +23176,7 @@
         <v>7.6641393978782802E-3</v>
       </c>
       <c r="D1587" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1588" spans="1:4" x14ac:dyDescent="0.3">
@@ -23177,7 +23190,7 @@
         <v>6.7358392784492328E-3</v>
       </c>
       <c r="D1588" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1589" spans="1:4" x14ac:dyDescent="0.3">
@@ -23191,7 +23204,7 @@
         <v>6.4473201301457278E-3</v>
       </c>
       <c r="D1589" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1590" spans="1:4" x14ac:dyDescent="0.3">
@@ -23205,7 +23218,7 @@
         <v>6.0169699130478713E-3</v>
       </c>
       <c r="D1590" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1591" spans="1:4" x14ac:dyDescent="0.3">
@@ -23219,7 +23232,7 @@
         <v>5.9749006923533882E-3</v>
       </c>
       <c r="D1591" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1592" spans="1:4" x14ac:dyDescent="0.3">
@@ -23233,7 +23246,7 @@
         <v>5.7249512220656166E-3</v>
       </c>
       <c r="D1592" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1593" spans="1:4" x14ac:dyDescent="0.3">
@@ -23247,7 +23260,7 @@
         <v>5.3594421578416181E-3</v>
       </c>
       <c r="D1593" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1594" spans="1:4" x14ac:dyDescent="0.3">
@@ -23261,7 +23274,7 @@
         <v>4.880889174601521E-3</v>
       </c>
       <c r="D1594" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1595" spans="1:4" x14ac:dyDescent="0.3">
@@ -23275,7 +23288,7 @@
         <v>4.8387203233310524E-3</v>
       </c>
       <c r="D1595" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1596" spans="1:4" x14ac:dyDescent="0.3">
@@ -23289,7 +23302,7 @@
         <v>4.5699032221062329E-3</v>
       </c>
       <c r="D1596" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1597" spans="1:4" x14ac:dyDescent="0.3">
@@ -23303,7 +23316,7 @@
         <v>4.1612912598941428E-3</v>
       </c>
       <c r="D1597" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1598" spans="1:4" x14ac:dyDescent="0.3">
@@ -23317,7 +23330,7 @@
         <v>2.598994996265347E-3</v>
       </c>
       <c r="D1598" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1599" spans="1:4" x14ac:dyDescent="0.3">
@@ -23331,7 +23344,7 @@
         <v>1.8824794161659011E-3</v>
       </c>
       <c r="D1599" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1600" spans="1:4" x14ac:dyDescent="0.3">
@@ -23345,7 +23358,7 @@
         <v>1.3285243929734649E-3</v>
       </c>
       <c r="D1600" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1601" spans="1:4" x14ac:dyDescent="0.3">
@@ -23359,7 +23372,7 @@
         <v>1.175117439820895E-3</v>
       </c>
       <c r="D1601" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1602" spans="1:4" x14ac:dyDescent="0.3">
@@ -23373,7 +23386,7 @@
         <v>7.9691786338295602E-4</v>
       </c>
       <c r="D1602" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1603" spans="1:4" x14ac:dyDescent="0.3">
@@ -23387,7 +23400,7 @@
         <v>7.6786917615148231E-4</v>
       </c>
       <c r="D1603" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1604" spans="1:4" x14ac:dyDescent="0.3">
@@ -23401,7 +23414,7 @@
         <v>6.5786401271495916E-4</v>
       </c>
       <c r="D1604" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1605" spans="1:4" x14ac:dyDescent="0.3">
@@ -23415,7 +23428,7 @@
         <v>5.2044161704347433E-4</v>
       </c>
       <c r="D1605" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1606" spans="1:4" x14ac:dyDescent="0.3">
@@ -23429,7 +23442,7 @@
         <v>3.2084320654125878E-4</v>
       </c>
       <c r="D1606" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1607" spans="1:4" x14ac:dyDescent="0.3">
@@ -23443,7 +23456,7 @@
         <v>2.7554843012848711E-4</v>
       </c>
       <c r="D1607" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1608" spans="1:4" x14ac:dyDescent="0.3">
@@ -23457,7 +23470,7 @@
         <v>2.6615819944132761E-4</v>
       </c>
       <c r="D1608" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1609" spans="1:4" x14ac:dyDescent="0.3">
@@ -23471,7 +23484,7 @@
         <v>2.6422784696385313E-4</v>
       </c>
       <c r="D1609" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1610" spans="1:4" x14ac:dyDescent="0.3">
@@ -23485,7 +23498,7 @@
         <v>2.53909805818706E-4</v>
       </c>
       <c r="D1610" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1611" spans="1:4" x14ac:dyDescent="0.3">
@@ -23499,7 +23512,7 @@
         <v>1.9941782936411649E-4</v>
       </c>
       <c r="D1611" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1612" spans="1:4" x14ac:dyDescent="0.3">
@@ -23513,7 +23526,7 @@
         <v>1.8807234143198971E-4</v>
       </c>
       <c r="D1612" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1613" spans="1:4" x14ac:dyDescent="0.3">
@@ -23527,7 +23540,7 @@
         <v>1.322789369829649E-4</v>
       </c>
       <c r="D1613" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1614" spans="1:4" x14ac:dyDescent="0.3">
@@ -23541,7 +23554,7 @@
         <v>1.2659996538677651E-4</v>
       </c>
       <c r="D1614" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1615" spans="1:4" x14ac:dyDescent="0.3">
@@ -23555,7 +23568,7 @@
         <v>1.199122327704869E-4</v>
       </c>
       <c r="D1615" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1616" spans="1:4" x14ac:dyDescent="0.3">
@@ -23569,7 +23582,7 @@
         <v>1.190404566011063E-4</v>
       </c>
       <c r="D1616" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1617" spans="1:4" x14ac:dyDescent="0.3">
@@ -23583,7 +23596,7 @@
         <v>9.7775449827773071E-5</v>
       </c>
       <c r="D1617" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1618" spans="1:4" x14ac:dyDescent="0.3">
@@ -23597,7 +23610,7 @@
         <v>7.1429254914162339E-5</v>
       </c>
       <c r="D1618" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1619" spans="1:4" x14ac:dyDescent="0.3">
@@ -23611,7 +23624,7 @@
         <v>6.459207643389496E-5</v>
       </c>
       <c r="D1619" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1620" spans="1:4" x14ac:dyDescent="0.3">
@@ -23625,7 +23638,7 @@
         <v>4.2660785149779917E-5</v>
       </c>
       <c r="D1620" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1621" spans="1:4" x14ac:dyDescent="0.3">
@@ -23639,7 +23652,7 @@
         <v>2.8812060298753561E-5</v>
       </c>
       <c r="D1621" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1622" spans="1:4" x14ac:dyDescent="0.3">
@@ -23653,7 +23666,7 @@
         <v>2.2504169972533139E-5</v>
       </c>
       <c r="D1622" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1623" spans="1:4" x14ac:dyDescent="0.3">
@@ -23667,7 +23680,7 @@
         <v>1.6407996058532899E-5</v>
       </c>
       <c r="D1623" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1624" spans="1:4" x14ac:dyDescent="0.3">
@@ -23681,7 +23694,7 @@
         <v>1.6264774948176619E-5</v>
       </c>
       <c r="D1624" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1625" spans="1:4" x14ac:dyDescent="0.3">
@@ -23695,7 +23708,7 @@
         <v>1.0697889188223329E-5</v>
       </c>
       <c r="D1625" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1626" spans="1:4" x14ac:dyDescent="0.3">
@@ -23709,7 +23722,7 @@
         <v>6.7437784109107044E-6</v>
       </c>
       <c r="D1626" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1627" spans="1:4" x14ac:dyDescent="0.3">
@@ -23723,7 +23736,7 @@
         <v>5.5917962804530936E-6</v>
       </c>
       <c r="D1627" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1628" spans="1:4" x14ac:dyDescent="0.3">
@@ -23737,7 +23750,7 @@
         <v>1.4757843789128451E-6</v>
       </c>
       <c r="D1628" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1629" spans="1:4" x14ac:dyDescent="0.3">
@@ -23751,7 +23764,7 @@
         <v>1.382378556549133E-6</v>
       </c>
       <c r="D1629" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1630" spans="1:4" x14ac:dyDescent="0.3">
@@ -23765,7 +23778,7 @@
         <v>7.6591508676694506E-7</v>
       </c>
       <c r="D1630" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1631" spans="1:4" x14ac:dyDescent="0.3">
@@ -23779,7 +23792,7 @@
         <v>5.9778920891789789E-7</v>
       </c>
       <c r="D1631" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1632" spans="1:4" x14ac:dyDescent="0.3">
@@ -23793,7 +23806,7 @@
         <v>5.5419867454675657E-7</v>
       </c>
       <c r="D1632" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1633" spans="1:4" x14ac:dyDescent="0.3">
@@ -23807,7 +23820,7 @@
         <v>2.4285168634142591E-7</v>
       </c>
       <c r="D1633" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1634" spans="1:4" x14ac:dyDescent="0.3">
@@ -23821,7 +23834,7 @@
         <v>2.366211797129521E-7</v>
       </c>
       <c r="D1634" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1635" spans="1:4" x14ac:dyDescent="0.3">
@@ -23835,7 +23848,7 @@
         <v>1.120858362350461E-7</v>
       </c>
       <c r="D1635" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1636" spans="1:4" x14ac:dyDescent="0.3">
@@ -23849,7 +23862,7 @@
         <v>8.717531573523859E-8</v>
       </c>
       <c r="D1636" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1637" spans="1:4" x14ac:dyDescent="0.3">
@@ -23863,7 +23876,7 @@
         <v>2.49105204998075E-8</v>
       </c>
       <c r="D1637" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -23872,15 +23885,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="03763a1d-3ef6-4dac-84db-711c24c35716">
@@ -23888,6 +23892,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24069,19 +24082,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2543F6D-492F-4C9B-8AF7-7639E4005A4C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C50C39B-429F-409A-A7E6-0609DFF42D17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="03763a1d-3ef6-4dac-84db-711c24c35716"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C50C39B-429F-409A-A7E6-0609DFF42D17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2543F6D-492F-4C9B-8AF7-7639E4005A4C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="03763a1d-3ef6-4dac-84db-711c24c35716"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/material_market_share.xlsx
+++ b/data/material_market_share.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\GitHub\FLIM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607C465D-4EFC-41B1-9174-6FCC4236BA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA479B2-404B-41E5-8137-372E009CFCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -563,9 +563,6 @@
     <t>PE</t>
   </si>
   <si>
-    <t xml:space="preserve">Panelen van plantaardige vezels </t>
-  </si>
-  <si>
     <t>Hout - MDF</t>
   </si>
   <si>
@@ -594,6 +591,9 @@
   </si>
   <si>
     <t>Metaal (gerecycled)</t>
+  </si>
+  <si>
+    <t>Biocomposiet</t>
   </si>
 </sst>
 </file>
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -8840,7 +8840,7 @@
         <v>0.31020687415783721</v>
       </c>
       <c r="D563" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.3">
@@ -8854,7 +8854,7 @@
         <v>0.13747311891599531</v>
       </c>
       <c r="D564" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.3">
@@ -8868,7 +8868,7 @@
         <v>6.6851776484848968E-2</v>
       </c>
       <c r="D565" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.3">
@@ -8882,7 +8882,7 @@
         <v>5.606177855361269E-2</v>
       </c>
       <c r="D566" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.3">
@@ -8896,7 +8896,7 @@
         <v>5.5201117442186892E-2</v>
       </c>
       <c r="D567" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.3">
@@ -8910,7 +8910,7 @@
         <v>5.1137777799324068E-2</v>
       </c>
       <c r="D568" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.3">
@@ -8924,7 +8924,7 @@
         <v>3.2291764404665517E-2</v>
       </c>
       <c r="D569" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.3">
@@ -8938,7 +8938,7 @@
         <v>3.088262692698068E-2</v>
       </c>
       <c r="D570" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.3">
@@ -8952,7 +8952,7 @@
         <v>2.9367978846214421E-2</v>
       </c>
       <c r="D571" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.3">
@@ -8966,7 +8966,7 @@
         <v>2.556539746678109E-2</v>
       </c>
       <c r="D572" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.3">
@@ -8980,7 +8980,7 @@
         <v>2.1039164213287321E-2</v>
       </c>
       <c r="D573" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.3">
@@ -8994,7 +8994,7 @@
         <v>1.8666108725327799E-2</v>
       </c>
       <c r="D574" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.3">
@@ -9008,7 +9008,7 @@
         <v>1.791645157719882E-2</v>
       </c>
       <c r="D575" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.3">
@@ -9022,7 +9022,7 @@
         <v>1.317913025096094E-2</v>
       </c>
       <c r="D576" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.3">
@@ -9036,7 +9036,7 @@
         <v>1.262746471969523E-2</v>
       </c>
       <c r="D577" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.3">
@@ -9050,7 +9050,7 @@
         <v>1.2528306518743371E-2</v>
       </c>
       <c r="D578" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.3">
@@ -9064,7 +9064,7 @@
         <v>1.2117527851756269E-2</v>
       </c>
       <c r="D579" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.3">
@@ -9078,7 +9078,7 @@
         <v>9.6709912414705626E-3</v>
       </c>
       <c r="D580" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.3">
@@ -9092,7 +9092,7 @@
         <v>8.6924886345599289E-3</v>
       </c>
       <c r="D581" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.3">
@@ -9106,7 +9106,7 @@
         <v>7.0427977626547102E-3</v>
       </c>
       <c r="D582" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.3">
@@ -9120,7 +9120,7 @@
         <v>6.5467181388802398E-3</v>
       </c>
       <c r="D583" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
@@ -9134,7 +9134,7 @@
         <v>5.3597830494389511E-3</v>
       </c>
       <c r="D584" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.3">
@@ -9148,7 +9148,7 @@
         <v>5.0075754410211469E-3</v>
       </c>
       <c r="D585" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.3">
@@ -9162,7 +9162,7 @@
         <v>4.7853798754735827E-3</v>
       </c>
       <c r="D586" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.3">
@@ -9176,7 +9176,7 @@
         <v>4.5799782604338188E-3</v>
       </c>
       <c r="D587" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
@@ -9190,7 +9190,7 @@
         <v>4.4397723513941454E-3</v>
       </c>
       <c r="D588" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.3">
@@ -9204,7 +9204,7 @@
         <v>4.2590604971775997E-3</v>
       </c>
       <c r="D589" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.3">
@@ -9218,7 +9218,7 @@
         <v>4.2157611317290844E-3</v>
       </c>
       <c r="D590" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.3">
@@ -9232,7 +9232,7 @@
         <v>3.9749832548617433E-3</v>
       </c>
       <c r="D591" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.3">
@@ -9246,7 +9246,7 @@
         <v>3.3859504511888519E-3</v>
       </c>
       <c r="D592" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.3">
@@ -9260,7 +9260,7 @@
         <v>3.1864331665361419E-3</v>
       </c>
       <c r="D593" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.3">
@@ -9274,7 +9274,7 @@
         <v>3.0535697063807988E-3</v>
       </c>
       <c r="D594" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.3">
@@ -9288,7 +9288,7 @@
         <v>3.044960188985904E-3</v>
       </c>
       <c r="D595" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.3">
@@ -9302,7 +9302,7 @@
         <v>2.224697216197398E-3</v>
       </c>
       <c r="D596" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.3">
@@ -9316,7 +9316,7 @@
         <v>1.773710095137965E-3</v>
       </c>
       <c r="D597" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.3">
@@ -9330,7 +9330,7 @@
         <v>1.679895145003475E-3</v>
       </c>
       <c r="D598" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.3">
@@ -9344,7 +9344,7 @@
         <v>1.499919514086996E-3</v>
       </c>
       <c r="D599" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.3">
@@ -9358,7 +9358,7 @@
         <v>1.3446445610637891E-3</v>
       </c>
       <c r="D600" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.3">
@@ -9372,7 +9372,7 @@
         <v>1.301798939254915E-3</v>
       </c>
       <c r="D601" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
@@ -9386,7 +9386,7 @@
         <v>1.247143034633167E-3</v>
       </c>
       <c r="D602" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
@@ -9400,7 +9400,7 @@
         <v>1.060359893786529E-3</v>
       </c>
       <c r="D603" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
@@ -9414,7 +9414,7 @@
         <v>7.7652828680765127E-4</v>
       </c>
       <c r="D604" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
@@ -9428,7 +9428,7 @@
         <v>4.8608294946803429E-4</v>
       </c>
       <c r="D605" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
@@ -9442,7 +9442,7 @@
         <v>4.5575176401203268E-4</v>
       </c>
       <c r="D606" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.3">
@@ -9456,7 +9456,7 @@
         <v>3.4007390598622428E-4</v>
       </c>
       <c r="D607" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
@@ -9470,7 +9470,7 @@
         <v>2.8787298994291231E-4</v>
       </c>
       <c r="D608" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
@@ -9484,7 +9484,7 @@
         <v>2.7088526112646941E-4</v>
       </c>
       <c r="D609" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.3">
@@ -9498,7 +9498,7 @@
         <v>2.0572571736934169E-4</v>
       </c>
       <c r="D610" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.3">
@@ -9512,7 +9512,7 @@
         <v>7.7963284357581981E-5</v>
       </c>
       <c r="D611" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.3">
@@ -9526,7 +9526,7 @@
         <v>7.7582549805900558E-5</v>
       </c>
       <c r="D612" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.3">
@@ -9540,7 +9540,7 @@
         <v>7.2480158501351174E-5</v>
       </c>
       <c r="D613" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
@@ -9554,7 +9554,7 @@
         <v>6.9942609186643244E-5</v>
       </c>
       <c r="D614" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.3">
@@ -9568,7 +9568,7 @@
         <v>5.7952876167982442E-5</v>
       </c>
       <c r="D615" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.3">
@@ -9582,7 +9582,7 @@
         <v>5.6348741385950153E-5</v>
       </c>
       <c r="D616" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.3">
@@ -9596,7 +9596,7 @@
         <v>3.8372329975693292E-5</v>
       </c>
       <c r="D617" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.3">
@@ -9610,7 +9610,7 @@
         <v>3.1809091221548422E-5</v>
       </c>
       <c r="D618" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
@@ -9624,7 +9624,7 @@
         <v>2.6658937262723888E-5</v>
       </c>
       <c r="D619" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.3">
@@ -9638,7 +9638,7 @@
         <v>2.4263310489098941E-5</v>
       </c>
       <c r="D620" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.3">
@@ -9652,7 +9652,7 @@
         <v>2.2328932761979391E-5</v>
       </c>
       <c r="D621" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
@@ -9666,7 +9666,7 @@
         <v>2.0363850066147439E-5</v>
       </c>
       <c r="D622" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.3">
@@ -9680,7 +9680,7 @@
         <v>1.985825065894577E-5</v>
       </c>
       <c r="D623" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.3">
@@ -9694,7 +9694,7 @@
         <v>1.9207317047470858E-5</v>
       </c>
       <c r="D624" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.3">
@@ -9708,7 +9708,7 @@
         <v>1.427687054184564E-5</v>
       </c>
       <c r="D625" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
@@ -9722,7 +9722,7 @@
         <v>1.2134384512062819E-5</v>
       </c>
       <c r="D626" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
@@ -9736,7 +9736,7 @@
         <v>8.2192305645138114E-6</v>
       </c>
       <c r="D627" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
@@ -9750,7 +9750,7 @@
         <v>7.7729929621232997E-6</v>
       </c>
       <c r="D628" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.3">
@@ -9764,7 +9764,7 @@
         <v>7.2476062866512464E-6</v>
       </c>
       <c r="D629" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.3">
@@ -9778,7 +9778,7 @@
         <v>5.9887252634324753E-6</v>
       </c>
       <c r="D630" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.3">
@@ -9792,7 +9792,7 @@
         <v>4.9345402492980977E-6</v>
       </c>
       <c r="D631" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.3">
@@ -9806,7 +9806,7 @@
         <v>2.1349799925310602E-6</v>
       </c>
       <c r="D632" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.3">
@@ -9820,7 +9820,7 @@
         <v>2.0449138493961059E-6</v>
       </c>
       <c r="D633" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.3">
@@ -9834,7 +9834,7 @@
         <v>1.686695518304111E-6</v>
       </c>
       <c r="D634" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.3">
@@ -9848,7 +9848,7 @@
         <v>5.8952493482731016E-7</v>
       </c>
       <c r="D635" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.3">
@@ -9862,7 +9862,7 @@
         <v>4.735302775240411E-7</v>
       </c>
       <c r="D636" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.3">
@@ -9876,7 +9876,7 @@
         <v>4.694365338511658E-7</v>
       </c>
       <c r="D637" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.3">
@@ -9890,7 +9890,7 @@
         <v>4.1621534454932178E-7</v>
       </c>
       <c r="D638" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.3">
@@ -9904,7 +9904,7 @@
         <v>2.3062452325270749E-7</v>
       </c>
       <c r="D639" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.3">
@@ -9918,7 +9918,7 @@
         <v>2.2243640551834071E-7</v>
       </c>
       <c r="D640" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.3">
@@ -9932,7 +9932,7 @@
         <v>8.1195944917980258E-8</v>
       </c>
       <c r="D641" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.3">
@@ -9946,7 +9946,7 @@
         <v>7.6420120762497713E-8</v>
       </c>
       <c r="D642" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.3">
@@ -9960,7 +9960,7 @@
         <v>4.5033071567477118E-8</v>
       </c>
       <c r="D643" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.3">
@@ -9974,7 +9974,7 @@
         <v>4.4350991084869927E-8</v>
       </c>
       <c r="D644" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.3">
@@ -9988,7 +9988,7 @@
         <v>3.8892456058164093E-8</v>
       </c>
       <c r="D645" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.3">
@@ -10002,7 +10002,7 @@
         <v>2.7975386004752438E-8</v>
       </c>
       <c r="D646" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.3">
@@ -10016,7 +10016,7 @@
         <v>2.729267513352915E-8</v>
       </c>
       <c r="D647" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.3">
@@ -10030,7 +10030,7 @@
         <v>1.432873324367981E-8</v>
       </c>
       <c r="D648" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.3">
@@ -10044,7 +10044,7 @@
         <v>4.776454544098634E-9</v>
       </c>
       <c r="D649" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.3">
@@ -10058,7 +10058,7 @@
         <v>4.776454544098634E-9</v>
       </c>
       <c r="D650" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.3">
@@ -10072,7 +10072,7 @@
         <v>1.364791353830479E-9</v>
       </c>
       <c r="D651" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.3">
@@ -10086,7 +10086,7 @@
         <v>1.364791353830479E-9</v>
       </c>
       <c r="D652" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.3">
@@ -12018,7 +12018,7 @@
         <v>0.19389267234486021</v>
       </c>
       <c r="D790" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="791" spans="1:4" x14ac:dyDescent="0.3">
@@ -12032,7 +12032,7 @@
         <v>0.15870780556683819</v>
       </c>
       <c r="D791" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="792" spans="1:4" x14ac:dyDescent="0.3">
@@ -12046,7 +12046,7 @@
         <v>0.106662942147218</v>
       </c>
       <c r="D792" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="793" spans="1:4" x14ac:dyDescent="0.3">
@@ -12060,7 +12060,7 @@
         <v>9.921777319410334E-2</v>
       </c>
       <c r="D793" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="794" spans="1:4" x14ac:dyDescent="0.3">
@@ -12074,7 +12074,7 @@
         <v>7.0198696465555058E-2</v>
       </c>
       <c r="D794" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="795" spans="1:4" x14ac:dyDescent="0.3">
@@ -12088,7 +12088,7 @@
         <v>5.042597054702401E-2</v>
       </c>
       <c r="D795" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="796" spans="1:4" x14ac:dyDescent="0.3">
@@ -12102,7 +12102,7 @@
         <v>4.9963159247655937E-2</v>
       </c>
       <c r="D796" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="797" spans="1:4" x14ac:dyDescent="0.3">
@@ -12116,7 +12116,7 @@
         <v>4.7801099917873811E-2</v>
       </c>
       <c r="D797" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="798" spans="1:4" x14ac:dyDescent="0.3">
@@ -12130,7 +12130,7 @@
         <v>3.9507092206462008E-2</v>
       </c>
       <c r="D798" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="799" spans="1:4" x14ac:dyDescent="0.3">
@@ -12144,7 +12144,7 @@
         <v>3.5757959341955768E-2</v>
       </c>
       <c r="D799" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="800" spans="1:4" x14ac:dyDescent="0.3">
@@ -12158,7 +12158,7 @@
         <v>3.5126907795650787E-2</v>
       </c>
       <c r="D800" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="801" spans="1:4" x14ac:dyDescent="0.3">
@@ -12172,7 +12172,7 @@
         <v>3.0667551503928071E-2</v>
       </c>
       <c r="D801" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.3">
@@ -12186,7 +12186,7 @@
         <v>2.1333035920436609E-2</v>
       </c>
       <c r="D802" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="803" spans="1:4" x14ac:dyDescent="0.3">
@@ -12200,7 +12200,7 @@
         <v>1.7701542139876739E-2</v>
       </c>
       <c r="D803" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="804" spans="1:4" x14ac:dyDescent="0.3">
@@ -12214,7 +12214,7 @@
         <v>1.3401626820984889E-2</v>
       </c>
       <c r="D804" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="805" spans="1:4" x14ac:dyDescent="0.3">
@@ -12228,7 +12228,7 @@
         <v>9.28537738176256E-3</v>
       </c>
       <c r="D805" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="806" spans="1:4" x14ac:dyDescent="0.3">
@@ -12242,7 +12242,7 @@
         <v>7.785651073983324E-3</v>
       </c>
       <c r="D806" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.3">
@@ -12256,7 +12256,7 @@
         <v>3.6118083827668202E-3</v>
       </c>
       <c r="D807" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.3">
@@ -12270,7 +12270,7 @@
         <v>2.5451824124775408E-3</v>
       </c>
       <c r="D808" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="809" spans="1:4" x14ac:dyDescent="0.3">
@@ -12284,7 +12284,7 @@
         <v>1.904836782718311E-3</v>
       </c>
       <c r="D809" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.3">
@@ -12298,7 +12298,7 @@
         <v>1.897586515895759E-3</v>
       </c>
       <c r="D810" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="811" spans="1:4" x14ac:dyDescent="0.3">
@@ -12312,7 +12312,7 @@
         <v>4.2034244946168828E-4</v>
       </c>
       <c r="D811" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="812" spans="1:4" x14ac:dyDescent="0.3">
@@ -12326,7 +12326,7 @@
         <v>3.5394994323812459E-4</v>
       </c>
       <c r="D812" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="813" spans="1:4" x14ac:dyDescent="0.3">
@@ -12340,7 +12340,7 @@
         <v>3.2025888077813431E-4</v>
       </c>
       <c r="D813" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="814" spans="1:4" x14ac:dyDescent="0.3">
@@ -12354,7 +12354,7 @@
         <v>2.7432626605103871E-4</v>
       </c>
       <c r="D814" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="815" spans="1:4" x14ac:dyDescent="0.3">
@@ -12368,7 +12368,7 @@
         <v>2.1841112018813891E-4</v>
       </c>
       <c r="D815" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.3">
@@ -12382,7 +12382,7 @@
         <v>2.0474967936197209E-4</v>
       </c>
       <c r="D816" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="817" spans="1:4" x14ac:dyDescent="0.3">
@@ -12396,7 +12396,7 @@
         <v>2.028994613103132E-4</v>
       </c>
       <c r="D817" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="818" spans="1:4" x14ac:dyDescent="0.3">
@@ -12410,7 +12410,7 @@
         <v>1.5442820072665781E-4</v>
       </c>
       <c r="D818" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="819" spans="1:4" x14ac:dyDescent="0.3">
@@ -12424,7 +12424,7 @@
         <v>1.174239589533852E-4</v>
       </c>
       <c r="D819" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="820" spans="1:4" x14ac:dyDescent="0.3">
@@ -12438,7 +12438,7 @@
         <v>1.1101274519646861E-4</v>
       </c>
       <c r="D820" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.3">
@@ -12452,7 +12452,7 @@
         <v>5.7722330965299018E-5</v>
       </c>
       <c r="D821" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.3">
@@ -12466,7 +12466,7 @@
         <v>5.2795604882960992E-5</v>
       </c>
       <c r="D822" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.3">
@@ -12480,7 +12480,7 @@
         <v>4.03389276228591E-5</v>
       </c>
       <c r="D823" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="824" spans="1:4" x14ac:dyDescent="0.3">
@@ -12494,7 +12494,7 @@
         <v>3.5713412308688217E-5</v>
       </c>
       <c r="D824" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="825" spans="1:4" x14ac:dyDescent="0.3">
@@ -12508,7 +12508,7 @@
         <v>1.555469182708541E-5</v>
       </c>
       <c r="D825" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="826" spans="1:4" x14ac:dyDescent="0.3">
@@ -12522,7 +12522,7 @@
         <v>5.1203644156813231E-6</v>
       </c>
       <c r="D826" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="827" spans="1:4" x14ac:dyDescent="0.3">
@@ -12536,7 +12536,7 @@
         <v>4.8406800604695004E-6</v>
       </c>
       <c r="D827" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="828" spans="1:4" x14ac:dyDescent="0.3">
@@ -12550,7 +12550,7 @@
         <v>3.141067392894168E-6</v>
       </c>
       <c r="D828" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="829" spans="1:4" x14ac:dyDescent="0.3">
@@ -12564,7 +12564,7 @@
         <v>2.4525998346913479E-6</v>
       </c>
       <c r="D829" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="830" spans="1:4" x14ac:dyDescent="0.3">
@@ -12578,7 +12578,7 @@
         <v>2.2374748416945779E-6</v>
       </c>
       <c r="D830" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="831" spans="1:4" x14ac:dyDescent="0.3">
@@ -12592,7 +12592,7 @@
         <v>1.957790486482756E-6</v>
       </c>
       <c r="D831" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="832" spans="1:4" x14ac:dyDescent="0.3">
@@ -12606,7 +12606,7 @@
         <v>1.6350731820112081E-6</v>
       </c>
       <c r="D832" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="833" spans="1:4" x14ac:dyDescent="0.3">
@@ -12620,7 +12620,7 @@
         <v>1.2693229282799351E-6</v>
       </c>
       <c r="D833" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="834" spans="1:4" x14ac:dyDescent="0.3">
@@ -12634,7 +12634,7 @@
         <v>1.097211007891962E-6</v>
       </c>
       <c r="D834" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="835" spans="1:4" x14ac:dyDescent="0.3">
@@ -12648,7 +12648,7 @@
         <v>4.3032949259725328E-8</v>
       </c>
       <c r="D835" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="836" spans="1:4" x14ac:dyDescent="0.3">
@@ -12662,7 +12662,7 @@
         <v>0.49230269587589581</v>
       </c>
       <c r="D836" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="837" spans="1:4" x14ac:dyDescent="0.3">
@@ -12676,7 +12676,7 @@
         <v>0.11023519823071019</v>
       </c>
       <c r="D837" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="838" spans="1:4" x14ac:dyDescent="0.3">
@@ -12690,7 +12690,7 @@
         <v>5.5535601988050777E-2</v>
       </c>
       <c r="D838" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="839" spans="1:4" x14ac:dyDescent="0.3">
@@ -12704,7 +12704,7 @@
         <v>4.5296906380373952E-2</v>
       </c>
       <c r="D839" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="840" spans="1:4" x14ac:dyDescent="0.3">
@@ -12718,7 +12718,7 @@
         <v>4.331742754279938E-2</v>
       </c>
       <c r="D840" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="841" spans="1:4" x14ac:dyDescent="0.3">
@@ -12732,7 +12732,7 @@
         <v>3.069477602583242E-2</v>
       </c>
       <c r="D841" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="842" spans="1:4" x14ac:dyDescent="0.3">
@@ -12746,7 +12746,7 @@
         <v>2.9189195681513611E-2</v>
       </c>
       <c r="D842" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="843" spans="1:4" x14ac:dyDescent="0.3">
@@ -12760,7 +12760,7 @@
         <v>1.8984691713662939E-2</v>
       </c>
       <c r="D843" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="844" spans="1:4" x14ac:dyDescent="0.3">
@@ -12774,7 +12774,7 @@
         <v>1.7007184779190831E-2</v>
       </c>
       <c r="D844" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="845" spans="1:4" x14ac:dyDescent="0.3">
@@ -12788,7 +12788,7 @@
         <v>1.47171996372294E-2</v>
       </c>
       <c r="D845" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="846" spans="1:4" x14ac:dyDescent="0.3">
@@ -12802,7 +12802,7 @@
         <v>7.8638340075726093E-3</v>
       </c>
       <c r="D846" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="847" spans="1:4" x14ac:dyDescent="0.3">
@@ -12816,7 +12816,7 @@
         <v>7.8623564909186712E-3</v>
       </c>
       <c r="D847" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="848" spans="1:4" x14ac:dyDescent="0.3">
@@ -12830,7 +12830,7 @@
         <v>7.4777655950945942E-3</v>
       </c>
       <c r="D848" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="849" spans="1:4" x14ac:dyDescent="0.3">
@@ -12844,7 +12844,7 @@
         <v>6.8494556756922504E-3</v>
       </c>
       <c r="D849" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="850" spans="1:4" x14ac:dyDescent="0.3">
@@ -12858,7 +12858,7 @@
         <v>6.7544806206707919E-3</v>
       </c>
       <c r="D850" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="851" spans="1:4" x14ac:dyDescent="0.3">
@@ -12872,7 +12872,7 @@
         <v>6.2123589399165329E-3</v>
       </c>
       <c r="D851" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="852" spans="1:4" x14ac:dyDescent="0.3">
@@ -12886,7 +12886,7 @@
         <v>6.1137440451461871E-3</v>
       </c>
       <c r="D852" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="853" spans="1:4" x14ac:dyDescent="0.3">
@@ -12900,7 +12900,7 @@
         <v>6.0548838703763444E-3</v>
       </c>
       <c r="D853" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="854" spans="1:4" x14ac:dyDescent="0.3">
@@ -12914,7 +12914,7 @@
         <v>5.634374861343867E-3</v>
       </c>
       <c r="D854" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="855" spans="1:4" x14ac:dyDescent="0.3">
@@ -12928,7 +12928,7 @@
         <v>4.6041310320027277E-3</v>
       </c>
       <c r="D855" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="856" spans="1:4" x14ac:dyDescent="0.3">
@@ -12942,7 +12942,7 @@
         <v>4.5733979796779437E-3</v>
       </c>
       <c r="D856" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="857" spans="1:4" x14ac:dyDescent="0.3">
@@ -12956,7 +12956,7 @@
         <v>4.4466453840446537E-3</v>
       </c>
       <c r="D857" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="858" spans="1:4" x14ac:dyDescent="0.3">
@@ -12970,7 +12970,7 @@
         <v>4.2866814574447883E-3</v>
       </c>
       <c r="D858" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="859" spans="1:4" x14ac:dyDescent="0.3">
@@ -12984,7 +12984,7 @@
         <v>3.690185751588913E-3</v>
       </c>
       <c r="D859" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="860" spans="1:4" x14ac:dyDescent="0.3">
@@ -12998,7 +12998,7 @@
         <v>3.4305314103855022E-3</v>
       </c>
       <c r="D860" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="861" spans="1:4" x14ac:dyDescent="0.3">
@@ -13012,7 +13012,7 @@
         <v>3.359870849850176E-3</v>
       </c>
       <c r="D861" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="862" spans="1:4" x14ac:dyDescent="0.3">
@@ -13026,7 +13026,7 @@
         <v>2.9177929178431858E-3</v>
       </c>
       <c r="D862" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="863" spans="1:4" x14ac:dyDescent="0.3">
@@ -13040,7 +13040,7 @@
         <v>2.5361492969517602E-3</v>
       </c>
       <c r="D863" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="864" spans="1:4" x14ac:dyDescent="0.3">
@@ -13054,7 +13054,7 @@
         <v>2.4328098755059349E-3</v>
       </c>
       <c r="D864" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="865" spans="1:4" x14ac:dyDescent="0.3">
@@ -13068,7 +13068,7 @@
         <v>2.27740403442224E-3</v>
       </c>
       <c r="D865" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="866" spans="1:4" x14ac:dyDescent="0.3">
@@ -13082,7 +13082,7 @@
         <v>2.1374095042935009E-3</v>
       </c>
       <c r="D866" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="867" spans="1:4" x14ac:dyDescent="0.3">
@@ -13096,7 +13096,7 @@
         <v>2.0485645561019381E-3</v>
       </c>
       <c r="D867" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="868" spans="1:4" x14ac:dyDescent="0.3">
@@ -13110,7 +13110,7 @@
         <v>2.0388207040399069E-3</v>
       </c>
       <c r="D868" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="869" spans="1:4" x14ac:dyDescent="0.3">
@@ -13124,7 +13124,7 @@
         <v>1.9520823635533031E-3</v>
       </c>
       <c r="D869" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="870" spans="1:4" x14ac:dyDescent="0.3">
@@ -13138,7 +13138,7 @@
         <v>1.9391401634951629E-3</v>
       </c>
       <c r="D870" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="871" spans="1:4" x14ac:dyDescent="0.3">
@@ -13152,7 +13152,7 @@
         <v>1.934643434757469E-3</v>
       </c>
       <c r="D871" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="872" spans="1:4" x14ac:dyDescent="0.3">
@@ -13166,7 +13166,7 @@
         <v>1.6914068078853529E-3</v>
       </c>
       <c r="D872" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="873" spans="1:4" x14ac:dyDescent="0.3">
@@ -13180,7 +13180,7 @@
         <v>1.5710114133122401E-3</v>
       </c>
       <c r="D873" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="874" spans="1:4" x14ac:dyDescent="0.3">
@@ -13194,7 +13194,7 @@
         <v>1.5183187246207541E-3</v>
       </c>
       <c r="D874" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="875" spans="1:4" x14ac:dyDescent="0.3">
@@ -13208,7 +13208,7 @@
         <v>1.4468407687254999E-3</v>
       </c>
       <c r="D875" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="876" spans="1:4" x14ac:dyDescent="0.3">
@@ -13222,7 +13222,7 @@
         <v>1.3616025130530961E-3</v>
       </c>
       <c r="D876" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="877" spans="1:4" x14ac:dyDescent="0.3">
@@ -13236,7 +13236,7 @@
         <v>1.3538989742365661E-3</v>
       </c>
       <c r="D877" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="878" spans="1:4" x14ac:dyDescent="0.3">
@@ -13250,7 +13250,7 @@
         <v>1.279954023779653E-3</v>
       </c>
       <c r="D878" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="879" spans="1:4" x14ac:dyDescent="0.3">
@@ -13264,7 +13264,7 @@
         <v>1.17188795932319E-3</v>
       </c>
       <c r="D879" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="880" spans="1:4" x14ac:dyDescent="0.3">
@@ -13278,7 +13278,7 @@
         <v>1.161847192866512E-3</v>
       </c>
       <c r="D880" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="881" spans="1:4" x14ac:dyDescent="0.3">
@@ -13292,7 +13292,7 @@
         <v>1.066011722499759E-3</v>
       </c>
       <c r="D881" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="882" spans="1:4" x14ac:dyDescent="0.3">
@@ -13306,7 +13306,7 @@
         <v>9.8747553864536619E-4</v>
       </c>
       <c r="D882" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="883" spans="1:4" x14ac:dyDescent="0.3">
@@ -13320,7 +13320,7 @@
         <v>9.410215675210962E-4</v>
       </c>
       <c r="D883" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="884" spans="1:4" x14ac:dyDescent="0.3">
@@ -13334,7 +13334,7 @@
         <v>8.6640803238428388E-4</v>
       </c>
       <c r="D884" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="885" spans="1:4" x14ac:dyDescent="0.3">
@@ -13348,7 +13348,7 @@
         <v>7.9774970018374827E-4</v>
       </c>
       <c r="D885" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="886" spans="1:4" x14ac:dyDescent="0.3">
@@ -13362,7 +13362,7 @@
         <v>7.9169435054761959E-4</v>
       </c>
       <c r="D886" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="887" spans="1:4" x14ac:dyDescent="0.3">
@@ -13376,7 +13376,7 @@
         <v>6.6053670949059841E-4</v>
       </c>
       <c r="D887" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="888" spans="1:4" x14ac:dyDescent="0.3">
@@ -13390,7 +13390,7 @@
         <v>6.58997130395938E-4</v>
       </c>
       <c r="D888" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="889" spans="1:4" x14ac:dyDescent="0.3">
@@ -13404,7 +13404,7 @@
         <v>6.5010311460973649E-4</v>
       </c>
       <c r="D889" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="890" spans="1:4" x14ac:dyDescent="0.3">
@@ -13418,7 +13418,7 @@
         <v>6.2037928700711307E-4</v>
       </c>
       <c r="D890" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="891" spans="1:4" x14ac:dyDescent="0.3">
@@ -13432,7 +13432,7 @@
         <v>6.0643844064469786E-4</v>
       </c>
       <c r="D891" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="892" spans="1:4" x14ac:dyDescent="0.3">
@@ -13446,7 +13446,7 @@
         <v>6.0549268903617112E-4</v>
       </c>
       <c r="D892" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="893" spans="1:4" x14ac:dyDescent="0.3">
@@ -13460,7 +13460,7 @@
         <v>5.6563429597932956E-4</v>
       </c>
       <c r="D893" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="894" spans="1:4" x14ac:dyDescent="0.3">
@@ -13474,7 +13474,7 @@
         <v>5.5181263877212118E-4</v>
       </c>
       <c r="D894" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="895" spans="1:4" x14ac:dyDescent="0.3">
@@ -13488,7 +13488,7 @@
         <v>5.5068492990541858E-4</v>
       </c>
       <c r="D895" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="896" spans="1:4" x14ac:dyDescent="0.3">
@@ -13502,7 +13502,7 @@
         <v>4.9549280508479044E-4</v>
       </c>
       <c r="D896" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="897" spans="1:4" x14ac:dyDescent="0.3">
@@ -13516,7 +13516,7 @@
         <v>4.8108155175860252E-4</v>
       </c>
       <c r="D897" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="898" spans="1:4" x14ac:dyDescent="0.3">
@@ -13530,7 +13530,7 @@
         <v>4.7700374661342461E-4</v>
       </c>
       <c r="D898" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="899" spans="1:4" x14ac:dyDescent="0.3">
@@ -13544,7 +13544,7 @@
         <v>4.5774243040581892E-4</v>
       </c>
       <c r="D899" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="900" spans="1:4" x14ac:dyDescent="0.3">
@@ -13558,7 +13558,7 @@
         <v>4.47572601386714E-4</v>
       </c>
       <c r="D900" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="901" spans="1:4" x14ac:dyDescent="0.3">
@@ -13572,7 +13572,7 @@
         <v>4.1365037011395608E-4</v>
       </c>
       <c r="D901" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="902" spans="1:4" x14ac:dyDescent="0.3">
@@ -13586,7 +13586,7 @@
         <v>3.9008979722253672E-4</v>
       </c>
       <c r="D902" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="903" spans="1:4" x14ac:dyDescent="0.3">
@@ -13600,7 +13600,7 @@
         <v>3.6095415506598108E-4</v>
       </c>
       <c r="D903" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="904" spans="1:4" x14ac:dyDescent="0.3">
@@ -13614,7 +13614,7 @@
         <v>3.5792295389142819E-4</v>
       </c>
       <c r="D904" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="905" spans="1:4" x14ac:dyDescent="0.3">
@@ -13628,7 +13628,7 @@
         <v>3.5017780445928062E-4</v>
       </c>
       <c r="D905" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="906" spans="1:4" x14ac:dyDescent="0.3">
@@ -13642,7 +13642,7 @@
         <v>3.3526652199291772E-4</v>
       </c>
       <c r="D906" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="907" spans="1:4" x14ac:dyDescent="0.3">
@@ -13656,7 +13656,7 @@
         <v>3.2688099808119922E-4</v>
       </c>
       <c r="D907" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="908" spans="1:4" x14ac:dyDescent="0.3">
@@ -13670,7 +13670,7 @@
         <v>2.6129900402732301E-4</v>
       </c>
       <c r="D908" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="909" spans="1:4" x14ac:dyDescent="0.3">
@@ -13684,7 +13684,7 @@
         <v>2.5162920349681192E-4</v>
       </c>
       <c r="D909" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="910" spans="1:4" x14ac:dyDescent="0.3">
@@ -13698,7 +13698,7 @@
         <v>2.000289607587226E-4</v>
       </c>
       <c r="D910" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="911" spans="1:4" x14ac:dyDescent="0.3">
@@ -13712,7 +13712,7 @@
         <v>1.7610588467544401E-4</v>
       </c>
       <c r="D911" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="912" spans="1:4" x14ac:dyDescent="0.3">
@@ -13726,7 +13726,7 @@
         <v>1.6090826818706151E-4</v>
       </c>
       <c r="D912" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="913" spans="1:4" x14ac:dyDescent="0.3">
@@ -13740,7 +13740,7 @@
         <v>1.60421639462176E-4</v>
       </c>
       <c r="D913" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="914" spans="1:4" x14ac:dyDescent="0.3">
@@ -13754,7 +13754,7 @@
         <v>1.380910378208882E-4</v>
       </c>
       <c r="D914" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="915" spans="1:4" x14ac:dyDescent="0.3">
@@ -13768,7 +13768,7 @@
         <v>1.3252936897104151E-4</v>
       </c>
       <c r="D915" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="916" spans="1:4" x14ac:dyDescent="0.3">
@@ -13782,7 +13782,7 @@
         <v>1.264147769368517E-4</v>
       </c>
       <c r="D916" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="917" spans="1:4" x14ac:dyDescent="0.3">
@@ -13796,7 +13796,7 @@
         <v>1.2537663635211579E-4</v>
       </c>
       <c r="D917" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="918" spans="1:4" x14ac:dyDescent="0.3">
@@ -13810,7 +13810,7 @@
         <v>1.2244840257165699E-4</v>
       </c>
       <c r="D918" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="919" spans="1:4" x14ac:dyDescent="0.3">
@@ -13824,7 +13824,7 @@
         <v>1.1742414080728701E-4</v>
       </c>
       <c r="D919" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="920" spans="1:4" x14ac:dyDescent="0.3">
@@ -13838,7 +13838,7 @@
         <v>1.106543638569063E-4</v>
       </c>
       <c r="D920" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="921" spans="1:4" x14ac:dyDescent="0.3">
@@ -13852,7 +13852,7 @@
         <v>1.104759336068E-4</v>
       </c>
       <c r="D921" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="922" spans="1:4" x14ac:dyDescent="0.3">
@@ -13866,7 +13866,7 @@
         <v>1.014182973555314E-4</v>
       </c>
       <c r="D922" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="923" spans="1:4" x14ac:dyDescent="0.3">
@@ -13880,7 +13880,7 @@
         <v>9.4400269339097999E-5</v>
       </c>
       <c r="D923" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="924" spans="1:4" x14ac:dyDescent="0.3">
@@ -13894,7 +13894,7 @@
         <v>8.6011219070890755E-5</v>
       </c>
       <c r="D924" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="925" spans="1:4" x14ac:dyDescent="0.3">
@@ -13908,7 +13908,7 @@
         <v>6.5069270812239207E-5</v>
       </c>
       <c r="D925" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="926" spans="1:4" x14ac:dyDescent="0.3">
@@ -13922,7 +13922,7 @@
         <v>5.8706428363577821E-5</v>
       </c>
       <c r="D926" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="927" spans="1:4" x14ac:dyDescent="0.3">
@@ -13936,7 +13936,7 @@
         <v>4.9108564332590117E-5</v>
       </c>
       <c r="D927" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="928" spans="1:4" x14ac:dyDescent="0.3">
@@ -13950,7 +13950,7 @@
         <v>4.1131384943921597E-5</v>
       </c>
       <c r="D928" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="929" spans="1:4" x14ac:dyDescent="0.3">
@@ -13964,7 +13964,7 @@
         <v>4.042330533198136E-5</v>
       </c>
       <c r="D929" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="930" spans="1:4" x14ac:dyDescent="0.3">
@@ -13978,7 +13978,7 @@
         <v>3.4848941729091609E-5</v>
       </c>
       <c r="D930" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="931" spans="1:4" x14ac:dyDescent="0.3">
@@ -13992,7 +13992,7 @@
         <v>3.039805497416952E-5</v>
       </c>
       <c r="D931" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="932" spans="1:4" x14ac:dyDescent="0.3">
@@ -14006,7 +14006,7 @@
         <v>2.1019526146659579E-5</v>
       </c>
       <c r="D932" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="933" spans="1:4" x14ac:dyDescent="0.3">
@@ -14020,7 +14020,7 @@
         <v>1.9649208905551011E-5</v>
       </c>
       <c r="D933" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="934" spans="1:4" x14ac:dyDescent="0.3">
@@ -14034,7 +14034,7 @@
         <v>1.857227905102058E-5</v>
       </c>
       <c r="D934" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="935" spans="1:4" x14ac:dyDescent="0.3">
@@ -14048,7 +14048,7 @@
         <v>1.8271133940799741E-5</v>
       </c>
       <c r="D935" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="936" spans="1:4" x14ac:dyDescent="0.3">
@@ -14062,7 +14062,7 @@
         <v>1.8199197441276381E-5</v>
       </c>
       <c r="D936" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="937" spans="1:4" x14ac:dyDescent="0.3">
@@ -14076,7 +14076,7 @@
         <v>1.5964937846803101E-5</v>
       </c>
       <c r="D937" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="938" spans="1:4" x14ac:dyDescent="0.3">
@@ -14090,7 +14090,7 @@
         <v>1.0457573714036349E-5</v>
       </c>
       <c r="D938" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="939" spans="1:4" x14ac:dyDescent="0.3">
@@ -14104,7 +14104,7 @@
         <v>7.8213179504060922E-7</v>
       </c>
       <c r="D939" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="940" spans="1:4" x14ac:dyDescent="0.3">
@@ -14118,7 +14118,7 @@
         <v>2.3837765883287659E-7</v>
       </c>
       <c r="D940" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="941" spans="1:4" x14ac:dyDescent="0.3">
@@ -14132,7 +14132,7 @@
         <v>6.0652419391978331E-8</v>
       </c>
       <c r="D941" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="942" spans="1:4" x14ac:dyDescent="0.3">
@@ -14146,7 +14146,7 @@
         <v>2.2568160262776621E-8</v>
       </c>
       <c r="D942" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="943" spans="1:4" x14ac:dyDescent="0.3">
@@ -14160,7 +14160,7 @@
         <v>1.4106729116789291E-9</v>
       </c>
       <c r="D943" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="944" spans="1:4" x14ac:dyDescent="0.3">
@@ -14174,7 +14174,7 @@
         <v>7.0501066532868414E-10</v>
       </c>
       <c r="D944" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="945" spans="1:4" x14ac:dyDescent="0.3">
@@ -19102,7 +19102,7 @@
         <v>0.23737492362583121</v>
       </c>
       <c r="D1296" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1297" spans="1:4" x14ac:dyDescent="0.3">
@@ -19116,7 +19116,7 @@
         <v>0.21219499481822171</v>
       </c>
       <c r="D1297" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1298" spans="1:4" x14ac:dyDescent="0.3">
@@ -19130,7 +19130,7 @@
         <v>0.162788361975549</v>
       </c>
       <c r="D1298" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1299" spans="1:4" x14ac:dyDescent="0.3">
@@ -19144,7 +19144,7 @@
         <v>7.9087044945683083E-2</v>
       </c>
       <c r="D1299" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1300" spans="1:4" x14ac:dyDescent="0.3">
@@ -19158,7 +19158,7 @@
         <v>7.2520507730200634E-2</v>
       </c>
       <c r="D1300" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1301" spans="1:4" x14ac:dyDescent="0.3">
@@ -19172,7 +19172,7 @@
         <v>7.0790668383710759E-2</v>
       </c>
       <c r="D1301" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1302" spans="1:4" x14ac:dyDescent="0.3">
@@ -19186,7 +19186,7 @@
         <v>5.5722584688568493E-2</v>
       </c>
       <c r="D1302" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1303" spans="1:4" x14ac:dyDescent="0.3">
@@ -19200,7 +19200,7 @@
         <v>2.446083380614349E-2</v>
       </c>
       <c r="D1303" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1304" spans="1:4" x14ac:dyDescent="0.3">
@@ -19214,7 +19214,7 @@
         <v>2.30084890116336E-2</v>
       </c>
       <c r="D1304" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1305" spans="1:4" x14ac:dyDescent="0.3">
@@ -19228,7 +19228,7 @@
         <v>1.7819821194029379E-2</v>
       </c>
       <c r="D1305" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1306" spans="1:4" x14ac:dyDescent="0.3">
@@ -19242,7 +19242,7 @@
         <v>1.135321801871908E-2</v>
       </c>
       <c r="D1306" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1307" spans="1:4" x14ac:dyDescent="0.3">
@@ -19256,7 +19256,7 @@
         <v>9.5838652360301299E-3</v>
       </c>
       <c r="D1307" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1308" spans="1:4" x14ac:dyDescent="0.3">
@@ -19270,7 +19270,7 @@
         <v>8.3861571536461132E-3</v>
       </c>
       <c r="D1308" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1309" spans="1:4" x14ac:dyDescent="0.3">
@@ -19284,7 +19284,7 @@
         <v>6.1190347502964072E-3</v>
       </c>
       <c r="D1309" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1310" spans="1:4" x14ac:dyDescent="0.3">
@@ -19298,7 +19298,7 @@
         <v>2.6314965617182341E-3</v>
       </c>
       <c r="D1310" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1311" spans="1:4" x14ac:dyDescent="0.3">
@@ -19312,7 +19312,7 @@
         <v>1.644910412181428E-3</v>
       </c>
       <c r="D1311" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1312" spans="1:4" x14ac:dyDescent="0.3">
@@ -19326,7 +19326,7 @@
         <v>1.238221877458111E-3</v>
       </c>
       <c r="D1312" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1313" spans="1:4" x14ac:dyDescent="0.3">
@@ -19340,7 +19340,7 @@
         <v>1.0178467636477819E-3</v>
       </c>
       <c r="D1313" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1314" spans="1:4" x14ac:dyDescent="0.3">
@@ -19354,7 +19354,7 @@
         <v>7.9372044268685542E-4</v>
       </c>
       <c r="D1314" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1315" spans="1:4" x14ac:dyDescent="0.3">
@@ -19368,7 +19368,7 @@
         <v>6.3946785829053566E-4</v>
       </c>
       <c r="D1315" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1316" spans="1:4" x14ac:dyDescent="0.3">
@@ -19382,7 +19382,7 @@
         <v>3.5487088768666047E-4</v>
       </c>
       <c r="D1316" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1317" spans="1:4" x14ac:dyDescent="0.3">
@@ -19396,7 +19396,7 @@
         <v>2.0501987309831131E-4</v>
       </c>
       <c r="D1317" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1318" spans="1:4" x14ac:dyDescent="0.3">
@@ -19410,7 +19410,7 @@
         <v>5.5018767710534393E-5</v>
       </c>
       <c r="D1318" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1319" spans="1:4" x14ac:dyDescent="0.3">
@@ -19424,7 +19424,7 @@
         <v>3.6112317686565323E-5</v>
       </c>
       <c r="D1319" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1320" spans="1:4" x14ac:dyDescent="0.3">
@@ -19438,7 +19438,7 @@
         <v>3.4511780454737108E-5</v>
       </c>
       <c r="D1320" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1321" spans="1:4" x14ac:dyDescent="0.3">
@@ -19452,7 +19452,7 @@
         <v>3.1160615191652977E-5</v>
       </c>
       <c r="D1321" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1322" spans="1:4" x14ac:dyDescent="0.3">
@@ -19466,7 +19466,7 @@
         <v>2.270774905467183E-5</v>
       </c>
       <c r="D1322" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1323" spans="1:4" x14ac:dyDescent="0.3">
@@ -19480,7 +19480,7 @@
         <v>1.895644948363065E-5</v>
       </c>
       <c r="D1323" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1324" spans="1:4" x14ac:dyDescent="0.3">
@@ -19494,7 +19494,7 @@
         <v>1.870635976487981E-5</v>
       </c>
       <c r="D1324" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1325" spans="1:4" x14ac:dyDescent="0.3">
@@ -19508,7 +19508,7 @@
         <v>1.50051058637217E-5</v>
       </c>
       <c r="D1325" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1326" spans="1:4" x14ac:dyDescent="0.3">
@@ -19522,7 +19522,7 @@
         <v>1.2804344064847159E-5</v>
       </c>
       <c r="D1326" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1327" spans="1:4" x14ac:dyDescent="0.3">
@@ -19536,7 +19536,7 @@
         <v>8.8030009852766443E-6</v>
       </c>
       <c r="D1327" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1328" spans="1:4" x14ac:dyDescent="0.3">
@@ -19550,7 +19550,7 @@
         <v>4.8016579057061233E-6</v>
       </c>
       <c r="D1328" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1329" spans="1:4" x14ac:dyDescent="0.3">
@@ -19564,7 +19564,7 @@
         <v>2.3008069284191731E-6</v>
       </c>
       <c r="D1329" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1330" spans="1:4" x14ac:dyDescent="0.3">
@@ -19578,7 +19578,7 @@
         <v>1.9006264102406229E-6</v>
       </c>
       <c r="D1330" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1331" spans="1:4" x14ac:dyDescent="0.3">
@@ -19592,7 +19592,7 @@
         <v>1.150403464209587E-6</v>
       </c>
       <c r="D1331" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1332" spans="1:4" x14ac:dyDescent="0.3">
@@ -19606,7 +19606,7 @@
         <v>0.22183996193259301</v>
       </c>
       <c r="D1332" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1333" spans="1:4" x14ac:dyDescent="0.3">
@@ -19620,7 +19620,7 @@
         <v>0.17627334933169361</v>
       </c>
       <c r="D1333" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1334" spans="1:4" x14ac:dyDescent="0.3">
@@ -19634,7 +19634,7 @@
         <v>0.16298296550556901</v>
       </c>
       <c r="D1334" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1335" spans="1:4" x14ac:dyDescent="0.3">
@@ -19648,7 +19648,7 @@
         <v>0.12973584657735079</v>
       </c>
       <c r="D1335" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1336" spans="1:4" x14ac:dyDescent="0.3">
@@ -19662,7 +19662,7 @@
         <v>9.8035822407204667E-2</v>
       </c>
       <c r="D1336" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1337" spans="1:4" x14ac:dyDescent="0.3">
@@ -19676,7 +19676,7 @@
         <v>7.795736058557251E-2</v>
       </c>
       <c r="D1337" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1338" spans="1:4" x14ac:dyDescent="0.3">
@@ -19690,7 +19690,7 @@
         <v>3.7389792633098481E-2</v>
       </c>
       <c r="D1338" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1339" spans="1:4" x14ac:dyDescent="0.3">
@@ -19704,7 +19704,7 @@
         <v>2.4096379151411339E-2</v>
       </c>
       <c r="D1339" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1340" spans="1:4" x14ac:dyDescent="0.3">
@@ -19718,7 +19718,7 @@
         <v>1.747855066178898E-2</v>
       </c>
       <c r="D1340" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1341" spans="1:4" x14ac:dyDescent="0.3">
@@ -19732,7 +19732,7 @@
         <v>1.6146349468064852E-2</v>
       </c>
       <c r="D1341" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1342" spans="1:4" x14ac:dyDescent="0.3">
@@ -19746,7 +19746,7 @@
         <v>1.000557659770103E-2</v>
       </c>
       <c r="D1342" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1343" spans="1:4" x14ac:dyDescent="0.3">
@@ -19760,7 +19760,7 @@
         <v>9.0871748188303507E-3</v>
       </c>
       <c r="D1343" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1344" spans="1:4" x14ac:dyDescent="0.3">
@@ -19774,7 +19774,7 @@
         <v>6.3487869868839022E-3</v>
       </c>
       <c r="D1344" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1345" spans="1:4" x14ac:dyDescent="0.3">
@@ -19788,7 +19788,7 @@
         <v>3.3815151208409942E-3</v>
       </c>
       <c r="D1345" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1346" spans="1:4" x14ac:dyDescent="0.3">
@@ -19802,7 +19802,7 @@
         <v>3.037484715582931E-3</v>
       </c>
       <c r="D1346" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1347" spans="1:4" x14ac:dyDescent="0.3">
@@ -19816,7 +19816,7 @@
         <v>2.47120851367141E-3</v>
       </c>
       <c r="D1347" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1348" spans="1:4" x14ac:dyDescent="0.3">
@@ -19830,7 +19830,7 @@
         <v>1.247206691180198E-3</v>
       </c>
       <c r="D1348" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1349" spans="1:4" x14ac:dyDescent="0.3">
@@ -19844,7 +19844,7 @@
         <v>1.105999462965273E-3</v>
       </c>
       <c r="D1349" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1350" spans="1:4" x14ac:dyDescent="0.3">
@@ -19858,7 +19858,7 @@
         <v>2.4358849870750979E-4</v>
       </c>
       <c r="D1350" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1351" spans="1:4" x14ac:dyDescent="0.3">
@@ -19872,7 +19872,7 @@
         <v>2.2971381600539359E-4</v>
       </c>
       <c r="D1351" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1352" spans="1:4" x14ac:dyDescent="0.3">
@@ -19886,7 +19886,7 @@
         <v>1.9452537578226761E-4</v>
       </c>
       <c r="D1352" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1353" spans="1:4" x14ac:dyDescent="0.3">
@@ -19900,7 +19900,7 @@
         <v>1.4609906824092711E-4</v>
       </c>
       <c r="D1353" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1354" spans="1:4" x14ac:dyDescent="0.3">
@@ -19914,7 +19914,7 @@
         <v>1.1353505120355279E-4</v>
       </c>
       <c r="D1354" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1355" spans="1:4" x14ac:dyDescent="0.3">
@@ -19928,7 +19928,7 @@
         <v>9.6235116854031716E-5</v>
       </c>
       <c r="D1355" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1356" spans="1:4" x14ac:dyDescent="0.3">
@@ -19942,7 +19942,7 @@
         <v>9.351420594864407E-5</v>
       </c>
       <c r="D1356" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1357" spans="1:4" x14ac:dyDescent="0.3">
@@ -19956,7 +19956,7 @@
         <v>7.6445836777705995E-5</v>
       </c>
       <c r="D1357" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1358" spans="1:4" x14ac:dyDescent="0.3">
@@ -19970,7 +19970,7 @@
         <v>4.5666815810880438E-5</v>
       </c>
       <c r="D1358" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1359" spans="1:4" x14ac:dyDescent="0.3">
@@ -19984,7 +19984,7 @@
         <v>3.5526138327613027E-5</v>
       </c>
       <c r="D1359" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1360" spans="1:4" x14ac:dyDescent="0.3">
@@ -19998,7 +19998,7 @@
         <v>2.7257290514023469E-5</v>
       </c>
       <c r="D1360" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1361" spans="1:4" x14ac:dyDescent="0.3">
@@ -20012,7 +20012,7 @@
         <v>2.4169736971105708E-5</v>
       </c>
       <c r="D1361" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1362" spans="1:4" x14ac:dyDescent="0.3">
@@ -20026,7 +20026,7 @@
         <v>1.3845738169073241E-5</v>
       </c>
       <c r="D1362" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1363" spans="1:4" x14ac:dyDescent="0.3">
@@ -20040,7 +20040,7 @@
         <v>1.1587966535090351E-5</v>
       </c>
       <c r="D1363" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1364" spans="1:4" x14ac:dyDescent="0.3">
@@ -20054,7 +20054,7 @@
         <v>8.4328787198183987E-6</v>
       </c>
       <c r="D1364" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1365" spans="1:4" x14ac:dyDescent="0.3">
@@ -20068,7 +20068,7 @@
         <v>4.9979729519067539E-6</v>
       </c>
       <c r="D1365" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1366" spans="1:4" x14ac:dyDescent="0.3">
@@ -20082,7 +20082,7 @@
         <v>4.1874903697468097E-6</v>
       </c>
       <c r="D1366" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1367" spans="1:4" x14ac:dyDescent="0.3">
@@ -20096,7 +20096,7 @@
         <v>3.840138144752921E-6</v>
       </c>
       <c r="D1367" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1368" spans="1:4" x14ac:dyDescent="0.3">
@@ -20110,7 +20110,7 @@
         <v>2.9621212902387789E-6</v>
       </c>
       <c r="D1368" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1369" spans="1:4" x14ac:dyDescent="0.3">
@@ -20124,7 +20124,7 @@
         <v>9.9380390092500347E-7</v>
       </c>
       <c r="D1369" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1370" spans="1:4" x14ac:dyDescent="0.3">
@@ -20138,7 +20138,7 @@
         <v>8.8767097502095268E-7</v>
       </c>
       <c r="D1370" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1371" spans="1:4" x14ac:dyDescent="0.3">
@@ -20152,7 +20152,7 @@
         <v>2.8945424466911048E-7</v>
       </c>
       <c r="D1371" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1372" spans="1:4" x14ac:dyDescent="0.3">
@@ -20166,7 +20166,7 @@
         <v>1.9297543927187039E-7</v>
       </c>
       <c r="D1372" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1373" spans="1:4" x14ac:dyDescent="0.3">
@@ -20180,7 +20180,7 @@
         <v>1.7367611249694439E-7</v>
       </c>
       <c r="D1373" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1374" spans="1:4" x14ac:dyDescent="0.3">
@@ -20194,7 +20194,7 @@
         <v>0.32958971051824593</v>
       </c>
       <c r="D1374" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1375" spans="1:4" x14ac:dyDescent="0.3">
@@ -20208,7 +20208,7 @@
         <v>0.1439902741824694</v>
       </c>
       <c r="D1375" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1376" spans="1:4" x14ac:dyDescent="0.3">
@@ -20222,7 +20222,7 @@
         <v>0.11942472392886939</v>
       </c>
       <c r="D1376" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1377" spans="1:4" x14ac:dyDescent="0.3">
@@ -20236,7 +20236,7 @@
         <v>8.357280160471281E-2</v>
       </c>
       <c r="D1377" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1378" spans="1:4" x14ac:dyDescent="0.3">
@@ -20250,7 +20250,7 @@
         <v>5.156225747693205E-2</v>
       </c>
       <c r="D1378" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1379" spans="1:4" x14ac:dyDescent="0.3">
@@ -20264,7 +20264,7 @@
         <v>4.2137472311439543E-2</v>
       </c>
       <c r="D1379" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1380" spans="1:4" x14ac:dyDescent="0.3">
@@ -20278,7 +20278,7 @@
         <v>3.3455547839205783E-2</v>
       </c>
       <c r="D1380" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1381" spans="1:4" x14ac:dyDescent="0.3">
@@ -20292,7 +20292,7 @@
         <v>3.0954621492070188E-2</v>
       </c>
       <c r="D1381" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1382" spans="1:4" x14ac:dyDescent="0.3">
@@ -20306,7 +20306,7 @@
         <v>2.3914659898659572E-2</v>
       </c>
       <c r="D1382" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1383" spans="1:4" x14ac:dyDescent="0.3">
@@ -20320,7 +20320,7 @@
         <v>2.352734505768202E-2</v>
       </c>
       <c r="D1383" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1384" spans="1:4" x14ac:dyDescent="0.3">
@@ -20334,7 +20334,7 @@
         <v>2.065117988047405E-2</v>
       </c>
       <c r="D1384" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1385" spans="1:4" x14ac:dyDescent="0.3">
@@ -20348,7 +20348,7 @@
         <v>2.024037642803465E-2</v>
       </c>
       <c r="D1385" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1386" spans="1:4" x14ac:dyDescent="0.3">
@@ -20362,7 +20362,7 @@
         <v>1.390373534449965E-2</v>
       </c>
       <c r="D1386" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1387" spans="1:4" x14ac:dyDescent="0.3">
@@ -20376,7 +20376,7 @@
         <v>1.220479881195252E-2</v>
       </c>
       <c r="D1387" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1388" spans="1:4" x14ac:dyDescent="0.3">
@@ -20390,7 +20390,7 @@
         <v>1.064060906314282E-2</v>
       </c>
       <c r="D1388" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1389" spans="1:4" x14ac:dyDescent="0.3">
@@ -20404,7 +20404,7 @@
         <v>8.706148709696767E-3</v>
       </c>
       <c r="D1389" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1390" spans="1:4" x14ac:dyDescent="0.3">
@@ -20418,7 +20418,7 @@
         <v>6.6011994710765401E-3</v>
       </c>
       <c r="D1390" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1391" spans="1:4" x14ac:dyDescent="0.3">
@@ -20432,7 +20432,7 @@
         <v>5.5536637029825033E-3</v>
       </c>
       <c r="D1391" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1392" spans="1:4" x14ac:dyDescent="0.3">
@@ -20446,7 +20446,7 @@
         <v>3.883696866252501E-3</v>
       </c>
       <c r="D1392" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1393" spans="1:4" x14ac:dyDescent="0.3">
@@ -20460,7 +20460,7 @@
         <v>3.6386417371846178E-3</v>
       </c>
       <c r="D1393" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1394" spans="1:4" x14ac:dyDescent="0.3">
@@ -20474,7 +20474,7 @@
         <v>2.5916702338842322E-3</v>
       </c>
       <c r="D1394" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1395" spans="1:4" x14ac:dyDescent="0.3">
@@ -20488,7 +20488,7 @@
         <v>2.1027754095119672E-3</v>
       </c>
       <c r="D1395" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1396" spans="1:4" x14ac:dyDescent="0.3">
@@ -20502,7 +20502,7 @@
         <v>1.753677604199587E-3</v>
       </c>
       <c r="D1396" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1397" spans="1:4" x14ac:dyDescent="0.3">
@@ -20516,7 +20516,7 @@
         <v>9.3169125842405159E-4</v>
       </c>
       <c r="D1397" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1398" spans="1:4" x14ac:dyDescent="0.3">
@@ -20530,7 +20530,7 @@
         <v>8.7934800766504943E-4</v>
       </c>
       <c r="D1398" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1399" spans="1:4" x14ac:dyDescent="0.3">
@@ -20544,7 +20544,7 @@
         <v>8.4345045711676473E-4</v>
       </c>
       <c r="D1399" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1400" spans="1:4" x14ac:dyDescent="0.3">
@@ -20558,7 +20558,7 @@
         <v>6.7541080097213257E-4</v>
       </c>
       <c r="D1400" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1401" spans="1:4" x14ac:dyDescent="0.3">
@@ -20572,7 +20572,7 @@
         <v>6.0240883225000581E-4</v>
       </c>
       <c r="D1401" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1402" spans="1:4" x14ac:dyDescent="0.3">
@@ -20586,7 +20586,7 @@
         <v>3.2557736965858989E-4</v>
       </c>
       <c r="D1402" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1403" spans="1:4" x14ac:dyDescent="0.3">
@@ -20600,7 +20600,7 @@
         <v>2.349632268226027E-4</v>
       </c>
       <c r="D1403" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1404" spans="1:4" x14ac:dyDescent="0.3">
@@ -20614,7 +20614,7 @@
         <v>2.161882495229273E-4</v>
       </c>
       <c r="D1404" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1405" spans="1:4" x14ac:dyDescent="0.3">
@@ -20628,7 +20628,7 @@
         <v>1.5829169875597731E-4</v>
       </c>
       <c r="D1405" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1406" spans="1:4" x14ac:dyDescent="0.3">
@@ -20642,7 +20642,7 @@
         <v>1.4492191717989429E-4</v>
       </c>
       <c r="D1406" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1407" spans="1:4" x14ac:dyDescent="0.3">
@@ -20656,7 +20656,7 @@
         <v>6.7052091018183395E-5</v>
       </c>
       <c r="D1407" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1408" spans="1:4" x14ac:dyDescent="0.3">
@@ -20670,7 +20670,7 @@
         <v>6.3552667047068017E-5</v>
       </c>
       <c r="D1408" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1409" spans="1:4" x14ac:dyDescent="0.3">
@@ -20684,7 +20684,7 @@
         <v>6.3386203521856045E-5</v>
       </c>
       <c r="D1409" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1410" spans="1:4" x14ac:dyDescent="0.3">
@@ -20698,7 +20698,7 @@
         <v>5.4059302063110112E-5</v>
       </c>
       <c r="D1410" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1411" spans="1:4" x14ac:dyDescent="0.3">
@@ -20712,7 +20712,7 @@
         <v>3.4398147333031231E-5</v>
       </c>
       <c r="D1411" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1412" spans="1:4" x14ac:dyDescent="0.3">
@@ -20726,7 +20726,7 @@
         <v>2.316547525265156E-5</v>
       </c>
       <c r="D1412" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1413" spans="1:4" x14ac:dyDescent="0.3">
@@ -20740,7 +20740,7 @@
         <v>2.1694223250326011E-5</v>
       </c>
       <c r="D1413" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1414" spans="1:4" x14ac:dyDescent="0.3">
@@ -20754,7 +20754,7 @@
         <v>1.313232483980002E-5</v>
       </c>
       <c r="D1414" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1415" spans="1:4" x14ac:dyDescent="0.3">
@@ -20768,7 +20768,7 @@
         <v>1.040647118568991E-5</v>
       </c>
       <c r="D1415" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1416" spans="1:4" x14ac:dyDescent="0.3">
@@ -20782,7 +20782,7 @@
         <v>9.8067092210825484E-6</v>
       </c>
       <c r="D1416" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1417" spans="1:4" x14ac:dyDescent="0.3">
@@ -20796,7 +20796,7 @@
         <v>7.5545443362523753E-6</v>
       </c>
       <c r="D1417" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1418" spans="1:4" x14ac:dyDescent="0.3">
@@ -20810,7 +20810,7 @@
         <v>5.1909959104666623E-6</v>
       </c>
       <c r="D1418" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1419" spans="1:4" x14ac:dyDescent="0.3">
@@ -20824,7 +20824,7 @@
         <v>2.8103106854237182E-6</v>
       </c>
       <c r="D1419" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1420" spans="1:4" x14ac:dyDescent="0.3">
@@ -20838,7 +20838,7 @@
         <v>1.8213158520067239E-6</v>
       </c>
       <c r="D1420" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1421" spans="1:4" x14ac:dyDescent="0.3">
@@ -20852,7 +20852,7 @@
         <v>1.470027299039582E-6</v>
       </c>
       <c r="D1421" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1422" spans="1:4" x14ac:dyDescent="0.3">
@@ -20866,7 +20866,7 @@
         <v>1.2876505470130571E-6</v>
       </c>
       <c r="D1422" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1423" spans="1:4" x14ac:dyDescent="0.3">
@@ -20880,7 +20880,7 @@
         <v>1.0807944302299481E-6</v>
       </c>
       <c r="D1423" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1424" spans="1:4" x14ac:dyDescent="0.3">
@@ -20894,7 +20894,7 @@
         <v>1.050193810730101E-6</v>
       </c>
       <c r="D1424" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1425" spans="1:4" x14ac:dyDescent="0.3">
@@ -20908,7 +20908,7 @@
         <v>1.0281627217021629E-6</v>
       </c>
       <c r="D1425" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1426" spans="1:4" x14ac:dyDescent="0.3">
@@ -20922,7 +20922,7 @@
         <v>8.3109744614705352E-7</v>
       </c>
       <c r="D1426" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1427" spans="1:4" x14ac:dyDescent="0.3">
@@ -20936,7 +20936,7 @@
         <v>5.8507344107877451E-7</v>
       </c>
       <c r="D1427" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1428" spans="1:4" x14ac:dyDescent="0.3">
@@ -20950,7 +20950,7 @@
         <v>3.439448566244954E-7</v>
       </c>
       <c r="D1428" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1429" spans="1:4" x14ac:dyDescent="0.3">
@@ -20964,7 +20964,7 @@
         <v>1.6891293178390939E-7</v>
       </c>
       <c r="D1429" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1430" spans="1:4" x14ac:dyDescent="0.3">
@@ -20978,7 +20978,7 @@
         <v>1.113846717988319E-7</v>
       </c>
       <c r="D1430" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1431" spans="1:4" x14ac:dyDescent="0.3">
@@ -20992,7 +20992,7 @@
         <v>6.2423680599077334E-8</v>
       </c>
       <c r="D1431" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1432" spans="1:4" x14ac:dyDescent="0.3">
@@ -21006,7 +21006,7 @@
         <v>5.0184563642431357E-8</v>
       </c>
       <c r="D1432" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1433" spans="1:4" x14ac:dyDescent="0.3">
@@ -21020,7 +21020,7 @@
         <v>2.815234377120034E-8</v>
       </c>
       <c r="D1433" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1434" spans="1:4" x14ac:dyDescent="0.3">
@@ -21034,7 +21034,7 @@
         <v>1.7135668413938498E-8</v>
       </c>
       <c r="D1434" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1435" spans="1:4" x14ac:dyDescent="0.3">
@@ -21048,7 +21048,7 @@
         <v>7.3436963426461148E-9</v>
       </c>
       <c r="D1435" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1436" spans="1:4" x14ac:dyDescent="0.3">
@@ -21062,7 +21062,7 @@
         <v>4.8965514572925277E-9</v>
       </c>
       <c r="D1436" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1437" spans="1:4" x14ac:dyDescent="0.3">
@@ -21076,7 +21076,7 @@
         <v>2.4482757286462639E-9</v>
       </c>
       <c r="D1437" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1438" spans="1:4" x14ac:dyDescent="0.3">
@@ -21090,7 +21090,7 @@
         <v>0.87836999408727479</v>
       </c>
       <c r="D1438" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1439" spans="1:4" x14ac:dyDescent="0.3">
@@ -21104,7 +21104,7 @@
         <v>0.1022804011865803</v>
       </c>
       <c r="D1439" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1440" spans="1:4" x14ac:dyDescent="0.3">
@@ -21118,7 +21118,7 @@
         <v>6.2643733845971598E-3</v>
       </c>
       <c r="D1440" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1441" spans="1:4" x14ac:dyDescent="0.3">
@@ -21132,7 +21132,7 @@
         <v>6.1731338276210202E-3</v>
       </c>
       <c r="D1441" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1442" spans="1:4" x14ac:dyDescent="0.3">
@@ -21146,7 +21146,7 @@
         <v>3.6898204405822728E-3</v>
       </c>
       <c r="D1442" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1443" spans="1:4" x14ac:dyDescent="0.3">
@@ -21160,7 +21160,7 @@
         <v>1.9252236320753779E-3</v>
       </c>
       <c r="D1443" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1444" spans="1:4" x14ac:dyDescent="0.3">
@@ -21174,7 +21174,7 @@
         <v>2.1589589821120029E-4</v>
       </c>
       <c r="D1444" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1445" spans="1:4" x14ac:dyDescent="0.3">
@@ -21188,7 +21188,7 @@
         <v>1.486609750578159E-4</v>
       </c>
       <c r="D1445" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1446" spans="1:4" x14ac:dyDescent="0.3">
@@ -21202,7 +21202,7 @@
         <v>1.3727885689086399E-4</v>
       </c>
       <c r="D1446" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1447" spans="1:4" x14ac:dyDescent="0.3">
@@ -21216,7 +21216,7 @@
         <v>9.5179526142334119E-5</v>
       </c>
       <c r="D1447" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1448" spans="1:4" x14ac:dyDescent="0.3">
@@ -21230,7 +21230,7 @@
         <v>9.5070053530960002E-5</v>
       </c>
       <c r="D1448" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1449" spans="1:4" x14ac:dyDescent="0.3">
@@ -21244,7 +21244,7 @@
         <v>7.6282254763960876E-5</v>
       </c>
       <c r="D1449" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1450" spans="1:4" x14ac:dyDescent="0.3">
@@ -21258,7 +21258,7 @@
         <v>7.0408752563068687E-5</v>
       </c>
       <c r="D1450" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1451" spans="1:4" x14ac:dyDescent="0.3">
@@ -21272,7 +21272,7 @@
         <v>6.9679148616512239E-5</v>
       </c>
       <c r="D1451" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1452" spans="1:4" x14ac:dyDescent="0.3">
@@ -21286,7 +21286,7 @@
         <v>6.5228419612644456E-5</v>
       </c>
       <c r="D1452" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1453" spans="1:4" x14ac:dyDescent="0.3">
@@ -21300,7 +21300,7 @@
         <v>6.2930101456979261E-5</v>
       </c>
       <c r="D1453" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1454" spans="1:4" x14ac:dyDescent="0.3">
@@ -21314,7 +21314,7 @@
         <v>4.7790389832005843E-5</v>
       </c>
       <c r="D1454" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1455" spans="1:4" x14ac:dyDescent="0.3">
@@ -21328,7 +21328,7 @@
         <v>4.6841908071944639E-5</v>
       </c>
       <c r="D1455" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1456" spans="1:4" x14ac:dyDescent="0.3">
@@ -21342,7 +21342,7 @@
         <v>4.4434117304905327E-5</v>
       </c>
       <c r="D1456" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1457" spans="1:4" x14ac:dyDescent="0.3">
@@ -21356,7 +21356,7 @@
         <v>4.2208769655282303E-5</v>
       </c>
       <c r="D1457" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1458" spans="1:4" x14ac:dyDescent="0.3">
@@ -21370,7 +21370,7 @@
         <v>1.751100028668076E-5</v>
       </c>
       <c r="D1458" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1459" spans="1:4" x14ac:dyDescent="0.3">
@@ -21384,7 +21384,7 @@
         <v>1.678136263550258E-5</v>
       </c>
       <c r="D1459" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1460" spans="1:4" x14ac:dyDescent="0.3">
@@ -21398,7 +21398,7 @@
         <v>1.2403604137676961E-5</v>
       </c>
       <c r="D1460" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1461" spans="1:4" x14ac:dyDescent="0.3">
@@ -21412,7 +21412,7 @@
         <v>9.1567705173288265E-6</v>
       </c>
       <c r="D1461" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1462" spans="1:4" x14ac:dyDescent="0.3">
@@ -21426,7 +21426,7 @@
         <v>7.2962416932948861E-6</v>
       </c>
       <c r="D1462" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1463" spans="1:4" x14ac:dyDescent="0.3">
@@ -21440,7 +21440,7 @@
         <v>3.7940618587317701E-6</v>
       </c>
       <c r="D1463" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1464" spans="1:4" x14ac:dyDescent="0.3">
@@ -21454,7 +21454,7 @@
         <v>2.9914537015114259E-6</v>
       </c>
       <c r="D1464" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1465" spans="1:4" x14ac:dyDescent="0.3">
@@ -21468,7 +21468,7 @@
         <v>2.954985300801209E-6</v>
       </c>
       <c r="D1465" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1466" spans="1:4" x14ac:dyDescent="0.3">
@@ -21482,7 +21482,7 @@
         <v>1.751089917281558E-6</v>
       </c>
       <c r="D1466" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1467" spans="1:4" x14ac:dyDescent="0.3">
@@ -21496,7 +21496,7 @@
         <v>1.751089917281558E-6</v>
       </c>
       <c r="D1467" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1468" spans="1:4" x14ac:dyDescent="0.3">
@@ -21510,7 +21510,7 @@
         <v>1.6781531158611231E-6</v>
       </c>
       <c r="D1468" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1469" spans="1:4" x14ac:dyDescent="0.3">
@@ -21524,7 +21524,7 @@
         <v>9.1204706397272496E-7</v>
       </c>
       <c r="D1469" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1470" spans="1:4" x14ac:dyDescent="0.3">
@@ -21538,7 +21538,7 @@
         <v>7.2970506042163692E-8</v>
       </c>
       <c r="D1470" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1471" spans="1:4" x14ac:dyDescent="0.3">
@@ -21552,7 +21552,7 @@
         <v>7.2970506042163692E-8</v>
       </c>
       <c r="D1471" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1472" spans="1:4" x14ac:dyDescent="0.3">
@@ -21566,7 +21566,7 @@
         <v>3.6468400710217613E-8</v>
       </c>
       <c r="D1472" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1473" spans="1:4" x14ac:dyDescent="0.3">
@@ -21580,7 +21580,7 @@
         <v>0.42741836600679822</v>
       </c>
       <c r="D1473" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1474" spans="1:4" x14ac:dyDescent="0.3">
@@ -21594,7 +21594,7 @@
         <v>0.23194183742658761</v>
       </c>
       <c r="D1474" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1475" spans="1:4" x14ac:dyDescent="0.3">
@@ -21608,7 +21608,7 @@
         <v>0.1228856896939787</v>
       </c>
       <c r="D1475" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1476" spans="1:4" x14ac:dyDescent="0.3">
@@ -21622,7 +21622,7 @@
         <v>5.1049350592614798E-2</v>
       </c>
       <c r="D1476" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1477" spans="1:4" x14ac:dyDescent="0.3">
@@ -21636,7 +21636,7 @@
         <v>4.390896308500656E-2</v>
       </c>
       <c r="D1477" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1478" spans="1:4" x14ac:dyDescent="0.3">
@@ -21650,7 +21650,7 @@
         <v>3.8958776778428003E-2</v>
       </c>
       <c r="D1478" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1479" spans="1:4" x14ac:dyDescent="0.3">
@@ -21664,7 +21664,7 @@
         <v>3.5144775910885412E-2</v>
       </c>
       <c r="D1479" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1480" spans="1:4" x14ac:dyDescent="0.3">
@@ -21678,7 +21678,7 @@
         <v>9.4868755120319625E-3</v>
       </c>
       <c r="D1480" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1481" spans="1:4" x14ac:dyDescent="0.3">
@@ -21692,7 +21692,7 @@
         <v>8.8240623603318882E-3</v>
       </c>
       <c r="D1481" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1482" spans="1:4" x14ac:dyDescent="0.3">
@@ -21706,7 +21706,7 @@
         <v>5.5265766785084882E-3</v>
       </c>
       <c r="D1482" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1483" spans="1:4" x14ac:dyDescent="0.3">
@@ -21720,7 +21720,7 @@
         <v>5.0588883715352679E-3</v>
       </c>
       <c r="D1483" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1484" spans="1:4" x14ac:dyDescent="0.3">
@@ -21734,7 +21734,7 @@
         <v>3.689759932872641E-3</v>
       </c>
       <c r="D1484" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1485" spans="1:4" x14ac:dyDescent="0.3">
@@ -21748,7 +21748,7 @@
         <v>3.5569275668787511E-3</v>
       </c>
       <c r="D1485" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1486" spans="1:4" x14ac:dyDescent="0.3">
@@ -21762,7 +21762,7 @@
         <v>2.971693073144654E-3</v>
       </c>
       <c r="D1486" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1487" spans="1:4" x14ac:dyDescent="0.3">
@@ -21776,7 +21776,7 @@
         <v>2.3561480415623249E-3</v>
       </c>
       <c r="D1487" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1488" spans="1:4" x14ac:dyDescent="0.3">
@@ -21790,7 +21790,7 @@
         <v>1.5087955958247789E-3</v>
       </c>
       <c r="D1488" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1489" spans="1:4" x14ac:dyDescent="0.3">
@@ -21804,7 +21804,7 @@
         <v>1.447769607246667E-3</v>
       </c>
       <c r="D1489" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1490" spans="1:4" x14ac:dyDescent="0.3">
@@ -21818,7 +21818,7 @@
         <v>1.072233739221473E-3</v>
       </c>
       <c r="D1490" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1491" spans="1:4" x14ac:dyDescent="0.3">
@@ -21832,7 +21832,7 @@
         <v>8.1165019037452183E-4</v>
       </c>
       <c r="D1491" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1492" spans="1:4" x14ac:dyDescent="0.3">
@@ -21846,7 +21846,7 @@
         <v>5.9427346212475999E-4</v>
       </c>
       <c r="D1492" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1493" spans="1:4" x14ac:dyDescent="0.3">
@@ -21860,7 +21860,7 @@
         <v>5.7685921265096106E-4</v>
       </c>
       <c r="D1493" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1494" spans="1:4" x14ac:dyDescent="0.3">
@@ -21874,7 +21874,7 @@
         <v>5.2728644441928064E-4</v>
       </c>
       <c r="D1494" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1495" spans="1:4" x14ac:dyDescent="0.3">
@@ -21888,7 +21888,7 @@
         <v>2.5158111507023612E-4</v>
       </c>
       <c r="D1495" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1496" spans="1:4" x14ac:dyDescent="0.3">
@@ -21902,7 +21902,7 @@
         <v>1.572945191230434E-4</v>
       </c>
       <c r="D1496" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1497" spans="1:4" x14ac:dyDescent="0.3">
@@ -21916,7 +21916,7 @@
         <v>6.7239708185706025E-5</v>
       </c>
       <c r="D1497" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1498" spans="1:4" x14ac:dyDescent="0.3">
@@ -21930,7 +21930,7 @@
         <v>6.3583324359536698E-5</v>
       </c>
       <c r="D1498" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1499" spans="1:4" x14ac:dyDescent="0.3">
@@ -21944,7 +21944,7 @@
         <v>5.3326573944725328E-5</v>
       </c>
       <c r="D1499" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1500" spans="1:4" x14ac:dyDescent="0.3">
@@ -21958,7 +21958,7 @@
         <v>4.0268930218565399E-5</v>
       </c>
       <c r="D1500" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1501" spans="1:4" x14ac:dyDescent="0.3">
@@ -21972,7 +21972,7 @@
         <v>2.3375281413901099E-5</v>
       </c>
       <c r="D1501" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1502" spans="1:4" x14ac:dyDescent="0.3">
@@ -21986,7 +21986,7 @@
         <v>8.5183705342616939E-6</v>
       </c>
       <c r="D1502" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1503" spans="1:4" x14ac:dyDescent="0.3">
@@ -22000,7 +22000,7 @@
         <v>8.3265701396997282E-6</v>
       </c>
       <c r="D1503" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1504" spans="1:4" x14ac:dyDescent="0.3">
@@ -22014,7 +22014,7 @@
         <v>5.3277868626757384E-6</v>
       </c>
       <c r="D1504" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1505" spans="1:4" x14ac:dyDescent="0.3">
@@ -22028,7 +22028,7 @@
         <v>3.4767597610993442E-6</v>
       </c>
       <c r="D1505" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1506" spans="1:4" x14ac:dyDescent="0.3">
@@ -22042,7 +22042,7 @@
         <v>1.2177735859451921E-7</v>
       </c>
       <c r="D1506" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1507" spans="1:4" x14ac:dyDescent="0.3">
@@ -22056,7 +22056,7 @@
         <v>0.23231266198185591</v>
       </c>
       <c r="D1507" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1508" spans="1:4" x14ac:dyDescent="0.3">
@@ -22070,7 +22070,7 @@
         <v>0.17665037003903411</v>
       </c>
       <c r="D1508" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1509" spans="1:4" x14ac:dyDescent="0.3">
@@ -22084,7 +22084,7 @@
         <v>0.12631797309203549</v>
       </c>
       <c r="D1509" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1510" spans="1:4" x14ac:dyDescent="0.3">
@@ -22098,7 +22098,7 @@
         <v>7.732250425882245E-2</v>
       </c>
       <c r="D1510" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1511" spans="1:4" x14ac:dyDescent="0.3">
@@ -22112,7 +22112,7 @@
         <v>6.8893616817312375E-2</v>
       </c>
       <c r="D1511" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1512" spans="1:4" x14ac:dyDescent="0.3">
@@ -22126,7 +22126,7 @@
         <v>5.9026546581412501E-2</v>
       </c>
       <c r="D1512" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1513" spans="1:4" x14ac:dyDescent="0.3">
@@ -22140,7 +22140,7 @@
         <v>5.6542715745731463E-2</v>
       </c>
       <c r="D1513" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1514" spans="1:4" x14ac:dyDescent="0.3">
@@ -22154,7 +22154,7 @@
         <v>4.283141882555324E-2</v>
       </c>
       <c r="D1514" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1515" spans="1:4" x14ac:dyDescent="0.3">
@@ -22168,7 +22168,7 @@
         <v>2.3104945388067882E-2</v>
       </c>
       <c r="D1515" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1516" spans="1:4" x14ac:dyDescent="0.3">
@@ -22182,7 +22182,7 @@
         <v>1.6086889458059549E-2</v>
       </c>
       <c r="D1516" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1517" spans="1:4" x14ac:dyDescent="0.3">
@@ -22196,7 +22196,7 @@
         <v>1.533763834800073E-2</v>
       </c>
       <c r="D1517" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1518" spans="1:4" x14ac:dyDescent="0.3">
@@ -22210,7 +22210,7 @@
         <v>1.5328954618887451E-2</v>
       </c>
       <c r="D1518" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1519" spans="1:4" x14ac:dyDescent="0.3">
@@ -22224,7 +22224,7 @@
         <v>1.358797460055302E-2</v>
       </c>
       <c r="D1519" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1520" spans="1:4" x14ac:dyDescent="0.3">
@@ -22238,7 +22238,7 @@
         <v>1.356982375576244E-2</v>
       </c>
       <c r="D1520" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1521" spans="1:4" x14ac:dyDescent="0.3">
@@ -22252,7 +22252,7 @@
         <v>1.1213448772990769E-2</v>
       </c>
       <c r="D1521" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1522" spans="1:4" x14ac:dyDescent="0.3">
@@ -22266,7 +22266,7 @@
         <v>1.093223584842771E-2</v>
       </c>
       <c r="D1522" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1523" spans="1:4" x14ac:dyDescent="0.3">
@@ -22280,7 +22280,7 @@
         <v>1.0044295042365399E-2</v>
       </c>
       <c r="D1523" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1524" spans="1:4" x14ac:dyDescent="0.3">
@@ -22294,7 +22294,7 @@
         <v>7.5143120774281442E-3</v>
       </c>
       <c r="D1524" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1525" spans="1:4" x14ac:dyDescent="0.3">
@@ -22308,7 +22308,7 @@
         <v>5.4949859262126109E-3</v>
       </c>
       <c r="D1525" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1526" spans="1:4" x14ac:dyDescent="0.3">
@@ -22322,7 +22322,7 @@
         <v>3.5601803219793659E-3</v>
       </c>
       <c r="D1526" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1527" spans="1:4" x14ac:dyDescent="0.3">
@@ -22336,7 +22336,7 @@
         <v>3.0455566677094199E-3</v>
       </c>
       <c r="D1527" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1528" spans="1:4" x14ac:dyDescent="0.3">
@@ -22350,7 +22350,7 @@
         <v>1.975340796543532E-3</v>
       </c>
       <c r="D1528" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1529" spans="1:4" x14ac:dyDescent="0.3">
@@ -22364,7 +22364,7 @@
         <v>1.6715935086978461E-3</v>
       </c>
       <c r="D1529" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1530" spans="1:4" x14ac:dyDescent="0.3">
@@ -22378,7 +22378,7 @@
         <v>1.4220153698733661E-3</v>
       </c>
       <c r="D1530" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1531" spans="1:4" x14ac:dyDescent="0.3">
@@ -22392,7 +22392,7 @@
         <v>1.391713972033631E-3</v>
       </c>
       <c r="D1531" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1532" spans="1:4" x14ac:dyDescent="0.3">
@@ -22406,7 +22406,7 @@
         <v>6.6251378837096778E-4</v>
       </c>
       <c r="D1532" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1533" spans="1:4" x14ac:dyDescent="0.3">
@@ -22420,7 +22420,7 @@
         <v>5.2209067270010245E-4</v>
       </c>
       <c r="D1533" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1534" spans="1:4" x14ac:dyDescent="0.3">
@@ -22434,7 +22434,7 @@
         <v>5.1610705793170752E-4</v>
       </c>
       <c r="D1534" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1535" spans="1:4" x14ac:dyDescent="0.3">
@@ -22448,7 +22448,7 @@
         <v>4.74205123776516E-4</v>
       </c>
       <c r="D1535" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1536" spans="1:4" x14ac:dyDescent="0.3">
@@ -22462,7 +22462,7 @@
         <v>4.025685008871839E-4</v>
       </c>
       <c r="D1536" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1537" spans="1:4" x14ac:dyDescent="0.3">
@@ -22476,7 +22476,7 @@
         <v>3.5909983980056133E-4</v>
       </c>
       <c r="D1537" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1538" spans="1:4" x14ac:dyDescent="0.3">
@@ -22490,7 +22490,7 @@
         <v>2.9776368847615731E-4</v>
       </c>
       <c r="D1538" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1539" spans="1:4" x14ac:dyDescent="0.3">
@@ -22504,7 +22504,7 @@
         <v>2.9098004096845268E-4</v>
       </c>
       <c r="D1539" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1540" spans="1:4" x14ac:dyDescent="0.3">
@@ -22518,7 +22518,7 @@
         <v>2.3002724443954291E-4</v>
       </c>
       <c r="D1540" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1541" spans="1:4" x14ac:dyDescent="0.3">
@@ -22532,7 +22532,7 @@
         <v>1.6125741323217021E-4</v>
       </c>
       <c r="D1541" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1542" spans="1:4" x14ac:dyDescent="0.3">
@@ -22546,7 +22546,7 @@
         <v>1.2285564156004161E-4</v>
       </c>
       <c r="D1542" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1543" spans="1:4" x14ac:dyDescent="0.3">
@@ -22560,7 +22560,7 @@
         <v>8.593728894854173E-5</v>
       </c>
       <c r="D1543" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1544" spans="1:4" x14ac:dyDescent="0.3">
@@ -22574,7 +22574,7 @@
         <v>8.3187159083439823E-5</v>
       </c>
       <c r="D1544" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1545" spans="1:4" x14ac:dyDescent="0.3">
@@ -22588,7 +22588,7 @@
         <v>8.2003771548636023E-5</v>
       </c>
       <c r="D1545" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1546" spans="1:4" x14ac:dyDescent="0.3">
@@ -22602,7 +22602,7 @@
         <v>7.7636899231887561E-5</v>
       </c>
       <c r="D1546" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1547" spans="1:4" x14ac:dyDescent="0.3">
@@ -22616,7 +22616,7 @@
         <v>7.6486850244271743E-5</v>
       </c>
       <c r="D1547" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1548" spans="1:4" x14ac:dyDescent="0.3">
@@ -22630,7 +22630,7 @@
         <v>7.5153446946555494E-5</v>
       </c>
       <c r="D1548" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1549" spans="1:4" x14ac:dyDescent="0.3">
@@ -22644,7 +22644,7 @@
         <v>6.4402958890624304E-5</v>
       </c>
       <c r="D1549" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1550" spans="1:4" x14ac:dyDescent="0.3">
@@ -22658,7 +22658,7 @@
         <v>6.0869457860373357E-5</v>
       </c>
       <c r="D1550" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1551" spans="1:4" x14ac:dyDescent="0.3">
@@ -22672,7 +22672,7 @@
         <v>4.4468709710192967E-5</v>
       </c>
       <c r="D1551" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1552" spans="1:4" x14ac:dyDescent="0.3">
@@ -22686,7 +22686,7 @@
         <v>2.5801186733101901E-5</v>
       </c>
       <c r="D1552" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1553" spans="1:4" x14ac:dyDescent="0.3">
@@ -22700,7 +22700,7 @@
         <v>2.440112173987672E-5</v>
       </c>
       <c r="D1553" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1554" spans="1:4" x14ac:dyDescent="0.3">
@@ -22714,7 +22714,7 @@
         <v>2.1567653206238359E-5</v>
       </c>
       <c r="D1554" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1555" spans="1:4" x14ac:dyDescent="0.3">
@@ -22728,7 +22728,7 @@
         <v>1.6967441856908049E-5</v>
       </c>
       <c r="D1555" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1556" spans="1:4" x14ac:dyDescent="0.3">
@@ -22742,7 +22742,7 @@
         <v>7.5003415784775994E-6</v>
       </c>
       <c r="D1556" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1557" spans="1:4" x14ac:dyDescent="0.3">
@@ -22756,7 +22756,7 @@
         <v>6.8503092032134683E-6</v>
       </c>
       <c r="D1557" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1558" spans="1:4" x14ac:dyDescent="0.3">
@@ -22770,7 +22770,7 @@
         <v>6.3336310167013201E-6</v>
       </c>
       <c r="D1558" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1559" spans="1:4" x14ac:dyDescent="0.3">
@@ -22784,7 +22784,7 @@
         <v>5.0502278403335274E-6</v>
       </c>
       <c r="D1559" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1560" spans="1:4" x14ac:dyDescent="0.3">
@@ -22798,7 +22798,7 @@
         <v>3.183484781944658E-6</v>
       </c>
       <c r="D1560" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1561" spans="1:4" x14ac:dyDescent="0.3">
@@ -22812,7 +22812,7 @@
         <v>2.5167754336530001E-6</v>
       </c>
       <c r="D1561" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1562" spans="1:4" x14ac:dyDescent="0.3">
@@ -22826,7 +22826,7 @@
         <v>2.3334365224196181E-6</v>
       </c>
       <c r="D1562" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1563" spans="1:4" x14ac:dyDescent="0.3">
@@ -22840,7 +22840,7 @@
         <v>1.883420031416398E-6</v>
       </c>
       <c r="D1563" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1564" spans="1:4" x14ac:dyDescent="0.3">
@@ -22854,7 +22854,7 @@
         <v>1.666742572995022E-6</v>
       </c>
       <c r="D1564" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1565" spans="1:4" x14ac:dyDescent="0.3">
@@ -22868,7 +22868,7 @@
         <v>1.183387534803807E-6</v>
       </c>
       <c r="D1565" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1566" spans="1:4" x14ac:dyDescent="0.3">
@@ -22882,7 +22882,7 @@
         <v>9.1670995503396809E-7</v>
       </c>
       <c r="D1566" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1567" spans="1:4" x14ac:dyDescent="0.3">
@@ -22896,7 +22896,7 @@
         <v>6.5003237526412959E-7</v>
       </c>
       <c r="D1567" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1568" spans="1:4" x14ac:dyDescent="0.3">
@@ -22910,7 +22910,7 @@
         <v>5.0001661235168193E-7</v>
       </c>
       <c r="D1568" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1569" spans="1:4" x14ac:dyDescent="0.3">
@@ -22924,7 +22924,7 @@
         <v>3.6667782246676268E-7</v>
       </c>
       <c r="D1569" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1570" spans="1:4" x14ac:dyDescent="0.3">
@@ -22938,7 +22938,7 @@
         <v>2.6667757976983861E-7</v>
       </c>
       <c r="D1570" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1571" spans="1:4" x14ac:dyDescent="0.3">
@@ -22952,7 +22952,7 @@
         <v>2.333390325818434E-7</v>
       </c>
       <c r="D1571" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1572" spans="1:4" x14ac:dyDescent="0.3">
@@ -22966,7 +22966,7 @@
         <v>2.333390325818434E-7</v>
       </c>
       <c r="D1572" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1573" spans="1:4" x14ac:dyDescent="0.3">
@@ -22980,7 +22980,7 @@
         <v>1.6667733707291451E-7</v>
       </c>
       <c r="D1573" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1574" spans="1:4" x14ac:dyDescent="0.3">
@@ -22994,7 +22994,7 @@
         <v>6.6677094375990361E-8</v>
       </c>
       <c r="D1574" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1575" spans="1:4" x14ac:dyDescent="0.3">
@@ -23008,7 +23008,7 @@
         <v>1.6661574160466878E-8</v>
       </c>
       <c r="D1575" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1576" spans="1:4" x14ac:dyDescent="0.3">
@@ -23022,7 +23022,7 @@
         <v>1.6661574160466878E-8</v>
       </c>
       <c r="D1576" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1577" spans="1:4" x14ac:dyDescent="0.3">
@@ -23036,7 +23036,7 @@
         <v>0.31544723207531611</v>
       </c>
       <c r="D1577" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1578" spans="1:4" x14ac:dyDescent="0.3">
@@ -23050,7 +23050,7 @@
         <v>0.19847429324547089</v>
       </c>
       <c r="D1578" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1579" spans="1:4" x14ac:dyDescent="0.3">
@@ -23064,7 +23064,7 @@
         <v>0.17720741060638989</v>
       </c>
       <c r="D1579" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1580" spans="1:4" x14ac:dyDescent="0.3">
@@ -23078,7 +23078,7 @@
         <v>0.11378070925157351</v>
       </c>
       <c r="D1580" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1581" spans="1:4" x14ac:dyDescent="0.3">
@@ -23092,7 +23092,7 @@
         <v>4.4543672845349713E-2</v>
       </c>
       <c r="D1581" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1582" spans="1:4" x14ac:dyDescent="0.3">
@@ -23106,7 +23106,7 @@
         <v>3.1398634777178552E-2</v>
       </c>
       <c r="D1582" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1583" spans="1:4" x14ac:dyDescent="0.3">
@@ -23120,7 +23120,7 @@
         <v>1.2875841118903259E-2</v>
       </c>
       <c r="D1583" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1584" spans="1:4" x14ac:dyDescent="0.3">
@@ -23134,7 +23134,7 @@
         <v>1.2638719151433161E-2</v>
       </c>
       <c r="D1584" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1585" spans="1:4" x14ac:dyDescent="0.3">
@@ -23148,7 +23148,7 @@
         <v>9.5326517843563052E-3</v>
       </c>
       <c r="D1585" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1586" spans="1:4" x14ac:dyDescent="0.3">
@@ -23162,7 +23162,7 @@
         <v>9.3432904644371231E-3</v>
       </c>
       <c r="D1586" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1587" spans="1:4" x14ac:dyDescent="0.3">
@@ -23176,7 +23176,7 @@
         <v>7.6641393978782802E-3</v>
       </c>
       <c r="D1587" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1588" spans="1:4" x14ac:dyDescent="0.3">
@@ -23190,7 +23190,7 @@
         <v>6.7358392784492328E-3</v>
       </c>
       <c r="D1588" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1589" spans="1:4" x14ac:dyDescent="0.3">
@@ -23204,7 +23204,7 @@
         <v>6.4473201301457278E-3</v>
       </c>
       <c r="D1589" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1590" spans="1:4" x14ac:dyDescent="0.3">
@@ -23218,7 +23218,7 @@
         <v>6.0169699130478713E-3</v>
       </c>
       <c r="D1590" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1591" spans="1:4" x14ac:dyDescent="0.3">
@@ -23232,7 +23232,7 @@
         <v>5.9749006923533882E-3</v>
       </c>
       <c r="D1591" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1592" spans="1:4" x14ac:dyDescent="0.3">
@@ -23246,7 +23246,7 @@
         <v>5.7249512220656166E-3</v>
       </c>
       <c r="D1592" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1593" spans="1:4" x14ac:dyDescent="0.3">
@@ -23260,7 +23260,7 @@
         <v>5.3594421578416181E-3</v>
       </c>
       <c r="D1593" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1594" spans="1:4" x14ac:dyDescent="0.3">
@@ -23274,7 +23274,7 @@
         <v>4.880889174601521E-3</v>
       </c>
       <c r="D1594" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1595" spans="1:4" x14ac:dyDescent="0.3">
@@ -23288,7 +23288,7 @@
         <v>4.8387203233310524E-3</v>
       </c>
       <c r="D1595" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1596" spans="1:4" x14ac:dyDescent="0.3">
@@ -23302,7 +23302,7 @@
         <v>4.5699032221062329E-3</v>
       </c>
       <c r="D1596" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1597" spans="1:4" x14ac:dyDescent="0.3">
@@ -23316,7 +23316,7 @@
         <v>4.1612912598941428E-3</v>
       </c>
       <c r="D1597" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1598" spans="1:4" x14ac:dyDescent="0.3">
@@ -23330,7 +23330,7 @@
         <v>2.598994996265347E-3</v>
       </c>
       <c r="D1598" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1599" spans="1:4" x14ac:dyDescent="0.3">
@@ -23344,7 +23344,7 @@
         <v>1.8824794161659011E-3</v>
       </c>
       <c r="D1599" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1600" spans="1:4" x14ac:dyDescent="0.3">
@@ -23358,7 +23358,7 @@
         <v>1.3285243929734649E-3</v>
       </c>
       <c r="D1600" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1601" spans="1:4" x14ac:dyDescent="0.3">
@@ -23372,7 +23372,7 @@
         <v>1.175117439820895E-3</v>
       </c>
       <c r="D1601" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1602" spans="1:4" x14ac:dyDescent="0.3">
@@ -23386,7 +23386,7 @@
         <v>7.9691786338295602E-4</v>
       </c>
       <c r="D1602" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1603" spans="1:4" x14ac:dyDescent="0.3">
@@ -23400,7 +23400,7 @@
         <v>7.6786917615148231E-4</v>
       </c>
       <c r="D1603" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1604" spans="1:4" x14ac:dyDescent="0.3">
@@ -23414,7 +23414,7 @@
         <v>6.5786401271495916E-4</v>
       </c>
       <c r="D1604" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1605" spans="1:4" x14ac:dyDescent="0.3">
@@ -23428,7 +23428,7 @@
         <v>5.2044161704347433E-4</v>
       </c>
       <c r="D1605" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1606" spans="1:4" x14ac:dyDescent="0.3">
@@ -23442,7 +23442,7 @@
         <v>3.2084320654125878E-4</v>
       </c>
       <c r="D1606" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1607" spans="1:4" x14ac:dyDescent="0.3">
@@ -23456,7 +23456,7 @@
         <v>2.7554843012848711E-4</v>
       </c>
       <c r="D1607" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1608" spans="1:4" x14ac:dyDescent="0.3">
@@ -23470,7 +23470,7 @@
         <v>2.6615819944132761E-4</v>
       </c>
       <c r="D1608" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1609" spans="1:4" x14ac:dyDescent="0.3">
@@ -23484,7 +23484,7 @@
         <v>2.6422784696385313E-4</v>
       </c>
       <c r="D1609" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1610" spans="1:4" x14ac:dyDescent="0.3">
@@ -23498,7 +23498,7 @@
         <v>2.53909805818706E-4</v>
       </c>
       <c r="D1610" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1611" spans="1:4" x14ac:dyDescent="0.3">
@@ -23512,7 +23512,7 @@
         <v>1.9941782936411649E-4</v>
       </c>
       <c r="D1611" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1612" spans="1:4" x14ac:dyDescent="0.3">
@@ -23526,7 +23526,7 @@
         <v>1.8807234143198971E-4</v>
       </c>
       <c r="D1612" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1613" spans="1:4" x14ac:dyDescent="0.3">
@@ -23540,7 +23540,7 @@
         <v>1.322789369829649E-4</v>
       </c>
       <c r="D1613" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1614" spans="1:4" x14ac:dyDescent="0.3">
@@ -23554,7 +23554,7 @@
         <v>1.2659996538677651E-4</v>
       </c>
       <c r="D1614" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1615" spans="1:4" x14ac:dyDescent="0.3">
@@ -23568,7 +23568,7 @@
         <v>1.199122327704869E-4</v>
       </c>
       <c r="D1615" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1616" spans="1:4" x14ac:dyDescent="0.3">
@@ -23582,7 +23582,7 @@
         <v>1.190404566011063E-4</v>
       </c>
       <c r="D1616" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1617" spans="1:4" x14ac:dyDescent="0.3">
@@ -23596,7 +23596,7 @@
         <v>9.7775449827773071E-5</v>
       </c>
       <c r="D1617" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1618" spans="1:4" x14ac:dyDescent="0.3">
@@ -23610,7 +23610,7 @@
         <v>7.1429254914162339E-5</v>
       </c>
       <c r="D1618" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1619" spans="1:4" x14ac:dyDescent="0.3">
@@ -23624,7 +23624,7 @@
         <v>6.459207643389496E-5</v>
       </c>
       <c r="D1619" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1620" spans="1:4" x14ac:dyDescent="0.3">
@@ -23638,7 +23638,7 @@
         <v>4.2660785149779917E-5</v>
       </c>
       <c r="D1620" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1621" spans="1:4" x14ac:dyDescent="0.3">
@@ -23652,7 +23652,7 @@
         <v>2.8812060298753561E-5</v>
       </c>
       <c r="D1621" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1622" spans="1:4" x14ac:dyDescent="0.3">
@@ -23666,7 +23666,7 @@
         <v>2.2504169972533139E-5</v>
       </c>
       <c r="D1622" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1623" spans="1:4" x14ac:dyDescent="0.3">
@@ -23680,7 +23680,7 @@
         <v>1.6407996058532899E-5</v>
       </c>
       <c r="D1623" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1624" spans="1:4" x14ac:dyDescent="0.3">
@@ -23694,7 +23694,7 @@
         <v>1.6264774948176619E-5</v>
       </c>
       <c r="D1624" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1625" spans="1:4" x14ac:dyDescent="0.3">
@@ -23708,7 +23708,7 @@
         <v>1.0697889188223329E-5</v>
       </c>
       <c r="D1625" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1626" spans="1:4" x14ac:dyDescent="0.3">
@@ -23722,7 +23722,7 @@
         <v>6.7437784109107044E-6</v>
       </c>
       <c r="D1626" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1627" spans="1:4" x14ac:dyDescent="0.3">
@@ -23736,7 +23736,7 @@
         <v>5.5917962804530936E-6</v>
       </c>
       <c r="D1627" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1628" spans="1:4" x14ac:dyDescent="0.3">
@@ -23750,7 +23750,7 @@
         <v>1.4757843789128451E-6</v>
       </c>
       <c r="D1628" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1629" spans="1:4" x14ac:dyDescent="0.3">
@@ -23764,7 +23764,7 @@
         <v>1.382378556549133E-6</v>
       </c>
       <c r="D1629" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1630" spans="1:4" x14ac:dyDescent="0.3">
@@ -23778,7 +23778,7 @@
         <v>7.6591508676694506E-7</v>
       </c>
       <c r="D1630" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1631" spans="1:4" x14ac:dyDescent="0.3">
@@ -23792,7 +23792,7 @@
         <v>5.9778920891789789E-7</v>
       </c>
       <c r="D1631" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1632" spans="1:4" x14ac:dyDescent="0.3">
@@ -23806,7 +23806,7 @@
         <v>5.5419867454675657E-7</v>
       </c>
       <c r="D1632" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1633" spans="1:4" x14ac:dyDescent="0.3">
@@ -23820,7 +23820,7 @@
         <v>2.4285168634142591E-7</v>
       </c>
       <c r="D1633" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1634" spans="1:4" x14ac:dyDescent="0.3">
@@ -23834,7 +23834,7 @@
         <v>2.366211797129521E-7</v>
       </c>
       <c r="D1634" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1635" spans="1:4" x14ac:dyDescent="0.3">
@@ -23848,7 +23848,7 @@
         <v>1.120858362350461E-7</v>
       </c>
       <c r="D1635" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1636" spans="1:4" x14ac:dyDescent="0.3">
@@ -23862,7 +23862,7 @@
         <v>8.717531573523859E-8</v>
       </c>
       <c r="D1636" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1637" spans="1:4" x14ac:dyDescent="0.3">
@@ -23876,7 +23876,7 @@
         <v>2.49105204998075E-8</v>
       </c>
       <c r="D1637" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -23895,15 +23895,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004E32BC299DDA75418A481CE8C1C04767" ma:contentTypeVersion="10" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="0fa4796f6798a7b079311364fca30a32">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="03763a1d-3ef6-4dac-84db-711c24c35716" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ccd651f340b356ff6f610107a3061652" ns2:_="">
     <xsd:import namespace="03763a1d-3ef6-4dac-84db-711c24c35716"/>
@@ -24081,6 +24072,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C50C39B-429F-409A-A7E6-0609DFF42D17}">
   <ds:schemaRefs>
@@ -24092,14 +24092,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2543F6D-492F-4C9B-8AF7-7639E4005A4C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613F8F29-F909-4A5C-BFEC-CB47403B45C6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24115,4 +24107,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2543F6D-492F-4C9B-8AF7-7639E4005A4C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>